--- a/Result/checksun_type/印刷材料.xlsx
+++ b/Result/checksun_type/印刷材料.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -903,17 +903,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-6.64</t>
+          <t>-5.99</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-11.62</t>
+          <t>-13.30</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-3.88</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>112</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1024,62 +1024,62 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>18.52</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-5.03</t>
+          <t>-5.16</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>53.73999999999999</t>
+          <t>53.27999999999999</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>55.81</t>
+          <t>55.51</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>58.76</t>
+          <t>58.53</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>57.38</t>
+          <t>57.37</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-13.29</t>
+          <t>-17.48</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-118.74</t>
+          <t>-119.60</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>91198.495658466</t>
+          <t>91079.31502890174</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>7133.0</t>
+          <t>5817.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>7319.2</t>
+          <t>7145.4</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>7839.6</t>
+          <t>7601.0</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>19212.02</t>
+          <t>17385.02</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-520</t>
+          <t>-455</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-1814.400883559504</t>
+          <t>-1744.158464240811</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-1373.77</v>
+        <v>-1357.83</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-5.41</t>
+          <t>-7.21</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1182,22 +1182,22 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>2.093686273733394</t>
+          <t>2.973959600876125</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>0.0455930000194012</t>
+          <t>7.507647901781631</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>10.59107509731473</t>
+          <t>9.97333412563415</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>22.34</t>
+          <t>21.11</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>34.99</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>2452</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>12.66</t>
+          <t>-6.64</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-8.25</t>
+          <t>-11.62</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,57 +1440,57 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>112</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>18.52</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-3.70</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-5.02</t>
+          <t>-5.03</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>53.96</t>
+          <t>53.73999999999999</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>56.14</t>
+          <t>55.81</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>59.1</t>
+          <t>58.76</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1500,17 +1500,17 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-10.55</t>
+          <t>-13.29</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-118.12</t>
+          <t>-118.74</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>91198.495658466</t>
+          <t>91079.31502890174</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>7209.0</t>
+          <t>7133.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>8433.0</t>
+          <t>7319.2</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>7485.2</t>
+          <t>7839.6</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>23000.42</t>
+          <t>19212.02</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>-520</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-1894.515625575336</t>
+          <t>-1814.400883559504</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-1488.48</v>
+        <v>-1373.77</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-5.41</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1613,22 +1613,22 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>2.093686273733394</t>
+          <t>2.973959600876125</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>0.0455930000194012</t>
+          <t>7.507647901781631</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>10.59107509731473</t>
+          <t>9.97333412563415</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1638,12 +1638,12 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>22.34</t>
+          <t>21.11</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>34.99</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>2452</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
+          <t>53.8</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
           <t>54.5</t>
         </is>
       </c>
-      <c r="CD3" t="inlineStr">
-        <is>
-          <t>55.0</t>
-        </is>
-      </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>12.66</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-8.75</t>
+          <t>-8.25</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1871,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>112</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>10.55</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.47</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-5.04</t>
+          <t>-5.02</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>53.86</t>
+          <t>53.96</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>56.38</t>
+          <t>56.14</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>59.37</t>
+          <t>59.1</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>57.36</t>
+          <t>57.38</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-19.01</t>
+          <t>-10.55</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-117.64</t>
+          <t>-118.12</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>91198.495658466</t>
+          <t>91079.31502890174</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>4672.0</t>
+          <t>7209.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>7837.8</t>
+          <t>8433.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>8182.9</t>
+          <t>7485.2</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>23577.74</t>
+          <t>23000.42</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-345</t>
+          <t>947</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-1968.339437718039</t>
+          <t>-1894.515625575336</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-1607.35</v>
+        <v>-1488.48</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2044,22 +2044,22 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>2.093686273733394</t>
+          <t>2.973959600876125</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>0.0455930000194012</t>
+          <t>7.507647901781631</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>10.59107509731473</t>
+          <t>9.97333412563415</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>22.34</t>
+          <t>21.11</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>34.99</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>2452</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
+          <t>54.5</t>
+        </is>
+      </c>
+      <c r="CD4" t="inlineStr">
+        <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
           <t>54.1</t>
         </is>
       </c>
-      <c r="CD4" t="inlineStr">
-        <is>
-          <t>54.4</t>
-        </is>
-      </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>53.8</t>
-        </is>
-      </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>201.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-9.60</t>
+          <t>-8.75</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>7.24</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,275 +2302,275 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>112</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>10.55</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>-4.47</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
+          <t>53.86</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>56.38</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>59.37</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>57.36</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>-19.01</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>-1.53</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>-1.29</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>-117.64</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>2025/10/08</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>91079.31502890174</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>4672.0</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>7837.8</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>8182.9</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>23577.74</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>-345</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>-1968.339437718039</t>
+        </is>
+      </c>
+      <c r="BC5" t="n">
+        <v>-1607.35</v>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>55.5</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>2025/08/20</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>-2.34</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>利機</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>利機</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>電子通路業</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>1.11</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>2.973959600876125</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>7.507647901781631</t>
+        </is>
+      </c>
+      <c r="BO5" t="inlineStr">
+        <is>
+          <t>9.97333412563415</t>
+        </is>
+      </c>
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+        </is>
+      </c>
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
+          <t>3.88</t>
+        </is>
+      </c>
+      <c r="BT5" t="inlineStr">
+        <is>
+          <t>6.82</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
+          <t>21.11</t>
+        </is>
+      </c>
+      <c r="BV5" t="inlineStr">
+        <is>
+          <t>20.15%</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
+          <t>3.13%</t>
+        </is>
+      </c>
+      <c r="BX5" t="inlineStr">
+        <is>
+          <t>34.99</t>
+        </is>
+      </c>
+      <c r="BY5" t="inlineStr">
+        <is>
+          <t>2317</t>
+        </is>
+      </c>
+      <c r="BZ5" t="inlineStr">
+        <is>
+          <t>半導體產品60.53%、光電產品37.52%、其他產品1.95% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
+          <t>利機-電子通路業-上櫃</t>
+        </is>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>電子通路業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CC5" t="inlineStr">
+        <is>
+          <t>54.1</t>
+        </is>
+      </c>
+      <c r="CD5" t="inlineStr">
+        <is>
+          <t>54.4</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
           <t>53.8</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>56.6</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>59.52</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>57.35</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>-27.97</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>-1.57</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>-1.23</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>7.3</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>-116.80</t>
-        </is>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>2025/10/08</t>
-        </is>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>91198.495658466</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>10896.0</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>8352.6</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>8330.8</t>
-        </is>
-      </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>24471.84</t>
-        </is>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>-2033.974659900123</t>
-        </is>
-      </c>
-      <c r="BC5" t="n">
-        <v>-1447.92</v>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE5" t="inlineStr">
-        <is>
-          <t>55.5</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>2025/08/20</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>-3.24</t>
-        </is>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>利機</t>
-        </is>
-      </c>
-      <c r="BI5" t="inlineStr">
-        <is>
-          <t>利機</t>
-        </is>
-      </c>
-      <c r="BJ5" t="inlineStr">
-        <is>
-          <t>電子通路業</t>
-        </is>
-      </c>
-      <c r="BK5" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL5" t="inlineStr">
-        <is>
-          <t>1.11</t>
-        </is>
-      </c>
-      <c r="BM5" t="inlineStr">
-        <is>
-          <t>2.093686273733394</t>
-        </is>
-      </c>
-      <c r="BN5" t="inlineStr">
-        <is>
-          <t>0.0455930000194012</t>
-        </is>
-      </c>
-      <c r="BO5" t="inlineStr">
-        <is>
-          <t>10.59107509731473</t>
-        </is>
-      </c>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ5" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BR5" t="inlineStr">
-        <is>
-          <t>2.32</t>
-        </is>
-      </c>
-      <c r="BS5" t="inlineStr">
-        <is>
-          <t>3.81</t>
-        </is>
-      </c>
-      <c r="BT5" t="inlineStr">
-        <is>
-          <t>6.82</t>
-        </is>
-      </c>
-      <c r="BU5" t="inlineStr">
-        <is>
-          <t>22.34</t>
-        </is>
-      </c>
-      <c r="BV5" t="inlineStr">
-        <is>
-          <t>20.15%</t>
-        </is>
-      </c>
-      <c r="BW5" t="inlineStr">
-        <is>
-          <t>3.13%</t>
-        </is>
-      </c>
-      <c r="BX5" t="inlineStr">
-        <is>
-          <t>36.0</t>
-        </is>
-      </c>
-      <c r="BY5" t="inlineStr">
-        <is>
-          <t>2452</t>
-        </is>
-      </c>
-      <c r="BZ5" t="inlineStr">
-        <is>
-          <t>半導體產品60.53%、光電產品37.52%、其他產品1.95% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA5" t="inlineStr">
-        <is>
-          <t>利機-電子通路業-上櫃</t>
-        </is>
-      </c>
-      <c r="CB5" t="inlineStr">
-        <is>
-          <t>電子通路業右下上櫃</t>
-        </is>
-      </c>
-      <c r="CC5" t="inlineStr">
-        <is>
-          <t>53.8</t>
-        </is>
-      </c>
-      <c r="CD5" t="inlineStr">
-        <is>
-          <t>54.9</t>
-        </is>
-      </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>53.7</t>
-        </is>
-      </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>201.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-9.43</t>
+          <t>-9.60</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>7.24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,77 +2733,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>112</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-5.37</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-4.36</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>53.96</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>57.02</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>59.63</t>
+          <t>59.52</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>57.34</t>
+          <t>57.35</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-35.26</t>
+          <t>-27.97</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-115.63</t>
+          <t>-116.80</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>91198.495658466</t>
+          <t>91079.31502890174</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>6686.0</t>
+          <t>10896.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>8056.6</t>
+          <t>8352.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>7881.1</t>
+          <t>8330.8</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>24960.08</t>
+          <t>24471.84</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>21</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-2140.52994480799</t>
+          <t>-2033.974659900123</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-1835.32</v>
+        <v>-1447.92</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2906,37 +2906,37 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>2.093686273733394</t>
+          <t>2.973959600876125</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>0.0455930000194012</t>
+          <t>7.507647901781631</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>10.59107509731473</t>
+          <t>9.97333412563415</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>22.34</t>
+          <t>21.11</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>34.99</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>2452</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>-4.47</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>7.73</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-9.76</t>
+          <t>-9.43</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>112</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-5.36</t>
+          <t>-5.37</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-4.36</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>54.46</t>
+          <t>53.96</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>57.54</t>
+          <t>57.02</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>59.69</t>
+          <t>59.63</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>57.33</t>
+          <t>57.34</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-43.90</t>
+          <t>-35.26</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-114.25</t>
+          <t>-115.63</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>91198.495658466</t>
+          <t>91079.31502890174</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>12702.0</t>
+          <t>6686.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>8360.0</t>
+          <t>8056.6</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>7759.9</t>
+          <t>7881.1</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>25027.0</t>
+          <t>24960.08</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>175</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-2196.023369214014</t>
+          <t>-2140.52994480799</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-1872.12</v>
+        <v>-1835.32</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-3.42</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3337,37 +3337,37 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>2.093686273733394</t>
+          <t>2.973959600876125</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>0.0455930000194012</t>
+          <t>7.507647901781631</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>10.59107509731473</t>
+          <t>9.97333412563415</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>22.34</t>
+          <t>21.11</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>34.99</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>2452</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>240.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-14.59</t>
+          <t>7.73</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-9.09</t>
+          <t>-9.76</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,17 +3595,17 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>112</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -3615,57 +3615,57 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-5.57</t>
+          <t>-5.36</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>54.88</t>
+          <t>54.46</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>58.12</t>
+          <t>57.54</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>59.75</t>
+          <t>59.69</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>57.31</t>
+          <t>57.33</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-50.73</t>
+          <t>-43.90</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-112.69</t>
+          <t>-114.25</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>91198.495658466</t>
+          <t>91079.31502890174</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>4233.0</t>
+          <t>12702.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>6537.4</t>
+          <t>8360.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>7654.3</t>
+          <t>7759.9</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>25071.18</t>
+          <t>25027.0</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-1116</t>
+          <t>600</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-2254.914918861746</t>
+          <t>-2196.023369214014</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-2502.41</v>
+        <v>-1872.12</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-2.70</t>
+          <t>-3.42</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3768,37 +3768,37 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>2.093686273733394</t>
+          <t>2.973959600876125</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>0.0455930000194012</t>
+          <t>7.507647901781631</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>10.59107509731473</t>
+          <t>9.97333412563415</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>22.34</t>
+          <t>21.11</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>34.99</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>2452</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>53.9</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>54.4</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>53.9</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-4.06</t>
+          <t>-14.59</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-9.26</t>
+          <t>-9.09</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>112</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>6.06</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-5.62</t>
+          <t>-5.57</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.88</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>58.59</t>
+          <t>58.12</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>59.78</t>
+          <t>59.75</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>57.28</t>
+          <t>57.31</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-59.20</t>
+          <t>-50.73</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-111.08</t>
+          <t>-112.69</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>91198.495658466</t>
+          <t>91079.31502890174</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>7246.0</t>
+          <t>4233.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>8528.0</t>
+          <t>6537.4</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>8888.7</t>
+          <t>7654.3</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>25403.62</t>
+          <t>25071.18</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-360</t>
+          <t>-1116</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-2209.916428335603</t>
+          <t>-2254.914918861746</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-2406.05</v>
+        <v>-2502.41</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-2.70</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4199,37 +4199,37 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>2.093686273733394</t>
+          <t>2.973959600876125</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>0.0455930000194012</t>
+          <t>7.507647901781631</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>10.59107509731473</t>
+          <t>9.97333412563415</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>22.34</t>
+          <t>21.11</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>34.99</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>2452</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
+          <t>53.9</t>
+        </is>
+      </c>
+      <c r="CD9" t="inlineStr">
+        <is>
+          <t>54.4</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>53.8</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
           <t>54.0</t>
-        </is>
-      </c>
-      <c r="CD9" t="inlineStr">
-        <is>
-          <t>54.5</t>
-        </is>
-      </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>53.2</t>
-        </is>
-      </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>53.9</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>53.9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-4.66</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-17.24</t>
+          <t>-4.06</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-8.25</t>
+          <t>-9.26</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>6.16</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,12 +4457,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>112</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4477,57 +4477,57 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-5.62</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>55.94000000000001</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>58.78</t>
+          <t>58.59</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>59.88</t>
+          <t>59.78</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>57.26</t>
+          <t>57.28</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-62.54</t>
+          <t>-59.20</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-109.44</t>
+          <t>-111.08</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>91198.495658466</t>
+          <t>91079.31502890174</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>9416.0</t>
+          <t>7246.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>8309.0</t>
+          <t>8528.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>10040.4</t>
+          <t>8888.7</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>26095.24</t>
+          <t>25403.62</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-1731</t>
+          <t>-360</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-2174.255457665703</t>
+          <t>-2209.916428335603</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-2505.29</v>
+        <v>-2406.05</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4630,22 +4630,22 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>2.093686273733394</t>
+          <t>2.973959600876125</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>0.0455930000194012</t>
+          <t>7.507647901781631</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>10.59107509731473</t>
+          <t>9.97333412563415</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>22.34</t>
+          <t>21.11</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>34.99</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>2452</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>53.9</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>-3.19</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>56.3</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-3.3</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-27.80</t>
+          <t>-17.24</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-5.22</t>
+          <t>-8.25</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>6.16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-3.49</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,17 +4888,17 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>112</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -4908,57 +4908,57 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-4.11</t>
+          <t>-4.84</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>4.70</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>56.52</t>
+          <t>55.94000000000001</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>58.94</t>
+          <t>58.78</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>59.9</t>
+          <t>59.88</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>57.21</t>
+          <t>57.26</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-63.61</t>
+          <t>-62.54</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-107.96</t>
+          <t>-109.44</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>91198.495658466</t>
+          <t>91079.31502890174</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>8203.0</t>
+          <t>9416.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>7705.6</t>
+          <t>8309.0</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>10672.9</t>
+          <t>10040.4</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>26485.84</t>
+          <t>26095.24</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-2967</t>
+          <t>-1731</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-2114.06681542231</t>
+          <t>-2174.255457665703</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-2790.09</v>
+        <v>-2505.29</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5061,22 +5061,22 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>2.093686273733394</t>
+          <t>2.973959600876125</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>0.0455930000194012</t>
+          <t>7.507647901781631</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>10.59107509731473</t>
+          <t>9.97333412563415</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>22.34</t>
+          <t>21.11</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>34.99</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>2452</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>56.3</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>56.3</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-2.2</t>
+          <t>-9.32</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-35.02</t>
+          <t>-27.80</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-6.23</t>
+          <t>-5.22</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>112</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.06</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-4.11</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>4.70</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>56.82000000000001</t>
+          <t>56.52</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>59.01</t>
+          <t>58.94</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>59.95</t>
+          <t>59.9</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>57.21</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-85.09</t>
+          <t>-63.61</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-106.70</t>
+          <t>-107.96</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>91198.495658466</t>
+          <t>91079.31502890174</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>3589.0</t>
+          <t>8203.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>7159.8</t>
+          <t>7705.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>11017.7</t>
+          <t>10672.9</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>26719.6</t>
+          <t>26485.84</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-3857</t>
+          <t>-2967</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-1991.153251671236</t>
+          <t>-2114.06681542231</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-2967.34</v>
+        <v>-2790.09</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5492,22 +5492,22 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>2.093686273733394</t>
+          <t>2.973959600876125</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>0.0455930000194012</t>
+          <t>7.507647901781631</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>10.59107509731473</t>
+          <t>9.97333412563415</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>22.34</t>
+          <t>21.11</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>34.99</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>2452</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>54.8</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>54.8</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>56.3</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/印刷材料.xlsx
+++ b/Result/checksun_type/印刷材料.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-5.99</t>
+          <t>-14.12</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-13.30</t>
+          <t>-15.15</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-3.88</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>129</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1024,62 +1024,62 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-5.16</t>
+          <t>-5.46</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>53.27999999999999</t>
+          <t>52.62</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>55.51</t>
+          <t>55.11</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>58.53</t>
+          <t>58.29</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>57.37</t>
+          <t>57.34</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-17.48</t>
+          <t>-22.24</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-119.60</t>
+          <t>-120.76</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>91079.31502890174</t>
+          <t>90962.16450216451</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>5817.0</t>
+          <t>6596.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>7145.4</t>
+          <t>6285.4</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>7601.0</t>
+          <t>7319.0</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>17385.02</t>
+          <t>16730.98</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-455</t>
+          <t>-1033</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-1744.158464240811</t>
+          <t>-1668.794589419023</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-1357.83</v>
+        <v>-1254.29</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-7.21</t>
+          <t>-9.19</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>21.11</t>
+          <t>20.66</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>34.99</t>
+          <t>33.98</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2268</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-6.64</t>
+          <t>-5.99</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-11.62</t>
+          <t>-13.30</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-3.88</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,12 +1440,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>129</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1455,62 +1455,62 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>18.52</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-5.03</t>
+          <t>-5.16</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>53.73999999999999</t>
+          <t>53.27999999999999</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>55.81</t>
+          <t>55.51</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>58.76</t>
+          <t>58.53</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>57.38</t>
+          <t>57.37</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-13.29</t>
+          <t>-17.48</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-118.74</t>
+          <t>-119.60</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>91079.31502890174</t>
+          <t>90962.16450216451</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>7133.0</t>
+          <t>5817.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>7319.2</t>
+          <t>7145.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>7839.6</t>
+          <t>7601.0</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>19212.02</t>
+          <t>17385.02</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-520</t>
+          <t>-455</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-1814.400883559504</t>
+          <t>-1744.158464240811</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-1373.77</v>
+        <v>-1357.83</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-5.41</t>
+          <t>-7.21</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1638,12 +1638,12 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>21.11</t>
+          <t>20.66</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>34.99</t>
+          <t>33.98</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2268</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>12.66</t>
+          <t>-6.64</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-8.25</t>
+          <t>-11.62</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,57 +1871,57 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>129</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>18.52</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-3.70</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-5.02</t>
+          <t>-5.03</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>53.96</t>
+          <t>53.73999999999999</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>56.14</t>
+          <t>55.81</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>59.1</t>
+          <t>58.76</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1931,17 +1931,17 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-10.55</t>
+          <t>-13.29</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-118.12</t>
+          <t>-118.74</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>91079.31502890174</t>
+          <t>90962.16450216451</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>7209.0</t>
+          <t>7133.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>8433.0</t>
+          <t>7319.2</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>7485.2</t>
+          <t>7839.6</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>23000.42</t>
+          <t>19212.02</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>-520</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-1894.515625575336</t>
+          <t>-1814.400883559504</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-1488.48</v>
+        <v>-1373.77</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-5.41</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>21.11</t>
+          <t>20.66</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>34.99</t>
+          <t>33.98</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2268</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
+          <t>53.8</t>
+        </is>
+      </c>
+      <c r="CD4" t="inlineStr">
+        <is>
           <t>54.5</t>
         </is>
       </c>
-      <c r="CD4" t="inlineStr">
-        <is>
-          <t>55.0</t>
-        </is>
-      </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-8.13</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>12.66</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-8.75</t>
+          <t>-8.25</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,77 +2302,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>129</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>10.55</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.47</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-5.04</t>
+          <t>-5.02</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>53.86</t>
+          <t>53.96</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>56.38</t>
+          <t>56.14</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>59.37</t>
+          <t>59.1</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>57.36</t>
+          <t>57.38</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-19.01</t>
+          <t>-10.55</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-117.64</t>
+          <t>-118.12</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>91079.31502890174</t>
+          <t>90962.16450216451</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>4672.0</t>
+          <t>7209.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>7837.8</t>
+          <t>8433.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>8182.9</t>
+          <t>7485.2</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>23577.74</t>
+          <t>23000.42</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-345</t>
+          <t>947</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-1968.339437718039</t>
+          <t>-1894.515625575336</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-1607.35</v>
+        <v>-1488.48</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2500,12 +2500,12 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>21.11</t>
+          <t>20.66</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>34.99</t>
+          <t>33.98</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2268</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
+          <t>54.5</t>
+        </is>
+      </c>
+      <c r="CD5" t="inlineStr">
+        <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
           <t>54.1</t>
         </is>
       </c>
-      <c r="CD5" t="inlineStr">
-        <is>
-          <t>54.4</t>
-        </is>
-      </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>53.8</t>
-        </is>
-      </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>201.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-7.54</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-9.60</t>
+          <t>-8.75</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>7.24</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,275 +2733,275 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>129</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>10.55</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>-4.47</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
+          <t>53.86</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>56.38</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>59.37</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>57.36</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>-19.01</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>-1.53</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>-1.29</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>-117.64</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>2025/10/08</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>90962.16450216451</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>4672.0</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>7837.8</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>8182.9</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>23577.74</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>-345</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>-1968.339437718039</t>
+        </is>
+      </c>
+      <c r="BC6" t="n">
+        <v>-1607.35</v>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>55.5</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>2025/08/20</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>-2.34</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>利機</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>利機</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>電子通路業</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>1.11</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>2.973959600876125</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>7.507647901781631</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>9.97333412563415</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>3.97</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>6.82</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>20.66</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>20.15%</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
+          <t>3.13%</t>
+        </is>
+      </c>
+      <c r="BX6" t="inlineStr">
+        <is>
+          <t>33.98</t>
+        </is>
+      </c>
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>2268</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr">
+        <is>
+          <t>半導體產品60.53%、光電產品37.52%、其他產品1.95% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
+          <t>利機-電子通路業-上櫃</t>
+        </is>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>電子通路業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CC6" t="inlineStr">
+        <is>
+          <t>54.1</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
+          <t>54.4</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
           <t>53.8</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>56.6</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>59.52</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>57.35</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>-27.97</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>-1.57</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>-1.23</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>7.3</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>-116.80</t>
-        </is>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>2025/10/08</t>
-        </is>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>91079.31502890174</t>
-        </is>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>10896.0</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>8352.6</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>8330.8</t>
-        </is>
-      </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>24471.84</t>
-        </is>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>-2033.974659900123</t>
-        </is>
-      </c>
-      <c r="BC6" t="n">
-        <v>-1447.92</v>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>55.5</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>2025/08/20</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>-3.24</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>利機</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>利機</t>
-        </is>
-      </c>
-      <c r="BJ6" t="inlineStr">
-        <is>
-          <t>電子通路業</t>
-        </is>
-      </c>
-      <c r="BK6" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>1.11</t>
-        </is>
-      </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>2.973959600876125</t>
-        </is>
-      </c>
-      <c r="BN6" t="inlineStr">
-        <is>
-          <t>7.507647901781631</t>
-        </is>
-      </c>
-      <c r="BO6" t="inlineStr">
-        <is>
-          <t>9.97333412563415</t>
-        </is>
-      </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ6" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BR6" t="inlineStr">
-        <is>
-          <t>2.32</t>
-        </is>
-      </c>
-      <c r="BS6" t="inlineStr">
-        <is>
-          <t>3.88</t>
-        </is>
-      </c>
-      <c r="BT6" t="inlineStr">
-        <is>
-          <t>6.82</t>
-        </is>
-      </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>21.11</t>
-        </is>
-      </c>
-      <c r="BV6" t="inlineStr">
-        <is>
-          <t>20.15%</t>
-        </is>
-      </c>
-      <c r="BW6" t="inlineStr">
-        <is>
-          <t>3.13%</t>
-        </is>
-      </c>
-      <c r="BX6" t="inlineStr">
-        <is>
-          <t>34.99</t>
-        </is>
-      </c>
-      <c r="BY6" t="inlineStr">
-        <is>
-          <t>2317</t>
-        </is>
-      </c>
-      <c r="BZ6" t="inlineStr">
-        <is>
-          <t>半導體產品60.53%、光電產品37.52%、其他產品1.95% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA6" t="inlineStr">
-        <is>
-          <t>利機-電子通路業-上櫃</t>
-        </is>
-      </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>電子通路業右下上櫃</t>
-        </is>
-      </c>
-      <c r="CC6" t="inlineStr">
-        <is>
-          <t>53.8</t>
-        </is>
-      </c>
-      <c r="CD6" t="inlineStr">
-        <is>
-          <t>54.9</t>
-        </is>
-      </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>53.7</t>
-        </is>
-      </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>201.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-4.47</t>
+          <t>-6.55</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-9.43</t>
+          <t>-9.60</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>7.24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>129</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-5.37</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-4.36</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>53.96</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>57.02</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>59.63</t>
+          <t>59.52</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>57.34</t>
+          <t>57.35</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-35.26</t>
+          <t>-27.97</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-115.63</t>
+          <t>-116.80</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>91079.31502890174</t>
+          <t>90962.16450216451</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>6686.0</t>
+          <t>10896.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>8056.6</t>
+          <t>8352.6</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>7881.1</t>
+          <t>8330.8</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>24960.08</t>
+          <t>24471.84</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>21</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-2140.52994480799</t>
+          <t>-2033.974659900123</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-1835.32</v>
+        <v>-1447.92</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3352,22 +3352,22 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>21.11</t>
+          <t>20.66</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>34.99</t>
+          <t>33.98</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2268</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-6.75</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>7.73</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-9.76</t>
+          <t>-9.43</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>129</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-5.36</t>
+          <t>-5.37</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-4.36</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>54.46</t>
+          <t>53.96</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>57.54</t>
+          <t>57.02</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>59.69</t>
+          <t>59.63</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>57.33</t>
+          <t>57.34</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-43.90</t>
+          <t>-35.26</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-114.25</t>
+          <t>-115.63</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>91079.31502890174</t>
+          <t>90962.16450216451</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>12702.0</t>
+          <t>6686.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>8360.0</t>
+          <t>8056.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>7759.9</t>
+          <t>7881.1</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>25027.0</t>
+          <t>24960.08</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>175</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-2196.023369214014</t>
+          <t>-2140.52994480799</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-1872.12</v>
+        <v>-1835.32</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-3.42</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3783,22 +3783,22 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>21.11</t>
+          <t>20.66</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>34.99</t>
+          <t>33.98</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2268</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3853,17 +3853,17 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>240.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-6.35</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-14.59</t>
+          <t>7.73</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-9.09</t>
+          <t>-9.76</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,17 +4026,17 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>129</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -4046,57 +4046,57 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-5.57</t>
+          <t>-5.36</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>54.88</t>
+          <t>54.46</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>58.12</t>
+          <t>57.54</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>59.75</t>
+          <t>59.69</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>57.31</t>
+          <t>57.33</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-50.73</t>
+          <t>-43.90</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-112.69</t>
+          <t>-114.25</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>91079.31502890174</t>
+          <t>90962.16450216451</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>4233.0</t>
+          <t>12702.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>6537.4</t>
+          <t>8360.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>7654.3</t>
+          <t>7759.9</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>25071.18</t>
+          <t>25027.0</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-1116</t>
+          <t>600</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-2254.914918861746</t>
+          <t>-2196.023369214014</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-2502.41</v>
+        <v>-1872.12</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-2.70</t>
+          <t>-3.42</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4214,22 +4214,22 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>21.11</t>
+          <t>20.66</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>34.99</t>
+          <t>33.98</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2268</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>53.9</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>54.4</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>53.9</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-4.66</t>
+          <t>-7.14</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-4.06</t>
+          <t>-14.59</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-9.26</t>
+          <t>-9.09</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>129</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>6.06</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-5.62</t>
+          <t>-5.57</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.88</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>58.59</t>
+          <t>58.12</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>59.78</t>
+          <t>59.75</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>57.28</t>
+          <t>57.31</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-59.20</t>
+          <t>-50.73</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-111.08</t>
+          <t>-112.69</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>91079.31502890174</t>
+          <t>90962.16450216451</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>7246.0</t>
+          <t>4233.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>8528.0</t>
+          <t>6537.4</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>8888.7</t>
+          <t>7654.3</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>25403.62</t>
+          <t>25071.18</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-360</t>
+          <t>-1116</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-2209.916428335603</t>
+          <t>-2254.914918861746</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-2406.05</v>
+        <v>-2502.41</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-2.70</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4645,22 +4645,22 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>21.11</t>
+          <t>20.66</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>34.99</t>
+          <t>33.98</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2268</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
+          <t>53.9</t>
+        </is>
+      </c>
+      <c r="CD10" t="inlineStr">
+        <is>
+          <t>54.4</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
+          <t>53.8</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
           <t>54.0</t>
-        </is>
-      </c>
-      <c r="CD10" t="inlineStr">
-        <is>
-          <t>54.5</t>
-        </is>
-      </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>53.2</t>
-        </is>
-      </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>53.9</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>53.9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-6.94</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-17.24</t>
+          <t>-4.06</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-8.25</t>
+          <t>-9.26</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>6.16</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,12 +4888,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>129</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4908,57 +4908,57 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-5.62</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>55.94000000000001</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>58.78</t>
+          <t>58.59</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>59.88</t>
+          <t>59.78</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>57.26</t>
+          <t>57.28</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-62.54</t>
+          <t>-59.20</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-109.44</t>
+          <t>-111.08</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>91079.31502890174</t>
+          <t>90962.16450216451</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>9416.0</t>
+          <t>7246.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>8309.0</t>
+          <t>8528.0</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>10040.4</t>
+          <t>8888.7</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>26095.24</t>
+          <t>25403.62</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-1731</t>
+          <t>-360</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-2174.255457665703</t>
+          <t>-2209.916428335603</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-2505.29</v>
+        <v>-2406.05</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>21.11</t>
+          <t>20.66</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>34.99</t>
+          <t>33.98</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2268</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>53.9</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>-3.19</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>56.3</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-9.32</t>
+          <t>-8.13</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-27.80</t>
+          <t>-17.24</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-5.22</t>
+          <t>-8.25</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>6.16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-3.49</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,17 +5319,17 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>129</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -5339,57 +5339,57 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-4.11</t>
+          <t>-4.84</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>4.70</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>56.52</t>
+          <t>55.94000000000001</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>58.94</t>
+          <t>58.78</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>59.9</t>
+          <t>59.88</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>57.21</t>
+          <t>57.26</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-63.61</t>
+          <t>-62.54</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-107.96</t>
+          <t>-109.44</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>91079.31502890174</t>
+          <t>90962.16450216451</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>8203.0</t>
+          <t>9416.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>7705.6</t>
+          <t>8309.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>10672.9</t>
+          <t>10040.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>26485.84</t>
+          <t>26095.24</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-2967</t>
+          <t>-1731</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-2114.06681542231</t>
+          <t>-2174.255457665703</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-2790.09</v>
+        <v>-2505.29</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>21.11</t>
+          <t>20.66</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>34.99</t>
+          <t>33.98</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2268</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>56.3</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/印刷材料.xlsx
+++ b/Result/checksun_type/印刷材料.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-14.12</t>
+          <t>-8.35</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-15.15</t>
+          <t>-14.48</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>125</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-5.05</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-5.46</t>
+          <t>-5.85</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>52.62</t>
+          <t>51.94</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>55.11</t>
+          <t>54.7</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>58.29</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>57.34</t>
+          <t>57.33</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-22.24</t>
+          <t>-20.92</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-120.76</t>
+          <t>-121.90</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>90962.16450216451</t>
+          <t>90844.90850144092</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>6596.0</t>
+          <t>6391.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>6285.4</t>
+          <t>6629.2</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>7319.0</t>
+          <t>7233.5</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>16730.98</t>
+          <t>16143.36</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-1033</t>
+          <t>-604</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-1668.794589419023</t>
+          <t>-1591.416749491411</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-1254.29</v>
+        <v>-1165.84</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-9.19</t>
+          <t>-8.47</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1197,22 +1197,22 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>20.66</t>
+          <t>20.82</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>33.98</t>
+          <t>33.41</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>2268</t>
+          <t>2286</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-5.99</t>
+          <t>-14.12</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-13.30</t>
+          <t>-15.15</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-3.88</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,12 +1440,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>125</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1455,62 +1455,62 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-5.16</t>
+          <t>-5.46</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>53.27999999999999</t>
+          <t>52.62</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>55.51</t>
+          <t>55.11</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>58.53</t>
+          <t>58.29</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>57.37</t>
+          <t>57.34</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-17.48</t>
+          <t>-22.24</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-119.60</t>
+          <t>-120.76</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>90962.16450216451</t>
+          <t>90844.90850144092</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>5817.0</t>
+          <t>6596.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>7145.4</t>
+          <t>6285.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>7601.0</t>
+          <t>7319.0</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>17385.02</t>
+          <t>16730.98</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-455</t>
+          <t>-1033</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-1744.158464240811</t>
+          <t>-1668.794589419023</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-1357.83</v>
+        <v>-1254.29</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-7.21</t>
+          <t>-9.19</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1638,12 +1638,12 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>20.66</t>
+          <t>20.82</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>33.98</t>
+          <t>33.41</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>2268</t>
+          <t>2286</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-6.64</t>
+          <t>-5.99</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-11.62</t>
+          <t>-13.30</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-3.88</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,12 +1871,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>125</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1886,62 +1886,62 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>18.52</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-5.03</t>
+          <t>-5.16</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>53.73999999999999</t>
+          <t>53.27999999999999</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>55.81</t>
+          <t>55.51</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>58.76</t>
+          <t>58.53</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>57.38</t>
+          <t>57.37</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-13.29</t>
+          <t>-17.48</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-118.74</t>
+          <t>-119.60</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>90962.16450216451</t>
+          <t>90844.90850144092</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>7133.0</t>
+          <t>5817.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>7319.2</t>
+          <t>7145.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>7839.6</t>
+          <t>7601.0</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>19212.02</t>
+          <t>17385.02</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-520</t>
+          <t>-455</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-1814.400883559504</t>
+          <t>-1744.158464240811</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-1373.77</v>
+        <v>-1357.83</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-5.41</t>
+          <t>-7.21</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>20.66</t>
+          <t>20.82</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>33.98</t>
+          <t>33.41</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>2268</t>
+          <t>2286</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-8.13</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>12.66</t>
+          <t>-6.64</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-8.25</t>
+          <t>-11.62</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,57 +2302,57 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>125</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>18.52</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-3.70</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-5.02</t>
+          <t>-5.03</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>53.96</t>
+          <t>53.73999999999999</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>56.14</t>
+          <t>55.81</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>59.1</t>
+          <t>58.76</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2362,17 +2362,17 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-10.55</t>
+          <t>-13.29</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-118.12</t>
+          <t>-118.74</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>90962.16450216451</t>
+          <t>90844.90850144092</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>7209.0</t>
+          <t>7133.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>8433.0</t>
+          <t>7319.2</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>7485.2</t>
+          <t>7839.6</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>23000.42</t>
+          <t>19212.02</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>-520</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-1894.515625575336</t>
+          <t>-1814.400883559504</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-1488.48</v>
+        <v>-1373.77</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-5.41</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2500,12 +2500,12 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>20.66</t>
+          <t>20.82</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>33.98</t>
+          <t>33.41</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>2268</t>
+          <t>2286</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
+          <t>53.8</t>
+        </is>
+      </c>
+      <c r="CD5" t="inlineStr">
+        <is>
           <t>54.5</t>
         </is>
       </c>
-      <c r="CD5" t="inlineStr">
-        <is>
-          <t>55.0</t>
-        </is>
-      </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-7.54</t>
+          <t>-7.28</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>12.66</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-8.75</t>
+          <t>-8.25</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,77 +2733,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>125</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>10.55</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.47</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-5.04</t>
+          <t>-5.02</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>53.86</t>
+          <t>53.96</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>56.38</t>
+          <t>56.14</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>59.37</t>
+          <t>59.1</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>57.36</t>
+          <t>57.38</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-19.01</t>
+          <t>-10.55</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-117.64</t>
+          <t>-118.12</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>90962.16450216451</t>
+          <t>90844.90850144092</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>4672.0</t>
+          <t>7209.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>7837.8</t>
+          <t>8433.0</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>8182.9</t>
+          <t>7485.2</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>23577.74</t>
+          <t>23000.42</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-345</t>
+          <t>947</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-1968.339437718039</t>
+          <t>-1894.515625575336</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-1607.35</v>
+        <v>-1488.48</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>20.66</t>
+          <t>20.82</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>33.98</t>
+          <t>33.41</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>2268</t>
+          <t>2286</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
+          <t>54.5</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
           <t>54.1</t>
         </is>
       </c>
-      <c r="CD6" t="inlineStr">
-        <is>
-          <t>54.4</t>
-        </is>
-      </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>53.8</t>
-        </is>
-      </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>201.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-6.55</t>
+          <t>-6.69</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-9.60</t>
+          <t>-8.75</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>7.24</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,275 +3164,275 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>125</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>10.55</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>-4.47</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
+          <t>53.86</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>56.38</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>59.37</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>57.36</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>-19.01</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>-1.53</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>-1.29</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>-117.64</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>2025/10/08</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>90844.90850144092</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>4672.0</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>7837.8</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>8182.9</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>23577.74</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>-345</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>-1968.339437718039</t>
+        </is>
+      </c>
+      <c r="BC7" t="n">
+        <v>-1607.35</v>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>55.5</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>2025/08/20</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>-2.34</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>利機</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>利機</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>電子通路業</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>2.973959600876125</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>7.507647901781631</t>
+        </is>
+      </c>
+      <c r="BO7" t="inlineStr">
+        <is>
+          <t>9.97333412563415</t>
+        </is>
+      </c>
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+        </is>
+      </c>
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
+          <t>3.94</t>
+        </is>
+      </c>
+      <c r="BT7" t="inlineStr">
+        <is>
+          <t>6.82</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
+          <t>20.82</t>
+        </is>
+      </c>
+      <c r="BV7" t="inlineStr">
+        <is>
+          <t>20.15%</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
+          <t>3.13%</t>
+        </is>
+      </c>
+      <c r="BX7" t="inlineStr">
+        <is>
+          <t>33.41</t>
+        </is>
+      </c>
+      <c r="BY7" t="inlineStr">
+        <is>
+          <t>2286</t>
+        </is>
+      </c>
+      <c r="BZ7" t="inlineStr">
+        <is>
+          <t>半導體產品60.53%、光電產品37.52%、其他產品1.95% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
+          <t>利機-電子通路業-上櫃</t>
+        </is>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>電子通路業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CC7" t="inlineStr">
+        <is>
+          <t>54.1</t>
+        </is>
+      </c>
+      <c r="CD7" t="inlineStr">
+        <is>
+          <t>54.4</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
           <t>53.8</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>56.6</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>59.52</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>57.35</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>-27.97</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>-1.57</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>-1.23</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>7.3</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>-116.80</t>
-        </is>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>2025/10/08</t>
-        </is>
-      </c>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>90962.16450216451</t>
-        </is>
-      </c>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>10896.0</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>8352.6</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>8330.8</t>
-        </is>
-      </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>24471.84</t>
-        </is>
-      </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>-2033.974659900123</t>
-        </is>
-      </c>
-      <c r="BC7" t="n">
-        <v>-1447.92</v>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE7" t="inlineStr">
-        <is>
-          <t>55.5</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>2025/08/20</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>-3.24</t>
-        </is>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>利機</t>
-        </is>
-      </c>
-      <c r="BI7" t="inlineStr">
-        <is>
-          <t>利機</t>
-        </is>
-      </c>
-      <c r="BJ7" t="inlineStr">
-        <is>
-          <t>電子通路業</t>
-        </is>
-      </c>
-      <c r="BK7" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL7" t="inlineStr">
-        <is>
-          <t>1.11</t>
-        </is>
-      </c>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>2.973959600876125</t>
-        </is>
-      </c>
-      <c r="BN7" t="inlineStr">
-        <is>
-          <t>7.507647901781631</t>
-        </is>
-      </c>
-      <c r="BO7" t="inlineStr">
-        <is>
-          <t>9.97333412563415</t>
-        </is>
-      </c>
-      <c r="BP7" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ7" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BR7" t="inlineStr">
-        <is>
-          <t>2.32</t>
-        </is>
-      </c>
-      <c r="BS7" t="inlineStr">
-        <is>
-          <t>3.97</t>
-        </is>
-      </c>
-      <c r="BT7" t="inlineStr">
-        <is>
-          <t>6.82</t>
-        </is>
-      </c>
-      <c r="BU7" t="inlineStr">
-        <is>
-          <t>20.66</t>
-        </is>
-      </c>
-      <c r="BV7" t="inlineStr">
-        <is>
-          <t>20.15%</t>
-        </is>
-      </c>
-      <c r="BW7" t="inlineStr">
-        <is>
-          <t>3.13%</t>
-        </is>
-      </c>
-      <c r="BX7" t="inlineStr">
-        <is>
-          <t>33.98</t>
-        </is>
-      </c>
-      <c r="BY7" t="inlineStr">
-        <is>
-          <t>2268</t>
-        </is>
-      </c>
-      <c r="BZ7" t="inlineStr">
-        <is>
-          <t>半導體產品60.53%、光電產品37.52%、其他產品1.95% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA7" t="inlineStr">
-        <is>
-          <t>利機-電子通路業-上櫃</t>
-        </is>
-      </c>
-      <c r="CB7" t="inlineStr">
-        <is>
-          <t>電子通路業右下上櫃</t>
-        </is>
-      </c>
-      <c r="CC7" t="inlineStr">
-        <is>
-          <t>53.8</t>
-        </is>
-      </c>
-      <c r="CD7" t="inlineStr">
-        <is>
-          <t>54.9</t>
-        </is>
-      </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>53.7</t>
-        </is>
-      </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>201.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-6.75</t>
+          <t>-5.71</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-9.43</t>
+          <t>-9.60</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>7.24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>125</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-5.37</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-4.36</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>53.96</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>57.02</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>59.63</t>
+          <t>59.52</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>57.34</t>
+          <t>57.35</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-35.26</t>
+          <t>-27.97</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-115.63</t>
+          <t>-116.80</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>90962.16450216451</t>
+          <t>90844.90850144092</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>6686.0</t>
+          <t>10896.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>8056.6</t>
+          <t>8352.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>7881.1</t>
+          <t>8330.8</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>24960.08</t>
+          <t>24471.84</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>21</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-2140.52994480799</t>
+          <t>-2033.974659900123</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-1835.32</v>
+        <v>-1447.92</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -3783,22 +3783,22 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>20.66</t>
+          <t>20.82</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>33.98</t>
+          <t>33.41</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>2268</t>
+          <t>2286</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-6.35</t>
+          <t>-5.91</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>7.73</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-9.76</t>
+          <t>-9.43</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>125</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-5.36</t>
+          <t>-5.37</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-4.36</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>54.46</t>
+          <t>53.96</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>57.54</t>
+          <t>57.02</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>59.69</t>
+          <t>59.63</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>57.33</t>
+          <t>57.34</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-43.90</t>
+          <t>-35.26</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-114.25</t>
+          <t>-115.63</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>90962.16450216451</t>
+          <t>90844.90850144092</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>12702.0</t>
+          <t>6686.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>8360.0</t>
+          <t>8056.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>7759.9</t>
+          <t>7881.1</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>25027.0</t>
+          <t>24960.08</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>175</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-2196.023369214014</t>
+          <t>-2140.52994480799</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-1872.12</v>
+        <v>-1835.32</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-3.42</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4214,22 +4214,22 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>20.66</t>
+          <t>20.82</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>33.98</t>
+          <t>33.41</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>2268</t>
+          <t>2286</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4284,17 +4284,17 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>240.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-7.14</t>
+          <t>-5.51</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-14.59</t>
+          <t>7.73</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-9.09</t>
+          <t>-9.76</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,17 +4457,17 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>125</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -4477,57 +4477,57 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-5.57</t>
+          <t>-5.36</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>54.88</t>
+          <t>54.46</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>58.12</t>
+          <t>57.54</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>59.75</t>
+          <t>59.69</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>57.31</t>
+          <t>57.33</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-50.73</t>
+          <t>-43.90</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-112.69</t>
+          <t>-114.25</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>90962.16450216451</t>
+          <t>90844.90850144092</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>4233.0</t>
+          <t>12702.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>6537.4</t>
+          <t>8360.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>7654.3</t>
+          <t>7759.9</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>25071.18</t>
+          <t>25027.0</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-1116</t>
+          <t>600</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-2254.914918861746</t>
+          <t>-2196.023369214014</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-2502.41</v>
+        <v>-1872.12</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-2.70</t>
+          <t>-3.42</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4645,22 +4645,22 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>20.66</t>
+          <t>20.82</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>33.98</t>
+          <t>33.41</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>2268</t>
+          <t>2286</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>53.9</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>54.4</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>53.9</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-6.94</t>
+          <t>-6.3</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-4.06</t>
+          <t>-14.59</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-9.26</t>
+          <t>-9.09</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>125</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>6.06</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-5.62</t>
+          <t>-5.57</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.88</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>58.59</t>
+          <t>58.12</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>59.78</t>
+          <t>59.75</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>57.28</t>
+          <t>57.31</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-59.20</t>
+          <t>-50.73</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-111.08</t>
+          <t>-112.69</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>90962.16450216451</t>
+          <t>90844.90850144092</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>7246.0</t>
+          <t>4233.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>8528.0</t>
+          <t>6537.4</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>8888.7</t>
+          <t>7654.3</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>25403.62</t>
+          <t>25071.18</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-360</t>
+          <t>-1116</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-2209.916428335603</t>
+          <t>-2254.914918861746</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-2406.05</v>
+        <v>-2502.41</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-2.70</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>20.66</t>
+          <t>20.82</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>33.98</t>
+          <t>33.41</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>2268</t>
+          <t>2286</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
+          <t>53.9</t>
+        </is>
+      </c>
+      <c r="CD11" t="inlineStr">
+        <is>
+          <t>54.4</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
+          <t>53.8</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
           <t>54.0</t>
-        </is>
-      </c>
-      <c r="CD11" t="inlineStr">
-        <is>
-          <t>54.5</t>
-        </is>
-      </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>53.2</t>
-        </is>
-      </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>53.9</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>53.9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-8.13</t>
+          <t>-6.1</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-17.24</t>
+          <t>-4.06</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-8.25</t>
+          <t>-9.26</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>6.16</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,12 +5319,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>125</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5339,57 +5339,57 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-5.62</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>55.94000000000001</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>58.78</t>
+          <t>58.59</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>59.88</t>
+          <t>59.78</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>57.26</t>
+          <t>57.28</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-62.54</t>
+          <t>-59.20</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-109.44</t>
+          <t>-111.08</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>90962.16450216451</t>
+          <t>90844.90850144092</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>9416.0</t>
+          <t>7246.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>8309.0</t>
+          <t>8528.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>10040.4</t>
+          <t>8888.7</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>26095.24</t>
+          <t>25403.62</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-1731</t>
+          <t>-360</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-2174.255457665703</t>
+          <t>-2209.916428335603</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-2505.29</v>
+        <v>-2406.05</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>20.66</t>
+          <t>20.82</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>33.98</t>
+          <t>33.41</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>2268</t>
+          <t>2286</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>53.9</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/印刷材料.xlsx
+++ b/Result/checksun_type/印刷材料.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>111.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-8.35</t>
+          <t>-14.34</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-14.48</t>
+          <t>-13.97</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>111</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>17.07</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>8.94</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-5.05</t>
+          <t>-5.65</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-5.85</t>
+          <t>-6.17</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>51.94</t>
+          <t>51.26000000000001</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>54.7</t>
+          <t>54.33</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>57.9</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>57.33</t>
+          <t>57.32</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-20.92</t>
+          <t>-16.87</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-121.90</t>
+          <t>-122.87</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>90844.90850144092</t>
+          <t>90726.3928057554</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>6391.0</t>
+          <t>5651.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>6629.2</t>
+          <t>6317.6</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>7233.5</t>
+          <t>7375.3</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>16143.36</t>
+          <t>15916.1</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-604</t>
+          <t>-1057</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-1591.416749491411</t>
+          <t>-1520.471774267434</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-1165.84</v>
+        <v>-1130.27</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-8.47</t>
+          <t>-7.93</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>20.82</t>
+          <t>20.94</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>33.41</t>
+          <t>33.64</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>2286</t>
+          <t>2299</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,102 +1334,102 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>-1.47</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-8.35</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-10-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>64.2</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>59.4</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>65.6</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>61.3</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>-14.48</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>4.73</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
           <t>-1.57</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>-14.12</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-10-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-10-15 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>64.2</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>59.4</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>65.6</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>61.3</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>-15.15</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>4.73</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>4.65</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>-2.78</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1440,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>111</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-5.05</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-5.46</t>
+          <t>-5.85</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>52.62</t>
+          <t>51.94</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>55.11</t>
+          <t>54.7</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>58.29</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>57.34</t>
+          <t>57.33</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-22.24</t>
+          <t>-20.92</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-120.76</t>
+          <t>-121.90</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>90844.90850144092</t>
+          <t>90726.3928057554</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>6596.0</t>
+          <t>6391.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>6285.4</t>
+          <t>6629.2</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>7319.0</t>
+          <t>7233.5</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>16730.98</t>
+          <t>16143.36</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-1033</t>
+          <t>-604</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-1668.794589419023</t>
+          <t>-1591.416749491411</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-1254.29</v>
+        <v>-1165.84</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-9.19</t>
+          <t>-8.47</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1628,22 +1628,22 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>20.82</t>
+          <t>20.94</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>33.41</t>
+          <t>33.64</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>2286</t>
+          <t>2299</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-5.99</t>
+          <t>-14.12</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-13.30</t>
+          <t>-15.15</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-3.88</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,12 +1871,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>111</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1886,62 +1886,62 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-5.16</t>
+          <t>-5.46</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>53.27999999999999</t>
+          <t>52.62</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>55.51</t>
+          <t>55.11</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>58.53</t>
+          <t>58.29</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>57.37</t>
+          <t>57.34</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-17.48</t>
+          <t>-22.24</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-119.60</t>
+          <t>-120.76</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>90844.90850144092</t>
+          <t>90726.3928057554</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>5817.0</t>
+          <t>6596.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>7145.4</t>
+          <t>6285.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>7601.0</t>
+          <t>7319.0</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>17385.02</t>
+          <t>16730.98</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-455</t>
+          <t>-1033</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-1744.158464240811</t>
+          <t>-1668.794589419023</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-1357.83</v>
+        <v>-1254.29</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-7.21</t>
+          <t>-9.19</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>20.82</t>
+          <t>20.94</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>33.41</t>
+          <t>33.64</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>2286</t>
+          <t>2299</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-6.64</t>
+          <t>-5.99</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-11.62</t>
+          <t>-13.30</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-3.88</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,12 +2302,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>111</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2317,62 +2317,62 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>18.52</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-5.03</t>
+          <t>-5.16</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>53.73999999999999</t>
+          <t>53.27999999999999</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>55.81</t>
+          <t>55.51</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>58.76</t>
+          <t>58.53</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>57.38</t>
+          <t>57.37</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-13.29</t>
+          <t>-17.48</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-118.74</t>
+          <t>-119.60</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>90844.90850144092</t>
+          <t>90726.3928057554</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>7133.0</t>
+          <t>5817.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>7319.2</t>
+          <t>7145.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>7839.6</t>
+          <t>7601.0</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>19212.02</t>
+          <t>17385.02</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-520</t>
+          <t>-455</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-1814.400883559504</t>
+          <t>-1744.158464240811</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-1373.77</v>
+        <v>-1357.83</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-5.41</t>
+          <t>-7.21</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2500,12 +2500,12 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>20.82</t>
+          <t>20.94</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>33.41</t>
+          <t>33.64</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>2286</t>
+          <t>2299</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-7.28</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>12.66</t>
+          <t>-6.64</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-8.25</t>
+          <t>-11.62</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,57 +2733,57 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>111</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>18.52</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-3.70</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-5.02</t>
+          <t>-5.03</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>53.96</t>
+          <t>53.73999999999999</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>56.14</t>
+          <t>55.81</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>59.1</t>
+          <t>58.76</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -2793,17 +2793,17 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-10.55</t>
+          <t>-13.29</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-118.12</t>
+          <t>-118.74</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>90844.90850144092</t>
+          <t>90726.3928057554</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>7209.0</t>
+          <t>7133.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>8433.0</t>
+          <t>7319.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>7485.2</t>
+          <t>7839.6</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>23000.42</t>
+          <t>19212.02</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>-520</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-1894.515625575336</t>
+          <t>-1814.400883559504</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-1488.48</v>
+        <v>-1373.77</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-5.41</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>20.82</t>
+          <t>20.94</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>33.41</t>
+          <t>33.64</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>2286</t>
+          <t>2299</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
+          <t>53.8</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
           <t>54.5</t>
         </is>
       </c>
-      <c r="CD6" t="inlineStr">
-        <is>
-          <t>55.0</t>
-        </is>
-      </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-6.69</t>
+          <t>-6.65</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>12.66</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-8.75</t>
+          <t>-8.25</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>111</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>10.55</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.47</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-5.04</t>
+          <t>-5.02</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>53.86</t>
+          <t>53.96</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>56.38</t>
+          <t>56.14</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>59.37</t>
+          <t>59.1</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>57.36</t>
+          <t>57.38</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-19.01</t>
+          <t>-10.55</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-117.64</t>
+          <t>-118.12</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>90844.90850144092</t>
+          <t>90726.3928057554</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>4672.0</t>
+          <t>7209.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>7837.8</t>
+          <t>8433.0</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>8182.9</t>
+          <t>7485.2</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>23577.74</t>
+          <t>23000.42</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-345</t>
+          <t>947</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-1968.339437718039</t>
+          <t>-1894.515625575336</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-1607.35</v>
+        <v>-1488.48</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>20.82</t>
+          <t>20.94</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>33.41</t>
+          <t>33.64</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>2286</t>
+          <t>2299</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
+          <t>54.5</t>
+        </is>
+      </c>
+      <c r="CD7" t="inlineStr">
+        <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
           <t>54.1</t>
         </is>
       </c>
-      <c r="CD7" t="inlineStr">
-        <is>
-          <t>54.4</t>
-        </is>
-      </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>53.8</t>
-        </is>
-      </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>201.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-5.71</t>
+          <t>-6.07</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-9.60</t>
+          <t>-8.75</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>7.24</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,275 +3595,275 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>111</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>10.55</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>-4.47</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
+          <t>53.86</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>56.38</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>59.37</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>57.36</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>-19.01</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>-1.53</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>-1.29</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>-117.64</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>2025/10/08</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>90726.3928057554</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>4672.0</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>7837.8</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>8182.9</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>23577.74</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>-345</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>-1968.339437718039</t>
+        </is>
+      </c>
+      <c r="BC8" t="n">
+        <v>-1607.35</v>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>55.5</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>2025/08/20</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>-2.34</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>利機</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>利機</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>電子通路業</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>2.973959600876125</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
+          <t>7.507647901781631</t>
+        </is>
+      </c>
+      <c r="BO8" t="inlineStr">
+        <is>
+          <t>9.97333412563415</t>
+        </is>
+      </c>
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+        </is>
+      </c>
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
+          <t>3.91</t>
+        </is>
+      </c>
+      <c r="BT8" t="inlineStr">
+        <is>
+          <t>6.82</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
+          <t>20.94</t>
+        </is>
+      </c>
+      <c r="BV8" t="inlineStr">
+        <is>
+          <t>20.15%</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
+          <t>3.13%</t>
+        </is>
+      </c>
+      <c r="BX8" t="inlineStr">
+        <is>
+          <t>33.64</t>
+        </is>
+      </c>
+      <c r="BY8" t="inlineStr">
+        <is>
+          <t>2299</t>
+        </is>
+      </c>
+      <c r="BZ8" t="inlineStr">
+        <is>
+          <t>半導體產品60.53%、光電產品37.52%、其他產品1.95% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
+          <t>利機-電子通路業-上櫃</t>
+        </is>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>電子通路業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CC8" t="inlineStr">
+        <is>
+          <t>54.1</t>
+        </is>
+      </c>
+      <c r="CD8" t="inlineStr">
+        <is>
+          <t>54.4</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
           <t>53.8</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>56.6</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>59.52</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>57.35</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>-27.97</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>-1.57</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>-1.23</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>7.3</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>-116.80</t>
-        </is>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>2025/10/08</t>
-        </is>
-      </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>90844.90850144092</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>10896.0</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>8352.6</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>8330.8</t>
-        </is>
-      </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>24471.84</t>
-        </is>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>-2033.974659900123</t>
-        </is>
-      </c>
-      <c r="BC8" t="n">
-        <v>-1447.92</v>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>55.5</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>2025/08/20</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>-3.24</t>
-        </is>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>利機</t>
-        </is>
-      </c>
-      <c r="BI8" t="inlineStr">
-        <is>
-          <t>利機</t>
-        </is>
-      </c>
-      <c r="BJ8" t="inlineStr">
-        <is>
-          <t>電子通路業</t>
-        </is>
-      </c>
-      <c r="BK8" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL8" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>2.973959600876125</t>
-        </is>
-      </c>
-      <c r="BN8" t="inlineStr">
-        <is>
-          <t>7.507647901781631</t>
-        </is>
-      </c>
-      <c r="BO8" t="inlineStr">
-        <is>
-          <t>9.97333412563415</t>
-        </is>
-      </c>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ8" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BR8" t="inlineStr">
-        <is>
-          <t>2.32</t>
-        </is>
-      </c>
-      <c r="BS8" t="inlineStr">
-        <is>
-          <t>3.94</t>
-        </is>
-      </c>
-      <c r="BT8" t="inlineStr">
-        <is>
-          <t>6.82</t>
-        </is>
-      </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>20.82</t>
-        </is>
-      </c>
-      <c r="BV8" t="inlineStr">
-        <is>
-          <t>20.15%</t>
-        </is>
-      </c>
-      <c r="BW8" t="inlineStr">
-        <is>
-          <t>3.13%</t>
-        </is>
-      </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>33.41</t>
-        </is>
-      </c>
-      <c r="BY8" t="inlineStr">
-        <is>
-          <t>2286</t>
-        </is>
-      </c>
-      <c r="BZ8" t="inlineStr">
-        <is>
-          <t>半導體產品60.53%、光電產品37.52%、其他產品1.95% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA8" t="inlineStr">
-        <is>
-          <t>利機-電子通路業-上櫃</t>
-        </is>
-      </c>
-      <c r="CB8" t="inlineStr">
-        <is>
-          <t>電子通路業右下上櫃</t>
-        </is>
-      </c>
-      <c r="CC8" t="inlineStr">
-        <is>
-          <t>53.8</t>
-        </is>
-      </c>
-      <c r="CD8" t="inlineStr">
-        <is>
-          <t>54.9</t>
-        </is>
-      </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>53.7</t>
-        </is>
-      </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>201.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-5.91</t>
+          <t>-5.09</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-9.43</t>
+          <t>-9.60</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>7.24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>111</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-5.37</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-4.36</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>53.96</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>57.02</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>59.63</t>
+          <t>59.52</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>57.34</t>
+          <t>57.35</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-35.26</t>
+          <t>-27.97</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-115.63</t>
+          <t>-116.80</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>90844.90850144092</t>
+          <t>90726.3928057554</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>6686.0</t>
+          <t>10896.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>8056.6</t>
+          <t>8352.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>7881.1</t>
+          <t>8330.8</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>24960.08</t>
+          <t>24471.84</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>21</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-2140.52994480799</t>
+          <t>-2033.974659900123</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-1835.32</v>
+        <v>-1447.92</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4214,22 +4214,22 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>20.82</t>
+          <t>20.94</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>33.41</t>
+          <t>33.64</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>2286</t>
+          <t>2299</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-5.51</t>
+          <t>-5.28</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>7.73</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-9.76</t>
+          <t>-9.43</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>111</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-5.36</t>
+          <t>-5.37</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-4.36</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>54.46</t>
+          <t>53.96</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>57.54</t>
+          <t>57.02</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>59.69</t>
+          <t>59.63</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>57.33</t>
+          <t>57.34</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-43.90</t>
+          <t>-35.26</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-114.25</t>
+          <t>-115.63</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>90844.90850144092</t>
+          <t>90726.3928057554</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>12702.0</t>
+          <t>6686.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>8360.0</t>
+          <t>8056.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>7759.9</t>
+          <t>7881.1</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>25027.0</t>
+          <t>24960.08</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>175</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-2196.023369214014</t>
+          <t>-2140.52994480799</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-1872.12</v>
+        <v>-1835.32</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-3.42</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>20.82</t>
+          <t>20.94</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>33.41</t>
+          <t>33.64</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>2286</t>
+          <t>2299</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4715,17 +4715,17 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>240.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-6.3</t>
+          <t>-4.89</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-14.59</t>
+          <t>7.73</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-9.09</t>
+          <t>-9.76</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,17 +4888,17 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>111</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -4908,57 +4908,57 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-5.57</t>
+          <t>-5.36</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>54.88</t>
+          <t>54.46</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>58.12</t>
+          <t>57.54</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>59.75</t>
+          <t>59.69</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>57.31</t>
+          <t>57.33</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-50.73</t>
+          <t>-43.90</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-112.69</t>
+          <t>-114.25</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>90844.90850144092</t>
+          <t>90726.3928057554</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>4233.0</t>
+          <t>12702.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>6537.4</t>
+          <t>8360.0</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>7654.3</t>
+          <t>7759.9</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>25071.18</t>
+          <t>25027.0</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-1116</t>
+          <t>600</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-2254.914918861746</t>
+          <t>-2196.023369214014</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-2502.41</v>
+        <v>-1872.12</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-2.70</t>
+          <t>-3.42</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>20.82</t>
+          <t>20.94</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>33.41</t>
+          <t>33.64</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>2286</t>
+          <t>2299</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>53.9</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>54.4</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>53.9</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-6.1</t>
+          <t>-5.68</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-4.06</t>
+          <t>-14.59</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-9.26</t>
+          <t>-9.09</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>111</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>6.06</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-5.62</t>
+          <t>-5.57</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.88</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>58.59</t>
+          <t>58.12</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>59.78</t>
+          <t>59.75</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>57.28</t>
+          <t>57.31</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-59.20</t>
+          <t>-50.73</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-111.08</t>
+          <t>-112.69</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>90844.90850144092</t>
+          <t>90726.3928057554</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>7246.0</t>
+          <t>4233.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>8528.0</t>
+          <t>6537.4</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>8888.7</t>
+          <t>7654.3</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>25403.62</t>
+          <t>25071.18</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-360</t>
+          <t>-1116</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-2209.916428335603</t>
+          <t>-2254.914918861746</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-2406.05</v>
+        <v>-2502.41</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-2.70</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>20.82</t>
+          <t>20.94</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>33.41</t>
+          <t>33.64</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>2286</t>
+          <t>2299</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
+          <t>53.9</t>
+        </is>
+      </c>
+      <c r="CD12" t="inlineStr">
+        <is>
+          <t>54.4</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
+          <t>53.8</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
           <t>54.0</t>
-        </is>
-      </c>
-      <c r="CD12" t="inlineStr">
-        <is>
-          <t>54.5</t>
-        </is>
-      </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>53.2</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>53.9</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/印刷材料.xlsx
+++ b/Result/checksun_type/印刷材料.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CI12"/>
+  <dimension ref="A1:CJ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -701,165 +701,170 @@
       </c>
       <c r="BC1" s="1" t="inlineStr">
         <is>
-          <t>Volume_Price_Change_sum</t>
+          <t>VPC_MACD</t>
         </is>
       </c>
       <c r="BD1" s="1" t="inlineStr">
         <is>
+          <t>Volume_Price_Change</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date收盤價</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>
@@ -878,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>111.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>49.85</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-14.34</t>
+          <t>-13.32</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-13.97</t>
+          <t>-16.08</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1019,12 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>17.07</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -1029,57 +1034,57 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-5.65</t>
+          <t>-5.95</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-6.17</t>
+          <t>-6.51</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>51.26000000000001</t>
+          <t>50.73</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>54.33</t>
+          <t>53.94</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>57.9</t>
+          <t>57.69</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>57.32</t>
+          <t>57.29</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-16.87</t>
+          <t>-17.10</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-122.87</t>
+          <t>-123.89</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,198 +1104,203 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>90726.3928057554</t>
+          <t>90603.6573275862</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>5651.0</t>
+          <t>3535.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>6317.6</t>
+          <t>5598.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>7375.3</t>
+          <t>6458.6</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>15916.1</t>
+          <t>15662.04</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-1057</t>
+          <t>-860</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-1520.471774267434</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>-1130.27</v>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-1476.679593106963</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>-1235.822596724375</t>
+        </is>
+      </c>
+      <c r="BD2" t="n">
+        <v>3535</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
           <t>55.5</t>
         </is>
       </c>
-      <c r="BF2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>2025/08/20</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>-7.93</t>
-        </is>
-      </c>
       <c r="BH2" t="inlineStr">
         <is>
+          <t>-10.18</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
           <t>利機</t>
         </is>
       </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BJ2" t="inlineStr">
         <is>
           <t>利機</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BK2" t="inlineStr">
         <is>
           <t>電子通路業</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BL2" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>1.09</t>
-        </is>
-      </c>
       <c r="BM2" t="inlineStr">
         <is>
+          <t>1.08</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
           <t>2.973959600876125</t>
         </is>
       </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>7.507647901781631</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>9.97333412563415</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
+          <t>4.01</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
           <t>6.82</t>
         </is>
       </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>20.94</t>
-        </is>
-      </c>
       <c r="BV2" t="inlineStr">
         <is>
+          <t>20.43</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
           <t>20.15%</t>
         </is>
       </c>
-      <c r="BW2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>3.13%</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>33.64</t>
-        </is>
-      </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>2299</t>
+          <t>32.84</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
+          <t>2243</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
           <t>半導體產品60.53%、光電產品37.52%、其他產品1.95% (2024年)</t>
         </is>
       </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>利機-電子通路業-上櫃</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>電子通路業右下上櫃</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>51.8</t>
-        </is>
-      </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
+          <t>49.85</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
           <t>23.11</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CI2" t="inlineStr">
         <is>
           <t>** 半導體 - 基板、導線架、IC封裝測試、IC模組、IC通路** 平面顯示器 - 驅動IC** 觸控面板 - 印刷材料** LED照明產業 - 封裝/模組</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1309,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>111.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-8.35</t>
+          <t>-14.34</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-14.48</t>
+          <t>-13.97</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1445,72 +1455,72 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>17.07</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>8.94</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-5.05</t>
+          <t>-5.65</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-5.85</t>
+          <t>-6.17</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>51.94</t>
+          <t>51.26000000000001</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>54.7</t>
+          <t>54.33</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>57.9</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>57.33</t>
+          <t>57.32</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-20.92</t>
+          <t>-16.87</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-121.90</t>
+          <t>-122.87</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,198 +1540,203 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>90726.3928057554</t>
+          <t>90603.6573275862</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>6391.0</t>
+          <t>5651.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>6629.2</t>
+          <t>6317.6</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>7233.5</t>
+          <t>7375.3</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>16143.36</t>
+          <t>15916.1</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-604</t>
+          <t>-1057</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-1591.416749491411</t>
-        </is>
-      </c>
-      <c r="BC3" t="n">
-        <v>-1165.84</v>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-1520.471774267434</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>-1130.274410535557</t>
+        </is>
+      </c>
+      <c r="BD3" t="n">
+        <v>5651</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
           <t>55.5</t>
         </is>
       </c>
-      <c r="BF3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>2025/08/20</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>-8.47</t>
-        </is>
-      </c>
       <c r="BH3" t="inlineStr">
         <is>
+          <t>-7.93</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
           <t>利機</t>
         </is>
       </c>
-      <c r="BI3" t="inlineStr">
+      <c r="BJ3" t="inlineStr">
         <is>
           <t>利機</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
+      <c r="BK3" t="inlineStr">
         <is>
           <t>電子通路業</t>
         </is>
       </c>
-      <c r="BK3" t="inlineStr">
+      <c r="BL3" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>1.09</t>
-        </is>
-      </c>
       <c r="BM3" t="inlineStr">
         <is>
+          <t>1.08</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
           <t>2.973959600876125</t>
         </is>
       </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>7.507647901781631</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>9.97333412563415</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ3" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
           <t>價漲量-</t>
         </is>
       </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
+          <t>4.01</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
           <t>6.82</t>
         </is>
       </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>20.94</t>
-        </is>
-      </c>
       <c r="BV3" t="inlineStr">
         <is>
+          <t>20.43</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
           <t>20.15%</t>
         </is>
       </c>
-      <c r="BW3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>3.13%</t>
         </is>
       </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>33.64</t>
-        </is>
-      </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>2299</t>
+          <t>32.84</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
+          <t>2243</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
           <t>半導體產品60.53%、光電產品37.52%、其他產品1.95% (2024年)</t>
         </is>
       </c>
-      <c r="CA3" t="inlineStr">
+      <c r="CB3" t="inlineStr">
         <is>
           <t>利機-電子通路業-上櫃</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>電子通路業右下上櫃</t>
         </is>
       </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>50.8</t>
-        </is>
-      </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
+          <t>51.1</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
           <t>23.11</t>
         </is>
       </c>
-      <c r="CH3" t="inlineStr">
+      <c r="CI3" t="inlineStr">
         <is>
           <t>** 半導體 - 基板、導線架、IC封裝測試、IC模組、IC通路** 平面顯示器 - 驅動IC** 觸控面板 - 印刷材料** LED照明產業 - 封裝/模組</t>
         </is>
       </c>
-      <c r="CI3" t="inlineStr">
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1740,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-14.12</t>
+          <t>-8.35</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-15.15</t>
+          <t>-14.48</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1876,72 +1891,72 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-5.05</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-5.46</t>
+          <t>-5.85</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>52.62</t>
+          <t>51.94</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>55.11</t>
+          <t>54.7</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>58.29</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>57.34</t>
+          <t>57.33</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-22.24</t>
+          <t>-20.92</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-120.76</t>
+          <t>-121.90</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,198 +1976,203 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>90726.3928057554</t>
+          <t>90603.6573275862</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>6596.0</t>
+          <t>6391.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>6285.4</t>
+          <t>6629.2</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>7319.0</t>
+          <t>7233.5</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>16730.98</t>
+          <t>16143.36</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-1033</t>
+          <t>-604</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-1668.794589419023</t>
-        </is>
-      </c>
-      <c r="BC4" t="n">
-        <v>-1254.29</v>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-1591.416749491411</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>-1165.838629889547</t>
+        </is>
+      </c>
+      <c r="BD4" t="n">
+        <v>6391</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
           <t>55.5</t>
         </is>
       </c>
-      <c r="BF4" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>2025/08/20</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>-9.19</t>
-        </is>
-      </c>
       <c r="BH4" t="inlineStr">
         <is>
+          <t>-8.47</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
           <t>利機</t>
         </is>
       </c>
-      <c r="BI4" t="inlineStr">
+      <c r="BJ4" t="inlineStr">
         <is>
           <t>利機</t>
         </is>
       </c>
-      <c r="BJ4" t="inlineStr">
+      <c r="BK4" t="inlineStr">
         <is>
           <t>電子通路業</t>
         </is>
       </c>
-      <c r="BK4" t="inlineStr">
+      <c r="BL4" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL4" t="inlineStr">
-        <is>
-          <t>1.09</t>
-        </is>
-      </c>
       <c r="BM4" t="inlineStr">
         <is>
+          <t>1.08</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
           <t>2.973959600876125</t>
         </is>
       </c>
-      <c r="BN4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>7.507647901781631</t>
         </is>
       </c>
-      <c r="BO4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
         <is>
           <t>9.97333412563415</t>
         </is>
       </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
+          <t>4.01</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
           <t>6.82</t>
         </is>
       </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>20.94</t>
-        </is>
-      </c>
       <c r="BV4" t="inlineStr">
         <is>
+          <t>20.43</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
           <t>20.15%</t>
         </is>
       </c>
-      <c r="BW4" t="inlineStr">
+      <c r="BX4" t="inlineStr">
         <is>
           <t>3.13%</t>
         </is>
       </c>
-      <c r="BX4" t="inlineStr">
-        <is>
-          <t>33.64</t>
-        </is>
-      </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>2299</t>
+          <t>32.84</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
+          <t>2243</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
           <t>半導體產品60.53%、光電產品37.52%、其他產品1.95% (2024年)</t>
         </is>
       </c>
-      <c r="CA4" t="inlineStr">
+      <c r="CB4" t="inlineStr">
         <is>
           <t>利機-電子通路業-上櫃</t>
         </is>
       </c>
-      <c r="CB4" t="inlineStr">
+      <c r="CC4" t="inlineStr">
         <is>
           <t>電子通路業右下上櫃</t>
         </is>
       </c>
-      <c r="CC4" t="inlineStr">
-        <is>
-          <t>50.9</t>
-        </is>
-      </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
+          <t>50.8</t>
+        </is>
+      </c>
+      <c r="CH4" t="inlineStr">
+        <is>
           <t>23.11</t>
         </is>
       </c>
-      <c r="CH4" t="inlineStr">
+      <c r="CI4" t="inlineStr">
         <is>
           <t>** 半導體 - 基板、導線架、IC封裝測試、IC模組、IC通路** 平面顯示器 - 驅動IC** 觸控面板 - 印刷材料** LED照明產業 - 封裝/模組</t>
         </is>
       </c>
-      <c r="CI4" t="inlineStr">
+      <c r="CJ4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2171,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-5.99</t>
+          <t>-14.12</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-13.30</t>
+          <t>-15.15</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-3.88</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2307,7 +2327,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2317,62 +2337,62 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-5.16</t>
+          <t>-5.46</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>53.27999999999999</t>
+          <t>52.62</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>55.51</t>
+          <t>55.11</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>58.53</t>
+          <t>58.29</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>57.37</t>
+          <t>57.34</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-17.48</t>
+          <t>-22.24</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-119.60</t>
+          <t>-120.76</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,198 +2412,203 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>90726.3928057554</t>
+          <t>90603.6573275862</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>5817.0</t>
+          <t>6596.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>7145.4</t>
+          <t>6285.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>7601.0</t>
+          <t>7319.0</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>17385.02</t>
+          <t>16730.98</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-455</t>
+          <t>-1033</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-1744.158464240811</t>
-        </is>
-      </c>
-      <c r="BC5" t="n">
-        <v>-1357.83</v>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-1668.794589419023</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>-1254.293277899191</t>
+        </is>
+      </c>
+      <c r="BD5" t="n">
+        <v>6596</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
           <t>55.5</t>
         </is>
       </c>
-      <c r="BF5" t="inlineStr">
+      <c r="BG5" t="inlineStr">
         <is>
           <t>2025/08/20</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>-7.21</t>
-        </is>
-      </c>
       <c r="BH5" t="inlineStr">
         <is>
+          <t>-9.19</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
           <t>利機</t>
         </is>
       </c>
-      <c r="BI5" t="inlineStr">
+      <c r="BJ5" t="inlineStr">
         <is>
           <t>利機</t>
         </is>
       </c>
-      <c r="BJ5" t="inlineStr">
+      <c r="BK5" t="inlineStr">
         <is>
           <t>電子通路業</t>
         </is>
       </c>
-      <c r="BK5" t="inlineStr">
+      <c r="BL5" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL5" t="inlineStr">
-        <is>
-          <t>1.09</t>
-        </is>
-      </c>
       <c r="BM5" t="inlineStr">
         <is>
+          <t>1.08</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
           <t>2.973959600876125</t>
         </is>
       </c>
-      <c r="BN5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>7.507647901781631</t>
         </is>
       </c>
-      <c r="BO5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>9.97333412563415</t>
         </is>
       </c>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ5" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR5" t="inlineStr">
-        <is>
-          <t>2.23</t>
-        </is>
-      </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
+          <t>4.01</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
           <t>6.82</t>
         </is>
       </c>
-      <c r="BU5" t="inlineStr">
-        <is>
-          <t>20.94</t>
-        </is>
-      </c>
       <c r="BV5" t="inlineStr">
         <is>
+          <t>20.43</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
           <t>20.15%</t>
         </is>
       </c>
-      <c r="BW5" t="inlineStr">
+      <c r="BX5" t="inlineStr">
         <is>
           <t>3.13%</t>
         </is>
       </c>
-      <c r="BX5" t="inlineStr">
-        <is>
-          <t>33.64</t>
-        </is>
-      </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>2299</t>
+          <t>32.84</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
+          <t>2243</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
           <t>半導體產品60.53%、光電產品37.52%、其他產品1.95% (2024年)</t>
         </is>
       </c>
-      <c r="CA5" t="inlineStr">
+      <c r="CB5" t="inlineStr">
         <is>
           <t>利機-電子通路業-上櫃</t>
         </is>
       </c>
-      <c r="CB5" t="inlineStr">
+      <c r="CC5" t="inlineStr">
         <is>
           <t>電子通路業右下上櫃</t>
         </is>
       </c>
-      <c r="CC5" t="inlineStr">
-        <is>
-          <t>53.1</t>
-        </is>
-      </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
+          <t>50.4</t>
+        </is>
+      </c>
+      <c r="CH5" t="inlineStr">
+        <is>
           <t>23.11</t>
         </is>
       </c>
-      <c r="CH5" t="inlineStr">
+      <c r="CI5" t="inlineStr">
         <is>
           <t>** 半導體 - 基板、導線架、IC封裝測試、IC模組、IC通路** 平面顯示器 - 驅動IC** 觸控面板 - 印刷材料** LED照明產業 - 封裝/模組</t>
         </is>
       </c>
-      <c r="CI5" t="inlineStr">
+      <c r="CJ5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2602,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-3.31</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-6.64</t>
+          <t>-5.99</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-11.62</t>
+          <t>-13.30</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-3.88</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2738,7 +2763,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2748,62 +2773,62 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>18.52</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-5.03</t>
+          <t>-5.16</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>53.73999999999999</t>
+          <t>53.27999999999999</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>55.81</t>
+          <t>55.51</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>58.76</t>
+          <t>58.53</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>57.38</t>
+          <t>57.37</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-13.29</t>
+          <t>-17.48</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-118.74</t>
+          <t>-119.60</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,198 +2848,203 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>90726.3928057554</t>
+          <t>90603.6573275862</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>7133.0</t>
+          <t>5817.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>7319.2</t>
+          <t>7145.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>7839.6</t>
+          <t>7601.0</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>19212.02</t>
+          <t>17385.02</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-520</t>
+          <t>-455</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-1814.400883559504</t>
-        </is>
-      </c>
-      <c r="BC6" t="n">
-        <v>-1373.77</v>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-1744.158464240811</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>-1357.825157987996</t>
+        </is>
+      </c>
+      <c r="BD6" t="n">
+        <v>5817</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
           <t>55.5</t>
         </is>
       </c>
-      <c r="BF6" t="inlineStr">
+      <c r="BG6" t="inlineStr">
         <is>
           <t>2025/08/20</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>-5.41</t>
-        </is>
-      </c>
       <c r="BH6" t="inlineStr">
         <is>
+          <t>-7.21</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
           <t>利機</t>
         </is>
       </c>
-      <c r="BI6" t="inlineStr">
+      <c r="BJ6" t="inlineStr">
         <is>
           <t>利機</t>
         </is>
       </c>
-      <c r="BJ6" t="inlineStr">
+      <c r="BK6" t="inlineStr">
         <is>
           <t>電子通路業</t>
         </is>
       </c>
-      <c r="BK6" t="inlineStr">
+      <c r="BL6" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>1.09</t>
-        </is>
-      </c>
       <c r="BM6" t="inlineStr">
         <is>
+          <t>1.08</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
           <t>2.973959600876125</t>
         </is>
       </c>
-      <c r="BN6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>7.507647901781631</t>
         </is>
       </c>
-      <c r="BO6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
         <is>
           <t>9.97333412563415</t>
         </is>
       </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
-        </is>
-      </c>
       <c r="BQ6" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR6" t="inlineStr">
-        <is>
-          <t>2.27</t>
-        </is>
-      </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
+          <t>4.01</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
           <t>6.82</t>
         </is>
       </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>20.94</t>
-        </is>
-      </c>
       <c r="BV6" t="inlineStr">
         <is>
+          <t>20.43</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
           <t>20.15%</t>
         </is>
       </c>
-      <c r="BW6" t="inlineStr">
+      <c r="BX6" t="inlineStr">
         <is>
           <t>3.13%</t>
         </is>
       </c>
-      <c r="BX6" t="inlineStr">
-        <is>
-          <t>33.64</t>
-        </is>
-      </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>2299</t>
+          <t>32.84</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
+          <t>2243</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
           <t>半導體產品60.53%、光電產品37.52%、其他產品1.95% (2024年)</t>
         </is>
       </c>
-      <c r="CA6" t="inlineStr">
+      <c r="CB6" t="inlineStr">
         <is>
           <t>利機-電子通路業-上櫃</t>
         </is>
       </c>
-      <c r="CB6" t="inlineStr">
+      <c r="CC6" t="inlineStr">
         <is>
           <t>電子通路業右下上櫃</t>
         </is>
       </c>
-      <c r="CC6" t="inlineStr">
-        <is>
-          <t>53.8</t>
-        </is>
-      </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
+          <t>51.5</t>
+        </is>
+      </c>
+      <c r="CH6" t="inlineStr">
+        <is>
           <t>23.11</t>
         </is>
       </c>
-      <c r="CH6" t="inlineStr">
+      <c r="CI6" t="inlineStr">
         <is>
           <t>** 半導體 - 基板、導線架、IC封裝測試、IC模組、IC通路** 平面顯示器 - 驅動IC** 觸控面板 - 印刷材料** LED照明產業 - 封裝/模組</t>
         </is>
       </c>
-      <c r="CI6" t="inlineStr">
+      <c r="CJ6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3033,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-6.65</t>
+          <t>-5.32</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>12.66</t>
+          <t>-6.64</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-8.25</t>
+          <t>-11.62</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3169,52 +3199,52 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>18.52</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-3.70</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-5.02</t>
+          <t>-5.03</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>53.96</t>
+          <t>53.73999999999999</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>56.14</t>
+          <t>55.81</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>59.1</t>
+          <t>58.76</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3224,17 +3254,17 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-10.55</t>
+          <t>-13.29</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-118.12</t>
+          <t>-118.74</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,198 +3284,203 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>90726.3928057554</t>
+          <t>90603.6573275862</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>7209.0</t>
+          <t>7133.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>8433.0</t>
+          <t>7319.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>7485.2</t>
+          <t>7839.6</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>23000.42</t>
+          <t>19212.02</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>-520</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-1894.515625575336</t>
-        </is>
-      </c>
-      <c r="BC7" t="n">
-        <v>-1488.48</v>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-1814.400883559504</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>-1373.769802472432</t>
+        </is>
+      </c>
+      <c r="BD7" t="n">
+        <v>7133</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
           <t>55.5</t>
         </is>
       </c>
-      <c r="BF7" t="inlineStr">
+      <c r="BG7" t="inlineStr">
         <is>
           <t>2025/08/20</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>-1.80</t>
-        </is>
-      </c>
       <c r="BH7" t="inlineStr">
         <is>
+          <t>-5.41</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
           <t>利機</t>
         </is>
       </c>
-      <c r="BI7" t="inlineStr">
+      <c r="BJ7" t="inlineStr">
         <is>
           <t>利機</t>
         </is>
       </c>
-      <c r="BJ7" t="inlineStr">
+      <c r="BK7" t="inlineStr">
         <is>
           <t>電子通路業</t>
         </is>
       </c>
-      <c r="BK7" t="inlineStr">
+      <c r="BL7" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL7" t="inlineStr">
-        <is>
-          <t>1.09</t>
-        </is>
-      </c>
       <c r="BM7" t="inlineStr">
         <is>
+          <t>1.08</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
           <t>2.973959600876125</t>
         </is>
       </c>
-      <c r="BN7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>7.507647901781631</t>
         </is>
       </c>
-      <c r="BO7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>9.97333412563415</t>
         </is>
       </c>
-      <c r="BP7" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ7" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR7" t="inlineStr">
-        <is>
-          <t>2.36</t>
-        </is>
-      </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
+          <t>4.01</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
           <t>6.82</t>
         </is>
       </c>
-      <c r="BU7" t="inlineStr">
-        <is>
-          <t>20.94</t>
-        </is>
-      </c>
       <c r="BV7" t="inlineStr">
         <is>
+          <t>20.43</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
           <t>20.15%</t>
         </is>
       </c>
-      <c r="BW7" t="inlineStr">
+      <c r="BX7" t="inlineStr">
         <is>
           <t>3.13%</t>
         </is>
       </c>
-      <c r="BX7" t="inlineStr">
-        <is>
-          <t>33.64</t>
-        </is>
-      </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>2299</t>
+          <t>32.84</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
+          <t>2243</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
           <t>半導體產品60.53%、光電產品37.52%、其他產品1.95% (2024年)</t>
         </is>
       </c>
-      <c r="CA7" t="inlineStr">
+      <c r="CB7" t="inlineStr">
         <is>
           <t>利機-電子通路業-上櫃</t>
         </is>
       </c>
-      <c r="CB7" t="inlineStr">
+      <c r="CC7" t="inlineStr">
         <is>
           <t>電子通路業右下上櫃</t>
         </is>
       </c>
-      <c r="CC7" t="inlineStr">
+      <c r="CD7" t="inlineStr">
+        <is>
+          <t>53.8</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
         <is>
           <t>54.5</t>
         </is>
       </c>
-      <c r="CD7" t="inlineStr">
-        <is>
-          <t>55.0</t>
-        </is>
-      </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>54.1</t>
-        </is>
-      </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
+          <t>52.5</t>
+        </is>
+      </c>
+      <c r="CH7" t="inlineStr">
+        <is>
           <t>23.11</t>
         </is>
       </c>
-      <c r="CH7" t="inlineStr">
+      <c r="CI7" t="inlineStr">
         <is>
           <t>** 半導體 - 基板、導線架、IC封裝測試、IC模組、IC通路** 平面顯示器 - 驅動IC** 觸控面板 - 印刷材料** LED照明產業 - 封裝/模組</t>
         </is>
       </c>
-      <c r="CI7" t="inlineStr">
+      <c r="CJ7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3464,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-6.07</t>
+          <t>-9.33</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>12.66</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-8.75</t>
+          <t>-8.25</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3600,72 +3635,72 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>10.55</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-4.47</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-5.04</t>
+          <t>-5.02</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>53.86</t>
+          <t>53.96</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>56.38</t>
+          <t>56.14</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>59.37</t>
+          <t>59.1</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>57.36</t>
+          <t>57.38</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-19.01</t>
+          <t>-10.55</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-117.64</t>
+          <t>-118.12</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,198 +3720,203 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>90726.3928057554</t>
+          <t>90603.6573275862</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>4672.0</t>
+          <t>7209.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>7837.8</t>
+          <t>8433.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>8182.9</t>
+          <t>7485.2</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>23577.74</t>
+          <t>23000.42</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-345</t>
+          <t>947</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-1968.339437718039</t>
-        </is>
-      </c>
-      <c r="BC8" t="n">
-        <v>-1607.35</v>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-1894.515625575336</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>-1488.484658790469</t>
+        </is>
+      </c>
+      <c r="BD8" t="n">
+        <v>7209</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
           <t>55.5</t>
         </is>
       </c>
-      <c r="BF8" t="inlineStr">
+      <c r="BG8" t="inlineStr">
         <is>
           <t>2025/08/20</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>-2.34</t>
-        </is>
-      </c>
       <c r="BH8" t="inlineStr">
         <is>
+          <t>-1.80</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
           <t>利機</t>
         </is>
       </c>
-      <c r="BI8" t="inlineStr">
+      <c r="BJ8" t="inlineStr">
         <is>
           <t>利機</t>
         </is>
       </c>
-      <c r="BJ8" t="inlineStr">
+      <c r="BK8" t="inlineStr">
         <is>
           <t>電子通路業</t>
         </is>
       </c>
-      <c r="BK8" t="inlineStr">
+      <c r="BL8" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL8" t="inlineStr">
-        <is>
-          <t>1.09</t>
-        </is>
-      </c>
       <c r="BM8" t="inlineStr">
         <is>
+          <t>1.08</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
           <t>2.973959600876125</t>
         </is>
       </c>
-      <c r="BN8" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>7.507647901781631</t>
         </is>
       </c>
-      <c r="BO8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
         <is>
           <t>9.97333412563415</t>
         </is>
       </c>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
-        </is>
-      </c>
       <c r="BQ8" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR8" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
-      </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
+          <t>4.01</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
           <t>6.82</t>
         </is>
       </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>20.94</t>
-        </is>
-      </c>
       <c r="BV8" t="inlineStr">
         <is>
+          <t>20.43</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
           <t>20.15%</t>
         </is>
       </c>
-      <c r="BW8" t="inlineStr">
+      <c r="BX8" t="inlineStr">
         <is>
           <t>3.13%</t>
         </is>
       </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>33.64</t>
-        </is>
-      </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>2299</t>
+          <t>32.84</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
+          <t>2243</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
           <t>半導體產品60.53%、光電產品37.52%、其他產品1.95% (2024年)</t>
         </is>
       </c>
-      <c r="CA8" t="inlineStr">
+      <c r="CB8" t="inlineStr">
         <is>
           <t>利機-電子通路業-上櫃</t>
         </is>
       </c>
-      <c r="CB8" t="inlineStr">
+      <c r="CC8" t="inlineStr">
         <is>
           <t>電子通路業右下上櫃</t>
         </is>
       </c>
-      <c r="CC8" t="inlineStr">
+      <c r="CD8" t="inlineStr">
+        <is>
+          <t>54.5</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
         <is>
           <t>54.1</t>
         </is>
       </c>
-      <c r="CD8" t="inlineStr">
-        <is>
-          <t>54.4</t>
-        </is>
-      </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>53.8</t>
-        </is>
-      </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>54.2</t>
-        </is>
-      </c>
       <c r="CG8" t="inlineStr">
         <is>
+          <t>54.5</t>
+        </is>
+      </c>
+      <c r="CH8" t="inlineStr">
+        <is>
           <t>23.11</t>
         </is>
       </c>
-      <c r="CH8" t="inlineStr">
+      <c r="CI8" t="inlineStr">
         <is>
           <t>** 半導體 - 基板、導線架、IC封裝測試、IC模組、IC通路** 平面顯示器 - 驅動IC** 觸控面板 - 印刷材料** LED照明產業 - 封裝/模組</t>
         </is>
       </c>
-      <c r="CI8" t="inlineStr">
+      <c r="CJ8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3895,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>201.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-5.09</t>
+          <t>-8.73</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-9.60</t>
+          <t>-8.75</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>7.24</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4031,283 +4071,288 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>10.55</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>-4.47</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
+          <t>53.86</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>56.38</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>59.37</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>57.36</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>-19.01</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>-1.53</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>-1.29</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>-117.64</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>2025/10/08</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>90603.6573275862</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>4672.0</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>7837.8</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>8182.9</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>23577.74</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>-345</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>-1968.339437718039</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>-1607.345715716578</t>
+        </is>
+      </c>
+      <c r="BD9" t="n">
+        <v>4672</v>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>55.5</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>2025/08/20</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>-2.34</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>利機</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>利機</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>電子通路業</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>1.08</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>2.973959600876125</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>7.507647901781631</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>9.97333412563415</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>4.01</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>6.82</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>20.43</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>20.15%</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
+        <is>
+          <t>3.13%</t>
+        </is>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>32.84</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>2243</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
+          <t>半導體產品60.53%、光電產品37.52%、其他產品1.95% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>利機-電子通路業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC9" t="inlineStr">
+        <is>
+          <t>電子通路業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CD9" t="inlineStr">
+        <is>
+          <t>54.1</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>54.4</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
           <t>53.8</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>56.6</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>59.52</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>57.35</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>-27.97</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>-1.57</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>-1.23</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>7.3</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>-116.80</t>
-        </is>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>2025/10/08</t>
-        </is>
-      </c>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>90726.3928057554</t>
-        </is>
-      </c>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>10896.0</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>8352.6</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>8330.8</t>
-        </is>
-      </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>24471.84</t>
-        </is>
-      </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>-2033.974659900123</t>
-        </is>
-      </c>
-      <c r="BC9" t="n">
-        <v>-1447.92</v>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE9" t="inlineStr">
-        <is>
-          <t>55.5</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>2025/08/20</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>-3.24</t>
-        </is>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>利機</t>
-        </is>
-      </c>
-      <c r="BI9" t="inlineStr">
-        <is>
-          <t>利機</t>
-        </is>
-      </c>
-      <c r="BJ9" t="inlineStr">
-        <is>
-          <t>電子通路業</t>
-        </is>
-      </c>
-      <c r="BK9" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL9" t="inlineStr">
-        <is>
-          <t>1.09</t>
-        </is>
-      </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>2.973959600876125</t>
-        </is>
-      </c>
-      <c r="BN9" t="inlineStr">
-        <is>
-          <t>7.507647901781631</t>
-        </is>
-      </c>
-      <c r="BO9" t="inlineStr">
-        <is>
-          <t>9.97333412563415</t>
-        </is>
-      </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ9" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BR9" t="inlineStr">
-        <is>
-          <t>2.32</t>
-        </is>
-      </c>
-      <c r="BS9" t="inlineStr">
-        <is>
-          <t>3.91</t>
-        </is>
-      </c>
-      <c r="BT9" t="inlineStr">
-        <is>
-          <t>6.82</t>
-        </is>
-      </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>20.94</t>
-        </is>
-      </c>
-      <c r="BV9" t="inlineStr">
-        <is>
-          <t>20.15%</t>
-        </is>
-      </c>
-      <c r="BW9" t="inlineStr">
-        <is>
-          <t>3.13%</t>
-        </is>
-      </c>
-      <c r="BX9" t="inlineStr">
-        <is>
-          <t>33.64</t>
-        </is>
-      </c>
-      <c r="BY9" t="inlineStr">
-        <is>
-          <t>2299</t>
-        </is>
-      </c>
-      <c r="BZ9" t="inlineStr">
-        <is>
-          <t>半導體產品60.53%、光電產品37.52%、其他產品1.95% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA9" t="inlineStr">
-        <is>
-          <t>利機-電子通路業-上櫃</t>
-        </is>
-      </c>
-      <c r="CB9" t="inlineStr">
-        <is>
-          <t>電子通路業右下上櫃</t>
-        </is>
-      </c>
-      <c r="CC9" t="inlineStr">
-        <is>
-          <t>53.8</t>
-        </is>
-      </c>
-      <c r="CD9" t="inlineStr">
-        <is>
-          <t>54.9</t>
-        </is>
-      </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>53.7</t>
-        </is>
-      </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>53.7</t>
-        </is>
-      </c>
       <c r="CG9" t="inlineStr">
         <is>
+          <t>54.2</t>
+        </is>
+      </c>
+      <c r="CH9" t="inlineStr">
+        <is>
           <t>23.11</t>
         </is>
       </c>
-      <c r="CH9" t="inlineStr">
+      <c r="CI9" t="inlineStr">
         <is>
           <t>** 半導體 - 基板、導線架、IC封裝測試、IC模組、IC通路** 平面顯示器 - 驅動IC** 觸控面板 - 印刷材料** LED照明產業 - 封裝/模組</t>
         </is>
       </c>
-      <c r="CI9" t="inlineStr">
+      <c r="CJ9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4326,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>201.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>-7.72</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-9.43</t>
+          <t>-9.60</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>7.24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4462,72 +4507,72 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-5.37</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-4.36</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>53.96</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>57.02</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>59.63</t>
+          <t>59.52</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>57.34</t>
+          <t>57.35</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-35.26</t>
+          <t>-27.97</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-115.63</t>
+          <t>-116.80</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,198 +4592,203 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>90726.3928057554</t>
+          <t>90603.6573275862</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>6686.0</t>
+          <t>10896.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>8056.6</t>
+          <t>8352.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>7881.1</t>
+          <t>8330.8</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>24960.08</t>
+          <t>24471.84</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>21</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-2140.52994480799</t>
-        </is>
-      </c>
-      <c r="BC10" t="n">
-        <v>-1835.32</v>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-2033.974659900123</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>-1447.920592906852</t>
+        </is>
+      </c>
+      <c r="BD10" t="n">
+        <v>10896</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
           <t>55.5</t>
         </is>
       </c>
-      <c r="BF10" t="inlineStr">
+      <c r="BG10" t="inlineStr">
         <is>
           <t>2025/08/20</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>-3.06</t>
-        </is>
-      </c>
       <c r="BH10" t="inlineStr">
         <is>
+          <t>-3.24</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
           <t>利機</t>
         </is>
       </c>
-      <c r="BI10" t="inlineStr">
+      <c r="BJ10" t="inlineStr">
         <is>
           <t>利機</t>
         </is>
       </c>
-      <c r="BJ10" t="inlineStr">
+      <c r="BK10" t="inlineStr">
         <is>
           <t>電子通路業</t>
         </is>
       </c>
-      <c r="BK10" t="inlineStr">
+      <c r="BL10" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL10" t="inlineStr">
-        <is>
-          <t>1.09</t>
-        </is>
-      </c>
       <c r="BM10" t="inlineStr">
         <is>
+          <t>1.08</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
           <t>2.973959600876125</t>
         </is>
       </c>
-      <c r="BN10" t="inlineStr">
+      <c r="BO10" t="inlineStr">
         <is>
           <t>7.507647901781631</t>
         </is>
       </c>
-      <c r="BO10" t="inlineStr">
+      <c r="BP10" t="inlineStr">
         <is>
           <t>9.97333412563415</t>
         </is>
       </c>
-      <c r="BP10" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ10" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="BR10" t="inlineStr">
-        <is>
-          <t>2.33</t>
-        </is>
-      </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
+          <t>4.01</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
           <t>6.82</t>
         </is>
       </c>
-      <c r="BU10" t="inlineStr">
-        <is>
-          <t>20.94</t>
-        </is>
-      </c>
       <c r="BV10" t="inlineStr">
         <is>
+          <t>20.43</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
           <t>20.15%</t>
         </is>
       </c>
-      <c r="BW10" t="inlineStr">
+      <c r="BX10" t="inlineStr">
         <is>
           <t>3.13%</t>
         </is>
       </c>
-      <c r="BX10" t="inlineStr">
-        <is>
-          <t>33.64</t>
-        </is>
-      </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>2299</t>
+          <t>32.84</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
+          <t>2243</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
           <t>半導體產品60.53%、光電產品37.52%、其他產品1.95% (2024年)</t>
         </is>
       </c>
-      <c r="CA10" t="inlineStr">
+      <c r="CB10" t="inlineStr">
         <is>
           <t>利機-電子通路業-上櫃</t>
         </is>
       </c>
-      <c r="CB10" t="inlineStr">
+      <c r="CC10" t="inlineStr">
         <is>
           <t>電子通路業右下上櫃</t>
         </is>
       </c>
-      <c r="CC10" t="inlineStr">
-        <is>
-          <t>54.0</t>
-        </is>
-      </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
+          <t>53.7</t>
+        </is>
+      </c>
+      <c r="CH10" t="inlineStr">
+        <is>
           <t>23.11</t>
         </is>
       </c>
-      <c r="CH10" t="inlineStr">
+      <c r="CI10" t="inlineStr">
         <is>
           <t>** 半導體 - 基板、導線架、IC封裝測試、IC模組、IC通路** 平面顯示器 - 驅動IC** 觸控面板 - 印刷材料** LED照明產業 - 封裝/模組</t>
         </is>
       </c>
-      <c r="CI10" t="inlineStr">
+      <c r="CJ10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4757,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-4.89</t>
+          <t>-7.92</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>7.73</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-9.76</t>
+          <t>-9.43</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4893,72 +4943,72 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-5.36</t>
+          <t>-5.37</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-4.36</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>54.46</t>
+          <t>53.96</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>57.54</t>
+          <t>57.02</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>59.69</t>
+          <t>59.63</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>57.33</t>
+          <t>57.34</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-43.90</t>
+          <t>-35.26</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-114.25</t>
+          <t>-115.63</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,198 +5028,203 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>90726.3928057554</t>
+          <t>90603.6573275862</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>12702.0</t>
+          <t>6686.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>8360.0</t>
+          <t>8056.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>7759.9</t>
+          <t>7881.1</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>25027.0</t>
+          <t>24960.08</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>175</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-2196.023369214014</t>
-        </is>
-      </c>
-      <c r="BC11" t="n">
-        <v>-1872.12</v>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-2140.52994480799</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>-1835.31611057486</t>
+        </is>
+      </c>
+      <c r="BD11" t="n">
+        <v>6686</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
           <t>55.5</t>
         </is>
       </c>
-      <c r="BF11" t="inlineStr">
+      <c r="BG11" t="inlineStr">
         <is>
           <t>2025/08/20</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>-3.42</t>
-        </is>
-      </c>
       <c r="BH11" t="inlineStr">
         <is>
+          <t>-3.06</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
           <t>利機</t>
         </is>
       </c>
-      <c r="BI11" t="inlineStr">
+      <c r="BJ11" t="inlineStr">
         <is>
           <t>利機</t>
         </is>
       </c>
-      <c r="BJ11" t="inlineStr">
+      <c r="BK11" t="inlineStr">
         <is>
           <t>電子通路業</t>
         </is>
       </c>
-      <c r="BK11" t="inlineStr">
+      <c r="BL11" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL11" t="inlineStr">
-        <is>
-          <t>1.09</t>
-        </is>
-      </c>
       <c r="BM11" t="inlineStr">
         <is>
+          <t>1.08</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
           <t>2.973959600876125</t>
         </is>
       </c>
-      <c r="BN11" t="inlineStr">
+      <c r="BO11" t="inlineStr">
         <is>
           <t>7.507647901781631</t>
         </is>
       </c>
-      <c r="BO11" t="inlineStr">
+      <c r="BP11" t="inlineStr">
         <is>
           <t>9.97333412563415</t>
         </is>
       </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ11" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>2.32</t>
-        </is>
-      </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
+          <t>4.01</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
           <t>6.82</t>
         </is>
       </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>20.94</t>
-        </is>
-      </c>
       <c r="BV11" t="inlineStr">
         <is>
+          <t>20.43</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
           <t>20.15%</t>
         </is>
       </c>
-      <c r="BW11" t="inlineStr">
+      <c r="BX11" t="inlineStr">
         <is>
           <t>3.13%</t>
         </is>
       </c>
-      <c r="BX11" t="inlineStr">
-        <is>
-          <t>33.64</t>
-        </is>
-      </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>2299</t>
+          <t>32.84</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
+          <t>2243</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
           <t>半導體產品60.53%、光電產品37.52%、其他產品1.95% (2024年)</t>
         </is>
       </c>
-      <c r="CA11" t="inlineStr">
+      <c r="CB11" t="inlineStr">
         <is>
           <t>利機-電子通路業-上櫃</t>
         </is>
       </c>
-      <c r="CB11" t="inlineStr">
+      <c r="CC11" t="inlineStr">
         <is>
           <t>電子通路業右下上櫃</t>
         </is>
       </c>
-      <c r="CC11" t="inlineStr">
+      <c r="CD11" t="inlineStr">
         <is>
           <t>54.0</t>
         </is>
       </c>
-      <c r="CD11" t="inlineStr">
-        <is>
-          <t>54.0</t>
-        </is>
-      </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
+          <t>53.8</t>
+        </is>
+      </c>
+      <c r="CH11" t="inlineStr">
+        <is>
           <t>23.11</t>
         </is>
       </c>
-      <c r="CH11" t="inlineStr">
+      <c r="CI11" t="inlineStr">
         <is>
           <t>** 半導體 - 基板、導線架、IC封裝測試、IC模組、IC通路** 平面顯示器 - 驅動IC** 觸控面板 - 印刷材料** LED照明產業 - 封裝/模組</t>
         </is>
       </c>
-      <c r="CI11" t="inlineStr">
+      <c r="CJ11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5188,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>240.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-5.68</t>
+          <t>-7.52</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-14.59</t>
+          <t>7.73</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-9.09</t>
+          <t>-9.76</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5324,12 +5379,12 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -5339,57 +5394,57 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-5.57</t>
+          <t>-5.36</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>54.88</t>
+          <t>54.46</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>58.12</t>
+          <t>57.54</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>59.75</t>
+          <t>59.69</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>57.31</t>
+          <t>57.33</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-50.73</t>
+          <t>-43.90</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-112.69</t>
+          <t>-114.25</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,198 +5464,203 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>90726.3928057554</t>
+          <t>90603.6573275862</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>4233.0</t>
+          <t>12702.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>6537.4</t>
+          <t>8360.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>7654.3</t>
+          <t>7759.9</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>25071.18</t>
+          <t>25027.0</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-1116</t>
+          <t>600</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-2254.914918861746</t>
-        </is>
-      </c>
-      <c r="BC12" t="n">
-        <v>-2502.41</v>
-      </c>
-      <c r="BD12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-2196.023369214014</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>-1872.119846151483</t>
+        </is>
+      </c>
+      <c r="BD12" t="n">
+        <v>12702</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
           <t>55.5</t>
         </is>
       </c>
-      <c r="BF12" t="inlineStr">
+      <c r="BG12" t="inlineStr">
         <is>
           <t>2025/08/20</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>-2.70</t>
-        </is>
-      </c>
       <c r="BH12" t="inlineStr">
         <is>
+          <t>-3.42</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
           <t>利機</t>
         </is>
       </c>
-      <c r="BI12" t="inlineStr">
+      <c r="BJ12" t="inlineStr">
         <is>
           <t>利機</t>
         </is>
       </c>
-      <c r="BJ12" t="inlineStr">
+      <c r="BK12" t="inlineStr">
         <is>
           <t>電子通路業</t>
         </is>
       </c>
-      <c r="BK12" t="inlineStr">
+      <c r="BL12" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL12" t="inlineStr">
-        <is>
-          <t>1.09</t>
-        </is>
-      </c>
       <c r="BM12" t="inlineStr">
         <is>
+          <t>1.08</t>
+        </is>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
           <t>2.973959600876125</t>
         </is>
       </c>
-      <c r="BN12" t="inlineStr">
+      <c r="BO12" t="inlineStr">
         <is>
           <t>7.507647901781631</t>
         </is>
       </c>
-      <c r="BO12" t="inlineStr">
+      <c r="BP12" t="inlineStr">
         <is>
           <t>9.97333412563415</t>
         </is>
       </c>
-      <c r="BP12" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ12" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR12" t="inlineStr">
-        <is>
-          <t>2.34</t>
-        </is>
-      </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
+          <t>4.01</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr">
+        <is>
           <t>6.82</t>
         </is>
       </c>
-      <c r="BU12" t="inlineStr">
-        <is>
-          <t>20.94</t>
-        </is>
-      </c>
       <c r="BV12" t="inlineStr">
         <is>
+          <t>20.43</t>
+        </is>
+      </c>
+      <c r="BW12" t="inlineStr">
+        <is>
           <t>20.15%</t>
         </is>
       </c>
-      <c r="BW12" t="inlineStr">
+      <c r="BX12" t="inlineStr">
         <is>
           <t>3.13%</t>
         </is>
       </c>
-      <c r="BX12" t="inlineStr">
-        <is>
-          <t>33.64</t>
-        </is>
-      </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>2299</t>
+          <t>32.84</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
+          <t>2243</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
+        <is>
           <t>半導體產品60.53%、光電產品37.52%、其他產品1.95% (2024年)</t>
         </is>
       </c>
-      <c r="CA12" t="inlineStr">
+      <c r="CB12" t="inlineStr">
         <is>
           <t>利機-電子通路業-上櫃</t>
         </is>
       </c>
-      <c r="CB12" t="inlineStr">
+      <c r="CC12" t="inlineStr">
         <is>
           <t>電子通路業右下上櫃</t>
         </is>
       </c>
-      <c r="CC12" t="inlineStr">
-        <is>
-          <t>53.9</t>
-        </is>
-      </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>54.4</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
+          <t>53.6</t>
+        </is>
+      </c>
+      <c r="CH12" t="inlineStr">
+        <is>
           <t>23.11</t>
         </is>
       </c>
-      <c r="CH12" t="inlineStr">
+      <c r="CI12" t="inlineStr">
         <is>
           <t>** 半導體 - 基板、導線架、IC封裝測試、IC模組、IC通路** 平面顯示器 - 驅動IC** 觸控面板 - 印刷材料** LED照明產業 - 封裝/模組</t>
         </is>
       </c>
-      <c r="CI12" t="inlineStr">
+      <c r="CJ12" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/印刷材料.xlsx
+++ b/Result/checksun_type/印刷材料.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>49.85</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>-3.41</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-13.32</t>
+          <t>-18.65</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-16.08</t>
+          <t>-15.82</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>46</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>8.94</t>
+          <t>6.77</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-5.95</t>
+          <t>-5.82</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-6.51</t>
+          <t>-6.81</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>50.73</t>
+          <t>50.42999999999999</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>53.94</t>
+          <t>53.55</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>57.69</t>
+          <t>57.46</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>57.29</t>
+          <t>57.28</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-17.10</t>
+          <t>-14.78</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-123.89</t>
+          <t>-124.80</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>90603.6573275862</t>
+          <t>90478.66571018651</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>3535.0</t>
+          <t>2323.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>5598.0</t>
+          <t>4899.2</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>6458.6</t>
+          <t>6022.3</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>15662.04</t>
+          <t>15417.3</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-860</t>
+          <t>-1123</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-1476.679593106963</t>
+          <t>-1460.222849881036</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-1235.822596724375</t>
+          <t>-1369.710762138438</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>3535</v>
+        <v>2323</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-10.18</t>
+          <t>-9.91</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>4</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>20.43</t>
+          <t>20.49</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>32.84</t>
+          <t>33.15</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>2243</t>
+          <t>2250</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>49.85</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>49.85</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>111.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>49.85</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>-3.41</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-14.34</t>
+          <t>-13.32</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-13.97</t>
+          <t>-16.08</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,17 +1450,17 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>46</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>17.07</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -1470,57 +1470,57 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-5.65</t>
+          <t>-5.95</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-6.17</t>
+          <t>-6.51</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>51.26000000000001</t>
+          <t>50.73</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>54.33</t>
+          <t>53.94</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>57.9</t>
+          <t>57.69</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>57.32</t>
+          <t>57.29</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-16.87</t>
+          <t>-17.10</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-122.87</t>
+          <t>-123.89</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>90603.6573275862</t>
+          <t>90478.66571018651</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>5651.0</t>
+          <t>3535.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>6317.6</t>
+          <t>5598.0</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>7375.3</t>
+          <t>6458.6</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>15916.1</t>
+          <t>15662.04</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-1057</t>
+          <t>-860</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-1520.471774267434</t>
+          <t>-1476.679593106963</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-1130.274410535557</t>
+          <t>-1235.822596724375</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>5651</v>
+        <v>3535</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-7.93</t>
+          <t>-10.18</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,22 +1643,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>4</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>20.43</t>
+          <t>20.49</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>32.84</t>
+          <t>33.15</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>2243</t>
+          <t>2250</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>49.85</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>111.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-2.2</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>-3.41</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-8.35</t>
+          <t>-14.34</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-14.48</t>
+          <t>-13.97</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>46</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>17.07</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>8.94</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-5.05</t>
+          <t>-5.65</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-5.85</t>
+          <t>-6.17</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>51.94</t>
+          <t>51.26000000000001</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>54.7</t>
+          <t>54.33</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>57.9</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>57.33</t>
+          <t>57.32</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-20.92</t>
+          <t>-16.87</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-121.90</t>
+          <t>-122.87</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>90603.6573275862</t>
+          <t>90478.66571018651</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>6391.0</t>
+          <t>5651.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>6629.2</t>
+          <t>6317.6</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>7233.5</t>
+          <t>7375.3</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>16143.36</t>
+          <t>15916.1</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-604</t>
+          <t>-1057</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-1591.416749491411</t>
+          <t>-1520.471774267434</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-1165.838629889547</t>
+          <t>-1130.274410535557</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>6391</v>
+        <v>5651</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-8.47</t>
+          <t>-7.93</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2089,12 +2089,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>4</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>20.43</t>
+          <t>20.49</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>32.84</t>
+          <t>33.15</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>2243</t>
+          <t>2250</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.1</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>-3.41</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-14.12</t>
+          <t>-8.35</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-15.15</t>
+          <t>-14.48</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,77 +2322,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>46</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-5.05</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-5.46</t>
+          <t>-5.85</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>52.62</t>
+          <t>51.94</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>55.11</t>
+          <t>54.7</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>58.29</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>57.34</t>
+          <t>57.33</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-22.24</t>
+          <t>-20.92</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-120.76</t>
+          <t>-121.90</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>90603.6573275862</t>
+          <t>90478.66571018651</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>6596.0</t>
+          <t>6391.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>6285.4</t>
+          <t>6629.2</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>7319.0</t>
+          <t>7233.5</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>16730.98</t>
+          <t>16143.36</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-1033</t>
+          <t>-604</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-1668.794589419023</t>
+          <t>-1591.416749491411</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-1254.293277899191</t>
+          <t>-1165.838629889547</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>6596</v>
+        <v>6391</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-9.19</t>
+          <t>-8.47</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,22 +2515,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>4</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>20.43</t>
+          <t>20.49</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>32.84</t>
+          <t>33.15</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>2243</t>
+          <t>2250</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>-3.41</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-5.99</t>
+          <t>-14.12</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-13.30</t>
+          <t>-15.15</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-3.88</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,12 +2758,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>46</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2773,62 +2773,62 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-5.16</t>
+          <t>-5.46</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>53.27999999999999</t>
+          <t>52.62</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>55.51</t>
+          <t>55.11</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>58.53</t>
+          <t>58.29</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>57.37</t>
+          <t>57.34</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-17.48</t>
+          <t>-22.24</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-119.60</t>
+          <t>-120.76</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>90603.6573275862</t>
+          <t>90478.66571018651</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>5817.0</t>
+          <t>6596.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>7145.4</t>
+          <t>6285.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>7601.0</t>
+          <t>7319.0</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>17385.02</t>
+          <t>16730.98</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-455</t>
+          <t>-1033</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-1744.158464240811</t>
+          <t>-1668.794589419023</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-1357.825157987996</t>
+          <t>-1254.293277899191</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>5817</v>
+        <v>6596</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-7.21</t>
+          <t>-9.19</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>4</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>20.43</t>
+          <t>20.49</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>32.84</t>
+          <t>33.15</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>2243</t>
+          <t>2250</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-5.32</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>-3.41</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-6.64</t>
+          <t>-5.99</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-11.62</t>
+          <t>-13.30</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-3.88</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,12 +3194,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>46</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3209,62 +3209,62 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>18.52</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-5.03</t>
+          <t>-5.16</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>53.73999999999999</t>
+          <t>53.27999999999999</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>55.81</t>
+          <t>55.51</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>58.76</t>
+          <t>58.53</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>57.38</t>
+          <t>57.37</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-13.29</t>
+          <t>-17.48</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-118.74</t>
+          <t>-119.60</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>90603.6573275862</t>
+          <t>90478.66571018651</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>7133.0</t>
+          <t>5817.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>7319.2</t>
+          <t>7145.4</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>7839.6</t>
+          <t>7601.0</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>19212.02</t>
+          <t>17385.02</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-520</t>
+          <t>-455</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-1814.400883559504</t>
+          <t>-1744.158464240811</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-1373.769802472432</t>
+          <t>-1357.825157987996</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>7133</v>
+        <v>5817</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-5.41</t>
+          <t>-7.21</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>4</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>20.43</t>
+          <t>20.49</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>32.84</t>
+          <t>33.15</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>2243</t>
+          <t>2250</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-9.33</t>
+          <t>-5.0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>-3.41</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>12.66</t>
+          <t>-6.64</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-8.25</t>
+          <t>-11.62</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,57 +3630,57 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>46</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>18.52</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-3.70</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-5.02</t>
+          <t>-5.03</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>53.96</t>
+          <t>53.73999999999999</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>56.14</t>
+          <t>55.81</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>59.1</t>
+          <t>58.76</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -3690,17 +3690,17 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-10.55</t>
+          <t>-13.29</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-118.12</t>
+          <t>-118.74</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>90603.6573275862</t>
+          <t>90478.66571018651</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>7209.0</t>
+          <t>7133.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>8433.0</t>
+          <t>7319.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>7485.2</t>
+          <t>7839.6</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>23000.42</t>
+          <t>19212.02</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>-520</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-1894.515625575336</t>
+          <t>-1814.400883559504</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-1488.484658790469</t>
+          <t>-1373.769802472432</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>7209</v>
+        <v>7133</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-5.41</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>4</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>20.43</t>
+          <t>20.49</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>32.84</t>
+          <t>33.15</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>2243</t>
+          <t>2250</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
+          <t>53.8</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
           <t>54.5</t>
         </is>
       </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>55.0</t>
-        </is>
-      </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-9.0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>-3.41</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>12.66</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-8.75</t>
+          <t>-8.25</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,77 +4066,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>46</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>10.55</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-4.47</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-5.04</t>
+          <t>-5.02</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>53.86</t>
+          <t>53.96</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>56.38</t>
+          <t>56.14</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>59.37</t>
+          <t>59.1</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>57.36</t>
+          <t>57.38</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-19.01</t>
+          <t>-10.55</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-117.64</t>
+          <t>-118.12</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>90603.6573275862</t>
+          <t>90478.66571018651</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>4672.0</t>
+          <t>7209.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>7837.8</t>
+          <t>8433.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>8182.9</t>
+          <t>7485.2</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>23577.74</t>
+          <t>23000.42</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-345</t>
+          <t>947</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-1968.339437718039</t>
+          <t>-1894.515625575336</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-1607.345715716578</t>
+          <t>-1488.484658790469</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>4672</v>
+        <v>7209</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>4</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>20.43</t>
+          <t>20.49</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>32.84</t>
+          <t>33.15</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>2243</t>
+          <t>2250</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
+          <t>54.5</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
           <t>54.1</t>
         </is>
       </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>54.4</t>
-        </is>
-      </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>53.8</t>
-        </is>
-      </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>201.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-7.72</t>
+          <t>-8.4</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>-3.41</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-9.60</t>
+          <t>-8.75</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>7.24</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,280 +4502,280 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>46</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>10.55</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>-4.47</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
+          <t>53.86</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>56.38</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>59.37</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>57.36</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>-19.01</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>-1.53</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>-1.29</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>-117.64</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>2025/10/08</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>90478.66571018651</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>4672.0</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>7837.8</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>8182.9</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>23577.74</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>-345</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>-1968.339437718039</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>-1607.345715716578</t>
+        </is>
+      </c>
+      <c r="BD10" t="n">
+        <v>4672</v>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>55.5</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>2025/08/20</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>-2.34</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>利機</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>利機</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>電子通路業</t>
+        </is>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
+          <t>1.08</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
+          <t>2.973959600876125</t>
+        </is>
+      </c>
+      <c r="BO10" t="inlineStr">
+        <is>
+          <t>7.507647901781631</t>
+        </is>
+      </c>
+      <c r="BP10" t="inlineStr">
+        <is>
+          <t>9.97333412563415</t>
+        </is>
+      </c>
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS10" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="BT10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
+          <t>6.82</t>
+        </is>
+      </c>
+      <c r="BV10" t="inlineStr">
+        <is>
+          <t>20.49</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
+          <t>20.15%</t>
+        </is>
+      </c>
+      <c r="BX10" t="inlineStr">
+        <is>
+          <t>3.13%</t>
+        </is>
+      </c>
+      <c r="BY10" t="inlineStr">
+        <is>
+          <t>33.15</t>
+        </is>
+      </c>
+      <c r="BZ10" t="inlineStr">
+        <is>
+          <t>2250</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
+          <t>半導體產品60.53%、光電產品37.52%、其他產品1.95% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>利機-電子通路業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC10" t="inlineStr">
+        <is>
+          <t>電子通路業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CD10" t="inlineStr">
+        <is>
+          <t>54.1</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
+          <t>54.4</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
           <t>53.8</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>56.6</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>59.52</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>57.35</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>-27.97</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>-1.57</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>-1.23</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>7.3</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>-116.80</t>
-        </is>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>2025/10/08</t>
-        </is>
-      </c>
-      <c r="AV10" t="inlineStr">
-        <is>
-          <t>90603.6573275862</t>
-        </is>
-      </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>10896.0</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>8352.6</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>8330.8</t>
-        </is>
-      </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>24471.84</t>
-        </is>
-      </c>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>-2033.974659900123</t>
-        </is>
-      </c>
-      <c r="BC10" t="inlineStr">
-        <is>
-          <t>-1447.920592906852</t>
-        </is>
-      </c>
-      <c r="BD10" t="n">
-        <v>10896</v>
-      </c>
-      <c r="BE10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>55.5</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>2025/08/20</t>
-        </is>
-      </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>-3.24</t>
-        </is>
-      </c>
-      <c r="BI10" t="inlineStr">
-        <is>
-          <t>利機</t>
-        </is>
-      </c>
-      <c r="BJ10" t="inlineStr">
-        <is>
-          <t>利機</t>
-        </is>
-      </c>
-      <c r="BK10" t="inlineStr">
-        <is>
-          <t>電子通路業</t>
-        </is>
-      </c>
-      <c r="BL10" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>1.08</t>
-        </is>
-      </c>
-      <c r="BN10" t="inlineStr">
-        <is>
-          <t>2.973959600876125</t>
-        </is>
-      </c>
-      <c r="BO10" t="inlineStr">
-        <is>
-          <t>7.507647901781631</t>
-        </is>
-      </c>
-      <c r="BP10" t="inlineStr">
-        <is>
-          <t>9.97333412563415</t>
-        </is>
-      </c>
-      <c r="BQ10" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR10" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS10" t="inlineStr">
-        <is>
-          <t>2.32</t>
-        </is>
-      </c>
-      <c r="BT10" t="inlineStr">
-        <is>
-          <t>4.01</t>
-        </is>
-      </c>
-      <c r="BU10" t="inlineStr">
-        <is>
-          <t>6.82</t>
-        </is>
-      </c>
-      <c r="BV10" t="inlineStr">
-        <is>
-          <t>20.43</t>
-        </is>
-      </c>
-      <c r="BW10" t="inlineStr">
-        <is>
-          <t>20.15%</t>
-        </is>
-      </c>
-      <c r="BX10" t="inlineStr">
-        <is>
-          <t>3.13%</t>
-        </is>
-      </c>
-      <c r="BY10" t="inlineStr">
-        <is>
-          <t>32.84</t>
-        </is>
-      </c>
-      <c r="BZ10" t="inlineStr">
-        <is>
-          <t>2243</t>
-        </is>
-      </c>
-      <c r="CA10" t="inlineStr">
-        <is>
-          <t>半導體產品60.53%、光電產品37.52%、其他產品1.95% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB10" t="inlineStr">
-        <is>
-          <t>利機-電子通路業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC10" t="inlineStr">
-        <is>
-          <t>電子通路業右下上櫃</t>
-        </is>
-      </c>
-      <c r="CD10" t="inlineStr">
-        <is>
-          <t>53.8</t>
-        </is>
-      </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>54.9</t>
-        </is>
-      </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>53.7</t>
-        </is>
-      </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>201.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-7.92</t>
+          <t>-7.4</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>-3.41</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-9.43</t>
+          <t>-9.60</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>7.24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,77 +4938,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>46</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-5.37</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-4.36</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>53.96</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>57.02</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>59.63</t>
+          <t>59.52</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>57.34</t>
+          <t>57.35</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-35.26</t>
+          <t>-27.97</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-115.63</t>
+          <t>-116.80</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>90603.6573275862</t>
+          <t>90478.66571018651</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>6686.0</t>
+          <t>10896.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>8056.6</t>
+          <t>8352.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>7881.1</t>
+          <t>8330.8</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>24960.08</t>
+          <t>24471.84</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>21</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-2140.52994480799</t>
+          <t>-2033.974659900123</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-1835.31611057486</t>
+          <t>-1447.920592906852</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>6686</v>
+        <v>10896</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>4</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>20.43</t>
+          <t>20.49</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>32.84</t>
+          <t>33.15</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>2243</t>
+          <t>2250</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-7.52</t>
+          <t>-7.6</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>-3.41</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>7.73</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-9.76</t>
+          <t>-9.43</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,77 +5374,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>46</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-5.36</t>
+          <t>-5.37</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-4.36</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>54.46</t>
+          <t>53.96</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>57.54</t>
+          <t>57.02</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>59.69</t>
+          <t>59.63</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>57.33</t>
+          <t>57.34</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-43.90</t>
+          <t>-35.26</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-114.25</t>
+          <t>-115.63</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>90603.6573275862</t>
+          <t>90478.66571018651</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>12702.0</t>
+          <t>6686.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>8360.0</t>
+          <t>8056.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>7759.9</t>
+          <t>7881.1</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>25027.0</t>
+          <t>24960.08</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>175</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-2196.023369214014</t>
+          <t>-2140.52994480799</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-1872.119846151483</t>
+          <t>-1835.31611057486</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>12702</v>
+        <v>6686</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-3.42</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>4</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>20.43</t>
+          <t>20.49</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>32.84</t>
+          <t>33.15</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>2243</t>
+          <t>2250</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5637,17 +5637,17 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/印刷材料.xlsx
+++ b/Result/checksun_type/印刷材料.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>334.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-3.41</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-18.65</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-15.82</t>
+          <t>-12.79</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>12.03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,72 +1019,72 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>334</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>41.94</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>6.77</t>
+          <t>15.05</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-5.82</t>
+          <t>-4.80</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-6.81</t>
+          <t>-6.85</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>50.42999999999999</t>
+          <t>50.71</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>53.55</t>
+          <t>53.27</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>57.46</t>
+          <t>57.18</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>57.28</t>
+          <t>57.29</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-14.78</t>
+          <t>-5.61</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-124.80</t>
+          <t>-125.16</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>90478.66571018651</t>
+          <t>90385.65042979943</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>2323.0</t>
+          <t>17036.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>4899.2</t>
+          <t>6987.2</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>6022.3</t>
+          <t>6636.3</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>15417.3</t>
+          <t>14299.4</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-1123</t>
+          <t>350</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-1460.222849881036</t>
+          <t>-1285.68313588008</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-1369.710762138438</t>
+          <t>-325.7147088748216</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>2323</v>
+        <v>17036</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-9.91</t>
+          <t>-6.67</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1207,22 +1207,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>20.49</t>
+          <t>21.23</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>33.15</t>
+          <t>31.27</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>2250</t>
+          <t>2331</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>49.85</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>49.85</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-3.41</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-13.32</t>
+          <t>-18.65</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-16.08</t>
+          <t>-15.82</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1455,72 +1455,72 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>334</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>8.94</t>
+          <t>6.77</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-5.95</t>
+          <t>-5.82</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-6.51</t>
+          <t>-6.81</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>50.73</t>
+          <t>50.42999999999999</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>53.94</t>
+          <t>53.55</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>57.69</t>
+          <t>57.46</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>57.29</t>
+          <t>57.28</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-17.10</t>
+          <t>-14.78</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-123.89</t>
+          <t>-124.80</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>90478.66571018651</t>
+          <t>90385.65042979943</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>3535.0</t>
+          <t>2323.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>5598.0</t>
+          <t>4899.2</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>6458.6</t>
+          <t>6022.3</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>15662.04</t>
+          <t>15417.3</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-860</t>
+          <t>-1123</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-1476.679593106963</t>
+          <t>-1460.222849881036</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-1235.822596724375</t>
+          <t>-1369.710762138438</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>3535</v>
+        <v>2323</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-10.18</t>
+          <t>-9.91</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>20.49</t>
+          <t>21.23</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>33.15</t>
+          <t>31.27</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>2250</t>
+          <t>2331</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>49.85</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>49.85</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>111.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>49.85</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.2</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-3.41</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-14.34</t>
+          <t>-13.32</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-13.97</t>
+          <t>-16.08</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1891,12 +1891,12 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>334</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>17.07</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1906,57 +1906,57 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-5.65</t>
+          <t>-5.95</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-6.17</t>
+          <t>-6.51</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>51.26000000000001</t>
+          <t>50.73</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>54.33</t>
+          <t>53.94</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>57.9</t>
+          <t>57.69</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>57.32</t>
+          <t>57.29</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-16.87</t>
+          <t>-17.10</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-122.87</t>
+          <t>-123.89</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>90478.66571018651</t>
+          <t>90385.65042979943</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>5651.0</t>
+          <t>3535.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>6317.6</t>
+          <t>5598.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>7375.3</t>
+          <t>6458.6</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>15916.1</t>
+          <t>15662.04</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-1057</t>
+          <t>-860</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-1520.471774267434</t>
+          <t>-1476.679593106963</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-1130.274410535557</t>
+          <t>-1235.822596724375</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>5651</v>
+        <v>3535</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-7.93</t>
+          <t>-10.18</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2079,22 +2079,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>20.49</t>
+          <t>21.23</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>33.15</t>
+          <t>31.27</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>2250</t>
+          <t>2331</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>49.85</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>111.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-3.41</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-8.35</t>
+          <t>-14.34</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-14.48</t>
+          <t>-13.97</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2327,72 +2327,72 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>334</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>17.07</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>8.94</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-5.05</t>
+          <t>-5.65</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-5.85</t>
+          <t>-6.17</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>51.94</t>
+          <t>51.26000000000001</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>54.7</t>
+          <t>54.33</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>57.9</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>57.33</t>
+          <t>57.32</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-20.92</t>
+          <t>-16.87</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-121.90</t>
+          <t>-122.87</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>90478.66571018651</t>
+          <t>90385.65042979943</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>6391.0</t>
+          <t>5651.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>6629.2</t>
+          <t>6317.6</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>7233.5</t>
+          <t>7375.3</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>16143.36</t>
+          <t>15916.1</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-604</t>
+          <t>-1057</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-1591.416749491411</t>
+          <t>-1520.471774267434</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-1165.838629889547</t>
+          <t>-1130.274410535557</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>6391</v>
+        <v>5651</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-8.47</t>
+          <t>-7.93</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>20.49</t>
+          <t>21.23</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>33.15</t>
+          <t>31.27</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>2250</t>
+          <t>2331</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-3.41</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-14.12</t>
+          <t>-8.35</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-15.15</t>
+          <t>-14.48</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2763,72 +2763,72 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>334</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-5.05</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-5.46</t>
+          <t>-5.85</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>52.62</t>
+          <t>51.94</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>55.11</t>
+          <t>54.7</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>58.29</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>57.34</t>
+          <t>57.33</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-22.24</t>
+          <t>-20.92</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-120.76</t>
+          <t>-121.90</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>90478.66571018651</t>
+          <t>90385.65042979943</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>6596.0</t>
+          <t>6391.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>6285.4</t>
+          <t>6629.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>7319.0</t>
+          <t>7233.5</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>16730.98</t>
+          <t>16143.36</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-1033</t>
+          <t>-604</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-1668.794589419023</t>
+          <t>-1591.416749491411</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-1254.293277899191</t>
+          <t>-1165.838629889547</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>6596</v>
+        <v>6391</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-9.19</t>
+          <t>-8.47</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2951,22 +2951,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>20.49</t>
+          <t>21.23</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>33.15</t>
+          <t>31.27</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>2250</t>
+          <t>2331</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-3.41</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-5.99</t>
+          <t>-14.12</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-13.30</t>
+          <t>-15.15</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-3.88</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3199,7 +3199,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>334</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3209,62 +3209,62 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-5.16</t>
+          <t>-5.46</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>53.27999999999999</t>
+          <t>52.62</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>55.51</t>
+          <t>55.11</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>58.53</t>
+          <t>58.29</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>57.37</t>
+          <t>57.34</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-17.48</t>
+          <t>-22.24</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-119.60</t>
+          <t>-120.76</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>90478.66571018651</t>
+          <t>90385.65042979943</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>5817.0</t>
+          <t>6596.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>7145.4</t>
+          <t>6285.4</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>7601.0</t>
+          <t>7319.0</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>17385.02</t>
+          <t>16730.98</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-455</t>
+          <t>-1033</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-1744.158464240811</t>
+          <t>-1668.794589419023</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-1357.825157987996</t>
+          <t>-1254.293277899191</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>5817</v>
+        <v>6596</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-7.21</t>
+          <t>-9.19</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>20.49</t>
+          <t>21.23</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>33.15</t>
+          <t>31.27</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>2250</t>
+          <t>2331</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-5.0</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-3.41</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-6.64</t>
+          <t>-5.99</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-11.62</t>
+          <t>-13.30</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-3.88</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3635,7 +3635,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>334</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3645,62 +3645,62 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>18.52</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-5.03</t>
+          <t>-5.16</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>53.73999999999999</t>
+          <t>53.27999999999999</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>55.81</t>
+          <t>55.51</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>58.76</t>
+          <t>58.53</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>57.38</t>
+          <t>57.37</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-13.29</t>
+          <t>-17.48</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-118.74</t>
+          <t>-119.60</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>90478.66571018651</t>
+          <t>90385.65042979943</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>7133.0</t>
+          <t>5817.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>7319.2</t>
+          <t>7145.4</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>7839.6</t>
+          <t>7601.0</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>19212.02</t>
+          <t>17385.02</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-520</t>
+          <t>-455</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-1814.400883559504</t>
+          <t>-1744.158464240811</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-1373.769802472432</t>
+          <t>-1357.825157987996</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>7133</v>
+        <v>5817</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-5.41</t>
+          <t>-7.21</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>20.49</t>
+          <t>21.23</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>33.15</t>
+          <t>31.27</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>2250</t>
+          <t>2331</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-9.0</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-3.41</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>12.66</t>
+          <t>-6.64</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-8.25</t>
+          <t>-11.62</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4071,52 +4071,52 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>334</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>18.52</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-3.70</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-5.02</t>
+          <t>-5.03</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>53.96</t>
+          <t>53.73999999999999</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>56.14</t>
+          <t>55.81</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>59.1</t>
+          <t>58.76</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4126,17 +4126,17 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-10.55</t>
+          <t>-13.29</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-118.12</t>
+          <t>-118.74</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>90478.66571018651</t>
+          <t>90385.65042979943</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>7209.0</t>
+          <t>7133.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>8433.0</t>
+          <t>7319.2</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>7485.2</t>
+          <t>7839.6</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>23000.42</t>
+          <t>19212.02</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>-520</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-1894.515625575336</t>
+          <t>-1814.400883559504</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-1488.484658790469</t>
+          <t>-1373.769802472432</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>7209</v>
+        <v>7133</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-5.41</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>20.49</t>
+          <t>21.23</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>33.15</t>
+          <t>31.27</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>2250</t>
+          <t>2331</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
+          <t>53.8</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
           <t>54.5</t>
         </is>
       </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>55.0</t>
-        </is>
-      </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-8.4</t>
+          <t>-5.21</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-3.41</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>12.66</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-8.75</t>
+          <t>-8.25</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4507,72 +4507,72 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>334</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>10.55</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-4.47</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-5.04</t>
+          <t>-5.02</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>53.86</t>
+          <t>53.96</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>56.38</t>
+          <t>56.14</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>59.37</t>
+          <t>59.1</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>57.36</t>
+          <t>57.38</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-19.01</t>
+          <t>-10.55</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-117.64</t>
+          <t>-118.12</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>90478.66571018651</t>
+          <t>90385.65042979943</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>4672.0</t>
+          <t>7209.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>7837.8</t>
+          <t>8433.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>8182.9</t>
+          <t>7485.2</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>23577.74</t>
+          <t>23000.42</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-345</t>
+          <t>947</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-1968.339437718039</t>
+          <t>-1894.515625575336</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-1607.345715716578</t>
+          <t>-1488.484658790469</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>4672</v>
+        <v>7209</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,12 +4705,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>20.49</t>
+          <t>21.23</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>33.15</t>
+          <t>31.27</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>2250</t>
+          <t>2331</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
+          <t>54.5</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
           <t>54.1</t>
         </is>
       </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>54.4</t>
-        </is>
-      </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>53.8</t>
-        </is>
-      </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>201.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-7.4</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-3.41</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-9.60</t>
+          <t>-8.75</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>7.24</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4943,275 +4943,275 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>334</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>10.55</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>-4.47</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
+          <t>53.86</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>56.38</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>59.37</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>57.36</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>-19.01</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>-1.53</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>-1.29</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>-117.64</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>2025/10/08</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>90385.65042979943</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>4672.0</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>7837.8</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>8182.9</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>23577.74</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>-345</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>-1968.339437718039</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>-1607.345715716578</t>
+        </is>
+      </c>
+      <c r="BD11" t="n">
+        <v>4672</v>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>55.5</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>2025/08/20</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>-2.34</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>利機</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>利機</t>
+        </is>
+      </c>
+      <c r="BK11" t="inlineStr">
+        <is>
+          <t>電子通路業</t>
+        </is>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
+          <t>2.973959600876125</t>
+        </is>
+      </c>
+      <c r="BO11" t="inlineStr">
+        <is>
+          <t>7.507647901781631</t>
+        </is>
+      </c>
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>9.97333412563415</t>
+        </is>
+      </c>
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS11" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="BT11" t="inlineStr">
+        <is>
+          <t>3.86</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
+          <t>6.82</t>
+        </is>
+      </c>
+      <c r="BV11" t="inlineStr">
+        <is>
+          <t>21.23</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
+          <t>20.15%</t>
+        </is>
+      </c>
+      <c r="BX11" t="inlineStr">
+        <is>
+          <t>3.13%</t>
+        </is>
+      </c>
+      <c r="BY11" t="inlineStr">
+        <is>
+          <t>31.27</t>
+        </is>
+      </c>
+      <c r="BZ11" t="inlineStr">
+        <is>
+          <t>2331</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
+          <t>半導體產品60.53%、光電產品37.52%、其他產品1.95% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>利機-電子通路業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC11" t="inlineStr">
+        <is>
+          <t>電子通路業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CD11" t="inlineStr">
+        <is>
+          <t>54.1</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
+          <t>54.4</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
           <t>53.8</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>56.6</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>59.52</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>57.35</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>-27.97</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>-1.57</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>-1.23</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>7.3</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>-116.80</t>
-        </is>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>2025/10/08</t>
-        </is>
-      </c>
-      <c r="AV11" t="inlineStr">
-        <is>
-          <t>90478.66571018651</t>
-        </is>
-      </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>10896.0</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>8352.6</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>8330.8</t>
-        </is>
-      </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>24471.84</t>
-        </is>
-      </c>
-      <c r="BA11" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>-2033.974659900123</t>
-        </is>
-      </c>
-      <c r="BC11" t="inlineStr">
-        <is>
-          <t>-1447.920592906852</t>
-        </is>
-      </c>
-      <c r="BD11" t="n">
-        <v>10896</v>
-      </c>
-      <c r="BE11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>55.5</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>2025/08/20</t>
-        </is>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>-3.24</t>
-        </is>
-      </c>
-      <c r="BI11" t="inlineStr">
-        <is>
-          <t>利機</t>
-        </is>
-      </c>
-      <c r="BJ11" t="inlineStr">
-        <is>
-          <t>利機</t>
-        </is>
-      </c>
-      <c r="BK11" t="inlineStr">
-        <is>
-          <t>電子通路業</t>
-        </is>
-      </c>
-      <c r="BL11" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM11" t="inlineStr">
-        <is>
-          <t>1.08</t>
-        </is>
-      </c>
-      <c r="BN11" t="inlineStr">
-        <is>
-          <t>2.973959600876125</t>
-        </is>
-      </c>
-      <c r="BO11" t="inlineStr">
-        <is>
-          <t>7.507647901781631</t>
-        </is>
-      </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>9.97333412563415</t>
-        </is>
-      </c>
-      <c r="BQ11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS11" t="inlineStr">
-        <is>
-          <t>2.32</t>
-        </is>
-      </c>
-      <c r="BT11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>6.82</t>
-        </is>
-      </c>
-      <c r="BV11" t="inlineStr">
-        <is>
-          <t>20.49</t>
-        </is>
-      </c>
-      <c r="BW11" t="inlineStr">
-        <is>
-          <t>20.15%</t>
-        </is>
-      </c>
-      <c r="BX11" t="inlineStr">
-        <is>
-          <t>3.13%</t>
-        </is>
-      </c>
-      <c r="BY11" t="inlineStr">
-        <is>
-          <t>33.15</t>
-        </is>
-      </c>
-      <c r="BZ11" t="inlineStr">
-        <is>
-          <t>2250</t>
-        </is>
-      </c>
-      <c r="CA11" t="inlineStr">
-        <is>
-          <t>半導體產品60.53%、光電產品37.52%、其他產品1.95% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB11" t="inlineStr">
-        <is>
-          <t>利機-電子通路業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC11" t="inlineStr">
-        <is>
-          <t>電子通路業右下上櫃</t>
-        </is>
-      </c>
-      <c r="CD11" t="inlineStr">
-        <is>
-          <t>53.8</t>
-        </is>
-      </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>54.9</t>
-        </is>
-      </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>53.7</t>
-        </is>
-      </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>201.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-7.6</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-3.41</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-9.43</t>
+          <t>-9.60</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>7.24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5379,72 +5379,72 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>334</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-5.37</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-4.36</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>53.96</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>57.02</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>59.63</t>
+          <t>59.52</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>57.34</t>
+          <t>57.35</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-35.26</t>
+          <t>-27.97</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-115.63</t>
+          <t>-116.80</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>90478.66571018651</t>
+          <t>90385.65042979943</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>6686.0</t>
+          <t>10896.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>8056.6</t>
+          <t>8352.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>7881.1</t>
+          <t>8330.8</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>24960.08</t>
+          <t>24471.84</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>21</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-2140.52994480799</t>
+          <t>-2033.974659900123</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-1835.31611057486</t>
+          <t>-1447.920592906852</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>6686</v>
+        <v>10896</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>20.49</t>
+          <t>21.23</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>33.15</t>
+          <t>31.27</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>2250</t>
+          <t>2331</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/印刷材料.xlsx
+++ b/Result/checksun_type/印刷材料.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>334.0</t>
+          <t>345.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>17.02</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-12.79</t>
+          <t>-10.27</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12.03</t>
+          <t>12.43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>345</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>41.94</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>15.05</t>
+          <t>48.39</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-4.80</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-6.85</t>
+          <t>-6.92</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>50.71</t>
+          <t>51.21</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>53.27</t>
+          <t>53.08</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>57.18</t>
+          <t>57.02</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>57.29</t>
+          <t>57.32</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-5.61</t>
+          <t>6.54</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,56 +1094,56 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-125.16</t>
+          <t>-124.75</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>2025/10/08</t>
+          <t>2025/11/26</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>90385.65042979943</t>
+          <t>90295.4034334764</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>17036.0</t>
+          <t>18202.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>6987.2</t>
+          <t>9349.4</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>6636.3</t>
+          <t>7989.3</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>14299.4</t>
+          <t>13460.24</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-1285.68313588008</t>
+          <t>-1010.858746339825</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-325.7147088748216</t>
+          <t>500.6753961315808</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>17036</v>
+        <v>18202</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-6.67</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,22 +1207,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>21.23</t>
+          <t>21.84</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>2331</t>
+          <t>2398</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>334.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-18.65</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-15.82</t>
+          <t>-12.79</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>12.03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>345</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>41.94</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>6.77</t>
+          <t>15.05</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-5.82</t>
+          <t>-4.80</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-6.81</t>
+          <t>-6.85</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>50.42999999999999</t>
+          <t>50.71</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>53.55</t>
+          <t>53.27</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>57.46</t>
+          <t>57.18</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>57.28</t>
+          <t>57.29</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-14.78</t>
+          <t>-5.61</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,56 +1530,56 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-124.80</t>
+          <t>-125.16</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2025/10/08</t>
+          <t>2025/11/26</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>90385.65042979943</t>
+          <t>90295.4034334764</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>2323.0</t>
+          <t>17036.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>4899.2</t>
+          <t>6987.2</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>6022.3</t>
+          <t>6636.3</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>15417.3</t>
+          <t>14299.4</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-1123</t>
+          <t>350</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-1460.222849881036</t>
+          <t>-1285.68313588008</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-1369.710762138438</t>
+          <t>-325.7147088748216</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>2323</v>
+        <v>17036</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-9.91</t>
+          <t>-6.67</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,22 +1643,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>21.23</t>
+          <t>21.84</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>2331</t>
+          <t>2398</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>49.85</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>49.85</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-13.32</t>
+          <t>-18.65</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-16.08</t>
+          <t>-15.82</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>345</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>8.94</t>
+          <t>6.77</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-5.95</t>
+          <t>-5.82</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-6.51</t>
+          <t>-6.81</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>50.73</t>
+          <t>50.42999999999999</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>53.94</t>
+          <t>53.55</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>57.69</t>
+          <t>57.46</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>57.29</t>
+          <t>57.28</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-17.10</t>
+          <t>-14.78</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,56 +1966,56 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-123.89</t>
+          <t>-124.80</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2025/10/08</t>
+          <t>2025/11/26</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>90385.65042979943</t>
+          <t>90295.4034334764</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>3535.0</t>
+          <t>2323.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>5598.0</t>
+          <t>4899.2</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>6458.6</t>
+          <t>6022.3</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>15662.04</t>
+          <t>15417.3</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-860</t>
+          <t>-1123</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-1476.679593106963</t>
+          <t>-1460.222849881036</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-1235.822596724375</t>
+          <t>-1369.710762138438</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>3535</v>
+        <v>2323</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-10.18</t>
+          <t>-9.91</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>21.23</t>
+          <t>21.84</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>2331</t>
+          <t>2398</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>49.85</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>49.85</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>111.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>49.85</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>6.47</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-14.34</t>
+          <t>-13.32</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-13.97</t>
+          <t>-16.08</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,17 +2322,17 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>345</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>17.07</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -2342,57 +2342,57 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-5.65</t>
+          <t>-5.95</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-6.17</t>
+          <t>-6.51</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>51.26000000000001</t>
+          <t>50.73</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>54.33</t>
+          <t>53.94</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>57.9</t>
+          <t>57.69</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>57.32</t>
+          <t>57.29</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-16.87</t>
+          <t>-17.10</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,56 +2402,56 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-122.87</t>
+          <t>-123.89</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2025/10/08</t>
+          <t>2025/11/26</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>90385.65042979943</t>
+          <t>90295.4034334764</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>5651.0</t>
+          <t>3535.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>6317.6</t>
+          <t>5598.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>7375.3</t>
+          <t>6458.6</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>15916.1</t>
+          <t>15662.04</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-1057</t>
+          <t>-860</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-1520.471774267434</t>
+          <t>-1476.679593106963</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-1130.274410535557</t>
+          <t>-1235.822596724375</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>5651</v>
+        <v>3535</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-7.93</t>
+          <t>-10.18</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,22 +2515,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>21.23</t>
+          <t>21.84</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2560,7 +2560,7 @@
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>2331</t>
+          <t>2398</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>49.85</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>111.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-8.35</t>
+          <t>-14.34</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-14.48</t>
+          <t>-13.97</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,77 +2758,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>345</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>17.07</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>8.94</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-5.05</t>
+          <t>-5.65</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-5.85</t>
+          <t>-6.17</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>51.94</t>
+          <t>51.26000000000001</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>54.7</t>
+          <t>54.33</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>57.9</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>57.33</t>
+          <t>57.32</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-20.92</t>
+          <t>-16.87</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,56 +2838,56 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-121.90</t>
+          <t>-122.87</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2025/10/08</t>
+          <t>2025/11/26</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>90385.65042979943</t>
+          <t>90295.4034334764</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>6391.0</t>
+          <t>5651.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>6629.2</t>
+          <t>6317.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>7233.5</t>
+          <t>7375.3</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>16143.36</t>
+          <t>15916.1</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-604</t>
+          <t>-1057</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-1591.416749491411</t>
+          <t>-1520.471774267434</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-1165.838629889547</t>
+          <t>-1130.274410535557</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>6391</v>
+        <v>5651</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-8.47</t>
+          <t>-7.93</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>21.23</t>
+          <t>21.84</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>2331</t>
+          <t>2398</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-14.12</t>
+          <t>-8.35</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-15.15</t>
+          <t>-14.48</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,77 +3194,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>345</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-5.05</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-5.46</t>
+          <t>-5.85</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>52.62</t>
+          <t>51.94</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>55.11</t>
+          <t>54.7</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>58.29</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>57.34</t>
+          <t>57.33</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-22.24</t>
+          <t>-20.92</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,56 +3274,56 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-120.76</t>
+          <t>-121.90</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2025/10/08</t>
+          <t>2025/11/26</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>90385.65042979943</t>
+          <t>90295.4034334764</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>6596.0</t>
+          <t>6391.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>6285.4</t>
+          <t>6629.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>7319.0</t>
+          <t>7233.5</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>16730.98</t>
+          <t>16143.36</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-1033</t>
+          <t>-604</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-1668.794589419023</t>
+          <t>-1591.416749491411</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-1254.293277899191</t>
+          <t>-1165.838629889547</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>6596</v>
+        <v>6391</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-9.19</t>
+          <t>-8.47</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,22 +3387,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>21.23</t>
+          <t>21.84</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>2331</t>
+          <t>2398</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-5.99</t>
+          <t>-14.12</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-13.30</t>
+          <t>-15.15</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-3.88</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,12 +3630,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>345</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3645,62 +3645,62 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-5.16</t>
+          <t>-5.46</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>53.27999999999999</t>
+          <t>52.62</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>55.51</t>
+          <t>55.11</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>58.53</t>
+          <t>58.29</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>57.37</t>
+          <t>57.34</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-17.48</t>
+          <t>-22.24</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,56 +3710,56 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-119.60</t>
+          <t>-120.76</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2025/10/08</t>
+          <t>2025/11/26</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>90385.65042979943</t>
+          <t>90295.4034334764</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>5817.0</t>
+          <t>6596.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>7145.4</t>
+          <t>6285.4</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>7601.0</t>
+          <t>7319.0</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>17385.02</t>
+          <t>16730.98</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-455</t>
+          <t>-1033</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-1744.158464240811</t>
+          <t>-1668.794589419023</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-1357.825157987996</t>
+          <t>-1254.293277899191</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>5817</v>
+        <v>6596</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-7.21</t>
+          <t>-9.19</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>21.23</t>
+          <t>21.84</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3868,7 +3868,7 @@
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>2331</t>
+          <t>2398</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-6.64</t>
+          <t>-5.99</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-11.62</t>
+          <t>-13.30</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-3.88</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,12 +4066,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>345</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4081,62 +4081,62 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>18.52</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-5.03</t>
+          <t>-5.16</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>53.73999999999999</t>
+          <t>53.27999999999999</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>55.81</t>
+          <t>55.51</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>58.76</t>
+          <t>58.53</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>57.38</t>
+          <t>57.37</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-13.29</t>
+          <t>-17.48</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,56 +4146,56 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-118.74</t>
+          <t>-119.60</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2025/10/08</t>
+          <t>2025/11/26</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>90385.65042979943</t>
+          <t>90295.4034334764</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>7133.0</t>
+          <t>5817.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>7319.2</t>
+          <t>7145.4</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>7839.6</t>
+          <t>7601.0</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>19212.02</t>
+          <t>17385.02</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-520</t>
+          <t>-455</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-1814.400883559504</t>
+          <t>-1744.158464240811</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-1373.769802472432</t>
+          <t>-1357.825157987996</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>7133</v>
+        <v>5817</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-5.41</t>
+          <t>-7.21</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>21.23</t>
+          <t>21.84</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>2331</t>
+          <t>2398</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-5.21</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>12.66</t>
+          <t>-6.64</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-8.25</t>
+          <t>-11.62</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,57 +4502,57 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>345</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>18.52</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-3.70</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-5.02</t>
+          <t>-5.03</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>53.96</t>
+          <t>53.73999999999999</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>56.14</t>
+          <t>55.81</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>59.1</t>
+          <t>58.76</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -4562,17 +4562,17 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-10.55</t>
+          <t>-13.29</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,56 +4582,56 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-118.12</t>
+          <t>-118.74</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2025/10/08</t>
+          <t>2025/11/26</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>90385.65042979943</t>
+          <t>90295.4034334764</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>7209.0</t>
+          <t>7133.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>8433.0</t>
+          <t>7319.2</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>7485.2</t>
+          <t>7839.6</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>23000.42</t>
+          <t>19212.02</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>-520</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-1894.515625575336</t>
+          <t>-1814.400883559504</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-1488.484658790469</t>
+          <t>-1373.769802472432</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>7209</v>
+        <v>7133</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-5.41</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,12 +4705,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>21.23</t>
+          <t>21.84</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>2331</t>
+          <t>2398</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
+          <t>53.8</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
           <t>54.5</t>
         </is>
       </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>55.0</t>
-        </is>
-      </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>12.66</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-8.75</t>
+          <t>-8.25</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,77 +4938,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>345</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>10.55</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-4.47</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-5.04</t>
+          <t>-5.02</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>53.86</t>
+          <t>53.96</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>56.38</t>
+          <t>56.14</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>59.37</t>
+          <t>59.1</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>57.36</t>
+          <t>57.38</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-19.01</t>
+          <t>-10.55</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,56 +5018,56 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-117.64</t>
+          <t>-118.12</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2025/10/08</t>
+          <t>2025/11/26</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>90385.65042979943</t>
+          <t>90295.4034334764</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>4672.0</t>
+          <t>7209.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>7837.8</t>
+          <t>8433.0</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>8182.9</t>
+          <t>7485.2</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>23577.74</t>
+          <t>23000.42</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-345</t>
+          <t>947</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-1968.339437718039</t>
+          <t>-1894.515625575336</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-1607.345715716578</t>
+          <t>-1488.484658790469</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>4672</v>
+        <v>7209</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>21.23</t>
+          <t>21.84</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>2331</t>
+          <t>2398</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
+          <t>54.5</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
           <t>54.1</t>
         </is>
       </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>54.4</t>
-        </is>
-      </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>53.8</t>
-        </is>
-      </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>201.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-9.60</t>
+          <t>-8.75</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>7.24</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,280 +5374,280 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>345</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>10.55</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>-4.47</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
+          <t>53.86</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>56.38</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>59.37</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>57.36</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>-19.01</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>-1.53</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>-1.29</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>-117.64</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>2025/11/26</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>90295.4034334764</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>4672.0</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>7837.8</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>8182.9</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>23577.74</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>-345</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>-1968.339437718039</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>-1607.345715716578</t>
+        </is>
+      </c>
+      <c r="BD12" t="n">
+        <v>4672</v>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>55.5</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>2025/08/20</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>-2.34</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>利機</t>
+        </is>
+      </c>
+      <c r="BJ12" t="inlineStr">
+        <is>
+          <t>利機</t>
+        </is>
+      </c>
+      <c r="BK12" t="inlineStr">
+        <is>
+          <t>電子通路業</t>
+        </is>
+      </c>
+      <c r="BL12" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM12" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
+          <t>2.973959600876125</t>
+        </is>
+      </c>
+      <c r="BO12" t="inlineStr">
+        <is>
+          <t>7.507647901781631</t>
+        </is>
+      </c>
+      <c r="BP12" t="inlineStr">
+        <is>
+          <t>9.97333412563415</t>
+        </is>
+      </c>
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS12" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="BT12" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr">
+        <is>
+          <t>6.82</t>
+        </is>
+      </c>
+      <c r="BV12" t="inlineStr">
+        <is>
+          <t>21.84</t>
+        </is>
+      </c>
+      <c r="BW12" t="inlineStr">
+        <is>
+          <t>20.15%</t>
+        </is>
+      </c>
+      <c r="BX12" t="inlineStr">
+        <is>
+          <t>3.13%</t>
+        </is>
+      </c>
+      <c r="BY12" t="inlineStr">
+        <is>
+          <t>31.27</t>
+        </is>
+      </c>
+      <c r="BZ12" t="inlineStr">
+        <is>
+          <t>2398</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
+        <is>
+          <t>半導體產品60.53%、光電產品37.52%、其他產品1.95% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>利機-電子通路業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC12" t="inlineStr">
+        <is>
+          <t>電子通路業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CD12" t="inlineStr">
+        <is>
+          <t>54.1</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
+          <t>54.4</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
           <t>53.8</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>56.6</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>59.52</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>57.35</t>
-        </is>
-      </c>
-      <c r="AP12" t="inlineStr">
-        <is>
-          <t>-27.97</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>-1.57</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>-1.23</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr">
-        <is>
-          <t>7.3</t>
-        </is>
-      </c>
-      <c r="AT12" t="inlineStr">
-        <is>
-          <t>-116.80</t>
-        </is>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>2025/10/08</t>
-        </is>
-      </c>
-      <c r="AV12" t="inlineStr">
-        <is>
-          <t>90385.65042979943</t>
-        </is>
-      </c>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>10896.0</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>8352.6</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>8330.8</t>
-        </is>
-      </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>24471.84</t>
-        </is>
-      </c>
-      <c r="BA12" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="BB12" t="inlineStr">
-        <is>
-          <t>-2033.974659900123</t>
-        </is>
-      </c>
-      <c r="BC12" t="inlineStr">
-        <is>
-          <t>-1447.920592906852</t>
-        </is>
-      </c>
-      <c r="BD12" t="n">
-        <v>10896</v>
-      </c>
-      <c r="BE12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF12" t="inlineStr">
-        <is>
-          <t>55.5</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>2025/08/20</t>
-        </is>
-      </c>
-      <c r="BH12" t="inlineStr">
-        <is>
-          <t>-3.24</t>
-        </is>
-      </c>
-      <c r="BI12" t="inlineStr">
-        <is>
-          <t>利機</t>
-        </is>
-      </c>
-      <c r="BJ12" t="inlineStr">
-        <is>
-          <t>利機</t>
-        </is>
-      </c>
-      <c r="BK12" t="inlineStr">
-        <is>
-          <t>電子通路業</t>
-        </is>
-      </c>
-      <c r="BL12" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM12" t="inlineStr">
-        <is>
-          <t>1.09</t>
-        </is>
-      </c>
-      <c r="BN12" t="inlineStr">
-        <is>
-          <t>2.973959600876125</t>
-        </is>
-      </c>
-      <c r="BO12" t="inlineStr">
-        <is>
-          <t>7.507647901781631</t>
-        </is>
-      </c>
-      <c r="BP12" t="inlineStr">
-        <is>
-          <t>9.97333412563415</t>
-        </is>
-      </c>
-      <c r="BQ12" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR12" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS12" t="inlineStr">
-        <is>
-          <t>2.32</t>
-        </is>
-      </c>
-      <c r="BT12" t="inlineStr">
-        <is>
-          <t>3.86</t>
-        </is>
-      </c>
-      <c r="BU12" t="inlineStr">
-        <is>
-          <t>6.82</t>
-        </is>
-      </c>
-      <c r="BV12" t="inlineStr">
-        <is>
-          <t>21.23</t>
-        </is>
-      </c>
-      <c r="BW12" t="inlineStr">
-        <is>
-          <t>20.15%</t>
-        </is>
-      </c>
-      <c r="BX12" t="inlineStr">
-        <is>
-          <t>3.13%</t>
-        </is>
-      </c>
-      <c r="BY12" t="inlineStr">
-        <is>
-          <t>31.27</t>
-        </is>
-      </c>
-      <c r="BZ12" t="inlineStr">
-        <is>
-          <t>2331</t>
-        </is>
-      </c>
-      <c r="CA12" t="inlineStr">
-        <is>
-          <t>半導體產品60.53%、光電產品37.52%、其他產品1.95% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB12" t="inlineStr">
-        <is>
-          <t>利機-電子通路業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC12" t="inlineStr">
-        <is>
-          <t>電子通路業右下上櫃</t>
-        </is>
-      </c>
-      <c r="CD12" t="inlineStr">
-        <is>
-          <t>53.8</t>
-        </is>
-      </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>54.9</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>53.7</t>
-        </is>
-      </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/印刷材料.xlsx
+++ b/Result/checksun_type/印刷材料.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>51.21</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>53.08</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>57.02</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>53.08</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>57.02</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>18202.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>9349.4</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>9349.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>7989.3</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>13460.24</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>13460.24</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>500.6753961315808</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>18202</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>18202.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>50.71</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>53.27</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>57.18</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>53.27</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>57.18</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>17036.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>6987.2</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>6987.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>6636.3</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>14299.4</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>14299.4</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-325.7147088748216</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>17036</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>17036.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>50.42999999999999</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>53.55</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>57.46</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>53.55</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>57.46</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>2323.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>4899.2</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>4899.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>6022.3</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>15417.3</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>15417.3</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-1369.710762138438</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>2323</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>2323.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>50.73</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>53.94</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>57.69</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>53.94</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>57.69</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>3535.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>5598.0</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>5598</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>6458.6</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>15662.04</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>15662.04</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-1235.822596724375</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>3535</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>3535.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>51.26000000000001</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>54.33</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>57.9</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>54.33</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>57.9</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>5651.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>6317.6</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>6317.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>7375.3</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>15916.1</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>15916.1</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-1130.274410535557</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>5651</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>5651.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>51.94</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>54.7</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>58.1</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>58.1</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>6391.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>6629.2</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>6629.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>7233.5</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>16143.36</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>16143.36</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-1165.838629889547</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>6391</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>6391.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>52.62</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>55.11</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>58.29</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>55.11</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>58.29</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>6596.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>6285.4</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>6285.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>7319.0</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>16730.98</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>16730.98</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-1254.293277899191</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>6596</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>6596.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>53.27999999999999</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>55.51</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>58.53</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>55.51</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>58.53</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>5817.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>7145.4</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>7145.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>7601.0</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>17385.02</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>17385.02</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-1357.825157987996</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>5817</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>5817.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>53.73999999999999</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>55.81</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>58.76</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>55.81</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>58.76</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>7133.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>7319.2</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>7319.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>7839.6</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>19212.02</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>19212.02</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-1373.769802472432</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>7133</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>7133.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>53.96</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>56.14</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>59.1</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>56.14</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>59.1</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>7209.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>8433.0</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>8433</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>7485.2</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>23000.42</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>23000.42</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-1488.484658790469</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>7209</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>7209.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>53.86</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>56.38</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>59.37</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>56.38</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>59.37</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>4672.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>7837.8</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>7837.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>8182.9</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>23577.74</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>23577.74</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-1607.345715716578</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>4672</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>4672.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>

--- a/Result/checksun_type/印刷材料.xlsx
+++ b/Result/checksun_type/印刷材料.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>345.0</t>
+          <t>255.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>26.75</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-10.27</t>
+          <t>-11.45</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12.43</t>
+          <t>9.19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,32 +1014,32 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>255</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>79.71</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>48.39</t>
+          <t>73.88</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -1049,19 +1049,19 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>51.21</t>
+          <t>51.51000000000001</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>53.08</v>
+        <v>52.9</v>
       </c>
       <c r="AN2" t="n">
-        <v>57.02</v>
+        <v>56.83</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>6.54</t>
+          <t>12.69</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-124.75</t>
+          <t>-123.99</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>90295.4034334764</t>
+          <t>90195.47571428571</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>18202.0</t>
+          <t>13564.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>9349.4</v>
+        <v>10932</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>7989.3</t>
+          <t>8624.8</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>13460.24</v>
+        <v>13461.08</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>2307</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-1010.858746339825</t>
+          <t>-744.7602338671172</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>500.6753961315808</t>
+          <t>718.7815847327729</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>18202.0</t>
+          <t>13564.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-5.23</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>21.84</t>
+          <t>21.56</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>31.27</t>
+          <t>31.32</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>2398</t>
+          <t>2367</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
+          <t>53.6</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>54.1</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
           <t>52.6</t>
         </is>
       </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>53.5</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>52.0</t>
-        </is>
-      </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1303,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>334.0</t>
+          <t>345.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>17.02</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-12.79</t>
+          <t>-10.27</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12.03</t>
+          <t>12.43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>255</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>41.94</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>15.05</t>
+          <t>48.39</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-4.80</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-6.85</t>
+          <t>-6.92</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>50.71</t>
+          <t>51.21</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>53.27</v>
+        <v>53.08</v>
       </c>
       <c r="AN3" t="n">
-        <v>57.18</v>
+        <v>57.02</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>57.29</t>
+          <t>57.32</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-5.61</t>
+          <t>6.54</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-125.16</t>
+          <t>-124.75</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>90295.4034334764</t>
+          <t>90195.47571428571</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>17036.0</t>
+          <t>18202.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>6987.2</v>
+        <v>9349.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>6636.3</t>
+          <t>7989.3</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>14299.4</v>
+        <v>13460.24</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-1285.68313588008</t>
+          <t>-1010.858746339825</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-325.7147088748216</t>
+          <t>500.6753961315808</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>17036.0</t>
+          <t>18202.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-6.67</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>21.84</t>
+          <t>21.56</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>31.27</t>
+          <t>31.32</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>2398</t>
+          <t>2367</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>334.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6.19</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-18.65</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-15.82</t>
+          <t>-12.79</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>12.03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>255</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>41.94</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>6.77</t>
+          <t>15.05</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-5.82</t>
+          <t>-4.80</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-6.81</t>
+          <t>-6.85</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>50.42999999999999</t>
+          <t>50.71</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>53.55</v>
+        <v>53.27</v>
       </c>
       <c r="AN4" t="n">
-        <v>57.46</v>
+        <v>57.18</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>57.28</t>
+          <t>57.29</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-14.78</t>
+          <t>-5.61</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-124.80</t>
+          <t>-125.16</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>90295.4034334764</t>
+          <t>90195.47571428571</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>2323.0</t>
+          <t>17036.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>4899.2</v>
+        <v>6987.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>6022.3</t>
+          <t>6636.3</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>15417.3</v>
+        <v>14299.4</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-1123</t>
+          <t>350</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-1460.222849881036</t>
+          <t>-1285.68313588008</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-1369.710762138438</t>
+          <t>-325.7147088748216</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>2323.0</t>
+          <t>17036.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-9.91</t>
+          <t>-6.67</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>21.84</t>
+          <t>21.56</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>31.27</t>
+          <t>31.32</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>2398</t>
+          <t>2367</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>49.85</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>49.85</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6.47</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-13.32</t>
+          <t>-18.65</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-16.08</t>
+          <t>-15.82</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>255</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>8.94</t>
+          <t>6.77</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-5.95</t>
+          <t>-5.82</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-6.51</t>
+          <t>-6.81</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>50.73</t>
+          <t>50.42999999999999</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>53.94</v>
+        <v>53.55</v>
       </c>
       <c r="AN5" t="n">
-        <v>57.69</v>
+        <v>57.46</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>57.29</t>
+          <t>57.28</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-17.10</t>
+          <t>-14.78</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-123.89</t>
+          <t>-124.80</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>90295.4034334764</t>
+          <t>90195.47571428571</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>3535.0</t>
+          <t>2323.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>5598</v>
+        <v>4899.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>6458.6</t>
+          <t>6022.3</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>15662.04</v>
+        <v>15417.3</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-860</t>
+          <t>-1123</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-1476.679593106963</t>
+          <t>-1460.222849881036</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-1235.822596724375</t>
+          <t>-1369.710762138438</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>3535.0</t>
+          <t>2323.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-10.18</t>
+          <t>-9.91</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>21.84</t>
+          <t>21.56</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>31.27</t>
+          <t>31.32</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>2398</t>
+          <t>2367</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>49.85</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>49.85</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>111.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>49.85</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>5.23</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-14.34</t>
+          <t>-13.32</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-13.97</t>
+          <t>-16.08</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,17 +2734,17 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>255</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>17.07</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -2754,53 +2754,53 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-5.65</t>
+          <t>-5.95</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-6.17</t>
+          <t>-6.51</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>51.26000000000001</t>
+          <t>50.73</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>54.33</v>
+        <v>53.94</v>
       </c>
       <c r="AN6" t="n">
-        <v>57.9</v>
+        <v>57.69</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>57.32</t>
+          <t>57.29</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-16.87</t>
+          <t>-17.10</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-122.87</t>
+          <t>-123.89</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>90295.4034334764</t>
+          <t>90195.47571428571</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>5651.0</t>
+          <t>3535.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>6317.6</v>
+        <v>5598</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>7375.3</t>
+          <t>6458.6</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>15916.1</v>
+        <v>15662.04</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-1057</t>
+          <t>-860</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-1520.471774267434</t>
+          <t>-1476.679593106963</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-1130.274410535557</t>
+          <t>-1235.822596724375</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>5651.0</t>
+          <t>3535.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-7.93</t>
+          <t>-10.18</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>21.84</t>
+          <t>21.56</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>31.27</t>
+          <t>31.32</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>2398</t>
+          <t>2367</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>49.85</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>111.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-8.35</t>
+          <t>-14.34</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-14.48</t>
+          <t>-13.97</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>255</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>17.07</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>8.94</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-5.05</t>
+          <t>-5.65</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-5.85</t>
+          <t>-6.17</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>51.94</t>
+          <t>51.26000000000001</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>54.7</v>
+        <v>54.33</v>
       </c>
       <c r="AN7" t="n">
-        <v>58.1</v>
+        <v>57.9</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>57.33</t>
+          <t>57.32</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-20.92</t>
+          <t>-16.87</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-121.90</t>
+          <t>-122.87</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>90295.4034334764</t>
+          <t>90195.47571428571</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>6391.0</t>
+          <t>5651.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>6629.2</v>
+        <v>6317.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>7233.5</t>
+          <t>7375.3</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>16143.36</v>
+        <v>15916.1</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-604</t>
+          <t>-1057</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-1591.416749491411</t>
+          <t>-1520.471774267434</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-1165.838629889547</t>
+          <t>-1130.274410535557</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>6391.0</t>
+          <t>5651.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-8.47</t>
+          <t>-7.93</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>21.84</t>
+          <t>21.56</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>31.27</t>
+          <t>31.32</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>2398</t>
+          <t>2367</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-14.12</t>
+          <t>-8.35</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-15.15</t>
+          <t>-14.48</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>255</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-5.05</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-5.46</t>
+          <t>-5.85</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>52.62</t>
+          <t>51.94</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>55.11</v>
+        <v>54.7</v>
       </c>
       <c r="AN8" t="n">
-        <v>58.29</v>
+        <v>58.1</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>57.34</t>
+          <t>57.33</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-22.24</t>
+          <t>-20.92</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-120.76</t>
+          <t>-121.90</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>90295.4034334764</t>
+          <t>90195.47571428571</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>6596.0</t>
+          <t>6391.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>6285.4</v>
+        <v>6629.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>7319.0</t>
+          <t>7233.5</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>16730.98</v>
+        <v>16143.36</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-1033</t>
+          <t>-604</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-1668.794589419023</t>
+          <t>-1591.416749491411</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-1254.293277899191</t>
+          <t>-1165.838629889547</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>6596.0</t>
+          <t>6391.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-9.19</t>
+          <t>-8.47</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>21.84</t>
+          <t>21.56</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>31.27</t>
+          <t>31.32</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>2398</t>
+          <t>2367</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-5.99</t>
+          <t>-14.12</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-13.30</t>
+          <t>-15.15</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-3.88</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,12 +4024,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>255</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4039,58 +4039,58 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-5.16</t>
+          <t>-5.46</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>53.27999999999999</t>
+          <t>52.62</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>55.51</v>
+        <v>55.11</v>
       </c>
       <c r="AN9" t="n">
-        <v>58.53</v>
+        <v>58.29</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>57.37</t>
+          <t>57.34</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-17.48</t>
+          <t>-22.24</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-119.60</t>
+          <t>-120.76</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>90295.4034334764</t>
+          <t>90195.47571428571</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>5817.0</t>
+          <t>6596.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>7145.4</v>
+        <v>6285.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>7601.0</t>
+          <t>7319.0</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>17385.02</v>
+        <v>16730.98</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-455</t>
+          <t>-1033</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-1744.158464240811</t>
+          <t>-1668.794589419023</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-1357.825157987996</t>
+          <t>-1254.293277899191</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>5817.0</t>
+          <t>6596.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-7.21</t>
+          <t>-9.19</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>21.84</t>
+          <t>21.56</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>31.27</t>
+          <t>31.32</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>2398</t>
+          <t>2367</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-6.64</t>
+          <t>-5.99</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-11.62</t>
+          <t>-13.30</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-3.88</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,12 +4454,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>255</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4469,58 +4469,58 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>18.52</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-5.03</t>
+          <t>-5.16</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>53.73999999999999</t>
+          <t>53.27999999999999</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>55.81</v>
+        <v>55.51</v>
       </c>
       <c r="AN10" t="n">
-        <v>58.76</v>
+        <v>58.53</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>57.38</t>
+          <t>57.37</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-13.29</t>
+          <t>-17.48</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-118.74</t>
+          <t>-119.60</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>90295.4034334764</t>
+          <t>90195.47571428571</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>7133.0</t>
+          <t>5817.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>7319.2</v>
+        <v>7145.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>7839.6</t>
+          <t>7601.0</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>19212.02</v>
+        <v>17385.02</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-520</t>
+          <t>-455</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-1814.400883559504</t>
+          <t>-1744.158464240811</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-1373.769802472432</t>
+          <t>-1357.825157987996</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>7133.0</t>
+          <t>5817.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-5.41</t>
+          <t>-7.21</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,22 +4641,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>21.84</t>
+          <t>21.56</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>31.27</t>
+          <t>31.32</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>2398</t>
+          <t>2367</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>12.66</t>
+          <t>-6.64</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-8.25</t>
+          <t>-11.62</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,54 +4884,54 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>255</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>18.52</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-3.70</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-5.02</t>
+          <t>-5.03</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>53.96</t>
+          <t>53.73999999999999</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>56.14</v>
+        <v>55.81</v>
       </c>
       <c r="AN11" t="n">
-        <v>59.1</v>
+        <v>58.76</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -4940,17 +4940,17 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-10.55</t>
+          <t>-13.29</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-118.12</t>
+          <t>-118.74</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>90295.4034334764</t>
+          <t>90195.47571428571</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>7209.0</t>
+          <t>7133.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>8433</v>
+        <v>7319.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>7485.2</t>
+          <t>7839.6</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>23000.42</v>
+        <v>19212.02</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>-520</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-1894.515625575336</t>
+          <t>-1814.400883559504</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-1488.484658790469</t>
+          <t>-1373.769802472432</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>7209.0</t>
+          <t>7133.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-5.41</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>21.84</t>
+          <t>21.56</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>31.27</t>
+          <t>31.32</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>2398</t>
+          <t>2367</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
+          <t>53.8</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
           <t>54.5</t>
         </is>
       </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>55.0</t>
-        </is>
-      </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>12.66</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-8.75</t>
+          <t>-8.25</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>255</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>10.55</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-4.47</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-5.04</t>
+          <t>-5.02</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>53.86</t>
+          <t>53.96</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>56.38</v>
+        <v>56.14</v>
       </c>
       <c r="AN12" t="n">
-        <v>59.37</v>
+        <v>59.1</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>57.36</t>
+          <t>57.38</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-19.01</t>
+          <t>-10.55</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-117.64</t>
+          <t>-118.12</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>90295.4034334764</t>
+          <t>90195.47571428571</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>4672.0</t>
+          <t>7209.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>7837.8</v>
+        <v>8433</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>8182.9</t>
+          <t>7485.2</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>23577.74</v>
+        <v>23000.42</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-345</t>
+          <t>947</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-1968.339437718039</t>
+          <t>-1894.515625575336</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-1607.345715716578</t>
+          <t>-1488.484658790469</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>4672.0</t>
+          <t>7209.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>21.84</t>
+          <t>21.56</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>31.27</t>
+          <t>31.32</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>2398</t>
+          <t>2367</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
+          <t>54.5</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
           <t>54.1</t>
         </is>
       </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>54.4</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>53.8</t>
-        </is>
-      </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/印刷材料.xlsx
+++ b/Result/checksun_type/印刷材料.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>255.0</t>
+          <t>167.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>26.75</t>
+          <t>36.29</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-11.45</t>
+          <t>-10.61</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>9.19</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,68 +1019,68 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>167</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>79.71</t>
+          <t>94.2</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>73.88</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-6.92</t>
+          <t>-6.89</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>51.51000000000001</t>
+          <t>52.16</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>52.9</v>
+        <v>52.77</v>
       </c>
       <c r="AN2" t="n">
-        <v>56.83</v>
+        <v>56.68</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>57.32</t>
+          <t>57.34</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>19.38</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-123.99</t>
+          <t>-122.88</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>90195.47571428571</t>
+          <t>90085.5427960057</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>13564.0</t>
+          <t>8755.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>10932</v>
+        <v>11976</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>8624.8</t>
+          <t>8787.0</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>13461.08</v>
+        <v>13401.56</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>2307</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-744.7602338671172</t>
+          <t>-554.3646014052089</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>718.7815847327729</t>
+          <t>492.8113771352873</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>13564.0</t>
+          <t>8755.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-5.23</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>21.56</t>
+          <t>21.76</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>31.32</t>
+          <t>31.49</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>2367</t>
+          <t>2389</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>345.0</t>
+          <t>255.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>26.75</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-10.27</t>
+          <t>-11.45</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12.43</t>
+          <t>9.19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1449,27 +1449,27 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>167</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>79.71</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>48.39</t>
+          <t>73.88</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -1479,19 +1479,19 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>51.21</t>
+          <t>51.51000000000001</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>53.08</v>
+        <v>52.9</v>
       </c>
       <c r="AN3" t="n">
-        <v>57.02</v>
+        <v>56.83</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1500,17 +1500,17 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>6.54</t>
+          <t>12.69</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-124.75</t>
+          <t>-123.99</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>90195.47571428571</t>
+          <t>90085.5427960057</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>18202.0</t>
+          <t>13564.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>9349.4</v>
+        <v>10932</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>7989.3</t>
+          <t>8624.8</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>13460.24</v>
+        <v>13461.08</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>2307</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-1010.858746339825</t>
+          <t>-744.7602338671172</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>500.6753961315808</t>
+          <t>718.7815847327729</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>18202.0</t>
+          <t>13564.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-5.23</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>21.56</t>
+          <t>21.76</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>31.32</t>
+          <t>31.49</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>2367</t>
+          <t>2389</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
+          <t>53.6</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>54.1</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
           <t>52.6</t>
         </is>
       </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>53.5</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>52.0</t>
-        </is>
-      </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>334.0</t>
+          <t>345.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>17.02</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-12.79</t>
+          <t>-10.27</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12.03</t>
+          <t>12.43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1879,68 +1879,68 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>167</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>41.94</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>15.05</t>
+          <t>48.39</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.80</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-6.85</t>
+          <t>-6.92</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>50.71</t>
+          <t>51.21</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>53.27</v>
+        <v>53.08</v>
       </c>
       <c r="AN4" t="n">
-        <v>57.18</v>
+        <v>57.02</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>57.29</t>
+          <t>57.32</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-5.61</t>
+          <t>6.54</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-125.16</t>
+          <t>-124.75</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>90195.47571428571</t>
+          <t>90085.5427960057</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>17036.0</t>
+          <t>18202.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>6987.2</v>
+        <v>9349.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>6636.3</t>
+          <t>7989.3</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>14299.4</v>
+        <v>13460.24</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-1285.68313588008</t>
+          <t>-1010.858746339825</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-325.7147088748216</t>
+          <t>500.6753961315808</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>17036.0</t>
+          <t>18202.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-6.67</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>21.56</t>
+          <t>21.76</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>31.32</t>
+          <t>31.49</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>2367</t>
+          <t>2389</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>334.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-18.65</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-15.82</t>
+          <t>-12.79</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>12.03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2309,68 +2309,68 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>167</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>41.94</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>6.77</t>
+          <t>15.05</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-5.82</t>
+          <t>-4.80</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-6.81</t>
+          <t>-6.85</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>50.42999999999999</t>
+          <t>50.71</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>53.55</v>
+        <v>53.27</v>
       </c>
       <c r="AN5" t="n">
-        <v>57.46</v>
+        <v>57.18</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>57.28</t>
+          <t>57.29</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-14.78</t>
+          <t>-5.61</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-124.80</t>
+          <t>-125.16</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>90195.47571428571</t>
+          <t>90085.5427960057</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>2323.0</t>
+          <t>17036.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>4899.2</v>
+        <v>6987.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>6022.3</t>
+          <t>6636.3</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>15417.3</v>
+        <v>14299.4</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-1123</t>
+          <t>350</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-1460.222849881036</t>
+          <t>-1285.68313588008</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-1369.710762138438</t>
+          <t>-325.7147088748216</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>2323.0</t>
+          <t>17036.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-9.91</t>
+          <t>-6.67</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>21.56</t>
+          <t>21.76</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>31.32</t>
+          <t>31.49</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>2367</t>
+          <t>2389</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>49.85</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>49.85</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5.23</t>
+          <t>5.84</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-13.32</t>
+          <t>-18.65</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-16.08</t>
+          <t>-15.82</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2739,68 +2739,68 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>167</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>8.94</t>
+          <t>6.77</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-5.95</t>
+          <t>-5.82</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-6.51</t>
+          <t>-6.81</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>50.73</t>
+          <t>50.42999999999999</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>53.94</v>
+        <v>53.55</v>
       </c>
       <c r="AN6" t="n">
-        <v>57.69</v>
+        <v>57.46</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>57.29</t>
+          <t>57.28</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-17.10</t>
+          <t>-14.78</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-123.89</t>
+          <t>-124.80</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>90195.47571428571</t>
+          <t>90085.5427960057</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>3535.0</t>
+          <t>2323.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>5598</v>
+        <v>4899.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>6458.6</t>
+          <t>6022.3</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>15662.04</v>
+        <v>15417.3</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-860</t>
+          <t>-1123</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-1476.679593106963</t>
+          <t>-1460.222849881036</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-1235.822596724375</t>
+          <t>-1369.710762138438</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>3535.0</t>
+          <t>2323.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-10.18</t>
+          <t>-9.91</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>21.56</t>
+          <t>21.76</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>31.32</t>
+          <t>31.49</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>2367</t>
+          <t>2389</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>49.85</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>49.85</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>111.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>49.85</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-14.34</t>
+          <t>-13.32</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-13.97</t>
+          <t>-16.08</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>167</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>17.07</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -3184,53 +3184,53 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-5.65</t>
+          <t>-5.95</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-6.17</t>
+          <t>-6.51</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>51.26000000000001</t>
+          <t>50.73</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>54.33</v>
+        <v>53.94</v>
       </c>
       <c r="AN7" t="n">
-        <v>57.9</v>
+        <v>57.69</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>57.32</t>
+          <t>57.29</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-16.87</t>
+          <t>-17.10</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-122.87</t>
+          <t>-123.89</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>90195.47571428571</t>
+          <t>90085.5427960057</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>5651.0</t>
+          <t>3535.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>6317.6</v>
+        <v>5598</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>7375.3</t>
+          <t>6458.6</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>15916.1</v>
+        <v>15662.04</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-1057</t>
+          <t>-860</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-1520.471774267434</t>
+          <t>-1476.679593106963</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-1130.274410535557</t>
+          <t>-1235.822596724375</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>5651.0</t>
+          <t>3535.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-7.93</t>
+          <t>-10.18</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>21.56</t>
+          <t>21.76</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>31.32</t>
+          <t>31.49</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>2367</t>
+          <t>2389</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>49.85</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>111.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-8.35</t>
+          <t>-14.34</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-14.48</t>
+          <t>-13.97</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3599,68 +3599,68 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>167</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>17.07</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>8.94</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-5.05</t>
+          <t>-5.65</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-5.85</t>
+          <t>-6.17</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>51.94</t>
+          <t>51.26000000000001</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>54.7</v>
+        <v>54.33</v>
       </c>
       <c r="AN8" t="n">
-        <v>58.1</v>
+        <v>57.9</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>57.33</t>
+          <t>57.32</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-20.92</t>
+          <t>-16.87</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-121.90</t>
+          <t>-122.87</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>90195.47571428571</t>
+          <t>90085.5427960057</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>6391.0</t>
+          <t>5651.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>6629.2</v>
+        <v>6317.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>7233.5</t>
+          <t>7375.3</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>16143.36</v>
+        <v>15916.1</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-604</t>
+          <t>-1057</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-1591.416749491411</t>
+          <t>-1520.471774267434</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-1165.838629889547</t>
+          <t>-1130.274410535557</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>6391.0</t>
+          <t>5651.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-8.47</t>
+          <t>-7.93</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>21.56</t>
+          <t>21.76</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>31.32</t>
+          <t>31.49</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>2367</t>
+          <t>2389</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-14.12</t>
+          <t>-8.35</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-15.15</t>
+          <t>-14.48</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4029,68 +4029,68 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>167</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-5.05</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-5.46</t>
+          <t>-5.85</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>52.62</t>
+          <t>51.94</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>55.11</v>
+        <v>54.7</v>
       </c>
       <c r="AN9" t="n">
-        <v>58.29</v>
+        <v>58.1</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>57.34</t>
+          <t>57.33</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-22.24</t>
+          <t>-20.92</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-120.76</t>
+          <t>-121.90</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>90195.47571428571</t>
+          <t>90085.5427960057</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>6596.0</t>
+          <t>6391.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>6285.4</v>
+        <v>6629.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>7319.0</t>
+          <t>7233.5</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>16730.98</v>
+        <v>16143.36</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-1033</t>
+          <t>-604</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-1668.794589419023</t>
+          <t>-1591.416749491411</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-1254.293277899191</t>
+          <t>-1165.838629889547</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>6596.0</t>
+          <t>6391.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-9.19</t>
+          <t>-8.47</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>21.56</t>
+          <t>21.76</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>31.32</t>
+          <t>31.49</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>2367</t>
+          <t>2389</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-5.99</t>
+          <t>-14.12</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-13.30</t>
+          <t>-15.15</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-3.88</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4459,7 +4459,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>167</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4469,58 +4469,58 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-5.16</t>
+          <t>-5.46</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>53.27999999999999</t>
+          <t>52.62</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>55.51</v>
+        <v>55.11</v>
       </c>
       <c r="AN10" t="n">
-        <v>58.53</v>
+        <v>58.29</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>57.37</t>
+          <t>57.34</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-17.48</t>
+          <t>-22.24</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-119.60</t>
+          <t>-120.76</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>90195.47571428571</t>
+          <t>90085.5427960057</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>5817.0</t>
+          <t>6596.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>7145.4</v>
+        <v>6285.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>7601.0</t>
+          <t>7319.0</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>17385.02</v>
+        <v>16730.98</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-455</t>
+          <t>-1033</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-1744.158464240811</t>
+          <t>-1668.794589419023</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-1357.825157987996</t>
+          <t>-1254.293277899191</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>5817.0</t>
+          <t>6596.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-7.21</t>
+          <t>-9.19</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>21.56</t>
+          <t>21.76</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>31.32</t>
+          <t>31.49</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>2367</t>
+          <t>2389</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-6.64</t>
+          <t>-5.99</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-11.62</t>
+          <t>-13.30</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-3.88</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>167</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4899,58 +4899,58 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>18.52</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-5.03</t>
+          <t>-5.16</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>53.73999999999999</t>
+          <t>53.27999999999999</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>55.81</v>
+        <v>55.51</v>
       </c>
       <c r="AN11" t="n">
-        <v>58.76</v>
+        <v>58.53</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>57.38</t>
+          <t>57.37</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-13.29</t>
+          <t>-17.48</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-118.74</t>
+          <t>-119.60</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>90195.47571428571</t>
+          <t>90085.5427960057</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>7133.0</t>
+          <t>5817.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>7319.2</v>
+        <v>7145.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>7839.6</t>
+          <t>7601.0</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>19212.02</v>
+        <v>17385.02</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-520</t>
+          <t>-455</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-1814.400883559504</t>
+          <t>-1744.158464240811</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-1373.769802472432</t>
+          <t>-1357.825157987996</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>7133.0</t>
+          <t>5817.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-5.41</t>
+          <t>-7.21</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>21.56</t>
+          <t>21.76</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>31.32</t>
+          <t>31.49</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>2367</t>
+          <t>2389</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>12.66</t>
+          <t>-6.64</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-8.25</t>
+          <t>-11.62</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,49 +5319,49 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>167</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>18.52</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-3.70</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-5.02</t>
+          <t>-5.03</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>53.96</t>
+          <t>53.73999999999999</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>56.14</v>
+        <v>55.81</v>
       </c>
       <c r="AN12" t="n">
-        <v>59.1</v>
+        <v>58.76</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5370,17 +5370,17 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-10.55</t>
+          <t>-13.29</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-118.12</t>
+          <t>-118.74</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>90195.47571428571</t>
+          <t>90085.5427960057</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>7209.0</t>
+          <t>7133.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>8433</v>
+        <v>7319.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>7485.2</t>
+          <t>7839.6</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>23000.42</v>
+        <v>19212.02</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>-520</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-1894.515625575336</t>
+          <t>-1814.400883559504</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-1488.484658790469</t>
+          <t>-1373.769802472432</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>7209.0</t>
+          <t>7133.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-5.41</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>21.56</t>
+          <t>21.76</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>31.32</t>
+          <t>31.49</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>2367</t>
+          <t>2389</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
+          <t>53.8</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
           <t>54.5</t>
         </is>
       </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>55.0</t>
-        </is>
-      </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/印刷材料.xlsx
+++ b/Result/checksun_type/印刷材料.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>167.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>36.29</t>
+          <t>43.16</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-10.61</t>
+          <t>-12.46</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,68 +1019,68 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>94.2</t>
+          <t>62.32</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>78.74</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-6.89</t>
+          <t>-6.98</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>52.16</t>
+          <t>52.56</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>52.77</v>
+        <v>52.56</v>
       </c>
       <c r="AN2" t="n">
-        <v>56.68</v>
+        <v>56.5</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>57.34</t>
+          <t>57.33</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>19.38</t>
+          <t>19.82</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-122.88</t>
+          <t>-121.80</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>90085.5427960057</t>
+          <t>89966.04700854702</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>8755.0</t>
+          <t>4133.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>11976</v>
+        <v>12338</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>8787.0</t>
+          <t>8618.6</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>13401.56</v>
+        <v>13299.38</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>3719</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-554.3646014052089</t>
+          <t>-472.8220554369204</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>492.8113771352873</t>
+          <t>-24.33805261133421</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>8755.0</t>
+          <t>4133.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-6.31</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>21.76</t>
+          <t>21.31</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>31.49</t>
+          <t>31.17</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>2389</t>
+          <t>2340</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>255.0</t>
+          <t>167.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>26.75</t>
+          <t>36.29</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-11.45</t>
+          <t>-10.61</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>9.19</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1449,68 +1449,68 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>79.71</t>
+          <t>94.2</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>73.88</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-6.92</t>
+          <t>-6.89</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>51.51000000000001</t>
+          <t>52.16</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>52.9</v>
+        <v>52.77</v>
       </c>
       <c r="AN3" t="n">
-        <v>56.83</v>
+        <v>56.68</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>57.32</t>
+          <t>57.34</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>19.38</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-123.99</t>
+          <t>-122.88</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>90085.5427960057</t>
+          <t>89966.04700854702</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>13564.0</t>
+          <t>8755.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>10932</v>
+        <v>11976</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>8624.8</t>
+          <t>8787.0</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>13461.08</v>
+        <v>13401.56</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>2307</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-744.7602338671172</t>
+          <t>-554.3646014052089</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>718.7815847327729</t>
+          <t>492.8113771352873</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>13564.0</t>
+          <t>8755.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-5.23</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>21.76</t>
+          <t>21.31</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>31.49</t>
+          <t>31.17</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>2389</t>
+          <t>2340</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>345.0</t>
+          <t>255.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>26.75</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-10.27</t>
+          <t>-11.45</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12.43</t>
+          <t>9.19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1879,27 +1879,27 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>79.71</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>48.39</t>
+          <t>73.88</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1909,19 +1909,19 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>51.21</t>
+          <t>51.51000000000001</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>53.08</v>
+        <v>52.9</v>
       </c>
       <c r="AN4" t="n">
-        <v>57.02</v>
+        <v>56.83</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1930,17 +1930,17 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>6.54</t>
+          <t>12.69</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-124.75</t>
+          <t>-123.99</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>90085.5427960057</t>
+          <t>89966.04700854702</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>18202.0</t>
+          <t>13564.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>9349.4</v>
+        <v>10932</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>7989.3</t>
+          <t>8624.8</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>13460.24</v>
+        <v>13461.08</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>2307</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-1010.858746339825</t>
+          <t>-744.7602338671172</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>500.6753961315808</t>
+          <t>718.7815847327729</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>18202.0</t>
+          <t>13564.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-5.23</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>21.76</t>
+          <t>21.31</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>31.49</t>
+          <t>31.17</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>2389</t>
+          <t>2340</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
+          <t>53.6</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>54.1</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
           <t>52.6</t>
         </is>
       </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>53.5</t>
-        </is>
-      </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>52.0</t>
-        </is>
-      </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2163,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>334.0</t>
+          <t>345.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>-2.5</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>17.02</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-12.79</t>
+          <t>-10.27</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12.03</t>
+          <t>12.43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2309,68 +2309,68 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>41.94</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>15.05</t>
+          <t>48.39</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.80</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-6.85</t>
+          <t>-6.92</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>50.71</t>
+          <t>51.21</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>53.27</v>
+        <v>53.08</v>
       </c>
       <c r="AN5" t="n">
-        <v>57.18</v>
+        <v>57.02</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>57.29</t>
+          <t>57.32</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-5.61</t>
+          <t>6.54</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-125.16</t>
+          <t>-124.75</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>90085.5427960057</t>
+          <t>89966.04700854702</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>17036.0</t>
+          <t>18202.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>6987.2</v>
+        <v>9349.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>6636.3</t>
+          <t>7989.3</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>14299.4</v>
+        <v>13460.24</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-1285.68313588008</t>
+          <t>-1010.858746339825</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-325.7147088748216</t>
+          <t>500.6753961315808</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>17036.0</t>
+          <t>18202.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-6.67</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>21.76</t>
+          <t>21.31</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>31.49</t>
+          <t>31.17</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>2389</t>
+          <t>2340</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>334.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5.84</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-18.65</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-15.82</t>
+          <t>-12.79</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>12.03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2739,68 +2739,68 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>41.94</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>6.77</t>
+          <t>15.05</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-5.82</t>
+          <t>-4.80</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-6.81</t>
+          <t>-6.85</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>50.42999999999999</t>
+          <t>50.71</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>53.55</v>
+        <v>53.27</v>
       </c>
       <c r="AN6" t="n">
-        <v>57.46</v>
+        <v>57.18</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>57.28</t>
+          <t>57.29</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-14.78</t>
+          <t>-5.61</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-124.80</t>
+          <t>-125.16</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>90085.5427960057</t>
+          <t>89966.04700854702</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>2323.0</t>
+          <t>17036.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>4899.2</v>
+        <v>6987.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>6022.3</t>
+          <t>6636.3</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>15417.3</v>
+        <v>14299.4</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-1123</t>
+          <t>350</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-1460.222849881036</t>
+          <t>-1285.68313588008</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-1369.710762138438</t>
+          <t>-325.7147088748216</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>2323.0</t>
+          <t>17036.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-9.91</t>
+          <t>-6.67</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>21.76</t>
+          <t>21.31</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>31.49</t>
+          <t>31.17</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>2389</t>
+          <t>2340</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>49.85</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>49.85</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-13.32</t>
+          <t>-18.65</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-16.08</t>
+          <t>-15.82</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3169,68 +3169,68 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>8.94</t>
+          <t>6.77</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-5.95</t>
+          <t>-5.82</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-6.51</t>
+          <t>-6.81</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>50.73</t>
+          <t>50.42999999999999</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>53.94</v>
+        <v>53.55</v>
       </c>
       <c r="AN7" t="n">
-        <v>57.69</v>
+        <v>57.46</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>57.29</t>
+          <t>57.28</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-17.10</t>
+          <t>-14.78</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-123.89</t>
+          <t>-124.80</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>90085.5427960057</t>
+          <t>89966.04700854702</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>3535.0</t>
+          <t>2323.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>5598</v>
+        <v>4899.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>6458.6</t>
+          <t>6022.3</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>15662.04</v>
+        <v>15417.3</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-860</t>
+          <t>-1123</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-1476.679593106963</t>
+          <t>-1460.222849881036</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-1235.822596724375</t>
+          <t>-1369.710762138438</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>3535.0</t>
+          <t>2323.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-10.18</t>
+          <t>-9.91</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>21.76</t>
+          <t>21.31</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>31.49</t>
+          <t>31.17</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>2389</t>
+          <t>2340</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>49.85</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>49.85</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>111.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>49.85</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-14.34</t>
+          <t>-13.32</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-13.97</t>
+          <t>-16.08</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3599,12 +3599,12 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>17.07</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -3614,53 +3614,53 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-5.65</t>
+          <t>-5.95</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-6.17</t>
+          <t>-6.51</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>51.26000000000001</t>
+          <t>50.73</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>54.33</v>
+        <v>53.94</v>
       </c>
       <c r="AN8" t="n">
-        <v>57.9</v>
+        <v>57.69</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>57.32</t>
+          <t>57.29</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-16.87</t>
+          <t>-17.10</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-122.87</t>
+          <t>-123.89</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>90085.5427960057</t>
+          <t>89966.04700854702</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>5651.0</t>
+          <t>3535.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>6317.6</v>
+        <v>5598</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>7375.3</t>
+          <t>6458.6</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>15916.1</v>
+        <v>15662.04</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-1057</t>
+          <t>-860</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-1520.471774267434</t>
+          <t>-1476.679593106963</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-1130.274410535557</t>
+          <t>-1235.822596724375</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>5651.0</t>
+          <t>3535.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-7.93</t>
+          <t>-10.18</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>21.76</t>
+          <t>21.31</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>31.49</t>
+          <t>31.17</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>2389</t>
+          <t>2340</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>49.85</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>111.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-8.35</t>
+          <t>-14.34</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-14.48</t>
+          <t>-13.97</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4029,68 +4029,68 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>17.07</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>8.94</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-5.05</t>
+          <t>-5.65</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-5.85</t>
+          <t>-6.17</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>51.94</t>
+          <t>51.26000000000001</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>54.7</v>
+        <v>54.33</v>
       </c>
       <c r="AN9" t="n">
-        <v>58.1</v>
+        <v>57.9</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>57.33</t>
+          <t>57.32</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-20.92</t>
+          <t>-16.87</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-121.90</t>
+          <t>-122.87</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>90085.5427960057</t>
+          <t>89966.04700854702</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>6391.0</t>
+          <t>5651.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>6629.2</v>
+        <v>6317.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>7233.5</t>
+          <t>7375.3</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>16143.36</v>
+        <v>15916.1</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-604</t>
+          <t>-1057</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-1591.416749491411</t>
+          <t>-1520.471774267434</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-1165.838629889547</t>
+          <t>-1130.274410535557</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>6391.0</t>
+          <t>5651.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-8.47</t>
+          <t>-7.93</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>21.76</t>
+          <t>21.31</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>31.49</t>
+          <t>31.17</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>2389</t>
+          <t>2340</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-14.12</t>
+          <t>-8.35</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-15.15</t>
+          <t>-14.48</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4459,68 +4459,68 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-5.05</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-5.46</t>
+          <t>-5.85</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>52.62</t>
+          <t>51.94</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>55.11</v>
+        <v>54.7</v>
       </c>
       <c r="AN10" t="n">
-        <v>58.29</v>
+        <v>58.1</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>57.34</t>
+          <t>57.33</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-22.24</t>
+          <t>-20.92</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-120.76</t>
+          <t>-121.90</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>90085.5427960057</t>
+          <t>89966.04700854702</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>6596.0</t>
+          <t>6391.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>6285.4</v>
+        <v>6629.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>7319.0</t>
+          <t>7233.5</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>16730.98</v>
+        <v>16143.36</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-1033</t>
+          <t>-604</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-1668.794589419023</t>
+          <t>-1591.416749491411</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-1254.293277899191</t>
+          <t>-1165.838629889547</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>6596.0</t>
+          <t>6391.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-9.19</t>
+          <t>-8.47</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,22 +4641,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>21.76</t>
+          <t>21.31</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>31.49</t>
+          <t>31.17</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>2389</t>
+          <t>2340</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-5.99</t>
+          <t>-14.12</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-13.30</t>
+          <t>-15.15</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-3.88</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4899,58 +4899,58 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-5.16</t>
+          <t>-5.46</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>53.27999999999999</t>
+          <t>52.62</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>55.51</v>
+        <v>55.11</v>
       </c>
       <c r="AN11" t="n">
-        <v>58.53</v>
+        <v>58.29</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>57.37</t>
+          <t>57.34</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-17.48</t>
+          <t>-22.24</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-119.60</t>
+          <t>-120.76</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>90085.5427960057</t>
+          <t>89966.04700854702</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>5817.0</t>
+          <t>6596.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>7145.4</v>
+        <v>6285.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>7601.0</t>
+          <t>7319.0</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>17385.02</v>
+        <v>16730.98</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-455</t>
+          <t>-1033</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-1744.158464240811</t>
+          <t>-1668.794589419023</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-1357.825157987996</t>
+          <t>-1254.293277899191</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>5817.0</t>
+          <t>6596.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-7.21</t>
+          <t>-9.19</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>21.76</t>
+          <t>21.31</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>31.49</t>
+          <t>31.17</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>2389</t>
+          <t>2340</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-6.64</t>
+          <t>-5.99</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-11.62</t>
+          <t>-13.30</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-3.88</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,7 +5319,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5329,58 +5329,58 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>18.52</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-5.03</t>
+          <t>-5.16</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>53.73999999999999</t>
+          <t>53.27999999999999</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>55.81</v>
+        <v>55.51</v>
       </c>
       <c r="AN12" t="n">
-        <v>58.76</v>
+        <v>58.53</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>57.38</t>
+          <t>57.37</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-13.29</t>
+          <t>-17.48</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-118.74</t>
+          <t>-119.60</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>90085.5427960057</t>
+          <t>89966.04700854702</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>7133.0</t>
+          <t>5817.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>7319.2</v>
+        <v>7145.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>7839.6</t>
+          <t>7601.0</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>19212.02</v>
+        <v>17385.02</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-520</t>
+          <t>-455</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-1814.400883559504</t>
+          <t>-1744.158464240811</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-1373.769802472432</t>
+          <t>-1357.825157987996</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>7133.0</t>
+          <t>5817.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-5.41</t>
+          <t>-7.21</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>21.76</t>
+          <t>21.31</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>31.49</t>
+          <t>31.17</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>2389</t>
+          <t>2340</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/印刷材料.xlsx
+++ b/Result/checksun_type/印刷材料.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>43.16</t>
+          <t>15.25</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-12.46</t>
+          <t>-12.29</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>62.32</t>
+          <t>65.22</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>78.74</t>
+          <t>73.91</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-6.98</t>
+          <t>-6.88</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>52.56</t>
+          <t>52.62</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>52.56</v>
+        <v>52.44</v>
       </c>
       <c r="AN2" t="n">
-        <v>56.5</v>
+        <v>56.31</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>57.33</t>
+          <t>57.32</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>19.82</t>
+          <t>20.79</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-121.80</t>
+          <t>-120.72</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>89966.04700854702</t>
+          <t>89844.15789473684</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>4133.0</t>
+          <t>2852.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>12338</v>
+        <v>9501.200000000001</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>8618.6</t>
+          <t>8244.2</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>13299.38</v>
+        <v>13064.54</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>3719</t>
+          <t>1257</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-472.8220554369204</t>
+          <t>-474.2046933879615</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-24.33805261133421</t>
+          <t>-481.8092021186876</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>4133.0</t>
+          <t>2852.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-6.31</t>
+          <t>-6.13</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>3.84</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>21.31</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>31.17</t>
+          <t>31.21</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>2340</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>167.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>36.29</t>
+          <t>43.16</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-10.61</t>
+          <t>-12.46</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>94.2</t>
+          <t>62.32</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>78.74</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-6.89</t>
+          <t>-6.98</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>52.16</t>
+          <t>52.56</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>52.77</v>
+        <v>52.56</v>
       </c>
       <c r="AN3" t="n">
-        <v>56.68</v>
+        <v>56.5</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>57.34</t>
+          <t>57.33</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>19.38</t>
+          <t>19.82</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-122.88</t>
+          <t>-121.80</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>89966.04700854702</t>
+          <t>89844.15789473684</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>8755.0</t>
+          <t>4133.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>11976</v>
+        <v>12338</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>8787.0</t>
+          <t>8618.6</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>13401.56</v>
+        <v>13299.38</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>3719</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-554.3646014052089</t>
+          <t>-472.8220554369204</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>492.8113771352873</t>
+          <t>-24.33805261133421</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>8755.0</t>
+          <t>4133.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-6.31</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>3.84</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>21.31</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>31.17</t>
+          <t>31.21</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>2340</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>255.0</t>
+          <t>167.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>26.75</t>
+          <t>36.29</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-11.45</t>
+          <t>-10.61</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>9.19</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>79.71</t>
+          <t>94.2</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>73.88</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-6.92</t>
+          <t>-6.89</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>51.51000000000001</t>
+          <t>52.16</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>52.9</v>
+        <v>52.77</v>
       </c>
       <c r="AN4" t="n">
-        <v>56.83</v>
+        <v>56.68</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>57.32</t>
+          <t>57.34</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>19.38</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-123.99</t>
+          <t>-122.88</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>89966.04700854702</t>
+          <t>89844.15789473684</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>13564.0</t>
+          <t>8755.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>10932</v>
+        <v>11976</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>8624.8</t>
+          <t>8787.0</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>13461.08</v>
+        <v>13401.56</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>2307</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-744.7602338671172</t>
+          <t>-554.3646014052089</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>718.7815847327729</t>
+          <t>492.8113771352873</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>13564.0</t>
+          <t>8755.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-5.23</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>3.84</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>21.31</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>31.17</t>
+          <t>31.21</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>2340</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>345.0</t>
+          <t>255.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>26.75</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-10.27</t>
+          <t>-11.45</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12.43</t>
+          <t>9.19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,32 +2304,32 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>79.71</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>48.39</t>
+          <t>73.88</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -2339,19 +2339,19 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>51.21</t>
+          <t>51.51000000000001</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>53.08</v>
+        <v>52.9</v>
       </c>
       <c r="AN5" t="n">
-        <v>57.02</v>
+        <v>56.83</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2360,17 +2360,17 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>6.54</t>
+          <t>12.69</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-124.75</t>
+          <t>-123.99</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>89966.04700854702</t>
+          <t>89844.15789473684</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>18202.0</t>
+          <t>13564.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>9349.4</v>
+        <v>10932</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>7989.3</t>
+          <t>8624.8</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>13460.24</v>
+        <v>13461.08</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>2307</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-1010.858746339825</t>
+          <t>-744.7602338671172</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>500.6753961315808</t>
+          <t>718.7815847327729</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>18202.0</t>
+          <t>13564.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-5.23</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>3.84</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>21.31</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>31.17</t>
+          <t>31.21</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>2340</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
+          <t>53.6</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>54.1</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
           <t>52.6</t>
         </is>
       </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>53.5</t>
-        </is>
-      </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>52.0</t>
-        </is>
-      </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2593,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>334.0</t>
+          <t>345.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>17.02</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-12.79</t>
+          <t>-10.27</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12.03</t>
+          <t>12.43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>41.94</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>15.05</t>
+          <t>48.39</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.80</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-6.85</t>
+          <t>-6.92</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>50.71</t>
+          <t>51.21</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>53.27</v>
+        <v>53.08</v>
       </c>
       <c r="AN6" t="n">
-        <v>57.18</v>
+        <v>57.02</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>57.29</t>
+          <t>57.32</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-5.61</t>
+          <t>6.54</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-125.16</t>
+          <t>-124.75</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>89966.04700854702</t>
+          <t>89844.15789473684</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>17036.0</t>
+          <t>18202.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>6987.2</v>
+        <v>9349.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>6636.3</t>
+          <t>7989.3</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>14299.4</v>
+        <v>13460.24</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-1285.68313588008</t>
+          <t>-1010.858746339825</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-325.7147088748216</t>
+          <t>500.6753961315808</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>17036.0</t>
+          <t>18202.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-6.67</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>3.84</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>21.31</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>31.17</t>
+          <t>31.21</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>2340</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>334.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-18.65</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-15.82</t>
+          <t>-12.79</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>12.03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>41.94</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>6.77</t>
+          <t>15.05</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-5.82</t>
+          <t>-4.80</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-6.81</t>
+          <t>-6.85</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>50.42999999999999</t>
+          <t>50.71</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>53.55</v>
+        <v>53.27</v>
       </c>
       <c r="AN7" t="n">
-        <v>57.46</v>
+        <v>57.18</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>57.28</t>
+          <t>57.29</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-14.78</t>
+          <t>-5.61</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-124.80</t>
+          <t>-125.16</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>89966.04700854702</t>
+          <t>89844.15789473684</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>2323.0</t>
+          <t>17036.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>4899.2</v>
+        <v>6987.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>6022.3</t>
+          <t>6636.3</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>15417.3</v>
+        <v>14299.4</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-1123</t>
+          <t>350</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-1460.222849881036</t>
+          <t>-1285.68313588008</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-1369.710762138438</t>
+          <t>-325.7147088748216</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>2323.0</t>
+          <t>17036.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-9.91</t>
+          <t>-6.67</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>3.84</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>21.31</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>31.17</t>
+          <t>31.21</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>2340</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>49.85</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>49.85</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-13.32</t>
+          <t>-18.65</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-16.08</t>
+          <t>-15.82</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>8.94</t>
+          <t>6.77</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-5.95</t>
+          <t>-5.82</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-6.51</t>
+          <t>-6.81</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>50.73</t>
+          <t>50.42999999999999</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>53.94</v>
+        <v>53.55</v>
       </c>
       <c r="AN8" t="n">
-        <v>57.69</v>
+        <v>57.46</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>57.29</t>
+          <t>57.28</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-17.10</t>
+          <t>-14.78</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-123.89</t>
+          <t>-124.80</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>89966.04700854702</t>
+          <t>89844.15789473684</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>3535.0</t>
+          <t>2323.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>5598</v>
+        <v>4899.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>6458.6</t>
+          <t>6022.3</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>15662.04</v>
+        <v>15417.3</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-860</t>
+          <t>-1123</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-1476.679593106963</t>
+          <t>-1460.222849881036</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-1235.822596724375</t>
+          <t>-1369.710762138438</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>3535.0</t>
+          <t>2323.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-10.18</t>
+          <t>-9.91</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>3.84</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>21.31</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>31.17</t>
+          <t>31.21</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>2340</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>49.85</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>49.85</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>111.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>49.85</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-14.34</t>
+          <t>-13.32</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-13.97</t>
+          <t>-16.08</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,17 +4024,17 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>17.07</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -4044,53 +4044,53 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-5.65</t>
+          <t>-5.95</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-6.17</t>
+          <t>-6.51</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>51.26000000000001</t>
+          <t>50.73</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>54.33</v>
+        <v>53.94</v>
       </c>
       <c r="AN9" t="n">
-        <v>57.9</v>
+        <v>57.69</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>57.32</t>
+          <t>57.29</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-16.87</t>
+          <t>-17.10</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-122.87</t>
+          <t>-123.89</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>89966.04700854702</t>
+          <t>89844.15789473684</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>5651.0</t>
+          <t>3535.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>6317.6</v>
+        <v>5598</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>7375.3</t>
+          <t>6458.6</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>15916.1</v>
+        <v>15662.04</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-1057</t>
+          <t>-860</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-1520.471774267434</t>
+          <t>-1476.679593106963</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-1130.274410535557</t>
+          <t>-1235.822596724375</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>5651.0</t>
+          <t>3535.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-7.93</t>
+          <t>-10.18</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>3.84</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>21.31</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>31.17</t>
+          <t>31.21</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>2340</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>49.85</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>111.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-8.35</t>
+          <t>-14.34</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-14.48</t>
+          <t>-13.97</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>17.07</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>8.94</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-5.05</t>
+          <t>-5.65</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-5.85</t>
+          <t>-6.17</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>51.94</t>
+          <t>51.26000000000001</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>54.7</v>
+        <v>54.33</v>
       </c>
       <c r="AN10" t="n">
-        <v>58.1</v>
+        <v>57.9</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>57.33</t>
+          <t>57.32</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-20.92</t>
+          <t>-16.87</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-121.90</t>
+          <t>-122.87</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>89966.04700854702</t>
+          <t>89844.15789473684</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>6391.0</t>
+          <t>5651.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>6629.2</v>
+        <v>6317.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>7233.5</t>
+          <t>7375.3</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>16143.36</v>
+        <v>15916.1</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-604</t>
+          <t>-1057</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-1591.416749491411</t>
+          <t>-1520.471774267434</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-1165.838629889547</t>
+          <t>-1130.274410535557</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>6391.0</t>
+          <t>5651.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-8.47</t>
+          <t>-7.93</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>3.84</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>21.31</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>31.17</t>
+          <t>31.21</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>2340</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-14.12</t>
+          <t>-8.35</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-15.15</t>
+          <t>-14.48</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-5.05</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-5.46</t>
+          <t>-5.85</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>52.62</t>
+          <t>51.94</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>55.11</v>
+        <v>54.7</v>
       </c>
       <c r="AN11" t="n">
-        <v>58.29</v>
+        <v>58.1</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>57.34</t>
+          <t>57.33</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-22.24</t>
+          <t>-20.92</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-120.76</t>
+          <t>-121.90</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>89966.04700854702</t>
+          <t>89844.15789473684</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>6596.0</t>
+          <t>6391.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>6285.4</v>
+        <v>6629.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>7319.0</t>
+          <t>7233.5</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>16730.98</v>
+        <v>16143.36</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-1033</t>
+          <t>-604</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-1668.794589419023</t>
+          <t>-1591.416749491411</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-1254.293277899191</t>
+          <t>-1165.838629889547</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>6596.0</t>
+          <t>6391.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-9.19</t>
+          <t>-8.47</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>3.84</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>21.31</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>31.17</t>
+          <t>31.21</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>2340</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-5.99</t>
+          <t>-14.12</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-13.30</t>
+          <t>-15.15</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-3.88</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5329,58 +5329,58 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-5.16</t>
+          <t>-5.46</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>53.27999999999999</t>
+          <t>52.62</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>55.51</v>
+        <v>55.11</v>
       </c>
       <c r="AN12" t="n">
-        <v>58.53</v>
+        <v>58.29</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>57.37</t>
+          <t>57.34</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-17.48</t>
+          <t>-22.24</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-119.60</t>
+          <t>-120.76</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>89966.04700854702</t>
+          <t>89844.15789473684</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>5817.0</t>
+          <t>6596.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>7145.4</v>
+        <v>6285.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>7601.0</t>
+          <t>7319.0</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>17385.02</v>
+        <v>16730.98</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-455</t>
+          <t>-1033</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-1744.158464240811</t>
+          <t>-1668.794589419023</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-1357.825157987996</t>
+          <t>-1254.293277899191</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>5817.0</t>
+          <t>6596.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-7.21</t>
+          <t>-9.19</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>3.84</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>21.31</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>31.17</t>
+          <t>31.21</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>2340</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/印刷材料.xlsx
+++ b/Result/checksun_type/印刷材料.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>156.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>15.25</t>
+          <t>-10.85</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-12.29</t>
+          <t>-10.94</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,54 +1014,54 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>156</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>65.22</t>
+          <t>88.41</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>73.91</t>
+          <t>71.98</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-6.88</t>
+          <t>-6.68</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>52.62</t>
+          <t>52.54</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>52.44</v>
+        <v>52.39</v>
       </c>
       <c r="AN2" t="n">
-        <v>56.31</v>
+        <v>56.14</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>20.79</t>
+          <t>25.48</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-120.72</t>
+          <t>-119.48</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>89844.15789473684</t>
+          <t>89734.20383522728</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>2852.0</t>
+          <t>8291.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>9501.200000000001</v>
+        <v>7519</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>8244.2</t>
+          <t>8434.2</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>13064.54</v>
+        <v>12897.76</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>1257</t>
+          <t>-915</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-474.2046933879615</t>
+          <t>-460.0299369776392</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-481.8092021186876</t>
+          <t>-382.0687767208665</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>2852.0</t>
+          <t>8291.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-6.13</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>3.84</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>21.68</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>31.21</t>
+          <t>31.49</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2380</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>54.3</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>43.16</t>
+          <t>15.25</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-12.46</t>
+          <t>-12.29</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>156</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>62.32</t>
+          <t>65.22</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>78.74</t>
+          <t>73.91</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-6.98</t>
+          <t>-6.88</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>52.56</t>
+          <t>52.62</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>52.56</v>
+        <v>52.44</v>
       </c>
       <c r="AN3" t="n">
-        <v>56.5</v>
+        <v>56.31</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>57.33</t>
+          <t>57.32</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>19.82</t>
+          <t>20.79</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-121.80</t>
+          <t>-120.72</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>89844.15789473684</t>
+          <t>89734.20383522728</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>4133.0</t>
+          <t>2852.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>12338</v>
+        <v>9501.200000000001</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>8618.6</t>
+          <t>8244.2</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>13299.38</v>
+        <v>13064.54</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>3719</t>
+          <t>1257</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-472.8220554369204</t>
+          <t>-474.2046933879615</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-24.33805261133421</t>
+          <t>-481.8092021186876</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>4133.0</t>
+          <t>2852.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-6.31</t>
+          <t>-6.13</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,12 +1631,12 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>3.84</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>21.68</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>31.21</t>
+          <t>31.49</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2380</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>167.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>36.29</t>
+          <t>43.16</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-10.61</t>
+          <t>-12.46</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>156</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>94.2</t>
+          <t>62.32</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>78.74</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-6.89</t>
+          <t>-6.98</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>52.16</t>
+          <t>52.56</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>52.77</v>
+        <v>52.56</v>
       </c>
       <c r="AN4" t="n">
-        <v>56.68</v>
+        <v>56.5</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>57.34</t>
+          <t>57.33</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>19.38</t>
+          <t>19.82</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-122.88</t>
+          <t>-121.80</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>89844.15789473684</t>
+          <t>89734.20383522728</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>8755.0</t>
+          <t>4133.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>11976</v>
+        <v>12338</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>8787.0</t>
+          <t>8618.6</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>13401.56</v>
+        <v>13299.38</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>3719</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-554.3646014052089</t>
+          <t>-472.8220554369204</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>492.8113771352873</t>
+          <t>-24.33805261133421</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>8755.0</t>
+          <t>4133.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-6.31</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>3.84</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>21.68</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>31.21</t>
+          <t>31.49</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2380</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>255.0</t>
+          <t>167.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>26.75</t>
+          <t>36.29</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-11.45</t>
+          <t>-10.61</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.19</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>156</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>79.71</t>
+          <t>94.2</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>73.88</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-6.92</t>
+          <t>-6.89</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>51.51000000000001</t>
+          <t>52.16</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>52.9</v>
+        <v>52.77</v>
       </c>
       <c r="AN5" t="n">
-        <v>56.83</v>
+        <v>56.68</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>57.32</t>
+          <t>57.34</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>19.38</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-123.99</t>
+          <t>-122.88</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>89844.15789473684</t>
+          <t>89734.20383522728</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>13564.0</t>
+          <t>8755.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>10932</v>
+        <v>11976</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>8624.8</t>
+          <t>8787.0</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>13461.08</v>
+        <v>13401.56</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>2307</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-744.7602338671172</t>
+          <t>-554.3646014052089</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>718.7815847327729</t>
+          <t>492.8113771352873</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>13564.0</t>
+          <t>8755.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-5.23</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>3.84</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>21.68</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>31.21</t>
+          <t>31.49</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2380</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>345.0</t>
+          <t>255.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>26.75</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-10.27</t>
+          <t>-11.45</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12.43</t>
+          <t>9.19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,32 +2734,32 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>156</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>79.71</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>48.39</t>
+          <t>73.88</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -2769,19 +2769,19 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>51.21</t>
+          <t>51.51000000000001</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>53.08</v>
+        <v>52.9</v>
       </c>
       <c r="AN6" t="n">
-        <v>57.02</v>
+        <v>56.83</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2790,17 +2790,17 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>6.54</t>
+          <t>12.69</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-124.75</t>
+          <t>-123.99</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>89844.15789473684</t>
+          <t>89734.20383522728</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>18202.0</t>
+          <t>13564.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>9349.4</v>
+        <v>10932</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>7989.3</t>
+          <t>8624.8</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>13460.24</v>
+        <v>13461.08</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>2307</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-1010.858746339825</t>
+          <t>-744.7602338671172</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>500.6753961315808</t>
+          <t>718.7815847327729</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>18202.0</t>
+          <t>13564.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-5.23</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>3.84</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>21.68</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>31.21</t>
+          <t>31.49</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2380</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
+          <t>53.6</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>54.1</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
           <t>52.6</t>
         </is>
       </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>53.5</t>
-        </is>
-      </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>52.0</t>
-        </is>
-      </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3023,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>334.0</t>
+          <t>345.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>17.02</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-12.79</t>
+          <t>-10.27</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12.03</t>
+          <t>12.43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>156</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>41.94</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>15.05</t>
+          <t>48.39</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.80</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-6.85</t>
+          <t>-6.92</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>50.71</t>
+          <t>51.21</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>53.27</v>
+        <v>53.08</v>
       </c>
       <c r="AN7" t="n">
-        <v>57.18</v>
+        <v>57.02</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>57.29</t>
+          <t>57.32</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-5.61</t>
+          <t>6.54</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-125.16</t>
+          <t>-124.75</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>89844.15789473684</t>
+          <t>89734.20383522728</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>17036.0</t>
+          <t>18202.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>6987.2</v>
+        <v>9349.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>6636.3</t>
+          <t>7989.3</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>14299.4</v>
+        <v>13460.24</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-1285.68313588008</t>
+          <t>-1010.858746339825</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-325.7147088748216</t>
+          <t>500.6753961315808</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>17036.0</t>
+          <t>18202.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-6.67</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>3.84</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>21.68</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>31.21</t>
+          <t>31.49</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2380</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>334.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-18.65</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-15.82</t>
+          <t>-12.79</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>12.03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>156</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>41.94</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>6.77</t>
+          <t>15.05</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-5.82</t>
+          <t>-4.80</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-6.81</t>
+          <t>-6.85</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>50.42999999999999</t>
+          <t>50.71</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>53.55</v>
+        <v>53.27</v>
       </c>
       <c r="AN8" t="n">
-        <v>57.46</v>
+        <v>57.18</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>57.28</t>
+          <t>57.29</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-14.78</t>
+          <t>-5.61</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-124.80</t>
+          <t>-125.16</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>89844.15789473684</t>
+          <t>89734.20383522728</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>2323.0</t>
+          <t>17036.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>4899.2</v>
+        <v>6987.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>6022.3</t>
+          <t>6636.3</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>15417.3</v>
+        <v>14299.4</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-1123</t>
+          <t>350</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-1460.222849881036</t>
+          <t>-1285.68313588008</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-1369.710762138438</t>
+          <t>-325.7147088748216</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>2323.0</t>
+          <t>17036.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-9.91</t>
+          <t>-6.67</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>3.84</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>21.68</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>31.21</t>
+          <t>31.49</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2380</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>49.85</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>49.85</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>5.48</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-13.32</t>
+          <t>-18.65</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-16.08</t>
+          <t>-15.82</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>156</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>8.94</t>
+          <t>6.77</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-5.95</t>
+          <t>-5.82</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-6.51</t>
+          <t>-6.81</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>50.73</t>
+          <t>50.42999999999999</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>53.94</v>
+        <v>53.55</v>
       </c>
       <c r="AN9" t="n">
-        <v>57.69</v>
+        <v>57.46</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>57.29</t>
+          <t>57.28</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-17.10</t>
+          <t>-14.78</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-123.89</t>
+          <t>-124.80</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>89844.15789473684</t>
+          <t>89734.20383522728</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>3535.0</t>
+          <t>2323.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>5598</v>
+        <v>4899.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>6458.6</t>
+          <t>6022.3</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>15662.04</v>
+        <v>15417.3</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-860</t>
+          <t>-1123</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-1476.679593106963</t>
+          <t>-1460.222849881036</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-1235.822596724375</t>
+          <t>-1369.710762138438</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>3535.0</t>
+          <t>2323.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-10.18</t>
+          <t>-9.91</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>3.84</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>21.68</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>31.21</t>
+          <t>31.49</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2380</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>49.85</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>49.85</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>111.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>49.85</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>5.77</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-14.34</t>
+          <t>-13.32</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-13.97</t>
+          <t>-16.08</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,17 +4454,17 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>156</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>17.07</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -4474,53 +4474,53 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-5.65</t>
+          <t>-5.95</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-6.17</t>
+          <t>-6.51</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>51.26000000000001</t>
+          <t>50.73</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>54.33</v>
+        <v>53.94</v>
       </c>
       <c r="AN10" t="n">
-        <v>57.9</v>
+        <v>57.69</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>57.32</t>
+          <t>57.29</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-16.87</t>
+          <t>-17.10</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-122.87</t>
+          <t>-123.89</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>89844.15789473684</t>
+          <t>89734.20383522728</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>5651.0</t>
+          <t>3535.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>6317.6</v>
+        <v>5598</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>7375.3</t>
+          <t>6458.6</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>15916.1</v>
+        <v>15662.04</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-1057</t>
+          <t>-860</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-1520.471774267434</t>
+          <t>-1476.679593106963</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-1130.274410535557</t>
+          <t>-1235.822596724375</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>5651.0</t>
+          <t>3535.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-7.93</t>
+          <t>-10.18</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>3.84</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>21.68</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>31.21</t>
+          <t>31.49</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2380</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>49.85</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>111.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-8.35</t>
+          <t>-14.34</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-14.48</t>
+          <t>-13.97</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>156</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>17.07</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>8.94</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-5.05</t>
+          <t>-5.65</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-5.85</t>
+          <t>-6.17</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>51.94</t>
+          <t>51.26000000000001</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>54.7</v>
+        <v>54.33</v>
       </c>
       <c r="AN11" t="n">
-        <v>58.1</v>
+        <v>57.9</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>57.33</t>
+          <t>57.32</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-20.92</t>
+          <t>-16.87</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-121.90</t>
+          <t>-122.87</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>89844.15789473684</t>
+          <t>89734.20383522728</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>6391.0</t>
+          <t>5651.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>6629.2</v>
+        <v>6317.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>7233.5</t>
+          <t>7375.3</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>16143.36</v>
+        <v>15916.1</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-604</t>
+          <t>-1057</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-1591.416749491411</t>
+          <t>-1520.471774267434</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-1165.838629889547</t>
+          <t>-1130.274410535557</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>6391.0</t>
+          <t>5651.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-8.47</t>
+          <t>-7.93</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>3.84</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>21.68</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>31.21</t>
+          <t>31.49</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2380</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-14.12</t>
+          <t>-8.35</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-15.15</t>
+          <t>-14.48</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>156</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-5.05</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-5.46</t>
+          <t>-5.85</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>52.62</t>
+          <t>51.94</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>55.11</v>
+        <v>54.7</v>
       </c>
       <c r="AN12" t="n">
-        <v>58.29</v>
+        <v>58.1</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>57.34</t>
+          <t>57.33</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-22.24</t>
+          <t>-20.92</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-120.76</t>
+          <t>-121.90</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>89844.15789473684</t>
+          <t>89734.20383522728</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>6596.0</t>
+          <t>6391.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>6285.4</v>
+        <v>6629.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>7319.0</t>
+          <t>7233.5</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>16730.98</v>
+        <v>16143.36</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-1033</t>
+          <t>-604</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-1668.794589419023</t>
+          <t>-1591.416749491411</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-1254.293277899191</t>
+          <t>-1165.838629889547</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>6596.0</t>
+          <t>6391.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-9.19</t>
+          <t>-8.47</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>3.84</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>21.68</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>31.21</t>
+          <t>31.49</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2380</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/印刷材料.xlsx
+++ b/Result/checksun_type/印刷材料.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>156.0</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-10.85</t>
+          <t>-33.34</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-10.94</t>
+          <t>-11.28</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>88.41</t>
+          <t>81.82</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>71.98</t>
+          <t>78.48</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-6.68</t>
+          <t>-6.53</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>52.54</t>
+          <t>52.56</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>52.39</v>
+        <v>52.32</v>
       </c>
       <c r="AN2" t="n">
-        <v>56.14</v>
+        <v>55.98</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>57.32</t>
+          <t>57.34</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>25.48</t>
+          <t>28.11</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-119.48</t>
+          <t>-118.20</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>89734.20383522728</t>
+          <t>89613.93404255318</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>8291.0</t>
+          <t>3296.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>7519</v>
+        <v>5465.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>8434.2</t>
+          <t>8198.7</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>12897.76</v>
+        <v>12704.54</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-915</t>
+          <t>-2733</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-460.0299369776392</t>
+          <t>-493.4597558309824</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-382.0687767208665</t>
+          <t>-677.32375952437</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>8291.0</t>
+          <t>3296.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-5.05</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>21.68</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>31.49</t>
+          <t>31.42</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>2380</t>
+          <t>2371</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>54.3</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>156.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>15.25</t>
+          <t>-10.85</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-12.29</t>
+          <t>-10.94</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,54 +1444,54 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>65.22</t>
+          <t>88.41</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>73.91</t>
+          <t>71.98</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-6.88</t>
+          <t>-6.68</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>52.62</t>
+          <t>52.54</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>52.44</v>
+        <v>52.39</v>
       </c>
       <c r="AN3" t="n">
-        <v>56.31</v>
+        <v>56.14</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1500,17 +1500,17 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>20.79</t>
+          <t>25.48</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-120.72</t>
+          <t>-119.48</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>89734.20383522728</t>
+          <t>89613.93404255318</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>2852.0</t>
+          <t>8291.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>9501.200000000001</v>
+        <v>7519</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>8244.2</t>
+          <t>8434.2</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>13064.54</v>
+        <v>12897.76</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>1257</t>
+          <t>-915</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-474.2046933879615</t>
+          <t>-460.0299369776392</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-481.8092021186876</t>
+          <t>-382.0687767208665</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>2852.0</t>
+          <t>8291.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-6.13</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>21.68</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>31.49</t>
+          <t>31.42</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>2380</t>
+          <t>2371</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>54.3</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>43.16</t>
+          <t>15.25</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-12.46</t>
+          <t>-12.29</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>62.32</t>
+          <t>65.22</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>78.74</t>
+          <t>73.91</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-6.98</t>
+          <t>-6.88</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>52.56</t>
+          <t>52.62</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>52.56</v>
+        <v>52.44</v>
       </c>
       <c r="AN4" t="n">
-        <v>56.5</v>
+        <v>56.31</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>57.33</t>
+          <t>57.32</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>19.82</t>
+          <t>20.79</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-121.80</t>
+          <t>-120.72</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>89734.20383522728</t>
+          <t>89613.93404255318</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>4133.0</t>
+          <t>2852.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>12338</v>
+        <v>9501.200000000001</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>8618.6</t>
+          <t>8244.2</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>13299.38</v>
+        <v>13064.54</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>3719</t>
+          <t>1257</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-472.8220554369204</t>
+          <t>-474.2046933879615</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-24.33805261133421</t>
+          <t>-481.8092021186876</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>4133.0</t>
+          <t>2852.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-6.31</t>
+          <t>-6.13</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>21.68</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>31.49</t>
+          <t>31.42</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>2380</t>
+          <t>2371</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>167.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>36.29</t>
+          <t>43.16</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-10.61</t>
+          <t>-12.46</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>94.2</t>
+          <t>62.32</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>78.74</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-6.89</t>
+          <t>-6.98</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>52.16</t>
+          <t>52.56</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>52.77</v>
+        <v>52.56</v>
       </c>
       <c r="AN5" t="n">
-        <v>56.68</v>
+        <v>56.5</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>57.34</t>
+          <t>57.33</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>19.38</t>
+          <t>19.82</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-122.88</t>
+          <t>-121.80</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>89734.20383522728</t>
+          <t>89613.93404255318</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>8755.0</t>
+          <t>4133.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>11976</v>
+        <v>12338</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>8787.0</t>
+          <t>8618.6</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>13401.56</v>
+        <v>13299.38</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>3719</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-554.3646014052089</t>
+          <t>-472.8220554369204</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>492.8113771352873</t>
+          <t>-24.33805261133421</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>8755.0</t>
+          <t>4133.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-6.31</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>21.68</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>31.49</t>
+          <t>31.42</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>2380</t>
+          <t>2371</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>255.0</t>
+          <t>167.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>26.75</t>
+          <t>36.29</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-11.45</t>
+          <t>-10.61</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>9.19</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>79.71</t>
+          <t>94.2</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>73.88</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-6.92</t>
+          <t>-6.89</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>51.51000000000001</t>
+          <t>52.16</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>52.9</v>
+        <v>52.77</v>
       </c>
       <c r="AN6" t="n">
-        <v>56.83</v>
+        <v>56.68</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>57.32</t>
+          <t>57.34</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>19.38</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-123.99</t>
+          <t>-122.88</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>89734.20383522728</t>
+          <t>89613.93404255318</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>13564.0</t>
+          <t>8755.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>10932</v>
+        <v>11976</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>8624.8</t>
+          <t>8787.0</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>13461.08</v>
+        <v>13401.56</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>2307</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-744.7602338671172</t>
+          <t>-554.3646014052089</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>718.7815847327729</t>
+          <t>492.8113771352873</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>13564.0</t>
+          <t>8755.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-5.23</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>21.68</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>31.49</t>
+          <t>31.42</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>2380</t>
+          <t>2371</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>345.0</t>
+          <t>255.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>26.75</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-10.27</t>
+          <t>-11.45</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12.43</t>
+          <t>9.19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,32 +3164,32 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>79.71</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>48.39</t>
+          <t>73.88</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -3199,19 +3199,19 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>51.21</t>
+          <t>51.51000000000001</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>53.08</v>
+        <v>52.9</v>
       </c>
       <c r="AN7" t="n">
-        <v>57.02</v>
+        <v>56.83</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3220,17 +3220,17 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>6.54</t>
+          <t>12.69</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-124.75</t>
+          <t>-123.99</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>89734.20383522728</t>
+          <t>89613.93404255318</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>18202.0</t>
+          <t>13564.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>9349.4</v>
+        <v>10932</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>7989.3</t>
+          <t>8624.8</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>13460.24</v>
+        <v>13461.08</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>2307</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-1010.858746339825</t>
+          <t>-744.7602338671172</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>500.6753961315808</t>
+          <t>718.7815847327729</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>18202.0</t>
+          <t>13564.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-5.23</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>21.68</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>31.49</t>
+          <t>31.42</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>2380</t>
+          <t>2371</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
+          <t>53.6</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
+          <t>54.1</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
           <t>52.6</t>
         </is>
       </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>53.5</t>
-        </is>
-      </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>52.0</t>
-        </is>
-      </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3453,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>334.0</t>
+          <t>345.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>17.02</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-12.79</t>
+          <t>-10.27</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12.03</t>
+          <t>12.43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>41.94</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>15.05</t>
+          <t>48.39</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-4.80</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-6.85</t>
+          <t>-6.92</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>50.71</t>
+          <t>51.21</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>53.27</v>
+        <v>53.08</v>
       </c>
       <c r="AN8" t="n">
-        <v>57.18</v>
+        <v>57.02</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>57.29</t>
+          <t>57.32</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-5.61</t>
+          <t>6.54</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-125.16</t>
+          <t>-124.75</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>89734.20383522728</t>
+          <t>89613.93404255318</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>17036.0</t>
+          <t>18202.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>6987.2</v>
+        <v>9349.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>6636.3</t>
+          <t>7989.3</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>14299.4</v>
+        <v>13460.24</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-1285.68313588008</t>
+          <t>-1010.858746339825</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-325.7147088748216</t>
+          <t>500.6753961315808</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>17036.0</t>
+          <t>18202.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-6.67</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>21.68</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>31.49</t>
+          <t>31.42</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>2380</t>
+          <t>2371</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>334.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-18.65</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-15.82</t>
+          <t>-12.79</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>12.03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>41.94</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>6.77</t>
+          <t>15.05</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-5.82</t>
+          <t>-4.80</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-6.81</t>
+          <t>-6.85</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>50.42999999999999</t>
+          <t>50.71</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>53.55</v>
+        <v>53.27</v>
       </c>
       <c r="AN9" t="n">
-        <v>57.46</v>
+        <v>57.18</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>57.28</t>
+          <t>57.29</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-14.78</t>
+          <t>-5.61</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-124.80</t>
+          <t>-125.16</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>89734.20383522728</t>
+          <t>89613.93404255318</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>2323.0</t>
+          <t>17036.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>4899.2</v>
+        <v>6987.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>6022.3</t>
+          <t>6636.3</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>15417.3</v>
+        <v>14299.4</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-1123</t>
+          <t>350</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-1460.222849881036</t>
+          <t>-1285.68313588008</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-1369.710762138438</t>
+          <t>-325.7147088748216</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>2323.0</t>
+          <t>17036.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-9.91</t>
+          <t>-6.67</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>21.68</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>31.49</t>
+          <t>31.42</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>2380</t>
+          <t>2371</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>49.85</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>49.85</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-13.32</t>
+          <t>-18.65</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-16.08</t>
+          <t>-15.82</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>8.94</t>
+          <t>6.77</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-5.95</t>
+          <t>-5.82</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-6.51</t>
+          <t>-6.81</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>50.73</t>
+          <t>50.42999999999999</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>53.94</v>
+        <v>53.55</v>
       </c>
       <c r="AN10" t="n">
-        <v>57.69</v>
+        <v>57.46</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>57.29</t>
+          <t>57.28</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-17.10</t>
+          <t>-14.78</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-123.89</t>
+          <t>-124.80</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>89734.20383522728</t>
+          <t>89613.93404255318</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>3535.0</t>
+          <t>2323.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>5598</v>
+        <v>4899.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>6458.6</t>
+          <t>6022.3</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>15662.04</v>
+        <v>15417.3</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-860</t>
+          <t>-1123</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-1476.679593106963</t>
+          <t>-1460.222849881036</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-1235.822596724375</t>
+          <t>-1369.710762138438</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>3535.0</t>
+          <t>2323.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-10.18</t>
+          <t>-9.91</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>21.68</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>31.49</t>
+          <t>31.42</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>2380</t>
+          <t>2371</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>49.85</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>49.85</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>111.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>49.85</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>5.41</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-14.34</t>
+          <t>-13.32</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-13.97</t>
+          <t>-16.08</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,17 +4884,17 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>17.07</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -4904,53 +4904,53 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-5.65</t>
+          <t>-5.95</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-6.17</t>
+          <t>-6.51</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>51.26000000000001</t>
+          <t>50.73</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>54.33</v>
+        <v>53.94</v>
       </c>
       <c r="AN11" t="n">
-        <v>57.9</v>
+        <v>57.69</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>57.32</t>
+          <t>57.29</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-16.87</t>
+          <t>-17.10</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-122.87</t>
+          <t>-123.89</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>89734.20383522728</t>
+          <t>89613.93404255318</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>5651.0</t>
+          <t>3535.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>6317.6</v>
+        <v>5598</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>7375.3</t>
+          <t>6458.6</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>15916.1</v>
+        <v>15662.04</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-1057</t>
+          <t>-860</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-1520.471774267434</t>
+          <t>-1476.679593106963</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-1130.274410535557</t>
+          <t>-1235.822596724375</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>5651.0</t>
+          <t>3535.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-7.93</t>
+          <t>-10.18</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>21.68</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>31.49</t>
+          <t>31.42</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>2380</t>
+          <t>2371</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>49.85</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>111.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-8.35</t>
+          <t>-14.34</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-14.48</t>
+          <t>-13.97</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>17.07</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>8.94</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-5.05</t>
+          <t>-5.65</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-5.85</t>
+          <t>-6.17</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>51.94</t>
+          <t>51.26000000000001</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>54.7</v>
+        <v>54.33</v>
       </c>
       <c r="AN12" t="n">
-        <v>58.1</v>
+        <v>57.9</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>57.33</t>
+          <t>57.32</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-20.92</t>
+          <t>-16.87</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-121.90</t>
+          <t>-122.87</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>89734.20383522728</t>
+          <t>89613.93404255318</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>6391.0</t>
+          <t>5651.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>6629.2</v>
+        <v>6317.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>7233.5</t>
+          <t>7375.3</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>16143.36</v>
+        <v>15916.1</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-604</t>
+          <t>-1057</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-1591.416749491411</t>
+          <t>-1520.471774267434</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-1165.838629889547</t>
+          <t>-1130.274410535557</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>6391.0</t>
+          <t>5651.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-8.47</t>
+          <t>-7.93</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>21.68</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>31.49</t>
+          <t>31.42</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>2380</t>
+          <t>2371</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/印刷材料.xlsx
+++ b/Result/checksun_type/印刷材料.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【d1】;【d2】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-33.34</t>
+          <t>-43.86</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-11.28</t>
+          <t>-12.96</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,74 +1014,66 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>92</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>81.82</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>78.48</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>0.27</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>0.45</t>
-        </is>
+          <t>56.74</t>
+        </is>
+      </c>
+      <c r="AH2" t="n">
+        <v>-1.11</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.1</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-6.53</t>
+          <t>-6.39</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-2.71</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>52.56</t>
+          <t>52.27999999999999</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>52.32</v>
+        <v>52.23</v>
       </c>
       <c r="AN2" t="n">
-        <v>55.98</v>
+        <v>55.8</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>57.34</t>
+          <t>57.35</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>28.11</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>-0.96</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>-1.33</t>
-        </is>
+          <t>24.71</t>
+        </is>
+      </c>
+      <c r="AQ2" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>-1.25</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1090,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-118.20</t>
+          <t>-117.14</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>89613.93404255318</t>
+          <t>89497.1940509915</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>3296.0</t>
+          <t>4797.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>5465.4</v>
+        <v>4673.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>8198.7</t>
+          <t>8324.9</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>12704.54</v>
+        <v>12556.78</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-2733</t>
+          <t>-3651</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-493.4597558309824</t>
+          <t>-533.6188939337103</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-677.32375952437</t>
+          <t>-754.4941534987138</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>3296.0</t>
+          <t>4797.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-5.05</t>
+          <t>-6.85</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1193,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1203,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.19</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>31.42</t>
+          <t>31.88</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>2371</t>
+          <t>2326</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1303,7 +1295,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【d1】;【d2】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1313,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>156.0</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-10.85</t>
+          <t>-33.34</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-10.94</t>
+          <t>-11.28</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,74 +1436,66 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>92</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>88.41</t>
+          <t>81.82</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>71.98</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>0.69</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0.29</t>
-        </is>
+          <t>78.48</t>
+        </is>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.45</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-6.68</t>
+          <t>-6.53</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>52.54</t>
+          <t>52.56</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>52.39</v>
+        <v>52.32</v>
       </c>
       <c r="AN3" t="n">
-        <v>56.14</v>
+        <v>55.98</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>57.32</t>
+          <t>57.34</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>25.48</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>-1.06</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>-1.42</t>
-        </is>
+          <t>28.11</t>
+        </is>
+      </c>
+      <c r="AQ3" t="n">
+        <v>-0.96</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>-1.33</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1520,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-119.48</t>
+          <t>-118.20</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>89613.93404255318</t>
+          <t>89497.1940509915</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>8291.0</t>
+          <t>3296.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>7519</v>
+        <v>5465.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>8434.2</t>
+          <t>8198.7</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>12897.76</v>
+        <v>12704.54</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-915</t>
+          <t>-2733</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-460.0299369776392</t>
+          <t>-493.4597558309824</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-382.0687767208665</t>
+          <t>-677.32375952437</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>8291.0</t>
+          <t>3296.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-5.05</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1615,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,12 +1625,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.19</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>31.42</t>
+          <t>31.88</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>2371</t>
+          <t>2326</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>54.3</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1733,7 +1717,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【d1】;【d2】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1743,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>156.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>15.25</t>
+          <t>-10.85</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-12.29</t>
+          <t>-10.94</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,54 +1858,50 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>92</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>65.22</t>
+          <t>88.41</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>73.91</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>-0.99</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0.35</t>
-        </is>
+          <t>71.98</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.29</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-6.88</t>
+          <t>-6.68</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>52.62</t>
+          <t>52.54</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>52.44</v>
+        <v>52.39</v>
       </c>
       <c r="AN4" t="n">
-        <v>56.31</v>
+        <v>56.14</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1930,18 +1910,14 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>20.79</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>-1.20</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>-1.51</t>
-        </is>
+          <t>25.48</t>
+        </is>
+      </c>
+      <c r="AQ4" t="n">
+        <v>-1.06</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>-1.42</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1950,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-120.72</t>
+          <t>-119.48</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>89613.93404255318</t>
+          <t>89497.1940509915</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>2852.0</t>
+          <t>8291.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>9501.200000000001</v>
+        <v>7519</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>8244.2</t>
+          <t>8434.2</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>13064.54</v>
+        <v>12897.76</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>1257</t>
+          <t>-915</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-474.2046933879615</t>
+          <t>-460.0299369776392</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-481.8092021186876</t>
+          <t>-382.0687767208665</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>2852.0</t>
+          <t>8291.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-6.13</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2037,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,12 +2047,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.19</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>31.42</t>
+          <t>31.88</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>2371</t>
+          <t>2326</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>54.3</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2163,7 +2139,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【d1】;【d2】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2173,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>43.16</t>
+          <t>15.25</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-12.46</t>
+          <t>-12.29</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,74 +2280,66 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>92</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>62.32</t>
+          <t>65.22</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>78.74</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>-1.07</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
+          <t>73.91</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>-0.99</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.35</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-6.98</t>
+          <t>-6.88</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>52.56</t>
+          <t>52.62</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>52.56</v>
+        <v>52.44</v>
       </c>
       <c r="AN5" t="n">
-        <v>56.5</v>
+        <v>56.31</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>57.33</t>
+          <t>57.32</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>19.82</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>-1.28</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>-1.59</t>
-        </is>
+          <t>20.79</t>
+        </is>
+      </c>
+      <c r="AQ5" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>-1.51</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2380,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-121.80</t>
+          <t>-120.72</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>89613.93404255318</t>
+          <t>89497.1940509915</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>4133.0</t>
+          <t>2852.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>12338</v>
+        <v>9501.200000000001</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>8618.6</t>
+          <t>8244.2</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>13299.38</v>
+        <v>13064.54</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>3719</t>
+          <t>1257</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-472.8220554369204</t>
+          <t>-474.2046933879615</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-24.33805261133421</t>
+          <t>-481.8092021186876</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>4133.0</t>
+          <t>2852.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-6.31</t>
+          <t>-6.13</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,12 +2459,12 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2506,7 +2474,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.19</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>31.42</t>
+          <t>31.88</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>2371</t>
+          <t>2326</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2591,11 +2559,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>【d】</t>
-        </is>
-      </c>
+      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
           <t>3444</t>
@@ -2603,12 +2567,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>167.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2582,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2592,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>36.29</t>
+          <t>43.16</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2667,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-10.61</t>
+          <t>-12.46</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2677,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,74 +2698,66 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>92</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>94.2</t>
+          <t>62.32</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>91.3</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>-1.16</t>
-        </is>
+          <t>78.74</t>
+        </is>
+      </c>
+      <c r="AH6" t="n">
+        <v>-1.07</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-6.89</t>
+          <t>-6.98</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>52.16</t>
+          <t>52.56</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>52.77</v>
+        <v>52.56</v>
       </c>
       <c r="AN6" t="n">
-        <v>56.68</v>
+        <v>56.5</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>57.34</t>
+          <t>57.33</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>19.38</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>-1.35</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>-1.67</t>
-        </is>
+          <t>19.82</t>
+        </is>
+      </c>
+      <c r="AQ6" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>-1.59</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2810,7 +2766,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-122.88</t>
+          <t>-121.80</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2776,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>89613.93404255318</t>
+          <t>89497.1940509915</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>8755.0</t>
+          <t>4133.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>11976</v>
+        <v>12338</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>8787.0</t>
+          <t>8618.6</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>13401.56</v>
+        <v>13299.38</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>3719</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-554.3646014052089</t>
+          <t>-472.8220554369204</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>492.8113771352873</t>
+          <t>-24.33805261133421</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>8755.0</t>
+          <t>4133.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2832,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-6.31</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,22 +2877,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2902,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.19</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2917,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>31.42</t>
+          <t>31.88</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>2371</t>
+          <t>2326</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2942,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3021,11 +2977,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>【d】</t>
-        </is>
-      </c>
+      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
           <t>3444</t>
@@ -3033,12 +2985,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>255.0</t>
+          <t>167.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3000,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3010,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-2.71</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>26.75</t>
+          <t>36.29</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3085,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-11.45</t>
+          <t>-10.61</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3095,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>9.19</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,74 +3116,66 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>92</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>79.71</t>
+          <t>94.2</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>73.88</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>2.12</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>-2.63</t>
-        </is>
+          <t>91.3</t>
+        </is>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>-1.16</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-6.92</t>
+          <t>-6.89</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>51.51000000000001</t>
+          <t>52.16</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>52.9</v>
+        <v>52.77</v>
       </c>
       <c r="AN7" t="n">
-        <v>56.83</v>
+        <v>56.68</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>57.32</t>
+          <t>57.34</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>12.69</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>-1.53</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>-1.75</t>
-        </is>
+          <t>19.38</t>
+        </is>
+      </c>
+      <c r="AQ7" t="n">
+        <v>-1.35</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>-1.67</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3240,7 +3184,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-123.99</t>
+          <t>-122.88</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3194,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>89613.93404255318</t>
+          <t>89497.1940509915</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>13564.0</t>
+          <t>8755.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>10932</v>
+        <v>11976</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>8624.8</t>
+          <t>8787.0</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>13461.08</v>
+        <v>13401.56</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>2307</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-744.7602338671172</t>
+          <t>-554.3646014052089</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>718.7815847327729</t>
+          <t>492.8113771352873</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>13564.0</t>
+          <t>8755.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3250,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-5.23</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,22 +3295,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3320,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.19</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3335,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>31.42</t>
+          <t>31.88</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>2371</t>
+          <t>2326</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3360,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3451,11 +3395,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>【d】</t>
-        </is>
-      </c>
+      <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
           <t>3444</t>
@@ -3463,12 +3403,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>345.0</t>
+          <t>255.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3418,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3428,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>26.75</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3503,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-10.27</t>
+          <t>-11.45</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3513,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12.43</t>
+          <t>9.19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,33 +3534,29 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>92</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>79.71</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>48.39</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>4.08</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>-3.52</t>
-        </is>
+          <t>73.88</t>
+        </is>
+      </c>
+      <c r="AH8" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>-2.63</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -3629,19 +3565,19 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>51.21</t>
+          <t>51.51000000000001</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>53.08</v>
+        <v>52.9</v>
       </c>
       <c r="AN8" t="n">
-        <v>57.02</v>
+        <v>56.83</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3650,18 +3586,14 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>6.54</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>-1.69</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>-1.81</t>
-        </is>
+          <t>12.69</t>
+        </is>
+      </c>
+      <c r="AQ8" t="n">
+        <v>-1.53</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>-1.75</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3670,7 +3602,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-124.75</t>
+          <t>-123.99</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3612,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>89613.93404255318</t>
+          <t>89497.1940509915</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>18202.0</t>
+          <t>13564.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>9349.4</v>
+        <v>10932</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>7989.3</t>
+          <t>8624.8</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>13460.24</v>
+        <v>13461.08</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>2307</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-1010.858746339825</t>
+          <t>-744.7602338671172</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>500.6753961315808</t>
+          <t>718.7815847327729</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>18202.0</t>
+          <t>13564.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3668,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-5.23</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3713,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3738,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.19</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3753,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>31.42</t>
+          <t>31.88</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>2371</t>
+          <t>2326</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3778,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
+          <t>53.6</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
+          <t>54.1</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
           <t>52.6</t>
         </is>
       </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>53.5</t>
-        </is>
-      </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>52.0</t>
-        </is>
-      </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3881,11 +3813,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>【e】</t>
-        </is>
-      </c>
+      <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
           <t>3444</t>
@@ -3893,12 +3821,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>334.0</t>
+          <t>345.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3836,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3846,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>17.02</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3921,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-12.79</t>
+          <t>-10.27</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +3931,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12.03</t>
+          <t>12.43</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,74 +3952,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>92</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>41.94</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>15.05</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>-4.80</t>
-        </is>
+          <t>48.39</t>
+        </is>
+      </c>
+      <c r="AH9" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>-3.52</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-6.85</t>
+          <t>-6.92</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>50.71</t>
+          <t>51.21</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>53.27</v>
+        <v>53.08</v>
       </c>
       <c r="AN9" t="n">
-        <v>57.18</v>
+        <v>57.02</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>57.29</t>
+          <t>57.32</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-5.61</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>-1.94</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>-1.84</t>
-        </is>
+          <t>6.54</t>
+        </is>
+      </c>
+      <c r="AQ9" t="n">
+        <v>-1.69</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>-1.81</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4100,7 +4020,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-125.16</t>
+          <t>-124.75</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4030,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>89613.93404255318</t>
+          <t>89497.1940509915</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>17036.0</t>
+          <t>18202.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>6987.2</v>
+        <v>9349.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>6636.3</t>
+          <t>7989.3</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>14299.4</v>
+        <v>13460.24</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-1285.68313588008</t>
+          <t>-1010.858746339825</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-325.7147088748216</t>
+          <t>500.6753961315808</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>17036.0</t>
+          <t>18202.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4086,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-6.67</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,22 +4131,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4156,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.19</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4171,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>31.42</t>
+          <t>31.88</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>2371</t>
+          <t>2326</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4196,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4243,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>334.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4258,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4268,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-18.65</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4343,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-15.82</t>
+          <t>-12.79</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4353,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>12.03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,74 +4374,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>92</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>41.94</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>6.77</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>-0.85</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>-5.82</t>
-        </is>
+          <t>15.05</t>
+        </is>
+      </c>
+      <c r="AH10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>-4.8</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-6.81</t>
+          <t>-6.85</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>50.42999999999999</t>
+          <t>50.71</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>53.55</v>
+        <v>53.27</v>
       </c>
       <c r="AN10" t="n">
-        <v>57.46</v>
+        <v>57.18</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>57.28</t>
+          <t>57.29</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-14.78</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>-2.08</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>-1.81</t>
-        </is>
+          <t>-5.61</t>
+        </is>
+      </c>
+      <c r="AQ10" t="n">
+        <v>-1.94</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>-1.84</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4530,7 +4442,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-124.80</t>
+          <t>-125.16</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4452,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>89613.93404255318</t>
+          <t>89497.1940509915</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>2323.0</t>
+          <t>17036.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>4899.2</v>
+        <v>6987.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>6022.3</t>
+          <t>6636.3</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>15417.3</v>
+        <v>14299.4</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-1123</t>
+          <t>350</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-1460.222849881036</t>
+          <t>-1285.68313588008</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-1369.710762138438</t>
+          <t>-325.7147088748216</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>2323.0</t>
+          <t>17036.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4508,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-9.91</t>
+          <t>-6.67</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4553,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4563,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4578,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.19</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4593,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>31.42</t>
+          <t>31.88</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>2371</t>
+          <t>2326</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4618,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>49.85</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4665,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4680,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>49.85</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4690,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5.41</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-13.32</t>
+          <t>-18.65</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4765,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-16.08</t>
+          <t>-15.82</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4775,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,74 +4796,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>92</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>8.94</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>-1.73</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>-5.95</t>
-        </is>
+          <t>6.77</t>
+        </is>
+      </c>
+      <c r="AH11" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>-5.82</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-6.51</t>
+          <t>-6.81</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>50.73</t>
+          <t>50.42999999999999</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>53.94</v>
+        <v>53.55</v>
       </c>
       <c r="AN11" t="n">
-        <v>57.69</v>
+        <v>57.46</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>57.29</t>
+          <t>57.28</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-17.10</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>-2.04</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>-1.74</t>
-        </is>
+          <t>-14.78</t>
+        </is>
+      </c>
+      <c r="AQ11" t="n">
+        <v>-2.08</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>-1.81</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4960,7 +4864,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-123.89</t>
+          <t>-124.80</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4874,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>89613.93404255318</t>
+          <t>89497.1940509915</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>3535.0</t>
+          <t>2323.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>5598</v>
+        <v>4899.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>6458.6</t>
+          <t>6022.3</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>15662.04</v>
+        <v>15417.3</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-860</t>
+          <t>-1123</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-1476.679593106963</t>
+          <t>-1460.222849881036</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-1235.822596724375</t>
+          <t>-1369.710762138438</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>3535.0</t>
+          <t>2323.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +4930,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-10.18</t>
+          <t>-9.91</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +4975,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5086,7 +4990,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5000,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.19</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5015,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>31.42</t>
+          <t>31.88</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>2371</t>
+          <t>2326</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5040,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>49.85</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>49.85</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5087,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>111.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5102,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>49.85</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5112,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-14.34</t>
+          <t>-13.32</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5187,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-13.97</t>
+          <t>-16.08</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5197,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,17 +5218,17 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>92</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>17.07</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -5332,56 +5236,48 @@
           <t>8.94</t>
         </is>
       </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>-0.31</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>-5.65</t>
-        </is>
+      <c r="AH12" t="n">
+        <v>-1.73</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>-5.95</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-6.17</t>
+          <t>-6.51</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>51.26000000000001</t>
+          <t>50.73</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>54.33</v>
+        <v>53.94</v>
       </c>
       <c r="AN12" t="n">
-        <v>57.9</v>
+        <v>57.69</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>57.32</t>
+          <t>57.29</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-16.87</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>-1.95</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>-1.67</t>
-        </is>
+          <t>-17.10</t>
+        </is>
+      </c>
+      <c r="AQ12" t="n">
+        <v>-2.04</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>-1.74</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5390,7 +5286,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-122.87</t>
+          <t>-123.89</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5296,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>89613.93404255318</t>
+          <t>89497.1940509915</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>5651.0</t>
+          <t>3535.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>6317.6</v>
+        <v>5598</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>7375.3</t>
+          <t>6458.6</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>15916.1</v>
+        <v>15662.04</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-1057</t>
+          <t>-860</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-1520.471774267434</t>
+          <t>-1476.679593106963</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-1130.274410535557</t>
+          <t>-1235.822596724375</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>5651.0</t>
+          <t>3535.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5352,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-7.93</t>
+          <t>-10.18</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5397,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5407,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5422,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.19</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5437,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>31.42</t>
+          <t>31.88</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>2371</t>
+          <t>2326</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5462,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>49.85</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/印刷材料.xlsx
+++ b/Result/checksun_type/印刷材料.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-43.86</t>
+          <t>-42.21</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-12.96</t>
+          <t>-10.94</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,61 +1019,61 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>112</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>56.74</t>
+          <t>52.27</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>-1.11</v>
+        <v>0.84</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.1</v>
+        <v>0.53</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-6.39</t>
+          <t>-6.24</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.71</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>52.27999999999999</t>
+          <t>52.46</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>52.23</v>
+        <v>52.18</v>
       </c>
       <c r="AN2" t="n">
-        <v>55.8</v>
+        <v>55.66</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>57.35</t>
+          <t>57.36</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>29.22</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.83</v>
       </c>
       <c r="AR2" t="n">
-        <v>-1.25</v>
+        <v>-1.17</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-117.14</t>
+          <t>-115.98</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>89497.1940509915</t>
+          <t>89382.98231966054</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>4797.0</t>
+          <t>5833.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>4673.8</v>
+        <v>5013.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>8324.9</t>
+          <t>8675.9</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>12556.78</v>
+        <v>12426.06</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-3651</t>
+          <t>-3662</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-533.6188939337103</t>
+          <t>-561.0546141659527</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-754.4941534987138</t>
+          <t>-711.9510754432858</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>4797.0</t>
+          <t>5833.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-6.85</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>21.19</t>
+          <t>21.68</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>31.88</t>
+          <t>32.42</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>2326</t>
+          <t>2380</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1288,14 +1288,14 @@
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-33.34</t>
+          <t>-43.86</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-11.28</t>
+          <t>-12.96</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1441,61 +1441,61 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>112</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>81.82</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>78.48</t>
+          <t>56.74</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>0.27</v>
+        <v>-1.11</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.45</v>
+        <v>0.1</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-6.53</t>
+          <t>-6.39</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-2.71</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>52.56</t>
+          <t>52.27999999999999</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>52.32</v>
+        <v>52.23</v>
       </c>
       <c r="AN3" t="n">
-        <v>55.98</v>
+        <v>55.8</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>57.34</t>
+          <t>57.35</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>28.11</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.96</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AR3" t="n">
-        <v>-1.33</v>
+        <v>-1.25</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-118.20</t>
+          <t>-117.14</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>89497.1940509915</t>
+          <t>89382.98231966054</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>3296.0</t>
+          <t>4797.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>5465.4</v>
+        <v>4673.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>8198.7</t>
+          <t>8324.9</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>12704.54</v>
+        <v>12556.78</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-2733</t>
+          <t>-3651</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-493.4597558309824</t>
+          <t>-533.6188939337103</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-677.32375952437</t>
+          <t>-754.4941534987138</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>3296.0</t>
+          <t>4797.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-5.05</t>
+          <t>-6.85</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1625,12 +1625,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>21.19</t>
+          <t>21.68</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>31.88</t>
+          <t>32.42</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>2326</t>
+          <t>2380</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1710,14 +1710,14 @@
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>156.0</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-10.85</t>
+          <t>-33.34</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-10.94</t>
+          <t>-11.28</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1863,61 +1863,61 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>112</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>88.41</t>
+          <t>81.82</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>71.98</t>
+          <t>78.48</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.27</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.29</v>
+        <v>0.45</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-6.68</t>
+          <t>-6.53</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>52.54</t>
+          <t>52.56</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>52.39</v>
+        <v>52.32</v>
       </c>
       <c r="AN4" t="n">
-        <v>56.14</v>
+        <v>55.98</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>57.32</t>
+          <t>57.34</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>25.48</t>
+          <t>28.11</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>-1.06</v>
+        <v>-0.96</v>
       </c>
       <c r="AR4" t="n">
-        <v>-1.42</v>
+        <v>-1.33</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-119.48</t>
+          <t>-118.20</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>89497.1940509915</t>
+          <t>89382.98231966054</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>8291.0</t>
+          <t>3296.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>7519</v>
+        <v>5465.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>8434.2</t>
+          <t>8198.7</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>12897.76</v>
+        <v>12704.54</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-915</t>
+          <t>-2733</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-460.0299369776392</t>
+          <t>-493.4597558309824</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-382.0687767208665</t>
+          <t>-677.32375952437</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>8291.0</t>
+          <t>3296.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-5.05</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>21.19</t>
+          <t>21.68</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>31.88</t>
+          <t>32.42</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>2326</t>
+          <t>2380</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>54.3</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2132,14 +2132,14 @@
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>156.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>15.25</t>
+          <t>-10.85</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-12.29</t>
+          <t>-10.94</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2285,45 +2285,45 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>112</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>65.22</t>
+          <t>88.41</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>73.91</t>
+          <t>71.98</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>-0.99</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.35</v>
+        <v>0.29</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-6.88</t>
+          <t>-6.68</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>52.62</t>
+          <t>52.54</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>52.44</v>
+        <v>52.39</v>
       </c>
       <c r="AN5" t="n">
-        <v>56.31</v>
+        <v>56.14</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2332,14 +2332,14 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>20.79</t>
+          <t>25.48</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>-1.2</v>
+        <v>-1.06</v>
       </c>
       <c r="AR5" t="n">
-        <v>-1.51</v>
+        <v>-1.42</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-120.72</t>
+          <t>-119.48</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>89497.1940509915</t>
+          <t>89382.98231966054</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>2852.0</t>
+          <t>8291.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>9501.200000000001</v>
+        <v>7519</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>8244.2</t>
+          <t>8434.2</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>13064.54</v>
+        <v>12897.76</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>1257</t>
+          <t>-915</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-474.2046933879615</t>
+          <t>-460.0299369776392</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-481.8092021186876</t>
+          <t>-382.0687767208665</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>2852.0</t>
+          <t>8291.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-6.13</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>21.19</t>
+          <t>21.68</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>31.88</t>
+          <t>32.42</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>2326</t>
+          <t>2380</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>54.3</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2554,12 +2554,16 @@
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>【d1】</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>3444</t>
@@ -2567,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2582,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2592,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>43.16</t>
+          <t>15.25</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2667,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-12.46</t>
+          <t>-12.29</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2677,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2703,61 +2707,61 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>112</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>62.32</t>
+          <t>65.22</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>78.74</t>
+          <t>73.91</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>-1.07</v>
+        <v>-0.99</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-6.98</t>
+          <t>-6.88</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>52.56</t>
+          <t>52.62</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>52.56</v>
+        <v>52.44</v>
       </c>
       <c r="AN6" t="n">
-        <v>56.5</v>
+        <v>56.31</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>57.33</t>
+          <t>57.32</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>19.82</t>
+          <t>20.79</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>-1.28</v>
+        <v>-1.2</v>
       </c>
       <c r="AR6" t="n">
-        <v>-1.59</v>
+        <v>-1.51</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2766,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-121.80</t>
+          <t>-120.72</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2776,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>89497.1940509915</t>
+          <t>89382.98231966054</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>4133.0</t>
+          <t>2852.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>12338</v>
+        <v>9501.200000000001</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>8618.6</t>
+          <t>8244.2</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>13299.38</v>
+        <v>13064.54</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>3719</t>
+          <t>1257</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-472.8220554369204</t>
+          <t>-474.2046933879615</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-24.33805261133421</t>
+          <t>-481.8092021186876</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>4133.0</t>
+          <t>2852.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2832,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-6.31</t>
+          <t>-6.13</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2877,12 +2881,12 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2892,7 +2896,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2902,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>21.19</t>
+          <t>21.68</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2917,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>31.88</t>
+          <t>32.42</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>2326</t>
+          <t>2380</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2942,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2972,12 +2976,16 @@
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>【d1】</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>3444</t>
@@ -2985,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>167.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3000,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3010,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-2.71</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>36.29</t>
+          <t>43.16</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3085,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-10.61</t>
+          <t>-12.46</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3095,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3121,61 +3129,61 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>112</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>94.2</t>
+          <t>62.32</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>78.74</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>1.8</v>
+        <v>-1.07</v>
       </c>
       <c r="AI7" t="n">
-        <v>-1.16</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-6.89</t>
+          <t>-6.98</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>52.16</t>
+          <t>52.56</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>52.77</v>
+        <v>52.56</v>
       </c>
       <c r="AN7" t="n">
-        <v>56.68</v>
+        <v>56.5</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>57.34</t>
+          <t>57.33</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>19.38</t>
+          <t>19.82</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>-1.35</v>
+        <v>-1.28</v>
       </c>
       <c r="AR7" t="n">
-        <v>-1.67</v>
+        <v>-1.59</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3184,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-122.88</t>
+          <t>-121.80</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3194,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>89497.1940509915</t>
+          <t>89382.98231966054</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>8755.0</t>
+          <t>4133.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>11976</v>
+        <v>12338</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>8787.0</t>
+          <t>8618.6</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>13401.56</v>
+        <v>13299.38</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>3719</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-554.3646014052089</t>
+          <t>-472.8220554369204</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>492.8113771352873</t>
+          <t>-24.33805261133421</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>8755.0</t>
+          <t>4133.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3250,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-6.31</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3295,22 +3303,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3320,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>21.19</t>
+          <t>21.68</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3335,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>31.88</t>
+          <t>32.42</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>2326</t>
+          <t>2380</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3360,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3390,12 +3398,16 @@
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>3444</t>
@@ -3403,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>255.0</t>
+          <t>167.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3418,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3428,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>26.75</t>
+          <t>36.29</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3503,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-11.45</t>
+          <t>-10.61</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3513,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>9.19</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3539,61 +3551,61 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>112</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>79.71</t>
+          <t>94.2</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>73.88</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>2.12</v>
+        <v>1.8</v>
       </c>
       <c r="AI8" t="n">
-        <v>-2.63</v>
+        <v>-1.16</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-6.92</t>
+          <t>-6.89</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>51.51000000000001</t>
+          <t>52.16</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>52.9</v>
+        <v>52.77</v>
       </c>
       <c r="AN8" t="n">
-        <v>56.83</v>
+        <v>56.68</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>57.32</t>
+          <t>57.34</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>19.38</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>-1.53</v>
+        <v>-1.35</v>
       </c>
       <c r="AR8" t="n">
-        <v>-1.75</v>
+        <v>-1.67</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3602,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-123.99</t>
+          <t>-122.88</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3612,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>89497.1940509915</t>
+          <t>89382.98231966054</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>13564.0</t>
+          <t>8755.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>10932</v>
+        <v>11976</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>8624.8</t>
+          <t>8787.0</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>13461.08</v>
+        <v>13401.56</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>2307</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-744.7602338671172</t>
+          <t>-554.3646014052089</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>718.7815847327729</t>
+          <t>492.8113771352873</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>13564.0</t>
+          <t>8755.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3668,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-5.23</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3713,22 +3725,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3738,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>21.19</t>
+          <t>21.68</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3753,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>31.88</t>
+          <t>32.42</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>2326</t>
+          <t>2380</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3778,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3808,12 +3820,16 @@
       </c>
       <c r="CJ8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>3444</t>
@@ -3821,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>345.0</t>
+          <t>255.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3836,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3846,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>26.75</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3921,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-10.27</t>
+          <t>-11.45</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3931,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12.43</t>
+          <t>9.19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3957,24 +3973,24 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>112</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>79.71</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>48.39</t>
+          <t>73.88</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>4.08</v>
+        <v>2.12</v>
       </c>
       <c r="AI9" t="n">
-        <v>-3.52</v>
+        <v>-2.63</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -3983,19 +3999,19 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>51.21</t>
+          <t>51.51000000000001</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>53.08</v>
+        <v>52.9</v>
       </c>
       <c r="AN9" t="n">
-        <v>57.02</v>
+        <v>56.83</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4004,14 +4020,14 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>6.54</t>
+          <t>12.69</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>-1.69</v>
+        <v>-1.53</v>
       </c>
       <c r="AR9" t="n">
-        <v>-1.81</v>
+        <v>-1.75</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4020,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-124.75</t>
+          <t>-123.99</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4030,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>89497.1940509915</t>
+          <t>89382.98231966054</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>18202.0</t>
+          <t>13564.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>9349.4</v>
+        <v>10932</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>7989.3</t>
+          <t>8624.8</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>13460.24</v>
+        <v>13461.08</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>2307</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-1010.858746339825</t>
+          <t>-744.7602338671172</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>500.6753961315808</t>
+          <t>718.7815847327729</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>18202.0</t>
+          <t>13564.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4086,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-5.23</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4131,22 +4147,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4156,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>21.19</t>
+          <t>21.68</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4171,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>31.88</t>
+          <t>32.42</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>2326</t>
+          <t>2380</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4196,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
+          <t>53.6</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>54.1</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
           <t>52.6</t>
         </is>
       </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>53.5</t>
-        </is>
-      </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>52.0</t>
-        </is>
-      </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4226,14 +4242,14 @@
       </c>
       <c r="CJ9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4243,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>334.0</t>
+          <t>345.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4258,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4268,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>17.02</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4343,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-12.79</t>
+          <t>-10.27</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4353,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12.03</t>
+          <t>12.43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4379,61 +4395,61 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>112</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>41.94</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>15.05</t>
+          <t>48.39</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>2.15</v>
+        <v>4.08</v>
       </c>
       <c r="AI10" t="n">
-        <v>-4.8</v>
+        <v>-3.52</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-6.85</t>
+          <t>-6.92</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>50.71</t>
+          <t>51.21</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>53.27</v>
+        <v>53.08</v>
       </c>
       <c r="AN10" t="n">
-        <v>57.18</v>
+        <v>57.02</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>57.29</t>
+          <t>57.32</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-5.61</t>
+          <t>6.54</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-1.94</v>
+        <v>-1.69</v>
       </c>
       <c r="AR10" t="n">
-        <v>-1.84</v>
+        <v>-1.81</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4442,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-125.16</t>
+          <t>-124.75</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4452,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>89497.1940509915</t>
+          <t>89382.98231966054</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>17036.0</t>
+          <t>18202.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>6987.2</v>
+        <v>9349.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>6636.3</t>
+          <t>7989.3</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>14299.4</v>
+        <v>13460.24</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-1285.68313588008</t>
+          <t>-1010.858746339825</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-325.7147088748216</t>
+          <t>500.6753961315808</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>17036.0</t>
+          <t>18202.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4508,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-6.67</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4553,22 +4569,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4578,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>21.19</t>
+          <t>21.68</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4593,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>31.88</t>
+          <t>32.42</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>2326</t>
+          <t>2380</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4618,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4648,7 +4664,7 @@
       </c>
       <c r="CJ10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -4665,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>334.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4680,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4690,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-18.65</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4765,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-15.82</t>
+          <t>-12.79</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4775,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>12.03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4801,61 +4817,61 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>112</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>41.94</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>6.77</t>
+          <t>15.05</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>-0.85</v>
+        <v>2.15</v>
       </c>
       <c r="AI11" t="n">
-        <v>-5.82</v>
+        <v>-4.8</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-6.81</t>
+          <t>-6.85</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>50.42999999999999</t>
+          <t>50.71</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>53.55</v>
+        <v>53.27</v>
       </c>
       <c r="AN11" t="n">
-        <v>57.46</v>
+        <v>57.18</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>57.28</t>
+          <t>57.29</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-14.78</t>
+          <t>-5.61</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-2.08</v>
+        <v>-1.94</v>
       </c>
       <c r="AR11" t="n">
-        <v>-1.81</v>
+        <v>-1.84</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4864,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-124.80</t>
+          <t>-125.16</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4874,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>89497.1940509915</t>
+          <t>89382.98231966054</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>2323.0</t>
+          <t>17036.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>4899.2</v>
+        <v>6987.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>6022.3</t>
+          <t>6636.3</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>15417.3</v>
+        <v>14299.4</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-1123</t>
+          <t>350</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-1460.222849881036</t>
+          <t>-1285.68313588008</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-1369.710762138438</t>
+          <t>-325.7147088748216</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>2323.0</t>
+          <t>17036.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4930,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-9.91</t>
+          <t>-6.67</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4975,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -4985,12 +5001,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5000,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>21.19</t>
+          <t>21.68</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5015,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>31.88</t>
+          <t>32.42</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>2326</t>
+          <t>2380</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5040,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>49.85</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5070,7 +5086,7 @@
       </c>
       <c r="CJ11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -5087,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5102,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>49.85</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5112,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>5.48</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-13.32</t>
+          <t>-18.65</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5187,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-16.08</t>
+          <t>-15.82</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5197,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5223,61 +5239,61 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>112</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>8.94</t>
+          <t>6.77</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>-1.73</v>
+        <v>-0.85</v>
       </c>
       <c r="AI12" t="n">
-        <v>-5.95</v>
+        <v>-5.82</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-6.51</t>
+          <t>-6.81</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>50.73</t>
+          <t>50.42999999999999</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>53.94</v>
+        <v>53.55</v>
       </c>
       <c r="AN12" t="n">
-        <v>57.69</v>
+        <v>57.46</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>57.29</t>
+          <t>57.28</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-17.10</t>
+          <t>-14.78</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-2.04</v>
+        <v>-2.08</v>
       </c>
       <c r="AR12" t="n">
-        <v>-1.74</v>
+        <v>-1.81</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5286,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-123.89</t>
+          <t>-124.80</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5296,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>89497.1940509915</t>
+          <t>89382.98231966054</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>3535.0</t>
+          <t>2323.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>5598</v>
+        <v>4899.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>6458.6</t>
+          <t>6022.3</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>15662.04</v>
+        <v>15417.3</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-860</t>
+          <t>-1123</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-1476.679593106963</t>
+          <t>-1460.222849881036</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-1235.822596724375</t>
+          <t>-1369.710762138438</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>3535.0</t>
+          <t>2323.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5352,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-10.18</t>
+          <t>-9.91</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5397,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5412,7 +5428,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5422,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>21.19</t>
+          <t>21.68</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5437,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>31.88</t>
+          <t>32.42</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>2326</t>
+          <t>2380</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5462,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>49.85</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>49.85</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5492,7 +5508,7 @@
       </c>
       <c r="CJ12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>

--- a/Result/checksun_type/印刷材料.xlsx
+++ b/Result/checksun_type/印刷材料.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-42.21</t>
+          <t>-30.07</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-10.94</t>
+          <t>-10.44</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,61 +1019,61 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>52.27</t>
+          <t>58.33</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>0.84</v>
+        <v>0.99</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.53</v>
+        <v>1</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-6.24</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>52.46</t>
+          <t>52.67999999999999</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>52.18</v>
+        <v>52.16</v>
       </c>
       <c r="AN2" t="n">
-        <v>55.66</v>
+        <v>55.52</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>57.36</t>
+          <t>57.37</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>29.22</t>
+          <t>34.70</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>-0.83</v>
+        <v>-0.7</v>
       </c>
       <c r="AR2" t="n">
-        <v>-1.17</v>
+        <v>-1.07</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-115.98</t>
+          <t>-114.70</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>89382.98231966054</t>
+          <t>89263.77754237289</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>5833.0</t>
+          <t>3324.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>5013.8</v>
+        <v>5108.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>8675.9</t>
+          <t>7304.7</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>12426.06</v>
+        <v>12325.42</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-3662</t>
+          <t>-2196</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-561.0546141659527</t>
+          <t>-605.8996187432529</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-711.9510754432858</t>
+          <t>-852.5471439184039</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>5833.0</t>
+          <t>3324.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>21.68</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>32.42</t>
+          <t>32.44</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>2380</t>
+          <t>2394</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-43.86</t>
+          <t>-42.21</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-12.96</t>
+          <t>-10.94</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1441,61 +1441,61 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>56.74</t>
+          <t>52.27</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>-1.11</v>
+        <v>0.84</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.1</v>
+        <v>0.53</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-6.39</t>
+          <t>-6.24</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.71</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>52.27999999999999</t>
+          <t>52.46</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>52.23</v>
+        <v>52.18</v>
       </c>
       <c r="AN3" t="n">
-        <v>55.8</v>
+        <v>55.66</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>57.35</t>
+          <t>57.36</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>29.22</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.83</v>
       </c>
       <c r="AR3" t="n">
-        <v>-1.25</v>
+        <v>-1.17</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-117.14</t>
+          <t>-115.98</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>89382.98231966054</t>
+          <t>89263.77754237289</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>4797.0</t>
+          <t>5833.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>4673.8</v>
+        <v>5013.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>8324.9</t>
+          <t>8675.9</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>12556.78</v>
+        <v>12426.06</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-3651</t>
+          <t>-3662</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-533.6188939337103</t>
+          <t>-561.0546141659527</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-754.4941534987138</t>
+          <t>-711.9510754432858</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>4797.0</t>
+          <t>5833.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-6.85</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1625,12 +1625,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>21.68</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>32.42</t>
+          <t>32.44</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>2380</t>
+          <t>2394</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-33.34</t>
+          <t>-43.86</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-11.28</t>
+          <t>-12.96</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1863,61 +1863,61 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>81.82</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>78.48</t>
+          <t>56.74</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>0.27</v>
+        <v>-1.11</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.45</v>
+        <v>0.1</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-6.53</t>
+          <t>-6.39</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-2.71</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>52.56</t>
+          <t>52.27999999999999</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>52.32</v>
+        <v>52.23</v>
       </c>
       <c r="AN4" t="n">
-        <v>55.98</v>
+        <v>55.8</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>57.34</t>
+          <t>57.35</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>28.11</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>-0.96</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AR4" t="n">
-        <v>-1.33</v>
+        <v>-1.25</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-118.20</t>
+          <t>-117.14</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>89382.98231966054</t>
+          <t>89263.77754237289</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>3296.0</t>
+          <t>4797.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>5465.4</v>
+        <v>4673.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>8198.7</t>
+          <t>8324.9</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>12704.54</v>
+        <v>12556.78</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-2733</t>
+          <t>-3651</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-493.4597558309824</t>
+          <t>-533.6188939337103</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-677.32375952437</t>
+          <t>-754.4941534987138</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>3296.0</t>
+          <t>4797.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-5.05</t>
+          <t>-6.85</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>21.68</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>32.42</t>
+          <t>32.44</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>2380</t>
+          <t>2394</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>156.0</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-10.85</t>
+          <t>-33.34</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-10.94</t>
+          <t>-11.28</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2285,61 +2285,61 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>88.41</t>
+          <t>81.82</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>71.98</t>
+          <t>78.48</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.27</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.29</v>
+        <v>0.45</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-6.68</t>
+          <t>-6.53</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>52.54</t>
+          <t>52.56</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>52.39</v>
+        <v>52.32</v>
       </c>
       <c r="AN5" t="n">
-        <v>56.14</v>
+        <v>55.98</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>57.32</t>
+          <t>57.34</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>25.48</t>
+          <t>28.11</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>-1.06</v>
+        <v>-0.96</v>
       </c>
       <c r="AR5" t="n">
-        <v>-1.42</v>
+        <v>-1.33</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-119.48</t>
+          <t>-118.20</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>89382.98231966054</t>
+          <t>89263.77754237289</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>8291.0</t>
+          <t>3296.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>7519</v>
+        <v>5465.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>8434.2</t>
+          <t>8198.7</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>12897.76</v>
+        <v>12704.54</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-915</t>
+          <t>-2733</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-460.0299369776392</t>
+          <t>-493.4597558309824</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-382.0687767208665</t>
+          <t>-677.32375952437</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>8291.0</t>
+          <t>3296.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-5.05</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>21.68</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>32.42</t>
+          <t>32.44</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>2380</t>
+          <t>2394</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>54.3</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>156.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>15.25</t>
+          <t>-10.85</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-12.29</t>
+          <t>-10.94</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2707,45 +2707,45 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>65.22</t>
+          <t>88.41</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>73.91</t>
+          <t>71.98</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>-0.99</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.35</v>
+        <v>0.29</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-6.88</t>
+          <t>-6.68</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>52.62</t>
+          <t>52.54</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>52.44</v>
+        <v>52.39</v>
       </c>
       <c r="AN6" t="n">
-        <v>56.31</v>
+        <v>56.14</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2754,14 +2754,14 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>20.79</t>
+          <t>25.48</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>-1.2</v>
+        <v>-1.06</v>
       </c>
       <c r="AR6" t="n">
-        <v>-1.51</v>
+        <v>-1.42</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-120.72</t>
+          <t>-119.48</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>89382.98231966054</t>
+          <t>89263.77754237289</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>2852.0</t>
+          <t>8291.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>9501.200000000001</v>
+        <v>7519</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>8244.2</t>
+          <t>8434.2</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>13064.54</v>
+        <v>12897.76</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>1257</t>
+          <t>-915</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-474.2046933879615</t>
+          <t>-460.0299369776392</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-481.8092021186876</t>
+          <t>-382.0687767208665</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>2852.0</t>
+          <t>8291.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-6.13</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2891,12 +2891,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>21.68</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>32.42</t>
+          <t>32.44</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>2380</t>
+          <t>2394</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>54.3</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.16</t>
+          <t>15.25</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-12.46</t>
+          <t>-12.29</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3129,61 +3129,61 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>62.32</t>
+          <t>65.22</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>78.74</t>
+          <t>73.91</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>-1.07</v>
+        <v>-0.99</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-6.98</t>
+          <t>-6.88</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>52.56</t>
+          <t>52.62</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>52.56</v>
+        <v>52.44</v>
       </c>
       <c r="AN7" t="n">
-        <v>56.5</v>
+        <v>56.31</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>57.33</t>
+          <t>57.32</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>19.82</t>
+          <t>20.79</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>-1.28</v>
+        <v>-1.2</v>
       </c>
       <c r="AR7" t="n">
-        <v>-1.59</v>
+        <v>-1.51</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-121.80</t>
+          <t>-120.72</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>89382.98231966054</t>
+          <t>89263.77754237289</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>4133.0</t>
+          <t>2852.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>12338</v>
+        <v>9501.200000000001</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>8618.6</t>
+          <t>8244.2</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>13299.38</v>
+        <v>13064.54</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>3719</t>
+          <t>1257</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-472.8220554369204</t>
+          <t>-474.2046933879615</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-24.33805261133421</t>
+          <t>-481.8092021186876</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>4133.0</t>
+          <t>2852.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-6.31</t>
+          <t>-6.13</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3303,12 +3303,12 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>21.68</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>32.42</t>
+          <t>32.44</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>2380</t>
+          <t>2394</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3368,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3405,7 +3405,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>167.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>36.29</t>
+          <t>43.16</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-10.61</t>
+          <t>-12.46</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3551,61 +3551,61 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>94.2</t>
+          <t>62.32</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>78.74</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>1.8</v>
+        <v>-1.07</v>
       </c>
       <c r="AI8" t="n">
-        <v>-1.16</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-6.89</t>
+          <t>-6.98</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>52.16</t>
+          <t>52.56</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>52.77</v>
+        <v>52.56</v>
       </c>
       <c r="AN8" t="n">
-        <v>56.68</v>
+        <v>56.5</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>57.34</t>
+          <t>57.33</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>19.38</t>
+          <t>19.82</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>-1.35</v>
+        <v>-1.28</v>
       </c>
       <c r="AR8" t="n">
-        <v>-1.67</v>
+        <v>-1.59</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-122.88</t>
+          <t>-121.80</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>89382.98231966054</t>
+          <t>89263.77754237289</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>8755.0</t>
+          <t>4133.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>11976</v>
+        <v>12338</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>8787.0</t>
+          <t>8618.6</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>13401.56</v>
+        <v>13299.38</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>3719</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-554.3646014052089</t>
+          <t>-472.8220554369204</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>492.8113771352873</t>
+          <t>-24.33805261133421</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>8755.0</t>
+          <t>4133.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-6.31</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3725,22 +3725,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>21.68</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>32.42</t>
+          <t>32.44</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>2380</t>
+          <t>2394</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>255.0</t>
+          <t>167.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>26.75</t>
+          <t>36.29</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-11.45</t>
+          <t>-10.61</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>9.19</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3973,61 +3973,61 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>79.71</t>
+          <t>94.2</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>73.88</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>2.12</v>
+        <v>1.8</v>
       </c>
       <c r="AI9" t="n">
-        <v>-2.63</v>
+        <v>-1.16</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-6.92</t>
+          <t>-6.89</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>51.51000000000001</t>
+          <t>52.16</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>52.9</v>
+        <v>52.77</v>
       </c>
       <c r="AN9" t="n">
-        <v>56.83</v>
+        <v>56.68</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>57.32</t>
+          <t>57.34</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>19.38</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>-1.53</v>
+        <v>-1.35</v>
       </c>
       <c r="AR9" t="n">
-        <v>-1.75</v>
+        <v>-1.67</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-123.99</t>
+          <t>-122.88</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>89382.98231966054</t>
+          <t>89263.77754237289</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>13564.0</t>
+          <t>8755.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>10932</v>
+        <v>11976</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>8624.8</t>
+          <t>8787.0</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>13461.08</v>
+        <v>13401.56</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>2307</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-744.7602338671172</t>
+          <t>-554.3646014052089</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>718.7815847327729</t>
+          <t>492.8113771352873</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>13564.0</t>
+          <t>8755.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-5.23</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4147,22 +4147,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>21.68</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>32.42</t>
+          <t>32.44</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>2380</t>
+          <t>2394</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>345.0</t>
+          <t>255.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>26.75</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-10.27</t>
+          <t>-11.45</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12.43</t>
+          <t>9.19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4395,24 +4395,24 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>79.71</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>48.39</t>
+          <t>73.88</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>4.08</v>
+        <v>2.12</v>
       </c>
       <c r="AI10" t="n">
-        <v>-3.52</v>
+        <v>-2.63</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -4421,19 +4421,19 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>51.21</t>
+          <t>51.51000000000001</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>53.08</v>
+        <v>52.9</v>
       </c>
       <c r="AN10" t="n">
-        <v>57.02</v>
+        <v>56.83</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4442,14 +4442,14 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>6.54</t>
+          <t>12.69</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-1.69</v>
+        <v>-1.53</v>
       </c>
       <c r="AR10" t="n">
-        <v>-1.81</v>
+        <v>-1.75</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-124.75</t>
+          <t>-123.99</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>89382.98231966054</t>
+          <t>89263.77754237289</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>18202.0</t>
+          <t>13564.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>9349.4</v>
+        <v>10932</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>7989.3</t>
+          <t>8624.8</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>13460.24</v>
+        <v>13461.08</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>2307</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-1010.858746339825</t>
+          <t>-744.7602338671172</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>500.6753961315808</t>
+          <t>718.7815847327729</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>18202.0</t>
+          <t>13564.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-5.23</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>21.68</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>32.42</t>
+          <t>32.44</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>2380</t>
+          <t>2394</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
+          <t>53.6</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
+          <t>54.1</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
           <t>52.6</t>
         </is>
       </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>53.5</t>
-        </is>
-      </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>52.0</t>
-        </is>
-      </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4671,7 +4671,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>334.0</t>
+          <t>345.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>17.02</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-12.79</t>
+          <t>-10.27</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12.03</t>
+          <t>12.43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4817,61 +4817,61 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>41.94</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>15.05</t>
+          <t>48.39</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>2.15</v>
+        <v>4.08</v>
       </c>
       <c r="AI11" t="n">
-        <v>-4.8</v>
+        <v>-3.52</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-6.85</t>
+          <t>-6.92</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>50.71</t>
+          <t>51.21</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>53.27</v>
+        <v>53.08</v>
       </c>
       <c r="AN11" t="n">
-        <v>57.18</v>
+        <v>57.02</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>57.29</t>
+          <t>57.32</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-5.61</t>
+          <t>6.54</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-1.94</v>
+        <v>-1.69</v>
       </c>
       <c r="AR11" t="n">
-        <v>-1.84</v>
+        <v>-1.81</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-125.16</t>
+          <t>-124.75</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>89382.98231966054</t>
+          <t>89263.77754237289</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>17036.0</t>
+          <t>18202.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>6987.2</v>
+        <v>9349.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>6636.3</t>
+          <t>7989.3</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>14299.4</v>
+        <v>13460.24</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-1285.68313588008</t>
+          <t>-1010.858746339825</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-325.7147088748216</t>
+          <t>500.6753961315808</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>17036.0</t>
+          <t>18202.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-6.67</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>21.68</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>32.42</t>
+          <t>32.44</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>2380</t>
+          <t>2394</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>334.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-18.65</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-15.82</t>
+          <t>-12.79</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>12.03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5239,61 +5239,61 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>41.94</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>6.77</t>
+          <t>15.05</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>-0.85</v>
+        <v>2.15</v>
       </c>
       <c r="AI12" t="n">
-        <v>-5.82</v>
+        <v>-4.8</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-6.81</t>
+          <t>-6.85</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>50.42999999999999</t>
+          <t>50.71</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>53.55</v>
+        <v>53.27</v>
       </c>
       <c r="AN12" t="n">
-        <v>57.46</v>
+        <v>57.18</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>57.28</t>
+          <t>57.29</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-14.78</t>
+          <t>-5.61</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-2.08</v>
+        <v>-1.94</v>
       </c>
       <c r="AR12" t="n">
-        <v>-1.81</v>
+        <v>-1.84</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-124.80</t>
+          <t>-125.16</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>89382.98231966054</t>
+          <t>89263.77754237289</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>2323.0</t>
+          <t>17036.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>4899.2</v>
+        <v>6987.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>6022.3</t>
+          <t>6636.3</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>15417.3</v>
+        <v>14299.4</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-1123</t>
+          <t>350</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-1460.222849881036</t>
+          <t>-1285.68313588008</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-1369.710762138438</t>
+          <t>-325.7147088748216</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>2323.0</t>
+          <t>17036.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-9.91</t>
+          <t>-6.67</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>21.68</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>32.42</t>
+          <t>32.44</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>2380</t>
+          <t>2394</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>49.85</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/印刷材料.xlsx
+++ b/Result/checksun_type/印刷材料.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-30.07</t>
+          <t>-20.25</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-10.44</t>
+          <t>-11.28</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,66 +1014,66 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>143</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>58.33</t>
+          <t>80.56</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>0.99</v>
+        <v>0.11</v>
       </c>
       <c r="AI2" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-6.06</t>
+          <t>-6.01</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-3.40</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>52.67999999999999</t>
+          <t>52.64</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>52.16</v>
+        <v>52.08</v>
       </c>
       <c r="AN2" t="n">
-        <v>55.52</v>
+        <v>55.41</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>57.37</t>
+          <t>57.36</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>34.70</t>
+          <t>35.57</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>-0.7</v>
+        <v>-0.63</v>
       </c>
       <c r="AR2" t="n">
-        <v>-1.07</v>
+        <v>-0.99</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-114.70</t>
+          <t>-113.50</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>89263.77754237289</t>
+          <t>89154.12905500706</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>3324.0</t>
+          <t>7682.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>5108.2</v>
+        <v>4986.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>7304.7</t>
+          <t>6252.7</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>12325.42</v>
+        <v>12234.7</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-2196</t>
+          <t>-1266</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-605.8996187432529</t>
+          <t>-605.422864052449</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-852.5471439184039</t>
+          <t>-602.8007132530274</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>3324.0</t>
+          <t>7682.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-5.05</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>32.44</t>
+          <t>32.36</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>2394</t>
+          <t>2371</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>54.8</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-42.21</t>
+          <t>-30.07</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-10.94</t>
+          <t>-10.44</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,66 +1436,66 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>143</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>52.27</t>
+          <t>58.33</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>0.84</v>
+        <v>0.99</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.53</v>
+        <v>1</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-6.24</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>52.46</t>
+          <t>52.67999999999999</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>52.18</v>
+        <v>52.16</v>
       </c>
       <c r="AN3" t="n">
-        <v>55.66</v>
+        <v>55.52</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>57.36</t>
+          <t>57.37</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>29.22</t>
+          <t>34.70</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.83</v>
+        <v>-0.7</v>
       </c>
       <c r="AR3" t="n">
-        <v>-1.17</v>
+        <v>-1.07</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-115.98</t>
+          <t>-114.70</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>89263.77754237289</t>
+          <t>89154.12905500706</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>5833.0</t>
+          <t>3324.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>5013.8</v>
+        <v>5108.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>8675.9</t>
+          <t>7304.7</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>12426.06</v>
+        <v>12325.42</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-3662</t>
+          <t>-2196</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-561.0546141659527</t>
+          <t>-605.8996187432529</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-711.9510754432858</t>
+          <t>-852.5471439184039</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>5833.0</t>
+          <t>3324.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1625,12 +1625,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>32.44</t>
+          <t>32.36</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>2394</t>
+          <t>2371</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-43.86</t>
+          <t>-42.21</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-12.96</t>
+          <t>-10.94</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,66 +1858,66 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>143</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>56.74</t>
+          <t>52.27</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>-1.11</v>
+        <v>0.84</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.1</v>
+        <v>0.53</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-6.39</t>
+          <t>-6.24</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.71</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>52.27999999999999</t>
+          <t>52.46</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>52.23</v>
+        <v>52.18</v>
       </c>
       <c r="AN4" t="n">
-        <v>55.8</v>
+        <v>55.66</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>57.35</t>
+          <t>57.36</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>29.22</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.83</v>
       </c>
       <c r="AR4" t="n">
-        <v>-1.25</v>
+        <v>-1.17</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-117.14</t>
+          <t>-115.98</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>89263.77754237289</t>
+          <t>89154.12905500706</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>4797.0</t>
+          <t>5833.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>4673.8</v>
+        <v>5013.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>8324.9</t>
+          <t>8675.9</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>12556.78</v>
+        <v>12426.06</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-3651</t>
+          <t>-3662</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-533.6188939337103</t>
+          <t>-561.0546141659527</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-754.4941534987138</t>
+          <t>-711.9510754432858</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>4797.0</t>
+          <t>5833.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-6.85</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>32.44</t>
+          <t>32.36</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>2394</t>
+          <t>2371</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,12 +2102,12 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-33.34</t>
+          <t>-43.86</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-11.28</t>
+          <t>-12.96</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,66 +2280,66 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>143</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>81.82</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>78.48</t>
+          <t>56.74</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>0.27</v>
+        <v>-1.11</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.45</v>
+        <v>0.1</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-6.53</t>
+          <t>-6.39</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-2.71</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>52.56</t>
+          <t>52.27999999999999</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>52.32</v>
+        <v>52.23</v>
       </c>
       <c r="AN5" t="n">
-        <v>55.98</v>
+        <v>55.8</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>57.34</t>
+          <t>57.35</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>28.11</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.96</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AR5" t="n">
-        <v>-1.33</v>
+        <v>-1.25</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-118.20</t>
+          <t>-117.14</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>89263.77754237289</t>
+          <t>89154.12905500706</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>3296.0</t>
+          <t>4797.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>5465.4</v>
+        <v>4673.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>8198.7</t>
+          <t>8324.9</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>12704.54</v>
+        <v>12556.78</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-2733</t>
+          <t>-3651</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-493.4597558309824</t>
+          <t>-533.6188939337103</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-677.32375952437</t>
+          <t>-754.4941534987138</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>3296.0</t>
+          <t>4797.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-5.05</t>
+          <t>-6.85</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>32.44</t>
+          <t>32.36</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>2394</t>
+          <t>2371</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2554,7 +2554,7 @@
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>156.0</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-10.85</t>
+          <t>-33.34</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-10.94</t>
+          <t>-11.28</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,66 +2702,66 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>143</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>88.41</t>
+          <t>81.82</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>71.98</t>
+          <t>78.48</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.27</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.29</v>
+        <v>0.45</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-6.68</t>
+          <t>-6.53</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>52.54</t>
+          <t>52.56</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>52.39</v>
+        <v>52.32</v>
       </c>
       <c r="AN6" t="n">
-        <v>56.14</v>
+        <v>55.98</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>57.32</t>
+          <t>57.34</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>25.48</t>
+          <t>28.11</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>-1.06</v>
+        <v>-0.96</v>
       </c>
       <c r="AR6" t="n">
-        <v>-1.42</v>
+        <v>-1.33</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-119.48</t>
+          <t>-118.20</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>89263.77754237289</t>
+          <t>89154.12905500706</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>8291.0</t>
+          <t>3296.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>7519</v>
+        <v>5465.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>8434.2</t>
+          <t>8198.7</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>12897.76</v>
+        <v>12704.54</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-915</t>
+          <t>-2733</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-460.0299369776392</t>
+          <t>-493.4597558309824</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-382.0687767208665</t>
+          <t>-677.32375952437</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>8291.0</t>
+          <t>3296.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-5.05</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2891,12 +2891,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>32.44</t>
+          <t>32.36</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>2394</t>
+          <t>2371</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>54.3</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>156.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>15.25</t>
+          <t>-10.85</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-12.29</t>
+          <t>-10.94</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,50 +3124,50 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>143</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>65.22</t>
+          <t>88.41</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>73.91</t>
+          <t>71.98</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>-0.99</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.35</v>
+        <v>0.29</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-6.88</t>
+          <t>-6.68</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>52.62</t>
+          <t>52.54</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>52.44</v>
+        <v>52.39</v>
       </c>
       <c r="AN7" t="n">
-        <v>56.31</v>
+        <v>56.14</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3176,14 +3176,14 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>20.79</t>
+          <t>25.48</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>-1.2</v>
+        <v>-1.06</v>
       </c>
       <c r="AR7" t="n">
-        <v>-1.51</v>
+        <v>-1.42</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-120.72</t>
+          <t>-119.48</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>89263.77754237289</t>
+          <t>89154.12905500706</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>2852.0</t>
+          <t>8291.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>9501.200000000001</v>
+        <v>7519</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>8244.2</t>
+          <t>8434.2</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>13064.54</v>
+        <v>12897.76</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>1257</t>
+          <t>-915</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-474.2046933879615</t>
+          <t>-460.0299369776392</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-481.8092021186876</t>
+          <t>-382.0687767208665</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>2852.0</t>
+          <t>8291.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-6.13</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>32.44</t>
+          <t>32.36</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>2394</t>
+          <t>2371</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3368,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>54.3</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>43.16</t>
+          <t>15.25</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-12.46</t>
+          <t>-12.29</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,66 +3546,66 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>143</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>62.32</t>
+          <t>65.22</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>78.74</t>
+          <t>73.91</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>-1.07</v>
+        <v>-0.99</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-6.98</t>
+          <t>-6.88</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>52.56</t>
+          <t>52.62</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>52.56</v>
+        <v>52.44</v>
       </c>
       <c r="AN8" t="n">
-        <v>56.5</v>
+        <v>56.31</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>57.33</t>
+          <t>57.32</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>19.82</t>
+          <t>20.79</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>-1.28</v>
+        <v>-1.2</v>
       </c>
       <c r="AR8" t="n">
-        <v>-1.59</v>
+        <v>-1.51</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-121.80</t>
+          <t>-120.72</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>89263.77754237289</t>
+          <t>89154.12905500706</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>4133.0</t>
+          <t>2852.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>12338</v>
+        <v>9501.200000000001</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>8618.6</t>
+          <t>8244.2</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>13299.38</v>
+        <v>13064.54</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>3719</t>
+          <t>1257</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-472.8220554369204</t>
+          <t>-474.2046933879615</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-24.33805261133421</t>
+          <t>-481.8092021186876</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>4133.0</t>
+          <t>2852.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-6.31</t>
+          <t>-6.13</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>32.44</t>
+          <t>32.36</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>2394</t>
+          <t>2371</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3820,14 +3820,14 @@
       </c>
       <c r="CJ8" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>167.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>36.29</t>
+          <t>43.16</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-10.61</t>
+          <t>-12.46</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,66 +3968,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>143</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>94.2</t>
+          <t>62.32</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>78.74</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>1.8</v>
+        <v>-1.07</v>
       </c>
       <c r="AI9" t="n">
-        <v>-1.16</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-6.89</t>
+          <t>-6.98</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>52.16</t>
+          <t>52.56</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>52.77</v>
+        <v>52.56</v>
       </c>
       <c r="AN9" t="n">
-        <v>56.68</v>
+        <v>56.5</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>57.34</t>
+          <t>57.33</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>19.38</t>
+          <t>19.82</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>-1.35</v>
+        <v>-1.28</v>
       </c>
       <c r="AR9" t="n">
-        <v>-1.67</v>
+        <v>-1.59</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-122.88</t>
+          <t>-121.80</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>89263.77754237289</t>
+          <t>89154.12905500706</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>8755.0</t>
+          <t>4133.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>11976</v>
+        <v>12338</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>8787.0</t>
+          <t>8618.6</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>13401.56</v>
+        <v>13299.38</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>3719</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-554.3646014052089</t>
+          <t>-472.8220554369204</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>492.8113771352873</t>
+          <t>-24.33805261133421</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>8755.0</t>
+          <t>4133.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-6.31</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4147,22 +4147,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>32.44</t>
+          <t>32.36</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>2394</t>
+          <t>2371</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4242,7 +4242,7 @@
       </c>
       <c r="CJ9" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>255.0</t>
+          <t>167.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>26.75</t>
+          <t>36.29</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-11.45</t>
+          <t>-10.61</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>9.19</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,66 +4390,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>143</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>79.71</t>
+          <t>94.2</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>73.88</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>2.12</v>
+        <v>1.8</v>
       </c>
       <c r="AI10" t="n">
-        <v>-2.63</v>
+        <v>-1.16</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-6.92</t>
+          <t>-6.89</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>51.51000000000001</t>
+          <t>52.16</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>52.9</v>
+        <v>52.77</v>
       </c>
       <c r="AN10" t="n">
-        <v>56.83</v>
+        <v>56.68</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>57.32</t>
+          <t>57.34</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>19.38</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-1.53</v>
+        <v>-1.35</v>
       </c>
       <c r="AR10" t="n">
-        <v>-1.75</v>
+        <v>-1.67</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-123.99</t>
+          <t>-122.88</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>89263.77754237289</t>
+          <t>89154.12905500706</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>13564.0</t>
+          <t>8755.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>10932</v>
+        <v>11976</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>8624.8</t>
+          <t>8787.0</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>13461.08</v>
+        <v>13401.56</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>2307</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-744.7602338671172</t>
+          <t>-554.3646014052089</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>718.7815847327729</t>
+          <t>492.8113771352873</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>13564.0</t>
+          <t>8755.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-5.23</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4569,22 +4569,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>32.44</t>
+          <t>32.36</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>2394</t>
+          <t>2371</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="CJ10" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>345.0</t>
+          <t>255.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>26.75</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-10.27</t>
+          <t>-11.45</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12.43</t>
+          <t>9.19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,29 +4812,29 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>143</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>79.71</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>48.39</t>
+          <t>73.88</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>4.08</v>
+        <v>2.12</v>
       </c>
       <c r="AI11" t="n">
-        <v>-3.52</v>
+        <v>-2.63</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -4843,19 +4843,19 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>51.21</t>
+          <t>51.51000000000001</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>53.08</v>
+        <v>52.9</v>
       </c>
       <c r="AN11" t="n">
-        <v>57.02</v>
+        <v>56.83</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -4864,14 +4864,14 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>6.54</t>
+          <t>12.69</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-1.69</v>
+        <v>-1.53</v>
       </c>
       <c r="AR11" t="n">
-        <v>-1.81</v>
+        <v>-1.75</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-124.75</t>
+          <t>-123.99</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>89263.77754237289</t>
+          <t>89154.12905500706</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>18202.0</t>
+          <t>13564.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>9349.4</v>
+        <v>10932</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>7989.3</t>
+          <t>8624.8</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>13460.24</v>
+        <v>13461.08</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>2307</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-1010.858746339825</t>
+          <t>-744.7602338671172</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>500.6753961315808</t>
+          <t>718.7815847327729</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>18202.0</t>
+          <t>13564.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-5.23</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>32.44</t>
+          <t>32.36</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>2394</t>
+          <t>2371</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
+          <t>53.6</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
+          <t>54.1</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
           <t>52.6</t>
         </is>
       </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>53.5</t>
-        </is>
-      </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>52.0</t>
-        </is>
-      </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5086,14 +5086,14 @@
       </c>
       <c r="CJ11" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>334.0</t>
+          <t>345.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>17.02</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-12.79</t>
+          <t>-10.27</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12.03</t>
+          <t>12.43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,66 +5234,66 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>143</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>41.94</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>15.05</t>
+          <t>48.39</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>2.15</v>
+        <v>4.08</v>
       </c>
       <c r="AI12" t="n">
-        <v>-4.8</v>
+        <v>-3.52</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-6.85</t>
+          <t>-6.92</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>50.71</t>
+          <t>51.21</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>53.27</v>
+        <v>53.08</v>
       </c>
       <c r="AN12" t="n">
-        <v>57.18</v>
+        <v>57.02</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>57.29</t>
+          <t>57.32</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-5.61</t>
+          <t>6.54</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-1.94</v>
+        <v>-1.69</v>
       </c>
       <c r="AR12" t="n">
-        <v>-1.84</v>
+        <v>-1.81</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-125.16</t>
+          <t>-124.75</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>89263.77754237289</t>
+          <t>89154.12905500706</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>17036.0</t>
+          <t>18202.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>6987.2</v>
+        <v>9349.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>6636.3</t>
+          <t>7989.3</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>14299.4</v>
+        <v>13460.24</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-1285.68313588008</t>
+          <t>-1010.858746339825</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-325.7147088748216</t>
+          <t>500.6753961315808</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>17036.0</t>
+          <t>18202.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-6.67</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>32.44</t>
+          <t>32.36</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>2394</t>
+          <t>2371</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="CJ12" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>

--- a/Result/checksun_type/印刷材料.xlsx
+++ b/Result/checksun_type/印刷材料.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-20.25</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-11.28</t>
+          <t>-11.95</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,66 +1014,66 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>164</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>80.56</t>
+          <t>68.89</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>0.11</v>
+        <v>-0.49</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-6.01</t>
+          <t>-6.04</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-3.40</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>52.64</t>
+          <t>52.56</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>52.08</v>
+        <v>51.97</v>
       </c>
       <c r="AN2" t="n">
-        <v>55.41</v>
+        <v>55.31</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>57.36</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>35.57</t>
+          <t>33.19</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>-0.63</v>
+        <v>-0.61</v>
       </c>
       <c r="AR2" t="n">
-        <v>-0.99</v>
+        <v>-0.91</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-113.50</t>
+          <t>-112.47</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>89154.12905500706</t>
+          <t>89046.53661971832</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>7682.0</t>
+          <t>8509.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>4986.4</v>
+        <v>6029</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>6252.7</t>
+          <t>5747.2</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>12234.7</v>
+        <v>12110</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-1266</t>
+          <t>281</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-605.422864052449</t>
+          <t>-566.2629148068319</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-602.8007132530274</t>
+          <t>-350.8831939559377</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>7682.0</t>
+          <t>8509.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-5.05</t>
+          <t>-5.77</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.43</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>32.36</t>
+          <t>32.34</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>2371</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>54.8</t>
+          <t>53.4</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-30.07</t>
+          <t>-20.25</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-10.44</t>
+          <t>-11.28</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,66 +1436,66 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>164</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>58.33</t>
+          <t>80.56</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>0.99</v>
+        <v>0.11</v>
       </c>
       <c r="AI3" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-6.06</t>
+          <t>-6.01</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-3.40</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>52.67999999999999</t>
+          <t>52.64</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>52.16</v>
+        <v>52.08</v>
       </c>
       <c r="AN3" t="n">
-        <v>55.52</v>
+        <v>55.41</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>57.37</t>
+          <t>57.36</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>34.70</t>
+          <t>35.57</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.7</v>
+        <v>-0.63</v>
       </c>
       <c r="AR3" t="n">
-        <v>-1.07</v>
+        <v>-0.99</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-114.70</t>
+          <t>-113.50</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>89154.12905500706</t>
+          <t>89046.53661971832</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>3324.0</t>
+          <t>7682.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>5108.2</v>
+        <v>4986.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>7304.7</t>
+          <t>6252.7</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>12325.42</v>
+        <v>12234.7</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-2196</t>
+          <t>-1266</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-605.8996187432529</t>
+          <t>-605.422864052449</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-852.5471439184039</t>
+          <t>-602.8007132530274</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>3324.0</t>
+          <t>7682.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-5.05</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1625,12 +1625,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.43</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>32.36</t>
+          <t>32.34</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>2371</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>54.8</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-42.21</t>
+          <t>-30.07</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-10.94</t>
+          <t>-10.44</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,66 +1858,66 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>164</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>52.27</t>
+          <t>58.33</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>0.84</v>
+        <v>0.99</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.53</v>
+        <v>1</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-6.24</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>52.46</t>
+          <t>52.67999999999999</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>52.18</v>
+        <v>52.16</v>
       </c>
       <c r="AN4" t="n">
-        <v>55.66</v>
+        <v>55.52</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>57.36</t>
+          <t>57.37</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>29.22</t>
+          <t>34.70</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>-0.83</v>
+        <v>-0.7</v>
       </c>
       <c r="AR4" t="n">
-        <v>-1.17</v>
+        <v>-1.07</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-115.98</t>
+          <t>-114.70</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>89154.12905500706</t>
+          <t>89046.53661971832</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>5833.0</t>
+          <t>3324.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>5013.8</v>
+        <v>5108.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>8675.9</t>
+          <t>7304.7</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>12426.06</v>
+        <v>12325.42</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-3662</t>
+          <t>-2196</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-561.0546141659527</t>
+          <t>-605.8996187432529</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-711.9510754432858</t>
+          <t>-852.5471439184039</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>5833.0</t>
+          <t>3324.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.43</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>32.36</t>
+          <t>32.34</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>2371</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-43.86</t>
+          <t>-42.21</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-12.96</t>
+          <t>-10.94</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,66 +2280,66 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>164</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>56.74</t>
+          <t>52.27</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>-1.11</v>
+        <v>0.84</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.1</v>
+        <v>0.53</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-6.39</t>
+          <t>-6.24</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.71</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>52.27999999999999</t>
+          <t>52.46</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>52.23</v>
+        <v>52.18</v>
       </c>
       <c r="AN5" t="n">
-        <v>55.8</v>
+        <v>55.66</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>57.35</t>
+          <t>57.36</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>29.22</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.83</v>
       </c>
       <c r="AR5" t="n">
-        <v>-1.25</v>
+        <v>-1.17</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-117.14</t>
+          <t>-115.98</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>89154.12905500706</t>
+          <t>89046.53661971832</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>4797.0</t>
+          <t>5833.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>4673.8</v>
+        <v>5013.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>8324.9</t>
+          <t>8675.9</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>12556.78</v>
+        <v>12426.06</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-3651</t>
+          <t>-3662</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-533.6188939337103</t>
+          <t>-561.0546141659527</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-754.4941534987138</t>
+          <t>-711.9510754432858</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>4797.0</t>
+          <t>5833.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-6.85</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.43</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>32.36</t>
+          <t>32.34</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>2371</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-33.34</t>
+          <t>-43.86</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-11.28</t>
+          <t>-12.96</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,66 +2702,66 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>164</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>81.82</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>78.48</t>
+          <t>56.74</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>0.27</v>
+        <v>-1.11</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.45</v>
+        <v>0.1</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-6.53</t>
+          <t>-6.39</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-2.71</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>52.56</t>
+          <t>52.27999999999999</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>52.32</v>
+        <v>52.23</v>
       </c>
       <c r="AN6" t="n">
-        <v>55.98</v>
+        <v>55.8</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>57.34</t>
+          <t>57.35</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>28.11</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.96</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AR6" t="n">
-        <v>-1.33</v>
+        <v>-1.25</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-118.20</t>
+          <t>-117.14</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>89154.12905500706</t>
+          <t>89046.53661971832</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>3296.0</t>
+          <t>4797.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>5465.4</v>
+        <v>4673.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>8198.7</t>
+          <t>8324.9</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>12704.54</v>
+        <v>12556.78</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-2733</t>
+          <t>-3651</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-493.4597558309824</t>
+          <t>-533.6188939337103</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-677.32375952437</t>
+          <t>-754.4941534987138</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>3296.0</t>
+          <t>4797.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-5.05</t>
+          <t>-6.85</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2891,12 +2891,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.43</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>32.36</t>
+          <t>32.34</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>2371</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>156.0</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-10.85</t>
+          <t>-33.34</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-10.94</t>
+          <t>-11.28</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,66 +3124,66 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>164</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>88.41</t>
+          <t>81.82</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>71.98</t>
+          <t>78.48</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.27</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.29</v>
+        <v>0.45</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-6.68</t>
+          <t>-6.53</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>52.54</t>
+          <t>52.56</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>52.39</v>
+        <v>52.32</v>
       </c>
       <c r="AN7" t="n">
-        <v>56.14</v>
+        <v>55.98</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>57.32</t>
+          <t>57.34</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>25.48</t>
+          <t>28.11</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>-1.06</v>
+        <v>-0.96</v>
       </c>
       <c r="AR7" t="n">
-        <v>-1.42</v>
+        <v>-1.33</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-119.48</t>
+          <t>-118.20</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>89154.12905500706</t>
+          <t>89046.53661971832</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>8291.0</t>
+          <t>3296.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>7519</v>
+        <v>5465.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>8434.2</t>
+          <t>8198.7</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>12897.76</v>
+        <v>12704.54</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-915</t>
+          <t>-2733</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-460.0299369776392</t>
+          <t>-493.4597558309824</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-382.0687767208665</t>
+          <t>-677.32375952437</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>8291.0</t>
+          <t>3296.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-5.05</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.43</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>32.36</t>
+          <t>32.34</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>2371</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3368,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>54.3</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>156.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>15.25</t>
+          <t>-10.85</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-12.29</t>
+          <t>-10.94</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,50 +3546,50 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>164</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>65.22</t>
+          <t>88.41</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>73.91</t>
+          <t>71.98</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>-0.99</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.35</v>
+        <v>0.29</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-6.88</t>
+          <t>-6.68</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>52.62</t>
+          <t>52.54</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>52.44</v>
+        <v>52.39</v>
       </c>
       <c r="AN8" t="n">
-        <v>56.31</v>
+        <v>56.14</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3598,14 +3598,14 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>20.79</t>
+          <t>25.48</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>-1.2</v>
+        <v>-1.06</v>
       </c>
       <c r="AR8" t="n">
-        <v>-1.51</v>
+        <v>-1.42</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-120.72</t>
+          <t>-119.48</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>89154.12905500706</t>
+          <t>89046.53661971832</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>2852.0</t>
+          <t>8291.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>9501.200000000001</v>
+        <v>7519</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>8244.2</t>
+          <t>8434.2</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>13064.54</v>
+        <v>12897.76</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>1257</t>
+          <t>-915</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-474.2046933879615</t>
+          <t>-460.0299369776392</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-481.8092021186876</t>
+          <t>-382.0687767208665</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>2852.0</t>
+          <t>8291.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-6.13</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.43</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>32.36</t>
+          <t>32.34</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>2371</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>54.3</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>43.16</t>
+          <t>15.25</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-12.46</t>
+          <t>-12.29</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,66 +3968,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>164</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>62.32</t>
+          <t>65.22</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>78.74</t>
+          <t>73.91</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>-1.07</v>
+        <v>-0.99</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-6.98</t>
+          <t>-6.88</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>52.56</t>
+          <t>52.62</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>52.56</v>
+        <v>52.44</v>
       </c>
       <c r="AN9" t="n">
-        <v>56.5</v>
+        <v>56.31</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>57.33</t>
+          <t>57.32</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>19.82</t>
+          <t>20.79</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>-1.28</v>
+        <v>-1.2</v>
       </c>
       <c r="AR9" t="n">
-        <v>-1.59</v>
+        <v>-1.51</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-121.80</t>
+          <t>-120.72</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>89154.12905500706</t>
+          <t>89046.53661971832</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>4133.0</t>
+          <t>2852.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>12338</v>
+        <v>9501.200000000001</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>8618.6</t>
+          <t>8244.2</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>13299.38</v>
+        <v>13064.54</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>3719</t>
+          <t>1257</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-472.8220554369204</t>
+          <t>-474.2046933879615</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-24.33805261133421</t>
+          <t>-481.8092021186876</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>4133.0</t>
+          <t>2852.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-6.31</t>
+          <t>-6.13</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4147,12 +4147,12 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.43</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>32.36</t>
+          <t>32.34</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>2371</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4249,7 +4249,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>167.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>36.29</t>
+          <t>43.16</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-10.61</t>
+          <t>-12.46</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,66 +4390,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>164</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>94.2</t>
+          <t>62.32</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>78.74</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>1.8</v>
+        <v>-1.07</v>
       </c>
       <c r="AI10" t="n">
-        <v>-1.16</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-6.89</t>
+          <t>-6.98</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>52.16</t>
+          <t>52.56</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>52.77</v>
+        <v>52.56</v>
       </c>
       <c r="AN10" t="n">
-        <v>56.68</v>
+        <v>56.5</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>57.34</t>
+          <t>57.33</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>19.38</t>
+          <t>19.82</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-1.35</v>
+        <v>-1.28</v>
       </c>
       <c r="AR10" t="n">
-        <v>-1.67</v>
+        <v>-1.59</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-122.88</t>
+          <t>-121.80</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>89154.12905500706</t>
+          <t>89046.53661971832</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>8755.0</t>
+          <t>4133.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>11976</v>
+        <v>12338</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>8787.0</t>
+          <t>8618.6</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>13401.56</v>
+        <v>13299.38</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>3719</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-554.3646014052089</t>
+          <t>-472.8220554369204</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>492.8113771352873</t>
+          <t>-24.33805261133421</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>8755.0</t>
+          <t>4133.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-6.31</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.43</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>32.36</t>
+          <t>32.34</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>2371</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>255.0</t>
+          <t>167.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>26.75</t>
+          <t>36.29</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-11.45</t>
+          <t>-10.61</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>9.19</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,66 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>164</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>79.71</t>
+          <t>94.2</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>73.88</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>2.12</v>
+        <v>1.8</v>
       </c>
       <c r="AI11" t="n">
-        <v>-2.63</v>
+        <v>-1.16</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-6.92</t>
+          <t>-6.89</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>51.51000000000001</t>
+          <t>52.16</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>52.9</v>
+        <v>52.77</v>
       </c>
       <c r="AN11" t="n">
-        <v>56.83</v>
+        <v>56.68</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>57.32</t>
+          <t>57.34</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>19.38</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-1.53</v>
+        <v>-1.35</v>
       </c>
       <c r="AR11" t="n">
-        <v>-1.75</v>
+        <v>-1.67</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-123.99</t>
+          <t>-122.88</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>89154.12905500706</t>
+          <t>89046.53661971832</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>13564.0</t>
+          <t>8755.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>10932</v>
+        <v>11976</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>8624.8</t>
+          <t>8787.0</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>13461.08</v>
+        <v>13401.56</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>2307</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-744.7602338671172</t>
+          <t>-554.3646014052089</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>718.7815847327729</t>
+          <t>492.8113771352873</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>13564.0</t>
+          <t>8755.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-5.23</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.43</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>32.36</t>
+          <t>32.34</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>2371</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>345.0</t>
+          <t>255.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>26.75</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-10.27</t>
+          <t>-11.45</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12.43</t>
+          <t>9.19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,29 +5234,29 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>164</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>79.71</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>48.39</t>
+          <t>73.88</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>4.08</v>
+        <v>2.12</v>
       </c>
       <c r="AI12" t="n">
-        <v>-3.52</v>
+        <v>-2.63</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -5265,19 +5265,19 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>51.21</t>
+          <t>51.51000000000001</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>53.08</v>
+        <v>52.9</v>
       </c>
       <c r="AN12" t="n">
-        <v>57.02</v>
+        <v>56.83</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5286,14 +5286,14 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>6.54</t>
+          <t>12.69</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-1.69</v>
+        <v>-1.53</v>
       </c>
       <c r="AR12" t="n">
-        <v>-1.81</v>
+        <v>-1.75</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-124.75</t>
+          <t>-123.99</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>89154.12905500706</t>
+          <t>89046.53661971832</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>18202.0</t>
+          <t>13564.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>9349.4</v>
+        <v>10932</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>7989.3</t>
+          <t>8624.8</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>13460.24</v>
+        <v>13461.08</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>2307</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-1010.858746339825</t>
+          <t>-744.7602338671172</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>500.6753961315808</t>
+          <t>718.7815847327729</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>18202.0</t>
+          <t>13564.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-5.23</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.43</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>32.36</t>
+          <t>32.34</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>2371</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
+          <t>53.6</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
+          <t>54.1</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
           <t>52.6</t>
         </is>
       </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>53.5</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>52.0</t>
-        </is>
-      </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/印刷材料.xlsx
+++ b/Result/checksun_type/印刷材料.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CJ12"/>
+  <dimension ref="A1:CR12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -551,320 +551,360 @@
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
+          <t>MA_last_cross_d2</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>MA_last_cross_d2收盤價</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>MA_death_cross</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>MA_death_cross_d</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>MA_death_cross_d收盤價</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>MA_death_cross_d2</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>MA_death_cross_d2收盤價</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_hist_diff</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>量能</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>價能</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>cond_entry</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>text_desc</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>盤後量</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>成交量</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>%K</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>%D</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>MA5_%</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>均價_%</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>均價long_%</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>均價longlong_%</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>MA_short</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>MA_long</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>MA_longlong</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>MA_longlonglong</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>MACD_%</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>MACD</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL_max</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>MACDSL_%</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>MACD_last_cross_date</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>成交金額平均</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>成交金額</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_short</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long50</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>Volume_Oscillator</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>volume_threshold</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>VPC_MACD</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Volume_Price_Change</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date收盤價</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CO1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CP1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CQ1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CR1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>
@@ -883,12 +923,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +938,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +953,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>13.27</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +1023,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-11.95</t>
+          <t>-11.78</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,300 +1033,340 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025/06/05</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
+          <t>2025/10/22</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>58.5</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>2025/06/11</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>55.7</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>3.57</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>-0.57</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr">
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>68.89</t>
-        </is>
-      </c>
-      <c r="AH2" t="n">
-        <v>-0.49</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>-6.04</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>-3.47</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>52.56</t>
-        </is>
-      </c>
-      <c r="AM2" t="n">
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>46.67</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>51.11</t>
+        </is>
+      </c>
+      <c r="AP2" t="n">
+        <v>-0.57</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>-5.87</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>-3.52</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>52.7</t>
+        </is>
+      </c>
+      <c r="AU2" t="n">
         <v>51.97</v>
       </c>
-      <c r="AN2" t="n">
-        <v>55.31</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>57.3</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>33.19</t>
-        </is>
-      </c>
-      <c r="AQ2" t="n">
-        <v>-0.61</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>-0.91</v>
-      </c>
-      <c r="AS2" t="inlineStr">
+      <c r="AV2" t="n">
+        <v>55.21</v>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>57.22</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>32.10</t>
+        </is>
+      </c>
+      <c r="AY2" t="n">
+        <v>-0.57</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>-0.84</v>
+      </c>
+      <c r="BA2" t="inlineStr">
         <is>
           <t>7.3</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>-112.47</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>-111.54</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
         <is>
           <t>2025/11/26</t>
         </is>
       </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>89046.53661971832</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>8509.0</t>
-        </is>
-      </c>
-      <c r="AX2" t="n">
-        <v>6029</v>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>5747.2</t>
-        </is>
-      </c>
-      <c r="AZ2" t="n">
-        <v>12110</v>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>-566.2629148068319</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>-350.8831939559377</t>
-        </is>
-      </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>8509.0</t>
+          <t>88932.20464135021</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
+          <t>5171.0</t>
+        </is>
+      </c>
+      <c r="BF2" t="n">
+        <v>6103.8</v>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>5388.8</t>
+        </is>
+      </c>
+      <c r="BH2" t="n">
+        <v>12016.5</v>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>715</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>-543.1638280056386</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>-416.1188505990758</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>5171.0</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
         <is>
           <t>55.5</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>2025/08/20</t>
         </is>
       </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>-5.77</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>-5.59</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
         <is>
           <t>利機</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BR2" t="inlineStr">
         <is>
           <t>利機</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BS2" t="inlineStr">
         <is>
           <t>電子通路業</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
+      <c r="BT2" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BM2" t="inlineStr">
+      <c r="BU2" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BV2" t="inlineStr">
         <is>
           <t>2.973959600876125</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BW2" t="inlineStr">
         <is>
           <t>7.507647901781631</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>9.97333412563415</t>
         </is>
       </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>2.26</t>
-        </is>
-      </c>
-      <c r="BT2" t="inlineStr">
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
         <is>
           <t>3.82</t>
         </is>
       </c>
-      <c r="BU2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>6.82</t>
         </is>
       </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>21.43</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr">
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>21.48</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
         <is>
           <t>20.15%</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
+      <c r="CF2" t="inlineStr">
         <is>
           <t>3.13%</t>
         </is>
       </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>32.34</t>
-        </is>
-      </c>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>2353</t>
-        </is>
-      </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CG2" t="inlineStr">
+        <is>
+          <t>32.3</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
+          <t>2358</t>
+        </is>
+      </c>
+      <c r="CI2" t="inlineStr">
         <is>
           <t>半導體產品60.53%、光電產品37.52%、其他產品1.95% (2024年)</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>利機-電子通路業-上櫃</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
+      <c r="CK2" t="inlineStr">
         <is>
           <t>電子通路業右下上櫃</t>
         </is>
       </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>52.9</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>53.4</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>51.0</t>
-        </is>
-      </c>
-      <c r="CG2" t="inlineStr">
-        <is>
-          <t>52.3</t>
-        </is>
-      </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CL2" t="inlineStr">
+        <is>
+          <t>52.6</t>
+        </is>
+      </c>
+      <c r="CM2" t="inlineStr">
+        <is>
+          <t>53.0</t>
+        </is>
+      </c>
+      <c r="CN2" t="inlineStr">
+        <is>
+          <t>52.1</t>
+        </is>
+      </c>
+      <c r="CO2" t="inlineStr">
+        <is>
+          <t>52.4</t>
+        </is>
+      </c>
+      <c r="CP2" t="inlineStr">
         <is>
           <t>23.11</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CQ2" t="inlineStr">
         <is>
           <t>** 半導體 - 基板、導線架、IC封裝測試、IC模組、IC通路** 平面顯示器 - 驅動IC** 觸控面板 - 印刷材料** LED照明產業 - 封裝/模組</t>
         </is>
       </c>
-      <c r="CJ2" t="inlineStr">
+      <c r="CR2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1305,12 +1385,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1400,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,17 +1410,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-20.25</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1405,7 +1485,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-11.28</t>
+          <t>-11.95</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,300 +1495,340 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025/06/05</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
+          <t>2025/10/22</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>58.5</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>2025/06/11</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>55.7</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>-0.05</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>5.91</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0.45</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr">
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>66.67</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>80.56</t>
-        </is>
-      </c>
-      <c r="AH3" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>-6.01</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>-3.40</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>52.64</t>
-        </is>
-      </c>
-      <c r="AM3" t="n">
-        <v>52.08</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>55.41</v>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>57.36</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>35.57</t>
-        </is>
+          <t>68.89</t>
+        </is>
+      </c>
+      <c r="AP3" t="n">
+        <v>-0.49</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.63</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>-0.99</v>
+        <v>1.13</v>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>-6.04</t>
+        </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
+          <t>-3.47</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>52.56</t>
+        </is>
+      </c>
+      <c r="AU3" t="n">
+        <v>51.97</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>55.31</v>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>57.3</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>33.19</t>
+        </is>
+      </c>
+      <c r="AY3" t="n">
+        <v>-0.61</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
           <t>7.3</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>-113.50</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>-112.47</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
         <is>
           <t>2025/11/26</t>
         </is>
       </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>89046.53661971832</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>7682.0</t>
-        </is>
-      </c>
-      <c r="AX3" t="n">
-        <v>4986.4</v>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>6252.7</t>
-        </is>
-      </c>
-      <c r="AZ3" t="n">
-        <v>12234.7</v>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>-1266</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>-605.422864052449</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>-602.8007132530274</t>
-        </is>
-      </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>7682.0</t>
+          <t>88932.20464135021</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
+          <t>8509.0</t>
+        </is>
+      </c>
+      <c r="BF3" t="n">
+        <v>6029</v>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>5747.2</t>
+        </is>
+      </c>
+      <c r="BH3" t="n">
+        <v>12110</v>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>-566.2629148068319</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>-350.8831939559377</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>8509.0</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
         <is>
           <t>55.5</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>2025/08/20</t>
         </is>
       </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>-5.05</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>-5.77</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
         <is>
           <t>利機</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
+      <c r="BR3" t="inlineStr">
         <is>
           <t>利機</t>
         </is>
       </c>
-      <c r="BK3" t="inlineStr">
+      <c r="BS3" t="inlineStr">
         <is>
           <t>電子通路業</t>
         </is>
       </c>
-      <c r="BL3" t="inlineStr">
+      <c r="BT3" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BM3" t="inlineStr">
+      <c r="BU3" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BV3" t="inlineStr">
         <is>
           <t>2.973959600876125</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BW3" t="inlineStr">
         <is>
           <t>7.507647901781631</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>9.97333412563415</t>
         </is>
       </c>
-      <c r="BQ3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR3" t="inlineStr">
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>2.28</t>
-        </is>
-      </c>
-      <c r="BT3" t="inlineStr">
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>2.26</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
         <is>
           <t>3.82</t>
         </is>
       </c>
-      <c r="BU3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>6.82</t>
         </is>
       </c>
-      <c r="BV3" t="inlineStr">
-        <is>
-          <t>21.43</t>
-        </is>
-      </c>
-      <c r="BW3" t="inlineStr">
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>21.48</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
         <is>
           <t>20.15%</t>
         </is>
       </c>
-      <c r="BX3" t="inlineStr">
+      <c r="CF3" t="inlineStr">
         <is>
           <t>3.13%</t>
         </is>
       </c>
-      <c r="BY3" t="inlineStr">
-        <is>
-          <t>32.34</t>
-        </is>
-      </c>
-      <c r="BZ3" t="inlineStr">
-        <is>
-          <t>2353</t>
-        </is>
-      </c>
-      <c r="CA3" t="inlineStr">
+      <c r="CG3" t="inlineStr">
+        <is>
+          <t>32.3</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
+          <t>2358</t>
+        </is>
+      </c>
+      <c r="CI3" t="inlineStr">
         <is>
           <t>半導體產品60.53%、光電產品37.52%、其他產品1.95% (2024年)</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>利機-電子通路業-上櫃</t>
         </is>
       </c>
-      <c r="CC3" t="inlineStr">
+      <c r="CK3" t="inlineStr">
         <is>
           <t>電子通路業右下上櫃</t>
         </is>
       </c>
-      <c r="CD3" t="inlineStr">
-        <is>
-          <t>53.6</t>
-        </is>
-      </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>54.8</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>52.7</t>
-        </is>
-      </c>
-      <c r="CG3" t="inlineStr">
-        <is>
-          <t>52.7</t>
-        </is>
-      </c>
-      <c r="CH3" t="inlineStr">
+      <c r="CL3" t="inlineStr">
+        <is>
+          <t>52.9</t>
+        </is>
+      </c>
+      <c r="CM3" t="inlineStr">
+        <is>
+          <t>53.4</t>
+        </is>
+      </c>
+      <c r="CN3" t="inlineStr">
+        <is>
+          <t>51.0</t>
+        </is>
+      </c>
+      <c r="CO3" t="inlineStr">
+        <is>
+          <t>52.3</t>
+        </is>
+      </c>
+      <c r="CP3" t="inlineStr">
         <is>
           <t>23.11</t>
         </is>
       </c>
-      <c r="CI3" t="inlineStr">
+      <c r="CQ3" t="inlineStr">
         <is>
           <t>** 半導體 - 基板、導線架、IC封裝測試、IC模組、IC通路** 平面顯示器 - 驅動IC** 觸控面板 - 印刷材料** LED照明產業 - 封裝/模組</t>
         </is>
       </c>
-      <c r="CJ3" t="inlineStr">
+      <c r="CR3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1727,12 +1847,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1862,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,17 +1872,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-30.07</t>
+          <t>-20.25</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1827,7 +1947,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-10.44</t>
+          <t>-11.28</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,300 +1957,340 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025/06/05</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
+          <t>2025/10/22</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>58.5</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>2025/06/11</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>55.7</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>5.15</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>-3.98</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr">
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>58.33</t>
-        </is>
-      </c>
-      <c r="AH4" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>-6.06</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>-3.21</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>52.67999999999999</t>
-        </is>
-      </c>
-      <c r="AM4" t="n">
-        <v>52.16</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>55.52</v>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>66.67</t>
+        </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>57.37</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>34.70</t>
-        </is>
+          <t>80.56</t>
+        </is>
+      </c>
+      <c r="AP4" t="n">
+        <v>0.11</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>-1.07</v>
+        <v>1.07</v>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>-6.01</t>
+        </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
+          <t>-3.40</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>52.64</t>
+        </is>
+      </c>
+      <c r="AU4" t="n">
+        <v>52.08</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>55.41</v>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>57.36</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>35.57</t>
+        </is>
+      </c>
+      <c r="AY4" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>-0.99</v>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
           <t>7.3</t>
         </is>
       </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>-114.70</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>-113.50</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
         <is>
           <t>2025/11/26</t>
         </is>
       </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>89046.53661971832</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>3324.0</t>
-        </is>
-      </c>
-      <c r="AX4" t="n">
-        <v>5108.2</v>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>7304.7</t>
-        </is>
-      </c>
-      <c r="AZ4" t="n">
-        <v>12325.42</v>
-      </c>
-      <c r="BA4" t="inlineStr">
-        <is>
-          <t>-2196</t>
-        </is>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>-605.8996187432529</t>
-        </is>
-      </c>
-      <c r="BC4" t="inlineStr">
-        <is>
-          <t>-852.5471439184039</t>
-        </is>
-      </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>3324.0</t>
+          <t>88932.20464135021</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
+          <t>7682.0</t>
+        </is>
+      </c>
+      <c r="BF4" t="n">
+        <v>4986.4</v>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>6252.7</t>
+        </is>
+      </c>
+      <c r="BH4" t="n">
+        <v>12234.7</v>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>-1266</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>-605.422864052449</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>-602.8007132530274</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>7682.0</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
         <is>
           <t>55.5</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>2025/08/20</t>
         </is>
       </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>-4.14</t>
-        </is>
-      </c>
-      <c r="BI4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>-5.05</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
         <is>
           <t>利機</t>
         </is>
       </c>
-      <c r="BJ4" t="inlineStr">
+      <c r="BR4" t="inlineStr">
         <is>
           <t>利機</t>
         </is>
       </c>
-      <c r="BK4" t="inlineStr">
+      <c r="BS4" t="inlineStr">
         <is>
           <t>電子通路業</t>
         </is>
       </c>
-      <c r="BL4" t="inlineStr">
+      <c r="BT4" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BM4" t="inlineStr">
+      <c r="BU4" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="BN4" t="inlineStr">
+      <c r="BV4" t="inlineStr">
         <is>
           <t>2.973959600876125</t>
         </is>
       </c>
-      <c r="BO4" t="inlineStr">
+      <c r="BW4" t="inlineStr">
         <is>
           <t>7.507647901781631</t>
         </is>
       </c>
-      <c r="BP4" t="inlineStr">
+      <c r="BX4" t="inlineStr">
         <is>
           <t>9.97333412563415</t>
         </is>
       </c>
-      <c r="BQ4" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR4" t="inlineStr">
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BS4" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-      <c r="BT4" t="inlineStr">
+      <c r="CA4" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="CB4" t="inlineStr">
         <is>
           <t>3.82</t>
         </is>
       </c>
-      <c r="BU4" t="inlineStr">
+      <c r="CC4" t="inlineStr">
         <is>
           <t>6.82</t>
         </is>
       </c>
-      <c r="BV4" t="inlineStr">
-        <is>
-          <t>21.43</t>
-        </is>
-      </c>
-      <c r="BW4" t="inlineStr">
+      <c r="CD4" t="inlineStr">
+        <is>
+          <t>21.48</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
         <is>
           <t>20.15%</t>
         </is>
       </c>
-      <c r="BX4" t="inlineStr">
+      <c r="CF4" t="inlineStr">
         <is>
           <t>3.13%</t>
         </is>
       </c>
-      <c r="BY4" t="inlineStr">
-        <is>
-          <t>32.34</t>
-        </is>
-      </c>
-      <c r="BZ4" t="inlineStr">
-        <is>
-          <t>2353</t>
-        </is>
-      </c>
-      <c r="CA4" t="inlineStr">
+      <c r="CG4" t="inlineStr">
+        <is>
+          <t>32.3</t>
+        </is>
+      </c>
+      <c r="CH4" t="inlineStr">
+        <is>
+          <t>2358</t>
+        </is>
+      </c>
+      <c r="CI4" t="inlineStr">
         <is>
           <t>半導體產品60.53%、光電產品37.52%、其他產品1.95% (2024年)</t>
         </is>
       </c>
-      <c r="CB4" t="inlineStr">
+      <c r="CJ4" t="inlineStr">
         <is>
           <t>利機-電子通路業-上櫃</t>
         </is>
       </c>
-      <c r="CC4" t="inlineStr">
+      <c r="CK4" t="inlineStr">
         <is>
           <t>電子通路業右下上櫃</t>
         </is>
       </c>
-      <c r="CD4" t="inlineStr">
-        <is>
-          <t>53.0</t>
-        </is>
-      </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>53.3</t>
-        </is>
-      </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>52.4</t>
-        </is>
-      </c>
-      <c r="CG4" t="inlineStr">
-        <is>
-          <t>53.2</t>
-        </is>
-      </c>
-      <c r="CH4" t="inlineStr">
+      <c r="CL4" t="inlineStr">
+        <is>
+          <t>53.6</t>
+        </is>
+      </c>
+      <c r="CM4" t="inlineStr">
+        <is>
+          <t>54.8</t>
+        </is>
+      </c>
+      <c r="CN4" t="inlineStr">
+        <is>
+          <t>52.7</t>
+        </is>
+      </c>
+      <c r="CO4" t="inlineStr">
+        <is>
+          <t>52.7</t>
+        </is>
+      </c>
+      <c r="CP4" t="inlineStr">
         <is>
           <t>23.11</t>
         </is>
       </c>
-      <c r="CI4" t="inlineStr">
+      <c r="CQ4" t="inlineStr">
         <is>
           <t>** 半導體 - 基板、導線架、IC封裝測試、IC模組、IC通路** 平面顯示器 - 驅動IC** 觸控面板 - 印刷材料** LED照明產業 - 封裝/模組</t>
         </is>
       </c>
-      <c r="CJ4" t="inlineStr">
+      <c r="CR4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2149,12 +2309,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2324,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,17 +2334,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-42.21</t>
+          <t>-30.07</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2249,7 +2409,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-10.94</t>
+          <t>-10.44</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2259,300 +2419,340 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025/06/05</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
+          <t>2025/10/22</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>58.5</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>2025/06/11</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>55.7</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr">
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>52.27</t>
-        </is>
-      </c>
-      <c r="AH5" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>-6.24</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>-2.97</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>52.46</t>
-        </is>
-      </c>
-      <c r="AM5" t="n">
-        <v>52.18</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>55.66</v>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>57.36</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>29.22</t>
-        </is>
+          <t>58.33</t>
+        </is>
+      </c>
+      <c r="AP5" t="n">
+        <v>0.99</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.83</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>-1.17</v>
+        <v>1</v>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>-6.06</t>
+        </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
+          <t>-3.21</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>52.67999999999999</t>
+        </is>
+      </c>
+      <c r="AU5" t="n">
+        <v>52.16</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>55.52</v>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>57.37</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>34.70</t>
+        </is>
+      </c>
+      <c r="AY5" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>-1.07</v>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
           <t>7.3</t>
         </is>
       </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>-115.98</t>
-        </is>
-      </c>
-      <c r="AU5" t="inlineStr">
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>-114.70</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
         <is>
           <t>2025/11/26</t>
         </is>
       </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>89046.53661971832</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>5833.0</t>
-        </is>
-      </c>
-      <c r="AX5" t="n">
-        <v>5013.8</v>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>8675.9</t>
-        </is>
-      </c>
-      <c r="AZ5" t="n">
-        <v>12426.06</v>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>-3662</t>
-        </is>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>-561.0546141659527</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>-711.9510754432858</t>
-        </is>
-      </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>5833.0</t>
+          <t>88932.20464135021</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
+          <t>3324.0</t>
+        </is>
+      </c>
+      <c r="BF5" t="n">
+        <v>5108.2</v>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>7304.7</t>
+        </is>
+      </c>
+      <c r="BH5" t="n">
+        <v>12325.42</v>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>-2196</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>-605.8996187432529</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>-852.5471439184039</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>3324.0</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
         <is>
           <t>55.5</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>2025/08/20</t>
         </is>
       </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>-4.68</t>
-        </is>
-      </c>
-      <c r="BI5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>-4.14</t>
+        </is>
+      </c>
+      <c r="BQ5" t="inlineStr">
         <is>
           <t>利機</t>
         </is>
       </c>
-      <c r="BJ5" t="inlineStr">
+      <c r="BR5" t="inlineStr">
         <is>
           <t>利機</t>
         </is>
       </c>
-      <c r="BK5" t="inlineStr">
+      <c r="BS5" t="inlineStr">
         <is>
           <t>電子通路業</t>
         </is>
       </c>
-      <c r="BL5" t="inlineStr">
+      <c r="BT5" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BM5" t="inlineStr">
+      <c r="BU5" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="BN5" t="inlineStr">
+      <c r="BV5" t="inlineStr">
         <is>
           <t>2.973959600876125</t>
         </is>
       </c>
-      <c r="BO5" t="inlineStr">
+      <c r="BW5" t="inlineStr">
         <is>
           <t>7.507647901781631</t>
         </is>
       </c>
-      <c r="BP5" t="inlineStr">
+      <c r="BX5" t="inlineStr">
         <is>
           <t>9.97333412563415</t>
         </is>
       </c>
-      <c r="BQ5" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR5" t="inlineStr">
+      <c r="BY5" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BZ5" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BS5" t="inlineStr">
-        <is>
-          <t>2.29</t>
-        </is>
-      </c>
-      <c r="BT5" t="inlineStr">
+      <c r="CA5" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="CB5" t="inlineStr">
         <is>
           <t>3.82</t>
         </is>
       </c>
-      <c r="BU5" t="inlineStr">
+      <c r="CC5" t="inlineStr">
         <is>
           <t>6.82</t>
         </is>
       </c>
-      <c r="BV5" t="inlineStr">
-        <is>
-          <t>21.43</t>
-        </is>
-      </c>
-      <c r="BW5" t="inlineStr">
+      <c r="CD5" t="inlineStr">
+        <is>
+          <t>21.48</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
         <is>
           <t>20.15%</t>
         </is>
       </c>
-      <c r="BX5" t="inlineStr">
+      <c r="CF5" t="inlineStr">
         <is>
           <t>3.13%</t>
         </is>
       </c>
-      <c r="BY5" t="inlineStr">
-        <is>
-          <t>32.34</t>
-        </is>
-      </c>
-      <c r="BZ5" t="inlineStr">
-        <is>
-          <t>2353</t>
-        </is>
-      </c>
-      <c r="CA5" t="inlineStr">
+      <c r="CG5" t="inlineStr">
+        <is>
+          <t>32.3</t>
+        </is>
+      </c>
+      <c r="CH5" t="inlineStr">
+        <is>
+          <t>2358</t>
+        </is>
+      </c>
+      <c r="CI5" t="inlineStr">
         <is>
           <t>半導體產品60.53%、光電產品37.52%、其他產品1.95% (2024年)</t>
         </is>
       </c>
-      <c r="CB5" t="inlineStr">
+      <c r="CJ5" t="inlineStr">
         <is>
           <t>利機-電子通路業-上櫃</t>
         </is>
       </c>
-      <c r="CC5" t="inlineStr">
+      <c r="CK5" t="inlineStr">
         <is>
           <t>電子通路業右下上櫃</t>
         </is>
       </c>
-      <c r="CD5" t="inlineStr">
-        <is>
-          <t>51.7</t>
-        </is>
-      </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>52.9</t>
-        </is>
-      </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>51.5</t>
-        </is>
-      </c>
-      <c r="CG5" t="inlineStr">
-        <is>
-          <t>52.9</t>
-        </is>
-      </c>
-      <c r="CH5" t="inlineStr">
+      <c r="CL5" t="inlineStr">
+        <is>
+          <t>53.0</t>
+        </is>
+      </c>
+      <c r="CM5" t="inlineStr">
+        <is>
+          <t>53.3</t>
+        </is>
+      </c>
+      <c r="CN5" t="inlineStr">
+        <is>
+          <t>52.4</t>
+        </is>
+      </c>
+      <c r="CO5" t="inlineStr">
+        <is>
+          <t>53.2</t>
+        </is>
+      </c>
+      <c r="CP5" t="inlineStr">
         <is>
           <t>23.11</t>
         </is>
       </c>
-      <c r="CI5" t="inlineStr">
+      <c r="CQ5" t="inlineStr">
         <is>
           <t>** 半導體 - 基板、導線架、IC封裝測試、IC模組、IC通路** 平面顯示器 - 驅動IC** 觸控面板 - 印刷材料** LED照明產業 - 封裝/模組</t>
         </is>
       </c>
-      <c r="CJ5" t="inlineStr">
+      <c r="CR5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2571,12 +2771,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,395 +2786,435 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>52.9</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-0.95</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>-1.33</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-42.21</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-10-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>64.2</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>59.4</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>65.6</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>61.3</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>-10.94</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>4.73</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025/06/05</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>56.7</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>2025/10/22</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>58.5</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>2025/06/11</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>55.7</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>4.03</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>2.72</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>52.27</t>
+        </is>
+      </c>
+      <c r="AP6" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>-6.24</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>-2.97</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>52.46</t>
+        </is>
+      </c>
+      <c r="AU6" t="n">
+        <v>52.18</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>55.66</v>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>57.36</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>29.22</t>
+        </is>
+      </c>
+      <c r="AY6" t="n">
+        <v>-0.83</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>-1.17</v>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>-115.98</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>2025/11/26</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>88932.20464135021</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>5833.0</t>
+        </is>
+      </c>
+      <c r="BF6" t="n">
+        <v>5013.8</v>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>8675.9</t>
+        </is>
+      </c>
+      <c r="BH6" t="n">
+        <v>12426.06</v>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>-3662</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>-561.0546141659527</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>-711.9510754432858</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>5833.0</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>55.5</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>2025/08/20</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>-4.68</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>利機</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>利機</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>電子通路業</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>2.973959600876125</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
+          <t>7.507647901781631</t>
+        </is>
+      </c>
+      <c r="BX6" t="inlineStr">
+        <is>
+          <t>9.97333412563415</t>
+        </is>
+      </c>
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
+          <t>2.29</t>
+        </is>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>3.82</t>
+        </is>
+      </c>
+      <c r="CC6" t="inlineStr">
+        <is>
+          <t>6.82</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
+          <t>21.48</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>20.15%</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
+          <t>3.13%</t>
+        </is>
+      </c>
+      <c r="CG6" t="inlineStr">
+        <is>
+          <t>32.3</t>
+        </is>
+      </c>
+      <c r="CH6" t="inlineStr">
+        <is>
+          <t>2358</t>
+        </is>
+      </c>
+      <c r="CI6" t="inlineStr">
+        <is>
+          <t>半導體產品60.53%、光電產品37.52%、其他產品1.95% (2024年)</t>
+        </is>
+      </c>
+      <c r="CJ6" t="inlineStr">
+        <is>
+          <t>利機-電子通路業-上櫃</t>
+        </is>
+      </c>
+      <c r="CK6" t="inlineStr">
+        <is>
+          <t>電子通路業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CL6" t="inlineStr">
+        <is>
           <t>51.7</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>1.15</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>-0.71</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>-43.86</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2025-10-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2025-10-15 00:00:00</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>64.2</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>59.4</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>65.6</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>61.3</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>-12.96</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>4.73</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>3.31</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>-2.13</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>56.74</t>
-        </is>
-      </c>
-      <c r="AH6" t="n">
-        <v>-1.11</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>-6.39</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>-2.71</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>52.27999999999999</t>
-        </is>
-      </c>
-      <c r="AM6" t="n">
-        <v>52.23</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>55.8</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>57.35</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>24.71</t>
-        </is>
-      </c>
-      <c r="AQ6" t="n">
-        <v>-0.9399999999999999</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>-1.25</v>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>7.3</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>-117.14</t>
-        </is>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>2025/11/26</t>
-        </is>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>89046.53661971832</t>
-        </is>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>4797.0</t>
-        </is>
-      </c>
-      <c r="AX6" t="n">
-        <v>4673.8</v>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>8324.9</t>
-        </is>
-      </c>
-      <c r="AZ6" t="n">
-        <v>12556.78</v>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>-3651</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>-533.6188939337103</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>-754.4941534987138</t>
-        </is>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>4797.0</t>
-        </is>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>55.5</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>2025/08/20</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>-6.85</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>利機</t>
-        </is>
-      </c>
-      <c r="BJ6" t="inlineStr">
-        <is>
-          <t>利機</t>
-        </is>
-      </c>
-      <c r="BK6" t="inlineStr">
-        <is>
-          <t>電子通路業</t>
-        </is>
-      </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="BN6" t="inlineStr">
-        <is>
-          <t>2.973959600876125</t>
-        </is>
-      </c>
-      <c r="BO6" t="inlineStr">
-        <is>
-          <t>7.507647901781631</t>
-        </is>
-      </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>9.97333412563415</t>
-        </is>
-      </c>
-      <c r="BQ6" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR6" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS6" t="inlineStr">
-        <is>
-          <t>2.24</t>
-        </is>
-      </c>
-      <c r="BT6" t="inlineStr">
-        <is>
-          <t>3.82</t>
-        </is>
-      </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>6.82</t>
-        </is>
-      </c>
-      <c r="BV6" t="inlineStr">
-        <is>
-          <t>21.43</t>
-        </is>
-      </c>
-      <c r="BW6" t="inlineStr">
-        <is>
-          <t>20.15%</t>
-        </is>
-      </c>
-      <c r="BX6" t="inlineStr">
-        <is>
-          <t>3.13%</t>
-        </is>
-      </c>
-      <c r="BY6" t="inlineStr">
-        <is>
-          <t>32.34</t>
-        </is>
-      </c>
-      <c r="BZ6" t="inlineStr">
-        <is>
-          <t>2353</t>
-        </is>
-      </c>
-      <c r="CA6" t="inlineStr">
-        <is>
-          <t>半導體產品60.53%、光電產品37.52%、其他產品1.95% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>利機-電子通路業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC6" t="inlineStr">
-        <is>
-          <t>電子通路業右下上櫃</t>
-        </is>
-      </c>
-      <c r="CD6" t="inlineStr">
-        <is>
-          <t>52.5</t>
-        </is>
-      </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>53.0</t>
-        </is>
-      </c>
-      <c r="CF6" t="inlineStr">
+      <c r="CM6" t="inlineStr">
+        <is>
+          <t>52.9</t>
+        </is>
+      </c>
+      <c r="CN6" t="inlineStr">
         <is>
           <t>51.5</t>
         </is>
       </c>
-      <c r="CG6" t="inlineStr">
-        <is>
-          <t>51.7</t>
-        </is>
-      </c>
-      <c r="CH6" t="inlineStr">
+      <c r="CO6" t="inlineStr">
+        <is>
+          <t>52.9</t>
+        </is>
+      </c>
+      <c r="CP6" t="inlineStr">
         <is>
           <t>23.11</t>
         </is>
       </c>
-      <c r="CI6" t="inlineStr">
+      <c r="CQ6" t="inlineStr">
         <is>
           <t>** 半導體 - 基板、導線架、IC封裝測試、IC模組、IC通路** 平面顯示器 - 驅動IC** 觸控面板 - 印刷材料** LED照明產業 - 封裝/模組</t>
         </is>
       </c>
-      <c r="CJ6" t="inlineStr">
+      <c r="CR6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2993,12 +3233,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,7 +3248,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,17 +3258,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-33.34</t>
+          <t>-43.86</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3093,7 +3333,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-11.28</t>
+          <t>-12.96</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3103,300 +3343,340 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025/06/05</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
+          <t>2025/10/22</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>58.5</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>2025/06/11</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>55.7</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>3.31</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>-2.13</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr">
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>81.82</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>78.48</t>
-        </is>
-      </c>
-      <c r="AH7" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>-6.53</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>-2.38</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>52.56</t>
-        </is>
-      </c>
-      <c r="AM7" t="n">
-        <v>52.32</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>55.98</v>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>57.34</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>28.11</t>
-        </is>
+          <t>56.74</t>
+        </is>
+      </c>
+      <c r="AP7" t="n">
+        <v>-1.11</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-0.96</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>-1.33</v>
+        <v>0.1</v>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>-6.39</t>
+        </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
+          <t>-2.71</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>52.27999999999999</t>
+        </is>
+      </c>
+      <c r="AU7" t="n">
+        <v>52.23</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>57.35</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>24.71</t>
+        </is>
+      </c>
+      <c r="AY7" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
           <t>7.3</t>
         </is>
       </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>-118.20</t>
-        </is>
-      </c>
-      <c r="AU7" t="inlineStr">
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>-117.14</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
         <is>
           <t>2025/11/26</t>
         </is>
       </c>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>89046.53661971832</t>
-        </is>
-      </c>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>3296.0</t>
-        </is>
-      </c>
-      <c r="AX7" t="n">
-        <v>5465.4</v>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>8198.7</t>
-        </is>
-      </c>
-      <c r="AZ7" t="n">
-        <v>12704.54</v>
-      </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>-2733</t>
-        </is>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>-493.4597558309824</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr">
-        <is>
-          <t>-677.32375952437</t>
-        </is>
-      </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>3296.0</t>
+          <t>88932.20464135021</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
+          <t>4797.0</t>
+        </is>
+      </c>
+      <c r="BF7" t="n">
+        <v>4673.8</v>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>8324.9</t>
+        </is>
+      </c>
+      <c r="BH7" t="n">
+        <v>12556.78</v>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>-3651</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>-533.6188939337103</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>-754.4941534987138</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>4797.0</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
         <is>
           <t>55.5</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>2025/08/20</t>
         </is>
       </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>-5.05</t>
-        </is>
-      </c>
-      <c r="BI7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>-6.85</t>
+        </is>
+      </c>
+      <c r="BQ7" t="inlineStr">
         <is>
           <t>利機</t>
         </is>
       </c>
-      <c r="BJ7" t="inlineStr">
+      <c r="BR7" t="inlineStr">
         <is>
           <t>利機</t>
         </is>
       </c>
-      <c r="BK7" t="inlineStr">
+      <c r="BS7" t="inlineStr">
         <is>
           <t>電子通路業</t>
         </is>
       </c>
-      <c r="BL7" t="inlineStr">
+      <c r="BT7" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BM7" t="inlineStr">
+      <c r="BU7" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="BN7" t="inlineStr">
+      <c r="BV7" t="inlineStr">
         <is>
           <t>2.973959600876125</t>
         </is>
       </c>
-      <c r="BO7" t="inlineStr">
+      <c r="BW7" t="inlineStr">
         <is>
           <t>7.507647901781631</t>
         </is>
       </c>
-      <c r="BP7" t="inlineStr">
+      <c r="BX7" t="inlineStr">
         <is>
           <t>9.97333412563415</t>
         </is>
       </c>
-      <c r="BQ7" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR7" t="inlineStr">
+      <c r="BY7" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BZ7" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BS7" t="inlineStr">
-        <is>
-          <t>2.28</t>
-        </is>
-      </c>
-      <c r="BT7" t="inlineStr">
+      <c r="CA7" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="CB7" t="inlineStr">
         <is>
           <t>3.82</t>
         </is>
       </c>
-      <c r="BU7" t="inlineStr">
+      <c r="CC7" t="inlineStr">
         <is>
           <t>6.82</t>
         </is>
       </c>
-      <c r="BV7" t="inlineStr">
-        <is>
-          <t>21.43</t>
-        </is>
-      </c>
-      <c r="BW7" t="inlineStr">
+      <c r="CD7" t="inlineStr">
+        <is>
+          <t>21.48</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
         <is>
           <t>20.15%</t>
         </is>
       </c>
-      <c r="BX7" t="inlineStr">
+      <c r="CF7" t="inlineStr">
         <is>
           <t>3.13%</t>
         </is>
       </c>
-      <c r="BY7" t="inlineStr">
-        <is>
-          <t>32.34</t>
-        </is>
-      </c>
-      <c r="BZ7" t="inlineStr">
-        <is>
-          <t>2353</t>
-        </is>
-      </c>
-      <c r="CA7" t="inlineStr">
+      <c r="CG7" t="inlineStr">
+        <is>
+          <t>32.3</t>
+        </is>
+      </c>
+      <c r="CH7" t="inlineStr">
+        <is>
+          <t>2358</t>
+        </is>
+      </c>
+      <c r="CI7" t="inlineStr">
         <is>
           <t>半導體產品60.53%、光電產品37.52%、其他產品1.95% (2024年)</t>
         </is>
       </c>
-      <c r="CB7" t="inlineStr">
+      <c r="CJ7" t="inlineStr">
         <is>
           <t>利機-電子通路業-上櫃</t>
         </is>
       </c>
-      <c r="CC7" t="inlineStr">
+      <c r="CK7" t="inlineStr">
         <is>
           <t>電子通路業右下上櫃</t>
         </is>
       </c>
-      <c r="CD7" t="inlineStr">
-        <is>
-          <t>53.6</t>
-        </is>
-      </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>53.7</t>
-        </is>
-      </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
-      <c r="CG7" t="inlineStr">
-        <is>
-          <t>52.7</t>
-        </is>
-      </c>
-      <c r="CH7" t="inlineStr">
+      <c r="CL7" t="inlineStr">
+        <is>
+          <t>52.5</t>
+        </is>
+      </c>
+      <c r="CM7" t="inlineStr">
+        <is>
+          <t>53.0</t>
+        </is>
+      </c>
+      <c r="CN7" t="inlineStr">
+        <is>
+          <t>51.5</t>
+        </is>
+      </c>
+      <c r="CO7" t="inlineStr">
+        <is>
+          <t>51.7</t>
+        </is>
+      </c>
+      <c r="CP7" t="inlineStr">
         <is>
           <t>23.11</t>
         </is>
       </c>
-      <c r="CI7" t="inlineStr">
+      <c r="CQ7" t="inlineStr">
         <is>
           <t>** 半導體 - 基板、導線架、IC封裝測試、IC模組、IC通路** 平面顯示器 - 驅動IC** 觸控面板 - 印刷材料** LED照明產業 - 封裝/模組</t>
         </is>
       </c>
-      <c r="CJ7" t="inlineStr">
+      <c r="CR7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3415,12 +3695,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>156.0</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3710,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,17 +3720,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-10.85</t>
+          <t>-33.34</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3515,7 +3795,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-10.94</t>
+          <t>-11.28</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3525,300 +3805,340 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025/06/05</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
+          <t>2025/10/22</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>58.5</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>2025/06/11</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>55.7</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>-1.71</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr">
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>88.41</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>71.98</t>
-        </is>
-      </c>
-      <c r="AH8" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>-6.68</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>-2.07</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>52.54</t>
-        </is>
-      </c>
-      <c r="AM8" t="n">
-        <v>52.39</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>56.14</v>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>81.82</t>
+        </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>57.32</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>25.48</t>
-        </is>
+          <t>78.48</t>
+        </is>
+      </c>
+      <c r="AP8" t="n">
+        <v>0.27</v>
       </c>
       <c r="AQ8" t="n">
-        <v>-1.06</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>-1.42</v>
+        <v>0.45</v>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>-6.53</t>
+        </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
+          <t>-2.38</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>52.56</t>
+        </is>
+      </c>
+      <c r="AU8" t="n">
+        <v>52.32</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>55.98</v>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>57.34</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>28.11</t>
+        </is>
+      </c>
+      <c r="AY8" t="n">
+        <v>-0.96</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>-1.33</v>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
           <t>7.3</t>
         </is>
       </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>-119.48</t>
-        </is>
-      </c>
-      <c r="AU8" t="inlineStr">
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>-118.20</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
         <is>
           <t>2025/11/26</t>
         </is>
       </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>89046.53661971832</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>8291.0</t>
-        </is>
-      </c>
-      <c r="AX8" t="n">
-        <v>7519</v>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>8434.2</t>
-        </is>
-      </c>
-      <c r="AZ8" t="n">
-        <v>12897.76</v>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>-915</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>-460.0299369776392</t>
-        </is>
-      </c>
-      <c r="BC8" t="inlineStr">
-        <is>
-          <t>-382.0687767208665</t>
-        </is>
-      </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>8291.0</t>
+          <t>88932.20464135021</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
+          <t>3296.0</t>
+        </is>
+      </c>
+      <c r="BF8" t="n">
+        <v>5465.4</v>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>8198.7</t>
+        </is>
+      </c>
+      <c r="BH8" t="n">
+        <v>12704.54</v>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>-2733</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>-493.4597558309824</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>-677.32375952437</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>3296.0</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
         <is>
           <t>55.5</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>2025/08/20</t>
         </is>
       </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>-4.68</t>
-        </is>
-      </c>
-      <c r="BI8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>-5.05</t>
+        </is>
+      </c>
+      <c r="BQ8" t="inlineStr">
         <is>
           <t>利機</t>
         </is>
       </c>
-      <c r="BJ8" t="inlineStr">
+      <c r="BR8" t="inlineStr">
         <is>
           <t>利機</t>
         </is>
       </c>
-      <c r="BK8" t="inlineStr">
+      <c r="BS8" t="inlineStr">
         <is>
           <t>電子通路業</t>
         </is>
       </c>
-      <c r="BL8" t="inlineStr">
+      <c r="BT8" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BM8" t="inlineStr">
+      <c r="BU8" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="BN8" t="inlineStr">
+      <c r="BV8" t="inlineStr">
         <is>
           <t>2.973959600876125</t>
         </is>
       </c>
-      <c r="BO8" t="inlineStr">
+      <c r="BW8" t="inlineStr">
         <is>
           <t>7.507647901781631</t>
         </is>
       </c>
-      <c r="BP8" t="inlineStr">
+      <c r="BX8" t="inlineStr">
         <is>
           <t>9.97333412563415</t>
         </is>
       </c>
-      <c r="BQ8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
-        </is>
-      </c>
-      <c r="BR8" t="inlineStr">
+      <c r="BY8" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BZ8" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BS8" t="inlineStr">
-        <is>
-          <t>2.29</t>
-        </is>
-      </c>
-      <c r="BT8" t="inlineStr">
+      <c r="CA8" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="CB8" t="inlineStr">
         <is>
           <t>3.82</t>
         </is>
       </c>
-      <c r="BU8" t="inlineStr">
+      <c r="CC8" t="inlineStr">
         <is>
           <t>6.82</t>
         </is>
       </c>
-      <c r="BV8" t="inlineStr">
-        <is>
-          <t>21.43</t>
-        </is>
-      </c>
-      <c r="BW8" t="inlineStr">
+      <c r="CD8" t="inlineStr">
+        <is>
+          <t>21.48</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
         <is>
           <t>20.15%</t>
         </is>
       </c>
-      <c r="BX8" t="inlineStr">
+      <c r="CF8" t="inlineStr">
         <is>
           <t>3.13%</t>
         </is>
       </c>
-      <c r="BY8" t="inlineStr">
-        <is>
-          <t>32.34</t>
-        </is>
-      </c>
-      <c r="BZ8" t="inlineStr">
-        <is>
-          <t>2353</t>
-        </is>
-      </c>
-      <c r="CA8" t="inlineStr">
+      <c r="CG8" t="inlineStr">
+        <is>
+          <t>32.3</t>
+        </is>
+      </c>
+      <c r="CH8" t="inlineStr">
+        <is>
+          <t>2358</t>
+        </is>
+      </c>
+      <c r="CI8" t="inlineStr">
         <is>
           <t>半導體產品60.53%、光電產品37.52%、其他產品1.95% (2024年)</t>
         </is>
       </c>
-      <c r="CB8" t="inlineStr">
+      <c r="CJ8" t="inlineStr">
         <is>
           <t>利機-電子通路業-上櫃</t>
         </is>
       </c>
-      <c r="CC8" t="inlineStr">
+      <c r="CK8" t="inlineStr">
         <is>
           <t>電子通路業右下上櫃</t>
         </is>
       </c>
-      <c r="CD8" t="inlineStr">
-        <is>
-          <t>52.8</t>
-        </is>
-      </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>54.3</t>
-        </is>
-      </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>52.2</t>
-        </is>
-      </c>
-      <c r="CG8" t="inlineStr">
-        <is>
-          <t>52.9</t>
-        </is>
-      </c>
-      <c r="CH8" t="inlineStr">
+      <c r="CL8" t="inlineStr">
+        <is>
+          <t>53.6</t>
+        </is>
+      </c>
+      <c r="CM8" t="inlineStr">
+        <is>
+          <t>53.7</t>
+        </is>
+      </c>
+      <c r="CN8" t="inlineStr">
+        <is>
+          <t>52.6</t>
+        </is>
+      </c>
+      <c r="CO8" t="inlineStr">
+        <is>
+          <t>52.7</t>
+        </is>
+      </c>
+      <c r="CP8" t="inlineStr">
         <is>
           <t>23.11</t>
         </is>
       </c>
-      <c r="CI8" t="inlineStr">
+      <c r="CQ8" t="inlineStr">
         <is>
           <t>** 半導體 - 基板、導線架、IC封裝測試、IC模組、IC通路** 平面顯示器 - 驅動IC** 觸控面板 - 印刷材料** LED照明產業 - 封裝/模組</t>
         </is>
       </c>
-      <c r="CJ8" t="inlineStr">
+      <c r="CR8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3837,12 +4157,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>156.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +4172,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,17 +4182,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>15.25</t>
+          <t>-10.85</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3937,7 +4257,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-12.29</t>
+          <t>-10.94</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3947,300 +4267,340 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025/06/05</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
+          <t>2025/10/22</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>58.5</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>2025/06/11</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>55.7</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>5.62</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>-1.31</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr">
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>65.22</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>73.91</t>
-        </is>
-      </c>
-      <c r="AH9" t="n">
-        <v>-0.99</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>-6.88</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>-1.76</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>52.62</t>
-        </is>
-      </c>
-      <c r="AM9" t="n">
-        <v>52.44</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>56.31</v>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>88.41</t>
+        </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
+          <t>71.98</t>
+        </is>
+      </c>
+      <c r="AP9" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>-6.68</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>-2.07</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>52.54</t>
+        </is>
+      </c>
+      <c r="AU9" t="n">
+        <v>52.39</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>56.14</v>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
           <t>57.32</t>
         </is>
       </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>20.79</t>
-        </is>
-      </c>
-      <c r="AQ9" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>-1.51</v>
-      </c>
-      <c r="AS9" t="inlineStr">
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>25.48</t>
+        </is>
+      </c>
+      <c r="AY9" t="n">
+        <v>-1.06</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>-1.42</v>
+      </c>
+      <c r="BA9" t="inlineStr">
         <is>
           <t>7.3</t>
         </is>
       </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>-120.72</t>
-        </is>
-      </c>
-      <c r="AU9" t="inlineStr">
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>-119.48</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
         <is>
           <t>2025/11/26</t>
         </is>
       </c>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>89046.53661971832</t>
-        </is>
-      </c>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>2852.0</t>
-        </is>
-      </c>
-      <c r="AX9" t="n">
-        <v>9501.200000000001</v>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>8244.2</t>
-        </is>
-      </c>
-      <c r="AZ9" t="n">
-        <v>13064.54</v>
-      </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>1257</t>
-        </is>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>-474.2046933879615</t>
-        </is>
-      </c>
-      <c r="BC9" t="inlineStr">
-        <is>
-          <t>-481.8092021186876</t>
-        </is>
-      </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>2852.0</t>
+          <t>88932.20464135021</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
+          <t>8291.0</t>
+        </is>
+      </c>
+      <c r="BF9" t="n">
+        <v>7519</v>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>8434.2</t>
+        </is>
+      </c>
+      <c r="BH9" t="n">
+        <v>12897.76</v>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>-915</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>-460.0299369776392</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>-382.0687767208665</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>8291.0</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
         <is>
           <t>55.5</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>2025/08/20</t>
         </is>
       </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>-6.13</t>
-        </is>
-      </c>
-      <c r="BI9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>-4.68</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
         <is>
           <t>利機</t>
         </is>
       </c>
-      <c r="BJ9" t="inlineStr">
+      <c r="BR9" t="inlineStr">
         <is>
           <t>利機</t>
         </is>
       </c>
-      <c r="BK9" t="inlineStr">
+      <c r="BS9" t="inlineStr">
         <is>
           <t>電子通路業</t>
         </is>
       </c>
-      <c r="BL9" t="inlineStr">
+      <c r="BT9" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BM9" t="inlineStr">
+      <c r="BU9" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="BN9" t="inlineStr">
+      <c r="BV9" t="inlineStr">
         <is>
           <t>2.973959600876125</t>
         </is>
       </c>
-      <c r="BO9" t="inlineStr">
+      <c r="BW9" t="inlineStr">
         <is>
           <t>7.507647901781631</t>
         </is>
       </c>
-      <c r="BP9" t="inlineStr">
+      <c r="BX9" t="inlineStr">
         <is>
           <t>9.97333412563415</t>
         </is>
       </c>
-      <c r="BQ9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR9" t="inlineStr">
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BS9" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="BT9" t="inlineStr">
+      <c r="CA9" t="inlineStr">
+        <is>
+          <t>2.29</t>
+        </is>
+      </c>
+      <c r="CB9" t="inlineStr">
         <is>
           <t>3.82</t>
         </is>
       </c>
-      <c r="BU9" t="inlineStr">
+      <c r="CC9" t="inlineStr">
         <is>
           <t>6.82</t>
         </is>
       </c>
-      <c r="BV9" t="inlineStr">
-        <is>
-          <t>21.43</t>
-        </is>
-      </c>
-      <c r="BW9" t="inlineStr">
+      <c r="CD9" t="inlineStr">
+        <is>
+          <t>21.48</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
         <is>
           <t>20.15%</t>
         </is>
       </c>
-      <c r="BX9" t="inlineStr">
+      <c r="CF9" t="inlineStr">
         <is>
           <t>3.13%</t>
         </is>
       </c>
-      <c r="BY9" t="inlineStr">
-        <is>
-          <t>32.34</t>
-        </is>
-      </c>
-      <c r="BZ9" t="inlineStr">
-        <is>
-          <t>2353</t>
-        </is>
-      </c>
-      <c r="CA9" t="inlineStr">
+      <c r="CG9" t="inlineStr">
+        <is>
+          <t>32.3</t>
+        </is>
+      </c>
+      <c r="CH9" t="inlineStr">
+        <is>
+          <t>2358</t>
+        </is>
+      </c>
+      <c r="CI9" t="inlineStr">
         <is>
           <t>半導體產品60.53%、光電產品37.52%、其他產品1.95% (2024年)</t>
         </is>
       </c>
-      <c r="CB9" t="inlineStr">
+      <c r="CJ9" t="inlineStr">
         <is>
           <t>利機-電子通路業-上櫃</t>
         </is>
       </c>
-      <c r="CC9" t="inlineStr">
+      <c r="CK9" t="inlineStr">
         <is>
           <t>電子通路業右下上櫃</t>
         </is>
       </c>
-      <c r="CD9" t="inlineStr">
-        <is>
-          <t>52.1</t>
-        </is>
-      </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>53.0</t>
-        </is>
-      </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>52.1</t>
-        </is>
-      </c>
-      <c r="CG9" t="inlineStr">
-        <is>
-          <t>52.1</t>
-        </is>
-      </c>
-      <c r="CH9" t="inlineStr">
+      <c r="CL9" t="inlineStr">
+        <is>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="CM9" t="inlineStr">
+        <is>
+          <t>54.3</t>
+        </is>
+      </c>
+      <c r="CN9" t="inlineStr">
+        <is>
+          <t>52.2</t>
+        </is>
+      </c>
+      <c r="CO9" t="inlineStr">
+        <is>
+          <t>52.9</t>
+        </is>
+      </c>
+      <c r="CP9" t="inlineStr">
         <is>
           <t>23.11</t>
         </is>
       </c>
-      <c r="CI9" t="inlineStr">
+      <c r="CQ9" t="inlineStr">
         <is>
           <t>** 半導體 - 基板、導線架、IC封裝測試、IC模組、IC通路** 平面顯示器 - 驅動IC** 觸控面板 - 印刷材料** LED照明產業 - 封裝/模組</t>
         </is>
       </c>
-      <c r="CJ9" t="inlineStr">
+      <c r="CR9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4259,12 +4619,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4634,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4289,12 +4649,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>43.16</t>
+          <t>15.25</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4359,7 +4719,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-12.46</t>
+          <t>-12.29</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4369,300 +4729,340 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025/06/05</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
+          <t>2025/10/22</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>58.5</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>2025/06/11</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>55.7</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>-0.0</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>-1.73</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr">
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>62.32</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>78.74</t>
-        </is>
-      </c>
-      <c r="AH10" t="n">
-        <v>-1.07</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>-6.98</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>-1.45</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>52.56</t>
-        </is>
-      </c>
-      <c r="AM10" t="n">
-        <v>52.56</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>56.5</v>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>65.22</t>
+        </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>57.33</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>19.82</t>
-        </is>
+          <t>73.91</t>
+        </is>
+      </c>
+      <c r="AP10" t="n">
+        <v>-0.99</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-1.28</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>-1.59</v>
+        <v>0.35</v>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>-6.88</t>
+        </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
+          <t>-1.76</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>52.62</t>
+        </is>
+      </c>
+      <c r="AU10" t="n">
+        <v>52.44</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>56.31</v>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>57.32</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>20.79</t>
+        </is>
+      </c>
+      <c r="AY10" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>-1.51</v>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
           <t>7.3</t>
         </is>
       </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>-121.80</t>
-        </is>
-      </c>
-      <c r="AU10" t="inlineStr">
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>-120.72</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
         <is>
           <t>2025/11/26</t>
         </is>
       </c>
-      <c r="AV10" t="inlineStr">
-        <is>
-          <t>89046.53661971832</t>
-        </is>
-      </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>4133.0</t>
-        </is>
-      </c>
-      <c r="AX10" t="n">
-        <v>12338</v>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>8618.6</t>
-        </is>
-      </c>
-      <c r="AZ10" t="n">
-        <v>13299.38</v>
-      </c>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>3719</t>
-        </is>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>-472.8220554369204</t>
-        </is>
-      </c>
-      <c r="BC10" t="inlineStr">
-        <is>
-          <t>-24.33805261133421</t>
-        </is>
-      </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>4133.0</t>
+          <t>88932.20464135021</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF10" t="inlineStr">
+          <t>2852.0</t>
+        </is>
+      </c>
+      <c r="BF10" t="n">
+        <v>9501.200000000001</v>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>8244.2</t>
+        </is>
+      </c>
+      <c r="BH10" t="n">
+        <v>13064.54</v>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>1257</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>-474.2046933879615</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>-481.8092021186876</t>
+        </is>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>2852.0</t>
+        </is>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
         <is>
           <t>55.5</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr">
+      <c r="BO10" t="inlineStr">
         <is>
           <t>2025/08/20</t>
         </is>
       </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>-6.31</t>
-        </is>
-      </c>
-      <c r="BI10" t="inlineStr">
+      <c r="BP10" t="inlineStr">
+        <is>
+          <t>-6.13</t>
+        </is>
+      </c>
+      <c r="BQ10" t="inlineStr">
         <is>
           <t>利機</t>
         </is>
       </c>
-      <c r="BJ10" t="inlineStr">
+      <c r="BR10" t="inlineStr">
         <is>
           <t>利機</t>
         </is>
       </c>
-      <c r="BK10" t="inlineStr">
+      <c r="BS10" t="inlineStr">
         <is>
           <t>電子通路業</t>
         </is>
       </c>
-      <c r="BL10" t="inlineStr">
+      <c r="BT10" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BM10" t="inlineStr">
+      <c r="BU10" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="BN10" t="inlineStr">
+      <c r="BV10" t="inlineStr">
         <is>
           <t>2.973959600876125</t>
         </is>
       </c>
-      <c r="BO10" t="inlineStr">
+      <c r="BW10" t="inlineStr">
         <is>
           <t>7.507647901781631</t>
         </is>
       </c>
-      <c r="BP10" t="inlineStr">
+      <c r="BX10" t="inlineStr">
         <is>
           <t>9.97333412563415</t>
         </is>
       </c>
-      <c r="BQ10" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR10" t="inlineStr">
+      <c r="BY10" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BZ10" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="BS10" t="inlineStr">
+      <c r="CA10" t="inlineStr">
         <is>
           <t>2.25</t>
         </is>
       </c>
-      <c r="BT10" t="inlineStr">
+      <c r="CB10" t="inlineStr">
         <is>
           <t>3.82</t>
         </is>
       </c>
-      <c r="BU10" t="inlineStr">
+      <c r="CC10" t="inlineStr">
         <is>
           <t>6.82</t>
         </is>
       </c>
-      <c r="BV10" t="inlineStr">
-        <is>
-          <t>21.43</t>
-        </is>
-      </c>
-      <c r="BW10" t="inlineStr">
+      <c r="CD10" t="inlineStr">
+        <is>
+          <t>21.48</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
         <is>
           <t>20.15%</t>
         </is>
       </c>
-      <c r="BX10" t="inlineStr">
+      <c r="CF10" t="inlineStr">
         <is>
           <t>3.13%</t>
         </is>
       </c>
-      <c r="BY10" t="inlineStr">
-        <is>
-          <t>32.34</t>
-        </is>
-      </c>
-      <c r="BZ10" t="inlineStr">
-        <is>
-          <t>2353</t>
-        </is>
-      </c>
-      <c r="CA10" t="inlineStr">
+      <c r="CG10" t="inlineStr">
+        <is>
+          <t>32.3</t>
+        </is>
+      </c>
+      <c r="CH10" t="inlineStr">
+        <is>
+          <t>2358</t>
+        </is>
+      </c>
+      <c r="CI10" t="inlineStr">
         <is>
           <t>半導體產品60.53%、光電產品37.52%、其他產品1.95% (2024年)</t>
         </is>
       </c>
-      <c r="CB10" t="inlineStr">
+      <c r="CJ10" t="inlineStr">
         <is>
           <t>利機-電子通路業-上櫃</t>
         </is>
       </c>
-      <c r="CC10" t="inlineStr">
+      <c r="CK10" t="inlineStr">
         <is>
           <t>電子通路業右下上櫃</t>
         </is>
       </c>
-      <c r="CD10" t="inlineStr">
-        <is>
-          <t>53.5</t>
-        </is>
-      </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>53.6</t>
-        </is>
-      </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>51.9</t>
-        </is>
-      </c>
-      <c r="CG10" t="inlineStr">
-        <is>
-          <t>52.0</t>
-        </is>
-      </c>
-      <c r="CH10" t="inlineStr">
+      <c r="CL10" t="inlineStr">
+        <is>
+          <t>52.1</t>
+        </is>
+      </c>
+      <c r="CM10" t="inlineStr">
+        <is>
+          <t>53.0</t>
+        </is>
+      </c>
+      <c r="CN10" t="inlineStr">
+        <is>
+          <t>52.1</t>
+        </is>
+      </c>
+      <c r="CO10" t="inlineStr">
+        <is>
+          <t>52.1</t>
+        </is>
+      </c>
+      <c r="CP10" t="inlineStr">
         <is>
           <t>23.11</t>
         </is>
       </c>
-      <c r="CI10" t="inlineStr">
+      <c r="CQ10" t="inlineStr">
         <is>
           <t>** 半導體 - 基板、導線架、IC封裝測試、IC模組、IC通路** 平面顯示器 - 驅動IC** 觸控面板 - 印刷材料** LED照明產業 - 封裝/模組</t>
         </is>
       </c>
-      <c r="CJ10" t="inlineStr">
+      <c r="CR10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4671,7 +5071,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4681,12 +5081,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>167.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +5096,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,17 +5106,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>36.29</t>
+          <t>43.16</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4781,7 +5181,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-10.61</t>
+          <t>-12.46</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4791,300 +5191,340 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025/06/05</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
+          <t>2025/10/22</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>58.5</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>2025/06/11</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>55.7</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>-2.88</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr">
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>94.2</t>
-        </is>
-      </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>91.3</t>
-        </is>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>-1.16</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>-6.89</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>-1.15</t>
-        </is>
-      </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>52.16</t>
-        </is>
-      </c>
-      <c r="AM11" t="n">
-        <v>52.77</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>56.68</v>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>62.32</t>
+        </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>57.34</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>19.38</t>
-        </is>
+          <t>78.74</t>
+        </is>
+      </c>
+      <c r="AP11" t="n">
+        <v>-1.07</v>
       </c>
       <c r="AQ11" t="n">
-        <v>-1.35</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>-1.67</v>
+        <v>0</v>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>-6.98</t>
+        </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
+          <t>-1.45</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>52.56</t>
+        </is>
+      </c>
+      <c r="AU11" t="n">
+        <v>52.56</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>57.33</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>19.82</t>
+        </is>
+      </c>
+      <c r="AY11" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>-1.59</v>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
           <t>7.3</t>
         </is>
       </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>-122.88</t>
-        </is>
-      </c>
-      <c r="AU11" t="inlineStr">
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>-121.80</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
         <is>
           <t>2025/11/26</t>
         </is>
       </c>
-      <c r="AV11" t="inlineStr">
-        <is>
-          <t>89046.53661971832</t>
-        </is>
-      </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>8755.0</t>
-        </is>
-      </c>
-      <c r="AX11" t="n">
-        <v>11976</v>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>8787.0</t>
-        </is>
-      </c>
-      <c r="AZ11" t="n">
-        <v>13401.56</v>
-      </c>
-      <c r="BA11" t="inlineStr">
-        <is>
-          <t>3189</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>-554.3646014052089</t>
-        </is>
-      </c>
-      <c r="BC11" t="inlineStr">
-        <is>
-          <t>492.8113771352873</t>
-        </is>
-      </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>8755.0</t>
+          <t>88932.20464135021</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
+          <t>4133.0</t>
+        </is>
+      </c>
+      <c r="BF11" t="n">
+        <v>12338</v>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>8618.6</t>
+        </is>
+      </c>
+      <c r="BH11" t="n">
+        <v>13299.38</v>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>3719</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>-472.8220554369204</t>
+        </is>
+      </c>
+      <c r="BK11" t="inlineStr">
+        <is>
+          <t>-24.33805261133421</t>
+        </is>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>4133.0</t>
+        </is>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
         <is>
           <t>55.5</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr">
+      <c r="BO11" t="inlineStr">
         <is>
           <t>2025/08/20</t>
         </is>
       </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>-4.32</t>
-        </is>
-      </c>
-      <c r="BI11" t="inlineStr">
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>-6.31</t>
+        </is>
+      </c>
+      <c r="BQ11" t="inlineStr">
         <is>
           <t>利機</t>
         </is>
       </c>
-      <c r="BJ11" t="inlineStr">
+      <c r="BR11" t="inlineStr">
         <is>
           <t>利機</t>
         </is>
       </c>
-      <c r="BK11" t="inlineStr">
+      <c r="BS11" t="inlineStr">
         <is>
           <t>電子通路業</t>
         </is>
       </c>
-      <c r="BL11" t="inlineStr">
+      <c r="BT11" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BM11" t="inlineStr">
+      <c r="BU11" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="BN11" t="inlineStr">
+      <c r="BV11" t="inlineStr">
         <is>
           <t>2.973959600876125</t>
         </is>
       </c>
-      <c r="BO11" t="inlineStr">
+      <c r="BW11" t="inlineStr">
         <is>
           <t>7.507647901781631</t>
         </is>
       </c>
-      <c r="BP11" t="inlineStr">
+      <c r="BX11" t="inlineStr">
         <is>
           <t>9.97333412563415</t>
         </is>
       </c>
-      <c r="BQ11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR11" t="inlineStr">
+      <c r="BY11" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BZ11" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BS11" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-      <c r="BT11" t="inlineStr">
+      <c r="CA11" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="CB11" t="inlineStr">
         <is>
           <t>3.82</t>
         </is>
       </c>
-      <c r="BU11" t="inlineStr">
+      <c r="CC11" t="inlineStr">
         <is>
           <t>6.82</t>
         </is>
       </c>
-      <c r="BV11" t="inlineStr">
-        <is>
-          <t>21.43</t>
-        </is>
-      </c>
-      <c r="BW11" t="inlineStr">
+      <c r="CD11" t="inlineStr">
+        <is>
+          <t>21.48</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
         <is>
           <t>20.15%</t>
         </is>
       </c>
-      <c r="BX11" t="inlineStr">
+      <c r="CF11" t="inlineStr">
         <is>
           <t>3.13%</t>
         </is>
       </c>
-      <c r="BY11" t="inlineStr">
-        <is>
-          <t>32.34</t>
-        </is>
-      </c>
-      <c r="BZ11" t="inlineStr">
-        <is>
-          <t>2353</t>
-        </is>
-      </c>
-      <c r="CA11" t="inlineStr">
+      <c r="CG11" t="inlineStr">
+        <is>
+          <t>32.3</t>
+        </is>
+      </c>
+      <c r="CH11" t="inlineStr">
+        <is>
+          <t>2358</t>
+        </is>
+      </c>
+      <c r="CI11" t="inlineStr">
         <is>
           <t>半導體產品60.53%、光電產品37.52%、其他產品1.95% (2024年)</t>
         </is>
       </c>
-      <c r="CB11" t="inlineStr">
+      <c r="CJ11" t="inlineStr">
         <is>
           <t>利機-電子通路業-上櫃</t>
         </is>
       </c>
-      <c r="CC11" t="inlineStr">
+      <c r="CK11" t="inlineStr">
         <is>
           <t>電子通路業右下上櫃</t>
         </is>
       </c>
-      <c r="CD11" t="inlineStr">
-        <is>
-          <t>52.9</t>
-        </is>
-      </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>53.3</t>
-        </is>
-      </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>51.7</t>
-        </is>
-      </c>
-      <c r="CG11" t="inlineStr">
-        <is>
-          <t>53.1</t>
-        </is>
-      </c>
-      <c r="CH11" t="inlineStr">
+      <c r="CL11" t="inlineStr">
+        <is>
+          <t>53.5</t>
+        </is>
+      </c>
+      <c r="CM11" t="inlineStr">
+        <is>
+          <t>53.6</t>
+        </is>
+      </c>
+      <c r="CN11" t="inlineStr">
+        <is>
+          <t>51.9</t>
+        </is>
+      </c>
+      <c r="CO11" t="inlineStr">
+        <is>
+          <t>52.0</t>
+        </is>
+      </c>
+      <c r="CP11" t="inlineStr">
         <is>
           <t>23.11</t>
         </is>
       </c>
-      <c r="CI11" t="inlineStr">
+      <c r="CQ11" t="inlineStr">
         <is>
           <t>** 半導體 - 基板、導線架、IC封裝測試、IC模組、IC通路** 平面顯示器 - 驅動IC** 觸控面板 - 印刷材料** LED照明產業 - 封裝/模組</t>
         </is>
       </c>
-      <c r="CJ11" t="inlineStr">
+      <c r="CR11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5103,12 +5543,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>255.0</t>
+          <t>167.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5558,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,17 +5568,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>26.75</t>
+          <t>36.29</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5203,7 +5643,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-11.45</t>
+          <t>-10.61</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5213,300 +5653,340 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025/06/05</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>9.19</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
+          <t>2025/10/22</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>58.5</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>2025/06/11</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>55.7</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>6.02</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="inlineStr">
+      <c r="AK12" t="inlineStr"/>
+      <c r="AL12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>79.71</t>
-        </is>
-      </c>
-      <c r="AG12" t="inlineStr">
-        <is>
-          <t>73.88</t>
-        </is>
-      </c>
-      <c r="AH12" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>-2.63</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>-6.92</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>-0.86</t>
-        </is>
-      </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>51.51000000000001</t>
-        </is>
-      </c>
-      <c r="AM12" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>56.83</v>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>94.2</t>
+        </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>57.32</t>
-        </is>
-      </c>
-      <c r="AP12" t="inlineStr">
-        <is>
-          <t>12.69</t>
-        </is>
+          <t>91.3</t>
+        </is>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.8</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-1.53</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>-1.75</v>
+        <v>-1.16</v>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>-6.89</t>
+        </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
+          <t>-1.15</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>52.16</t>
+        </is>
+      </c>
+      <c r="AU12" t="n">
+        <v>52.77</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>56.68</v>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>57.34</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>19.38</t>
+        </is>
+      </c>
+      <c r="AY12" t="n">
+        <v>-1.35</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>-1.67</v>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
           <t>7.3</t>
         </is>
       </c>
-      <c r="AT12" t="inlineStr">
-        <is>
-          <t>-123.99</t>
-        </is>
-      </c>
-      <c r="AU12" t="inlineStr">
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>-122.88</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
         <is>
           <t>2025/11/26</t>
         </is>
       </c>
-      <c r="AV12" t="inlineStr">
-        <is>
-          <t>89046.53661971832</t>
-        </is>
-      </c>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>13564.0</t>
-        </is>
-      </c>
-      <c r="AX12" t="n">
-        <v>10932</v>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>8624.8</t>
-        </is>
-      </c>
-      <c r="AZ12" t="n">
-        <v>13461.08</v>
-      </c>
-      <c r="BA12" t="inlineStr">
-        <is>
-          <t>2307</t>
-        </is>
-      </c>
-      <c r="BB12" t="inlineStr">
-        <is>
-          <t>-744.7602338671172</t>
-        </is>
-      </c>
-      <c r="BC12" t="inlineStr">
-        <is>
-          <t>718.7815847327729</t>
-        </is>
-      </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>13564.0</t>
+          <t>88932.20464135021</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF12" t="inlineStr">
+          <t>8755.0</t>
+        </is>
+      </c>
+      <c r="BF12" t="n">
+        <v>11976</v>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>8787.0</t>
+        </is>
+      </c>
+      <c r="BH12" t="n">
+        <v>13401.56</v>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>3189</t>
+        </is>
+      </c>
+      <c r="BJ12" t="inlineStr">
+        <is>
+          <t>-554.3646014052089</t>
+        </is>
+      </c>
+      <c r="BK12" t="inlineStr">
+        <is>
+          <t>492.8113771352873</t>
+        </is>
+      </c>
+      <c r="BL12" t="inlineStr">
+        <is>
+          <t>8755.0</t>
+        </is>
+      </c>
+      <c r="BM12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BN12" t="inlineStr">
         <is>
           <t>55.5</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr">
+      <c r="BO12" t="inlineStr">
         <is>
           <t>2025/08/20</t>
         </is>
       </c>
-      <c r="BH12" t="inlineStr">
-        <is>
-          <t>-5.23</t>
-        </is>
-      </c>
-      <c r="BI12" t="inlineStr">
+      <c r="BP12" t="inlineStr">
+        <is>
+          <t>-4.32</t>
+        </is>
+      </c>
+      <c r="BQ12" t="inlineStr">
         <is>
           <t>利機</t>
         </is>
       </c>
-      <c r="BJ12" t="inlineStr">
+      <c r="BR12" t="inlineStr">
         <is>
           <t>利機</t>
         </is>
       </c>
-      <c r="BK12" t="inlineStr">
+      <c r="BS12" t="inlineStr">
         <is>
           <t>電子通路業</t>
         </is>
       </c>
-      <c r="BL12" t="inlineStr">
+      <c r="BT12" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BM12" t="inlineStr">
+      <c r="BU12" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="BN12" t="inlineStr">
+      <c r="BV12" t="inlineStr">
         <is>
           <t>2.973959600876125</t>
         </is>
       </c>
-      <c r="BO12" t="inlineStr">
+      <c r="BW12" t="inlineStr">
         <is>
           <t>7.507647901781631</t>
         </is>
       </c>
-      <c r="BP12" t="inlineStr">
+      <c r="BX12" t="inlineStr">
         <is>
           <t>9.97333412563415</t>
         </is>
       </c>
-      <c r="BQ12" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR12" t="inlineStr">
+      <c r="BY12" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BZ12" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BS12" t="inlineStr">
-        <is>
-          <t>2.28</t>
-        </is>
-      </c>
-      <c r="BT12" t="inlineStr">
+      <c r="CA12" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="CB12" t="inlineStr">
         <is>
           <t>3.82</t>
         </is>
       </c>
-      <c r="BU12" t="inlineStr">
+      <c r="CC12" t="inlineStr">
         <is>
           <t>6.82</t>
         </is>
       </c>
-      <c r="BV12" t="inlineStr">
-        <is>
-          <t>21.43</t>
-        </is>
-      </c>
-      <c r="BW12" t="inlineStr">
+      <c r="CD12" t="inlineStr">
+        <is>
+          <t>21.48</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
         <is>
           <t>20.15%</t>
         </is>
       </c>
-      <c r="BX12" t="inlineStr">
+      <c r="CF12" t="inlineStr">
         <is>
           <t>3.13%</t>
         </is>
       </c>
-      <c r="BY12" t="inlineStr">
-        <is>
-          <t>32.34</t>
-        </is>
-      </c>
-      <c r="BZ12" t="inlineStr">
-        <is>
-          <t>2353</t>
-        </is>
-      </c>
-      <c r="CA12" t="inlineStr">
+      <c r="CG12" t="inlineStr">
+        <is>
+          <t>32.3</t>
+        </is>
+      </c>
+      <c r="CH12" t="inlineStr">
+        <is>
+          <t>2358</t>
+        </is>
+      </c>
+      <c r="CI12" t="inlineStr">
         <is>
           <t>半導體產品60.53%、光電產品37.52%、其他產品1.95% (2024年)</t>
         </is>
       </c>
-      <c r="CB12" t="inlineStr">
+      <c r="CJ12" t="inlineStr">
         <is>
           <t>利機-電子通路業-上櫃</t>
         </is>
       </c>
-      <c r="CC12" t="inlineStr">
+      <c r="CK12" t="inlineStr">
         <is>
           <t>電子通路業右下上櫃</t>
         </is>
       </c>
-      <c r="CD12" t="inlineStr">
-        <is>
-          <t>53.6</t>
-        </is>
-      </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>54.1</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
-      <c r="CG12" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
-      <c r="CH12" t="inlineStr">
+      <c r="CL12" t="inlineStr">
+        <is>
+          <t>52.9</t>
+        </is>
+      </c>
+      <c r="CM12" t="inlineStr">
+        <is>
+          <t>53.3</t>
+        </is>
+      </c>
+      <c r="CN12" t="inlineStr">
+        <is>
+          <t>51.7</t>
+        </is>
+      </c>
+      <c r="CO12" t="inlineStr">
+        <is>
+          <t>53.1</t>
+        </is>
+      </c>
+      <c r="CP12" t="inlineStr">
         <is>
           <t>23.11</t>
         </is>
       </c>
-      <c r="CI12" t="inlineStr">
+      <c r="CQ12" t="inlineStr">
         <is>
           <t>** 半導體 - 基板、導線架、IC封裝測試、IC模組、IC通路** 平面顯示器 - 驅動IC** 觸控面板 - 印刷材料** LED照明產業 - 封裝/模組</t>
         </is>
       </c>
-      <c r="CJ12" t="inlineStr">
+      <c r="CR12" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/印刷材料.xlsx
+++ b/Result/checksun_type/印刷材料.xlsx
@@ -923,12 +923,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>277.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -953,12 +953,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>13.27</t>
+          <t>22.50</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-11.78</t>
+          <t>-8.92</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1068,22 +1068,22 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -1099,61 +1099,61 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>277</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>46.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>51.11</t>
+          <t>62.22</t>
         </is>
       </c>
       <c r="AP2" t="n">
-        <v>-0.57</v>
+        <v>2.19</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.41</v>
+        <v>1.62</v>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-5.87</t>
+          <t>-5.52</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.94000000000001</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>51.97</v>
+        <v>52.1</v>
       </c>
       <c r="AV2" t="n">
-        <v>55.21</v>
+        <v>55.14</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>57.22</t>
+          <t>57.16</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>32.10</t>
+          <t>46.74</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>-0.57</v>
+        <v>-0.4</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-0.84</v>
+        <v>-0.75</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-111.54</t>
+          <t>-110.33</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
@@ -1172,43 +1172,43 @@
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>88932.20464135021</t>
+          <t>88838.76825842698</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>5171.0</t>
+          <t>14937.0</t>
         </is>
       </c>
       <c r="BF2" t="n">
-        <v>6103.8</v>
+        <v>7924.6</v>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>5388.8</t>
+          <t>6469.2</t>
         </is>
       </c>
       <c r="BH2" t="n">
-        <v>12016.5</v>
+        <v>12221.38</v>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>1455</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>-543.1638280056386</t>
+          <t>-416.3587527715858</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>-416.1188505990758</t>
+          <t>281.0691610157046</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>5171.0</t>
+          <t>14937.0</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-5.59</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1273,22 +1273,22 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>21.48</t>
+          <t>22.17</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>32.3</t>
+          <t>32.43</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>2358</t>
+          <t>2434</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1338,22 +1338,22 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>55.2</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="CO2" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="CP2" t="inlineStr">
@@ -1385,12 +1385,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1410,17 +1410,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>13.27</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-11.95</t>
+          <t>-11.78</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1530,22 +1530,22 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -1561,61 +1561,61 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>277</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>46.67</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>68.89</t>
+          <t>51.11</t>
         </is>
       </c>
       <c r="AP3" t="n">
-        <v>-0.49</v>
+        <v>-0.57</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.13</v>
+        <v>1.41</v>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-6.04</t>
+          <t>-5.87</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>52.56</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="AU3" t="n">
         <v>51.97</v>
       </c>
       <c r="AV3" t="n">
-        <v>55.31</v>
+        <v>55.21</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.22</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>33.19</t>
+          <t>32.10</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>-0.61</v>
+        <v>-0.57</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-0.91</v>
+        <v>-0.84</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-112.47</t>
+          <t>-111.54</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
@@ -1634,43 +1634,43 @@
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>88932.20464135021</t>
+          <t>88838.76825842698</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>8509.0</t>
+          <t>5171.0</t>
         </is>
       </c>
       <c r="BF3" t="n">
-        <v>6029</v>
+        <v>6103.8</v>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>5747.2</t>
+          <t>5388.8</t>
         </is>
       </c>
       <c r="BH3" t="n">
-        <v>12110</v>
+        <v>12016.5</v>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>715</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>-566.2629148068319</t>
+          <t>-543.1638280056386</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>-350.8831939559377</t>
+          <t>-416.1188505990758</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>8509.0</t>
+          <t>5171.0</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-5.77</t>
+          <t>-5.59</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1745,12 +1745,12 @@
       </c>
       <c r="CA3" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>21.48</t>
+          <t>22.17</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>32.3</t>
+          <t>32.43</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>2358</t>
+          <t>2434</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
@@ -1800,22 +1800,22 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>53.4</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CO3" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="CP3" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1872,17 +1872,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-20.25</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-11.28</t>
+          <t>-11.95</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1992,22 +1992,22 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -2023,61 +2023,61 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>277</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>80.56</t>
+          <t>68.89</t>
         </is>
       </c>
       <c r="AP4" t="n">
-        <v>0.11</v>
+        <v>-0.49</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-6.01</t>
+          <t>-6.04</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>-3.40</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>52.64</t>
+          <t>52.56</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>52.08</v>
+        <v>51.97</v>
       </c>
       <c r="AV4" t="n">
-        <v>55.41</v>
+        <v>55.31</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>57.36</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>35.57</t>
+          <t>33.19</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>-0.63</v>
+        <v>-0.61</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-0.99</v>
+        <v>-0.91</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-113.50</t>
+          <t>-112.47</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
@@ -2096,43 +2096,43 @@
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>88932.20464135021</t>
+          <t>88838.76825842698</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>7682.0</t>
+          <t>8509.0</t>
         </is>
       </c>
       <c r="BF4" t="n">
-        <v>4986.4</v>
+        <v>6029</v>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>6252.7</t>
+          <t>5747.2</t>
         </is>
       </c>
       <c r="BH4" t="n">
-        <v>12234.7</v>
+        <v>12110</v>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>-1266</t>
+          <t>281</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>-605.422864052449</t>
+          <t>-566.2629148068319</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>-602.8007132530274</t>
+          <t>-350.8831939559377</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>7682.0</t>
+          <t>8509.0</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>-5.05</t>
+          <t>-5.77</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2177,7 +2177,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2197,7 +2197,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2207,12 +2207,12 @@
       </c>
       <c r="CA4" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>21.48</t>
+          <t>22.17</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2237,12 +2237,12 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>32.3</t>
+          <t>32.43</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>2358</t>
+          <t>2434</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
@@ -2262,22 +2262,22 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>54.8</t>
+          <t>53.4</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="CO4" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CP4" t="inlineStr">
@@ -2309,12 +2309,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2334,17 +2334,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-30.07</t>
+          <t>-20.25</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-10.44</t>
+          <t>-11.28</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2454,22 +2454,22 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -2485,61 +2485,61 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>277</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>58.33</t>
+          <t>80.56</t>
         </is>
       </c>
       <c r="AP5" t="n">
-        <v>0.99</v>
+        <v>0.11</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-6.06</t>
+          <t>-6.01</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-3.40</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>52.67999999999999</t>
+          <t>52.64</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>52.16</v>
+        <v>52.08</v>
       </c>
       <c r="AV5" t="n">
-        <v>55.52</v>
+        <v>55.41</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>57.37</t>
+          <t>57.36</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>34.70</t>
+          <t>35.57</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>-0.7</v>
+        <v>-0.63</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-1.07</v>
+        <v>-0.99</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-114.70</t>
+          <t>-113.50</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
@@ -2558,43 +2558,43 @@
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>88932.20464135021</t>
+          <t>88838.76825842698</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>3324.0</t>
+          <t>7682.0</t>
         </is>
       </c>
       <c r="BF5" t="n">
-        <v>5108.2</v>
+        <v>4986.4</v>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>7304.7</t>
+          <t>6252.7</t>
         </is>
       </c>
       <c r="BH5" t="n">
-        <v>12325.42</v>
+        <v>12234.7</v>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>-2196</t>
+          <t>-1266</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>-605.8996187432529</t>
+          <t>-605.422864052449</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>-852.5471439184039</t>
+          <t>-602.8007132530274</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>3324.0</t>
+          <t>7682.0</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-5.05</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2669,12 +2669,12 @@
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>21.48</t>
+          <t>22.17</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2699,12 +2699,12 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>32.3</t>
+          <t>32.43</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>2358</t>
+          <t>2434</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
@@ -2724,22 +2724,22 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>54.8</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CO5" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CP5" t="inlineStr">
@@ -2771,12 +2771,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2796,17 +2796,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-42.21</t>
+          <t>-30.07</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-10.94</t>
+          <t>-10.44</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -2947,61 +2947,61 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>277</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>52.27</t>
+          <t>58.33</t>
         </is>
       </c>
       <c r="AP6" t="n">
-        <v>0.84</v>
+        <v>0.99</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.53</v>
+        <v>1</v>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-6.24</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>52.46</t>
+          <t>52.67999999999999</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>52.18</v>
+        <v>52.16</v>
       </c>
       <c r="AV6" t="n">
-        <v>55.66</v>
+        <v>55.52</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>57.36</t>
+          <t>57.37</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>29.22</t>
+          <t>34.70</t>
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>-0.83</v>
+        <v>-0.7</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-1.17</v>
+        <v>-1.07</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-115.98</t>
+          <t>-114.70</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -3020,43 +3020,43 @@
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>88932.20464135021</t>
+          <t>88838.76825842698</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>5833.0</t>
+          <t>3324.0</t>
         </is>
       </c>
       <c r="BF6" t="n">
-        <v>5013.8</v>
+        <v>5108.2</v>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>8675.9</t>
+          <t>7304.7</t>
         </is>
       </c>
       <c r="BH6" t="n">
-        <v>12426.06</v>
+        <v>12325.42</v>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>-3662</t>
+          <t>-2196</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>-561.0546141659527</t>
+          <t>-605.8996187432529</t>
         </is>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>-711.9510754432858</t>
+          <t>-852.5471439184039</t>
         </is>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>5833.0</t>
+          <t>3324.0</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="CA6" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>21.48</t>
+          <t>22.17</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>32.3</t>
+          <t>32.43</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>2358</t>
+          <t>2434</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
@@ -3186,22 +3186,22 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="CO6" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CP6" t="inlineStr">
@@ -3233,12 +3233,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3258,17 +3258,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-43.86</t>
+          <t>-42.21</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-12.96</t>
+          <t>-10.94</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3378,22 +3378,22 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -3409,61 +3409,61 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>277</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>56.74</t>
+          <t>52.27</t>
         </is>
       </c>
       <c r="AP7" t="n">
-        <v>-1.11</v>
+        <v>0.84</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.1</v>
+        <v>0.53</v>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-6.39</t>
+          <t>-6.24</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>-2.71</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>52.27999999999999</t>
+          <t>52.46</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>52.23</v>
+        <v>52.18</v>
       </c>
       <c r="AV7" t="n">
-        <v>55.8</v>
+        <v>55.66</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>57.35</t>
+          <t>57.36</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>29.22</t>
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.83</v>
       </c>
       <c r="AZ7" t="n">
-        <v>-1.25</v>
+        <v>-1.17</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-117.14</t>
+          <t>-115.98</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
@@ -3482,43 +3482,43 @@
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>88932.20464135021</t>
+          <t>88838.76825842698</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>4797.0</t>
+          <t>5833.0</t>
         </is>
       </c>
       <c r="BF7" t="n">
-        <v>4673.8</v>
+        <v>5013.8</v>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>8324.9</t>
+          <t>8675.9</t>
         </is>
       </c>
       <c r="BH7" t="n">
-        <v>12556.78</v>
+        <v>12426.06</v>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>-3651</t>
+          <t>-3662</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>-533.6188939337103</t>
+          <t>-561.0546141659527</t>
         </is>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>-754.4941534987138</t>
+          <t>-711.9510754432858</t>
         </is>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>4797.0</t>
+          <t>5833.0</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-6.85</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="CA7" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>21.48</t>
+          <t>22.17</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>32.3</t>
+          <t>32.43</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>2358</t>
+          <t>2434</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
@@ -3648,12 +3648,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="CO7" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="CP7" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3720,17 +3720,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-33.34</t>
+          <t>-43.86</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-11.28</t>
+          <t>-12.96</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3840,22 +3840,22 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -3871,61 +3871,61 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>277</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>81.82</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>78.48</t>
+          <t>56.74</t>
         </is>
       </c>
       <c r="AP8" t="n">
-        <v>0.27</v>
+        <v>-1.11</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.45</v>
+        <v>0.1</v>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-6.53</t>
+          <t>-6.39</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-2.71</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>52.56</t>
+          <t>52.27999999999999</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>52.32</v>
+        <v>52.23</v>
       </c>
       <c r="AV8" t="n">
-        <v>55.98</v>
+        <v>55.8</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>57.34</t>
+          <t>57.35</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>28.11</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AY8" t="n">
-        <v>-0.96</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AZ8" t="n">
-        <v>-1.33</v>
+        <v>-1.25</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-118.20</t>
+          <t>-117.14</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
@@ -3944,43 +3944,43 @@
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>88932.20464135021</t>
+          <t>88838.76825842698</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>3296.0</t>
+          <t>4797.0</t>
         </is>
       </c>
       <c r="BF8" t="n">
-        <v>5465.4</v>
+        <v>4673.8</v>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>8198.7</t>
+          <t>8324.9</t>
         </is>
       </c>
       <c r="BH8" t="n">
-        <v>12704.54</v>
+        <v>12556.78</v>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>-2733</t>
+          <t>-3651</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>-493.4597558309824</t>
+          <t>-533.6188939337103</t>
         </is>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>-677.32375952437</t>
+          <t>-754.4941534987138</t>
         </is>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>3296.0</t>
+          <t>4797.0</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-5.05</t>
+          <t>-6.85</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -4055,12 +4055,12 @@
       </c>
       <c r="CA8" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>21.48</t>
+          <t>22.17</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>32.3</t>
+          <t>32.43</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>2358</t>
+          <t>2434</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
@@ -4110,22 +4110,22 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="CO8" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CP8" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>156.0</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4182,17 +4182,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-10.85</t>
+          <t>-33.34</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-10.94</t>
+          <t>-11.28</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4302,22 +4302,22 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -4333,61 +4333,61 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>277</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>88.41</t>
+          <t>81.82</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>71.98</t>
+          <t>78.48</t>
         </is>
       </c>
       <c r="AP9" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.27</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.29</v>
+        <v>0.45</v>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-6.68</t>
+          <t>-6.53</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>52.54</t>
+          <t>52.56</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>52.39</v>
+        <v>52.32</v>
       </c>
       <c r="AV9" t="n">
-        <v>56.14</v>
+        <v>55.98</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>57.32</t>
+          <t>57.34</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>25.48</t>
+          <t>28.11</t>
         </is>
       </c>
       <c r="AY9" t="n">
-        <v>-1.06</v>
+        <v>-0.96</v>
       </c>
       <c r="AZ9" t="n">
-        <v>-1.42</v>
+        <v>-1.33</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-119.48</t>
+          <t>-118.20</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -4406,43 +4406,43 @@
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>88932.20464135021</t>
+          <t>88838.76825842698</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>8291.0</t>
+          <t>3296.0</t>
         </is>
       </c>
       <c r="BF9" t="n">
-        <v>7519</v>
+        <v>5465.4</v>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>8434.2</t>
+          <t>8198.7</t>
         </is>
       </c>
       <c r="BH9" t="n">
-        <v>12897.76</v>
+        <v>12704.54</v>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>-915</t>
+          <t>-2733</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>-460.0299369776392</t>
+          <t>-493.4597558309824</t>
         </is>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>-382.0687767208665</t>
+          <t>-677.32375952437</t>
         </is>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>8291.0</t>
+          <t>3296.0</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-5.05</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4517,12 +4517,12 @@
       </c>
       <c r="CA9" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>21.48</t>
+          <t>22.17</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>32.3</t>
+          <t>32.43</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>2358</t>
+          <t>2434</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
@@ -4572,22 +4572,22 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>54.3</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CO9" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CP9" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>156.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4644,17 +4644,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>15.25</t>
+          <t>-10.85</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-12.29</t>
+          <t>-10.94</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4764,22 +4764,22 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -4795,45 +4795,45 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>277</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>65.22</t>
+          <t>88.41</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>73.91</t>
+          <t>71.98</t>
         </is>
       </c>
       <c r="AP10" t="n">
-        <v>-0.99</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.35</v>
+        <v>0.29</v>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-6.88</t>
+          <t>-6.68</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>52.62</t>
+          <t>52.54</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>52.44</v>
+        <v>52.39</v>
       </c>
       <c r="AV10" t="n">
-        <v>56.31</v>
+        <v>56.14</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
@@ -4842,14 +4842,14 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>20.79</t>
+          <t>25.48</t>
         </is>
       </c>
       <c r="AY10" t="n">
-        <v>-1.2</v>
+        <v>-1.06</v>
       </c>
       <c r="AZ10" t="n">
-        <v>-1.51</v>
+        <v>-1.42</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4858,7 +4858,7 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-120.72</t>
+          <t>-119.48</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
@@ -4868,43 +4868,43 @@
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>88932.20464135021</t>
+          <t>88838.76825842698</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>2852.0</t>
+          <t>8291.0</t>
         </is>
       </c>
       <c r="BF10" t="n">
-        <v>9501.200000000001</v>
+        <v>7519</v>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>8244.2</t>
+          <t>8434.2</t>
         </is>
       </c>
       <c r="BH10" t="n">
-        <v>13064.54</v>
+        <v>12897.76</v>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>1257</t>
+          <t>-915</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>-474.2046933879615</t>
+          <t>-460.0299369776392</t>
         </is>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>-481.8092021186876</t>
+          <t>-382.0687767208665</t>
         </is>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>2852.0</t>
+          <t>8291.0</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>-6.13</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4979,12 +4979,12 @@
       </c>
       <c r="CA10" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>21.48</t>
+          <t>22.17</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>32.3</t>
+          <t>32.43</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>2358</t>
+          <t>2434</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
@@ -5034,22 +5034,22 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>54.3</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CO10" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="CP10" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5106,17 +5106,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>43.16</t>
+          <t>15.25</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-12.46</t>
+          <t>-12.29</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5226,22 +5226,22 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -5257,61 +5257,61 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>277</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>62.32</t>
+          <t>65.22</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>78.74</t>
+          <t>73.91</t>
         </is>
       </c>
       <c r="AP11" t="n">
-        <v>-1.07</v>
+        <v>-0.99</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-6.98</t>
+          <t>-6.88</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>52.56</t>
+          <t>52.62</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>52.56</v>
+        <v>52.44</v>
       </c>
       <c r="AV11" t="n">
-        <v>56.5</v>
+        <v>56.31</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>57.33</t>
+          <t>57.32</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>19.82</t>
+          <t>20.79</t>
         </is>
       </c>
       <c r="AY11" t="n">
-        <v>-1.28</v>
+        <v>-1.2</v>
       </c>
       <c r="AZ11" t="n">
-        <v>-1.59</v>
+        <v>-1.51</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-121.80</t>
+          <t>-120.72</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
@@ -5330,43 +5330,43 @@
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>88932.20464135021</t>
+          <t>88838.76825842698</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>4133.0</t>
+          <t>2852.0</t>
         </is>
       </c>
       <c r="BF11" t="n">
-        <v>12338</v>
+        <v>9501.200000000001</v>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>8618.6</t>
+          <t>8244.2</t>
         </is>
       </c>
       <c r="BH11" t="n">
-        <v>13299.38</v>
+        <v>13064.54</v>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>3719</t>
+          <t>1257</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>-472.8220554369204</t>
+          <t>-474.2046933879615</t>
         </is>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>-24.33805261133421</t>
+          <t>-481.8092021186876</t>
         </is>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>4133.0</t>
+          <t>2852.0</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>-6.31</t>
+          <t>-6.13</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="CC11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>21.48</t>
+          <t>22.17</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5471,12 +5471,12 @@
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>32.3</t>
+          <t>32.43</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>2358</t>
+          <t>2434</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
@@ -5496,22 +5496,22 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CO11" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CP11" t="inlineStr">
@@ -5533,7 +5533,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>167.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5558,7 +5558,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5568,17 +5568,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>36.29</t>
+          <t>43.16</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-10.61</t>
+          <t>-12.46</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5688,22 +5688,22 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -5719,61 +5719,61 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>277</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>94.2</t>
+          <t>62.32</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>78.74</t>
         </is>
       </c>
       <c r="AP12" t="n">
-        <v>1.8</v>
+        <v>-1.07</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-1.16</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-6.89</t>
+          <t>-6.98</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>52.16</t>
+          <t>52.56</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>52.77</v>
+        <v>52.56</v>
       </c>
       <c r="AV12" t="n">
-        <v>56.68</v>
+        <v>56.5</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>57.34</t>
+          <t>57.33</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>19.38</t>
+          <t>19.82</t>
         </is>
       </c>
       <c r="AY12" t="n">
-        <v>-1.35</v>
+        <v>-1.28</v>
       </c>
       <c r="AZ12" t="n">
-        <v>-1.67</v>
+        <v>-1.59</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-122.88</t>
+          <t>-121.80</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
@@ -5792,43 +5792,43 @@
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>88932.20464135021</t>
+          <t>88838.76825842698</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>8755.0</t>
+          <t>4133.0</t>
         </is>
       </c>
       <c r="BF12" t="n">
-        <v>11976</v>
+        <v>12338</v>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>8787.0</t>
+          <t>8618.6</t>
         </is>
       </c>
       <c r="BH12" t="n">
-        <v>13401.56</v>
+        <v>13299.38</v>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>3719</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>-554.3646014052089</t>
+          <t>-472.8220554369204</t>
         </is>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>492.8113771352873</t>
+          <t>-24.33805261133421</t>
         </is>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>8755.0</t>
+          <t>4133.0</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5848,7 +5848,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-6.31</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="CA12" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="CC12" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>21.48</t>
+          <t>22.17</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>32.3</t>
+          <t>32.43</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>2358</t>
+          <t>2434</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
@@ -5958,22 +5958,22 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CO12" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CP12" t="inlineStr">

--- a/Result/checksun_type/印刷材料.xlsx
+++ b/Result/checksun_type/印刷材料.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CR12"/>
+  <dimension ref="A1:CV12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,345 +566,365 @@
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
+          <t>MACD_hist_diff</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
           <t>MA_death_cross_d</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d收盤價</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d2</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d2收盤價</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>MACD_hist_diff</t>
-        </is>
-      </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
+          <t>MACD_death_cross_d</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d收盤價</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d2</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d2收盤價</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>量能</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>價能</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>cond_entry</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>text_desc</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>盤後量</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>成交量</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>%K</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>%D</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>MA5_%</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>均價_%</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>均價long_%</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>均價longlong_%</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>MA_short</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>MA_long</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>MA_longlong</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>MA_longlonglong</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>MACD_%</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>MACD</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL_max</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>MACDSL_%</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>MACD_last_cross_date</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>成交金額平均</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>成交金額</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_short</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long50</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>Volume_Oscillator</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>volume_threshold</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>VPC_MACD</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>Volume_Price_Change</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date收盤價</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CO1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CP1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CQ1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CR1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CS1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CT1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CU1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CV1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>
@@ -1048,325 +1068,345 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
+          <t>0.08</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
           <t>2025/10/22</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>58.5</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>2025/06/11</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>55.7</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0.08</t>
-        </is>
-      </c>
       <c r="AG2" t="inlineStr">
         <is>
+          <t>2025/10/15</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>59.4</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>2025/09/11</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>61.3</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
           <t>2025-12-15</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>9.98</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>4.25</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr">
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
+      <c r="AQ2" t="inlineStr">
         <is>
           <t>277</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
+      <c r="AR2" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="AS2" t="inlineStr">
         <is>
           <t>62.22</t>
         </is>
       </c>
-      <c r="AP2" t="n">
+      <c r="AT2" t="n">
         <v>2.19</v>
       </c>
-      <c r="AQ2" t="n">
+      <c r="AU2" t="n">
         <v>1.62</v>
       </c>
-      <c r="AR2" t="inlineStr">
+      <c r="AV2" t="inlineStr">
         <is>
           <t>-5.52</t>
         </is>
       </c>
-      <c r="AS2" t="inlineStr">
+      <c r="AW2" t="inlineStr">
         <is>
           <t>-3.54</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
+      <c r="AX2" t="inlineStr">
         <is>
           <t>52.94000000000001</t>
         </is>
       </c>
-      <c r="AU2" t="n">
+      <c r="AY2" t="n">
         <v>52.1</v>
       </c>
-      <c r="AV2" t="n">
+      <c r="AZ2" t="n">
         <v>55.14</v>
       </c>
-      <c r="AW2" t="inlineStr">
+      <c r="BA2" t="inlineStr">
         <is>
           <t>57.16</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="BB2" t="inlineStr">
         <is>
           <t>46.74</t>
         </is>
       </c>
-      <c r="AY2" t="n">
+      <c r="BC2" t="n">
         <v>-0.4</v>
       </c>
-      <c r="AZ2" t="n">
+      <c r="BD2" t="n">
         <v>-0.75</v>
       </c>
-      <c r="BA2" t="inlineStr">
+      <c r="BE2" t="inlineStr">
         <is>
           <t>7.3</t>
         </is>
       </c>
-      <c r="BB2" t="inlineStr">
+      <c r="BF2" t="inlineStr">
         <is>
           <t>-110.33</t>
         </is>
       </c>
-      <c r="BC2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>2025/11/26</t>
         </is>
       </c>
-      <c r="BD2" t="inlineStr">
+      <c r="BH2" t="inlineStr">
         <is>
           <t>88838.76825842698</t>
         </is>
       </c>
-      <c r="BE2" t="inlineStr">
+      <c r="BI2" t="inlineStr">
         <is>
           <t>14937.0</t>
         </is>
       </c>
-      <c r="BF2" t="n">
+      <c r="BJ2" t="n">
         <v>7924.6</v>
       </c>
-      <c r="BG2" t="inlineStr">
+      <c r="BK2" t="inlineStr">
         <is>
           <t>6469.2</t>
         </is>
       </c>
-      <c r="BH2" t="n">
+      <c r="BL2" t="n">
         <v>12221.38</v>
       </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BM2" t="inlineStr">
         <is>
           <t>1455</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BN2" t="inlineStr">
         <is>
           <t>-416.3587527715858</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>281.0691610157046</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>14937.0</t>
         </is>
       </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
         <is>
           <t>55.5</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BS2" t="inlineStr">
         <is>
           <t>2025/08/20</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
+      <c r="BT2" t="inlineStr">
         <is>
           <t>-2.52</t>
         </is>
       </c>
-      <c r="BQ2" t="inlineStr">
+      <c r="BU2" t="inlineStr">
         <is>
           <t>利機</t>
         </is>
       </c>
-      <c r="BR2" t="inlineStr">
+      <c r="BV2" t="inlineStr">
         <is>
           <t>利機</t>
         </is>
       </c>
-      <c r="BS2" t="inlineStr">
+      <c r="BW2" t="inlineStr">
         <is>
           <t>電子通路業</t>
         </is>
       </c>
-      <c r="BT2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU2" t="inlineStr">
+      <c r="BY2" t="inlineStr">
         <is>
           <t>1.09</t>
         </is>
       </c>
-      <c r="BV2" t="inlineStr">
+      <c r="BZ2" t="inlineStr">
         <is>
           <t>2.973959600876125</t>
         </is>
       </c>
-      <c r="BW2" t="inlineStr">
+      <c r="CA2" t="inlineStr">
         <is>
           <t>7.507647901781631</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>9.97333412563415</t>
         </is>
       </c>
-      <c r="BY2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ2" t="inlineStr">
+      <c r="CD2" t="inlineStr">
         <is>
           <t>價漲量增</t>
         </is>
       </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CE2" t="inlineStr">
         <is>
           <t>2.34</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CF2" t="inlineStr">
         <is>
           <t>3.7</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
+      <c r="CG2" t="inlineStr">
         <is>
           <t>6.82</t>
         </is>
       </c>
-      <c r="CD2" t="inlineStr">
+      <c r="CH2" t="inlineStr">
         <is>
           <t>22.17</t>
         </is>
       </c>
-      <c r="CE2" t="inlineStr">
+      <c r="CI2" t="inlineStr">
         <is>
           <t>20.15%</t>
         </is>
       </c>
-      <c r="CF2" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>3.13%</t>
         </is>
       </c>
-      <c r="CG2" t="inlineStr">
+      <c r="CK2" t="inlineStr">
         <is>
           <t>32.43</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CL2" t="inlineStr">
         <is>
           <t>2434</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CM2" t="inlineStr">
         <is>
           <t>半導體產品60.53%、光電產品37.52%、其他產品1.95% (2024年)</t>
         </is>
       </c>
-      <c r="CJ2" t="inlineStr">
+      <c r="CN2" t="inlineStr">
         <is>
           <t>利機-電子通路業-上櫃</t>
         </is>
       </c>
-      <c r="CK2" t="inlineStr">
+      <c r="CO2" t="inlineStr">
         <is>
           <t>電子通路業右下上櫃</t>
         </is>
       </c>
-      <c r="CL2" t="inlineStr">
+      <c r="CP2" t="inlineStr">
         <is>
           <t>50.9</t>
         </is>
       </c>
-      <c r="CM2" t="inlineStr">
+      <c r="CQ2" t="inlineStr">
         <is>
           <t>55.2</t>
         </is>
       </c>
-      <c r="CN2" t="inlineStr">
+      <c r="CR2" t="inlineStr">
         <is>
           <t>50.9</t>
         </is>
       </c>
-      <c r="CO2" t="inlineStr">
+      <c r="CS2" t="inlineStr">
         <is>
           <t>54.1</t>
         </is>
       </c>
-      <c r="CP2" t="inlineStr">
+      <c r="CT2" t="inlineStr">
         <is>
           <t>23.11</t>
         </is>
       </c>
-      <c r="CQ2" t="inlineStr">
+      <c r="CU2" t="inlineStr">
         <is>
           <t>** 半導體 - 基板、導線架、IC封裝測試、IC模組、IC通路** 平面顯示器 - 驅動IC** 觸控面板 - 印刷材料** LED照明產業 - 封裝/模組</t>
         </is>
       </c>
-      <c r="CR2" t="inlineStr">
+      <c r="CV2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1510,325 +1550,345 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
           <t>2025/10/22</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>58.5</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>2025/06/11</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>55.7</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
       <c r="AG3" t="inlineStr">
         <is>
+          <t>2025/10/15</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>59.4</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>2025/09/11</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>61.3</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
           <t>2025-12-12</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AL3" t="inlineStr">
         <is>
           <t>3.57</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>-0.57</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr">
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
+      <c r="AQ3" t="inlineStr">
         <is>
           <t>277</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
+      <c r="AR3" t="inlineStr">
         <is>
           <t>46.67</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
+      <c r="AS3" t="inlineStr">
         <is>
           <t>51.11</t>
         </is>
       </c>
-      <c r="AP3" t="n">
+      <c r="AT3" t="n">
         <v>-0.57</v>
       </c>
-      <c r="AQ3" t="n">
+      <c r="AU3" t="n">
         <v>1.41</v>
       </c>
-      <c r="AR3" t="inlineStr">
+      <c r="AV3" t="inlineStr">
         <is>
           <t>-5.87</t>
         </is>
       </c>
-      <c r="AS3" t="inlineStr">
+      <c r="AW3" t="inlineStr">
         <is>
           <t>-3.52</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>52.7</t>
         </is>
       </c>
-      <c r="AU3" t="n">
+      <c r="AY3" t="n">
         <v>51.97</v>
       </c>
-      <c r="AV3" t="n">
+      <c r="AZ3" t="n">
         <v>55.21</v>
       </c>
-      <c r="AW3" t="inlineStr">
+      <c r="BA3" t="inlineStr">
         <is>
           <t>57.22</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="BB3" t="inlineStr">
         <is>
           <t>32.10</t>
         </is>
       </c>
-      <c r="AY3" t="n">
+      <c r="BC3" t="n">
         <v>-0.57</v>
       </c>
-      <c r="AZ3" t="n">
+      <c r="BD3" t="n">
         <v>-0.84</v>
       </c>
-      <c r="BA3" t="inlineStr">
+      <c r="BE3" t="inlineStr">
         <is>
           <t>7.3</t>
         </is>
       </c>
-      <c r="BB3" t="inlineStr">
+      <c r="BF3" t="inlineStr">
         <is>
           <t>-111.54</t>
         </is>
       </c>
-      <c r="BC3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>2025/11/26</t>
         </is>
       </c>
-      <c r="BD3" t="inlineStr">
+      <c r="BH3" t="inlineStr">
         <is>
           <t>88838.76825842698</t>
         </is>
       </c>
-      <c r="BE3" t="inlineStr">
+      <c r="BI3" t="inlineStr">
         <is>
           <t>5171.0</t>
         </is>
       </c>
-      <c r="BF3" t="n">
+      <c r="BJ3" t="n">
         <v>6103.8</v>
       </c>
-      <c r="BG3" t="inlineStr">
+      <c r="BK3" t="inlineStr">
         <is>
           <t>5388.8</t>
         </is>
       </c>
-      <c r="BH3" t="n">
+      <c r="BL3" t="n">
         <v>12016.5</v>
       </c>
-      <c r="BI3" t="inlineStr">
+      <c r="BM3" t="inlineStr">
         <is>
           <t>715</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
+      <c r="BN3" t="inlineStr">
         <is>
           <t>-543.1638280056386</t>
         </is>
       </c>
-      <c r="BK3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>-416.1188505990758</t>
         </is>
       </c>
-      <c r="BL3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>5171.0</t>
         </is>
       </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
         <is>
           <t>55.5</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BS3" t="inlineStr">
         <is>
           <t>2025/08/20</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
+      <c r="BT3" t="inlineStr">
         <is>
           <t>-5.59</t>
         </is>
       </c>
-      <c r="BQ3" t="inlineStr">
+      <c r="BU3" t="inlineStr">
         <is>
           <t>利機</t>
         </is>
       </c>
-      <c r="BR3" t="inlineStr">
+      <c r="BV3" t="inlineStr">
         <is>
           <t>利機</t>
         </is>
       </c>
-      <c r="BS3" t="inlineStr">
+      <c r="BW3" t="inlineStr">
         <is>
           <t>電子通路業</t>
         </is>
       </c>
-      <c r="BT3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU3" t="inlineStr">
+      <c r="BY3" t="inlineStr">
         <is>
           <t>1.09</t>
         </is>
       </c>
-      <c r="BV3" t="inlineStr">
+      <c r="BZ3" t="inlineStr">
         <is>
           <t>2.973959600876125</t>
         </is>
       </c>
-      <c r="BW3" t="inlineStr">
+      <c r="CA3" t="inlineStr">
         <is>
           <t>7.507647901781631</t>
         </is>
       </c>
-      <c r="BX3" t="inlineStr">
+      <c r="CB3" t="inlineStr">
         <is>
           <t>9.97333412563415</t>
         </is>
       </c>
-      <c r="BY3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ3" t="inlineStr">
+      <c r="CD3" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA3" t="inlineStr">
+      <c r="CE3" t="inlineStr">
         <is>
           <t>2.27</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
+      <c r="CF3" t="inlineStr">
         <is>
           <t>3.7</t>
         </is>
       </c>
-      <c r="CC3" t="inlineStr">
+      <c r="CG3" t="inlineStr">
         <is>
           <t>6.82</t>
         </is>
       </c>
-      <c r="CD3" t="inlineStr">
+      <c r="CH3" t="inlineStr">
         <is>
           <t>22.17</t>
         </is>
       </c>
-      <c r="CE3" t="inlineStr">
+      <c r="CI3" t="inlineStr">
         <is>
           <t>20.15%</t>
         </is>
       </c>
-      <c r="CF3" t="inlineStr">
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>3.13%</t>
         </is>
       </c>
-      <c r="CG3" t="inlineStr">
+      <c r="CK3" t="inlineStr">
         <is>
           <t>32.43</t>
         </is>
       </c>
-      <c r="CH3" t="inlineStr">
+      <c r="CL3" t="inlineStr">
         <is>
           <t>2434</t>
         </is>
       </c>
-      <c r="CI3" t="inlineStr">
+      <c r="CM3" t="inlineStr">
         <is>
           <t>半導體產品60.53%、光電產品37.52%、其他產品1.95% (2024年)</t>
         </is>
       </c>
-      <c r="CJ3" t="inlineStr">
+      <c r="CN3" t="inlineStr">
         <is>
           <t>利機-電子通路業-上櫃</t>
         </is>
       </c>
-      <c r="CK3" t="inlineStr">
+      <c r="CO3" t="inlineStr">
         <is>
           <t>電子通路業右下上櫃</t>
         </is>
       </c>
-      <c r="CL3" t="inlineStr">
+      <c r="CP3" t="inlineStr">
         <is>
           <t>52.6</t>
         </is>
       </c>
-      <c r="CM3" t="inlineStr">
+      <c r="CQ3" t="inlineStr">
         <is>
           <t>53.0</t>
         </is>
       </c>
-      <c r="CN3" t="inlineStr">
+      <c r="CR3" t="inlineStr">
         <is>
           <t>52.1</t>
         </is>
       </c>
-      <c r="CO3" t="inlineStr">
+      <c r="CS3" t="inlineStr">
         <is>
           <t>52.4</t>
         </is>
       </c>
-      <c r="CP3" t="inlineStr">
+      <c r="CT3" t="inlineStr">
         <is>
           <t>23.11</t>
         </is>
       </c>
-      <c r="CQ3" t="inlineStr">
+      <c r="CU3" t="inlineStr">
         <is>
           <t>** 半導體 - 基板、導線架、IC封裝測試、IC模組、IC通路** 平面顯示器 - 驅動IC** 觸控面板 - 印刷材料** LED照明產業 - 封裝/模組</t>
         </is>
       </c>
-      <c r="CR3" t="inlineStr">
+      <c r="CV3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1972,325 +2032,345 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
+          <t>-0.05</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
           <t>2025/10/22</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>58.5</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>2025/06/11</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
         <is>
           <t>55.7</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
       <c r="AG4" t="inlineStr">
         <is>
+          <t>2025/10/15</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>59.4</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>2025/09/11</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>61.3</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AH4" t="inlineStr">
+      <c r="AL4" t="inlineStr">
         <is>
           <t>5.91</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
+      <c r="AM4" t="inlineStr">
         <is>
           <t>0.45</t>
         </is>
       </c>
-      <c r="AJ4" t="inlineStr">
+      <c r="AN4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr">
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
+      <c r="AQ4" t="inlineStr">
         <is>
           <t>277</t>
         </is>
       </c>
-      <c r="AN4" t="inlineStr">
+      <c r="AR4" t="inlineStr">
         <is>
           <t>40.0</t>
         </is>
       </c>
-      <c r="AO4" t="inlineStr">
+      <c r="AS4" t="inlineStr">
         <is>
           <t>68.89</t>
         </is>
       </c>
-      <c r="AP4" t="n">
+      <c r="AT4" t="n">
         <v>-0.49</v>
       </c>
-      <c r="AQ4" t="n">
+      <c r="AU4" t="n">
         <v>1.13</v>
       </c>
-      <c r="AR4" t="inlineStr">
+      <c r="AV4" t="inlineStr">
         <is>
           <t>-6.04</t>
         </is>
       </c>
-      <c r="AS4" t="inlineStr">
+      <c r="AW4" t="inlineStr">
         <is>
           <t>-3.47</t>
         </is>
       </c>
-      <c r="AT4" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>52.56</t>
         </is>
       </c>
-      <c r="AU4" t="n">
+      <c r="AY4" t="n">
         <v>51.97</v>
       </c>
-      <c r="AV4" t="n">
+      <c r="AZ4" t="n">
         <v>55.31</v>
       </c>
-      <c r="AW4" t="inlineStr">
+      <c r="BA4" t="inlineStr">
         <is>
           <t>57.3</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="BB4" t="inlineStr">
         <is>
           <t>33.19</t>
         </is>
       </c>
-      <c r="AY4" t="n">
+      <c r="BC4" t="n">
         <v>-0.61</v>
       </c>
-      <c r="AZ4" t="n">
+      <c r="BD4" t="n">
         <v>-0.91</v>
       </c>
-      <c r="BA4" t="inlineStr">
+      <c r="BE4" t="inlineStr">
         <is>
           <t>7.3</t>
         </is>
       </c>
-      <c r="BB4" t="inlineStr">
+      <c r="BF4" t="inlineStr">
         <is>
           <t>-112.47</t>
         </is>
       </c>
-      <c r="BC4" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>2025/11/26</t>
         </is>
       </c>
-      <c r="BD4" t="inlineStr">
+      <c r="BH4" t="inlineStr">
         <is>
           <t>88838.76825842698</t>
         </is>
       </c>
-      <c r="BE4" t="inlineStr">
+      <c r="BI4" t="inlineStr">
         <is>
           <t>8509.0</t>
         </is>
       </c>
-      <c r="BF4" t="n">
+      <c r="BJ4" t="n">
         <v>6029</v>
       </c>
-      <c r="BG4" t="inlineStr">
+      <c r="BK4" t="inlineStr">
         <is>
           <t>5747.2</t>
         </is>
       </c>
-      <c r="BH4" t="n">
+      <c r="BL4" t="n">
         <v>12110</v>
       </c>
-      <c r="BI4" t="inlineStr">
+      <c r="BM4" t="inlineStr">
         <is>
           <t>281</t>
         </is>
       </c>
-      <c r="BJ4" t="inlineStr">
+      <c r="BN4" t="inlineStr">
         <is>
           <t>-566.2629148068319</t>
         </is>
       </c>
-      <c r="BK4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>-350.8831939559377</t>
         </is>
       </c>
-      <c r="BL4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
         <is>
           <t>8509.0</t>
         </is>
       </c>
-      <c r="BM4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN4" t="inlineStr">
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
         <is>
           <t>55.5</t>
         </is>
       </c>
-      <c r="BO4" t="inlineStr">
+      <c r="BS4" t="inlineStr">
         <is>
           <t>2025/08/20</t>
         </is>
       </c>
-      <c r="BP4" t="inlineStr">
+      <c r="BT4" t="inlineStr">
         <is>
           <t>-5.77</t>
         </is>
       </c>
-      <c r="BQ4" t="inlineStr">
+      <c r="BU4" t="inlineStr">
         <is>
           <t>利機</t>
         </is>
       </c>
-      <c r="BR4" t="inlineStr">
+      <c r="BV4" t="inlineStr">
         <is>
           <t>利機</t>
         </is>
       </c>
-      <c r="BS4" t="inlineStr">
+      <c r="BW4" t="inlineStr">
         <is>
           <t>電子通路業</t>
         </is>
       </c>
-      <c r="BT4" t="inlineStr">
+      <c r="BX4" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU4" t="inlineStr">
+      <c r="BY4" t="inlineStr">
         <is>
           <t>1.09</t>
         </is>
       </c>
-      <c r="BV4" t="inlineStr">
+      <c r="BZ4" t="inlineStr">
         <is>
           <t>2.973959600876125</t>
         </is>
       </c>
-      <c r="BW4" t="inlineStr">
+      <c r="CA4" t="inlineStr">
         <is>
           <t>7.507647901781631</t>
         </is>
       </c>
-      <c r="BX4" t="inlineStr">
+      <c r="CB4" t="inlineStr">
         <is>
           <t>9.97333412563415</t>
         </is>
       </c>
-      <c r="BY4" t="inlineStr">
+      <c r="CC4" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ4" t="inlineStr">
+      <c r="CD4" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA4" t="inlineStr">
+      <c r="CE4" t="inlineStr">
         <is>
           <t>2.26</t>
         </is>
       </c>
-      <c r="CB4" t="inlineStr">
+      <c r="CF4" t="inlineStr">
         <is>
           <t>3.7</t>
         </is>
       </c>
-      <c r="CC4" t="inlineStr">
+      <c r="CG4" t="inlineStr">
         <is>
           <t>6.82</t>
         </is>
       </c>
-      <c r="CD4" t="inlineStr">
+      <c r="CH4" t="inlineStr">
         <is>
           <t>22.17</t>
         </is>
       </c>
-      <c r="CE4" t="inlineStr">
+      <c r="CI4" t="inlineStr">
         <is>
           <t>20.15%</t>
         </is>
       </c>
-      <c r="CF4" t="inlineStr">
+      <c r="CJ4" t="inlineStr">
         <is>
           <t>3.13%</t>
         </is>
       </c>
-      <c r="CG4" t="inlineStr">
+      <c r="CK4" t="inlineStr">
         <is>
           <t>32.43</t>
         </is>
       </c>
-      <c r="CH4" t="inlineStr">
+      <c r="CL4" t="inlineStr">
         <is>
           <t>2434</t>
         </is>
       </c>
-      <c r="CI4" t="inlineStr">
+      <c r="CM4" t="inlineStr">
         <is>
           <t>半導體產品60.53%、光電產品37.52%、其他產品1.95% (2024年)</t>
         </is>
       </c>
-      <c r="CJ4" t="inlineStr">
+      <c r="CN4" t="inlineStr">
         <is>
           <t>利機-電子通路業-上櫃</t>
         </is>
       </c>
-      <c r="CK4" t="inlineStr">
+      <c r="CO4" t="inlineStr">
         <is>
           <t>電子通路業右下上櫃</t>
         </is>
       </c>
-      <c r="CL4" t="inlineStr">
+      <c r="CP4" t="inlineStr">
         <is>
           <t>52.9</t>
         </is>
       </c>
-      <c r="CM4" t="inlineStr">
+      <c r="CQ4" t="inlineStr">
         <is>
           <t>53.4</t>
         </is>
       </c>
-      <c r="CN4" t="inlineStr">
+      <c r="CR4" t="inlineStr">
         <is>
           <t>51.0</t>
         </is>
       </c>
-      <c r="CO4" t="inlineStr">
+      <c r="CS4" t="inlineStr">
         <is>
           <t>52.3</t>
         </is>
       </c>
-      <c r="CP4" t="inlineStr">
+      <c r="CT4" t="inlineStr">
         <is>
           <t>23.11</t>
         </is>
       </c>
-      <c r="CQ4" t="inlineStr">
+      <c r="CU4" t="inlineStr">
         <is>
           <t>** 半導體 - 基板、導線架、IC封裝測試、IC模組、IC通路** 平面顯示器 - 驅動IC** 觸控面板 - 印刷材料** LED照明產業 - 封裝/模組</t>
         </is>
       </c>
-      <c r="CR4" t="inlineStr">
+      <c r="CV4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2434,325 +2514,345 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
           <t>2025/10/22</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>58.5</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>2025/06/11</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>55.7</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
       <c r="AG5" t="inlineStr">
         <is>
+          <t>2025/10/15</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>59.4</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>2025/09/11</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>61.3</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
           <t>2025-12-10</t>
         </is>
       </c>
-      <c r="AH5" t="inlineStr">
+      <c r="AL5" t="inlineStr">
         <is>
           <t>5.15</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>-3.98</t>
         </is>
       </c>
-      <c r="AJ5" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr">
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
+      <c r="AQ5" t="inlineStr">
         <is>
           <t>277</t>
         </is>
       </c>
-      <c r="AN5" t="inlineStr">
+      <c r="AR5" t="inlineStr">
         <is>
           <t>66.67</t>
         </is>
       </c>
-      <c r="AO5" t="inlineStr">
+      <c r="AS5" t="inlineStr">
         <is>
           <t>80.56</t>
         </is>
       </c>
-      <c r="AP5" t="n">
+      <c r="AT5" t="n">
         <v>0.11</v>
       </c>
-      <c r="AQ5" t="n">
+      <c r="AU5" t="n">
         <v>1.07</v>
       </c>
-      <c r="AR5" t="inlineStr">
+      <c r="AV5" t="inlineStr">
         <is>
           <t>-6.01</t>
         </is>
       </c>
-      <c r="AS5" t="inlineStr">
+      <c r="AW5" t="inlineStr">
         <is>
           <t>-3.40</t>
         </is>
       </c>
-      <c r="AT5" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>52.64</t>
         </is>
       </c>
-      <c r="AU5" t="n">
+      <c r="AY5" t="n">
         <v>52.08</v>
       </c>
-      <c r="AV5" t="n">
+      <c r="AZ5" t="n">
         <v>55.41</v>
       </c>
-      <c r="AW5" t="inlineStr">
+      <c r="BA5" t="inlineStr">
         <is>
           <t>57.36</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="BB5" t="inlineStr">
         <is>
           <t>35.57</t>
         </is>
       </c>
-      <c r="AY5" t="n">
+      <c r="BC5" t="n">
         <v>-0.63</v>
       </c>
-      <c r="AZ5" t="n">
+      <c r="BD5" t="n">
         <v>-0.99</v>
       </c>
-      <c r="BA5" t="inlineStr">
+      <c r="BE5" t="inlineStr">
         <is>
           <t>7.3</t>
         </is>
       </c>
-      <c r="BB5" t="inlineStr">
+      <c r="BF5" t="inlineStr">
         <is>
           <t>-113.50</t>
         </is>
       </c>
-      <c r="BC5" t="inlineStr">
+      <c r="BG5" t="inlineStr">
         <is>
           <t>2025/11/26</t>
         </is>
       </c>
-      <c r="BD5" t="inlineStr">
+      <c r="BH5" t="inlineStr">
         <is>
           <t>88838.76825842698</t>
         </is>
       </c>
-      <c r="BE5" t="inlineStr">
+      <c r="BI5" t="inlineStr">
         <is>
           <t>7682.0</t>
         </is>
       </c>
-      <c r="BF5" t="n">
+      <c r="BJ5" t="n">
         <v>4986.4</v>
       </c>
-      <c r="BG5" t="inlineStr">
+      <c r="BK5" t="inlineStr">
         <is>
           <t>6252.7</t>
         </is>
       </c>
-      <c r="BH5" t="n">
+      <c r="BL5" t="n">
         <v>12234.7</v>
       </c>
-      <c r="BI5" t="inlineStr">
+      <c r="BM5" t="inlineStr">
         <is>
           <t>-1266</t>
         </is>
       </c>
-      <c r="BJ5" t="inlineStr">
+      <c r="BN5" t="inlineStr">
         <is>
           <t>-605.422864052449</t>
         </is>
       </c>
-      <c r="BK5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>-602.8007132530274</t>
         </is>
       </c>
-      <c r="BL5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>7682.0</t>
         </is>
       </c>
-      <c r="BM5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN5" t="inlineStr">
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
         <is>
           <t>55.5</t>
         </is>
       </c>
-      <c r="BO5" t="inlineStr">
+      <c r="BS5" t="inlineStr">
         <is>
           <t>2025/08/20</t>
         </is>
       </c>
-      <c r="BP5" t="inlineStr">
+      <c r="BT5" t="inlineStr">
         <is>
           <t>-5.05</t>
         </is>
       </c>
-      <c r="BQ5" t="inlineStr">
+      <c r="BU5" t="inlineStr">
         <is>
           <t>利機</t>
         </is>
       </c>
-      <c r="BR5" t="inlineStr">
+      <c r="BV5" t="inlineStr">
         <is>
           <t>利機</t>
         </is>
       </c>
-      <c r="BS5" t="inlineStr">
+      <c r="BW5" t="inlineStr">
         <is>
           <t>電子通路業</t>
         </is>
       </c>
-      <c r="BT5" t="inlineStr">
+      <c r="BX5" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU5" t="inlineStr">
+      <c r="BY5" t="inlineStr">
         <is>
           <t>1.09</t>
         </is>
       </c>
-      <c r="BV5" t="inlineStr">
+      <c r="BZ5" t="inlineStr">
         <is>
           <t>2.973959600876125</t>
         </is>
       </c>
-      <c r="BW5" t="inlineStr">
+      <c r="CA5" t="inlineStr">
         <is>
           <t>7.507647901781631</t>
         </is>
       </c>
-      <c r="BX5" t="inlineStr">
+      <c r="CB5" t="inlineStr">
         <is>
           <t>9.97333412563415</t>
         </is>
       </c>
-      <c r="BY5" t="inlineStr">
+      <c r="CC5" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ5" t="inlineStr">
+      <c r="CD5" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA5" t="inlineStr">
+      <c r="CE5" t="inlineStr">
         <is>
           <t>2.28</t>
         </is>
       </c>
-      <c r="CB5" t="inlineStr">
+      <c r="CF5" t="inlineStr">
         <is>
           <t>3.7</t>
         </is>
       </c>
-      <c r="CC5" t="inlineStr">
+      <c r="CG5" t="inlineStr">
         <is>
           <t>6.82</t>
         </is>
       </c>
-      <c r="CD5" t="inlineStr">
+      <c r="CH5" t="inlineStr">
         <is>
           <t>22.17</t>
         </is>
       </c>
-      <c r="CE5" t="inlineStr">
+      <c r="CI5" t="inlineStr">
         <is>
           <t>20.15%</t>
         </is>
       </c>
-      <c r="CF5" t="inlineStr">
+      <c r="CJ5" t="inlineStr">
         <is>
           <t>3.13%</t>
         </is>
       </c>
-      <c r="CG5" t="inlineStr">
+      <c r="CK5" t="inlineStr">
         <is>
           <t>32.43</t>
         </is>
       </c>
-      <c r="CH5" t="inlineStr">
+      <c r="CL5" t="inlineStr">
         <is>
           <t>2434</t>
         </is>
       </c>
-      <c r="CI5" t="inlineStr">
+      <c r="CM5" t="inlineStr">
         <is>
           <t>半導體產品60.53%、光電產品37.52%、其他產品1.95% (2024年)</t>
         </is>
       </c>
-      <c r="CJ5" t="inlineStr">
+      <c r="CN5" t="inlineStr">
         <is>
           <t>利機-電子通路業-上櫃</t>
         </is>
       </c>
-      <c r="CK5" t="inlineStr">
+      <c r="CO5" t="inlineStr">
         <is>
           <t>電子通路業右下上櫃</t>
         </is>
       </c>
-      <c r="CL5" t="inlineStr">
+      <c r="CP5" t="inlineStr">
         <is>
           <t>53.6</t>
         </is>
       </c>
-      <c r="CM5" t="inlineStr">
+      <c r="CQ5" t="inlineStr">
         <is>
           <t>54.8</t>
         </is>
       </c>
-      <c r="CN5" t="inlineStr">
+      <c r="CR5" t="inlineStr">
         <is>
           <t>52.7</t>
         </is>
       </c>
-      <c r="CO5" t="inlineStr">
+      <c r="CS5" t="inlineStr">
         <is>
           <t>52.7</t>
         </is>
       </c>
-      <c r="CP5" t="inlineStr">
+      <c r="CT5" t="inlineStr">
         <is>
           <t>23.11</t>
         </is>
       </c>
-      <c r="CQ5" t="inlineStr">
+      <c r="CU5" t="inlineStr">
         <is>
           <t>** 半導體 - 基板、導線架、IC封裝測試、IC模組、IC通路** 平面顯示器 - 驅動IC** 觸控面板 - 印刷材料** LED照明產業 - 封裝/模組</t>
         </is>
       </c>
-      <c r="CR5" t="inlineStr">
+      <c r="CV5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2896,325 +2996,345 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
           <t>2025/10/22</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>58.5</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>2025/06/11</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
         <is>
           <t>55.7</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
       <c r="AG6" t="inlineStr">
         <is>
+          <t>2025/10/15</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>59.4</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>2025/09/11</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>61.3</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
           <t>2025-12-09</t>
         </is>
       </c>
-      <c r="AH6" t="inlineStr">
+      <c r="AL6" t="inlineStr">
         <is>
           <t>2.27</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
+      <c r="AM6" t="inlineStr">
         <is>
           <t>1.34</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr">
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
+      <c r="AQ6" t="inlineStr">
         <is>
           <t>277</t>
         </is>
       </c>
-      <c r="AN6" t="inlineStr">
+      <c r="AR6" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AO6" t="inlineStr">
+      <c r="AS6" t="inlineStr">
         <is>
           <t>58.33</t>
         </is>
       </c>
-      <c r="AP6" t="n">
+      <c r="AT6" t="n">
         <v>0.99</v>
       </c>
-      <c r="AQ6" t="n">
+      <c r="AU6" t="n">
         <v>1</v>
       </c>
-      <c r="AR6" t="inlineStr">
+      <c r="AV6" t="inlineStr">
         <is>
           <t>-6.06</t>
         </is>
       </c>
-      <c r="AS6" t="inlineStr">
+      <c r="AW6" t="inlineStr">
         <is>
           <t>-3.21</t>
         </is>
       </c>
-      <c r="AT6" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>52.67999999999999</t>
         </is>
       </c>
-      <c r="AU6" t="n">
+      <c r="AY6" t="n">
         <v>52.16</v>
       </c>
-      <c r="AV6" t="n">
+      <c r="AZ6" t="n">
         <v>55.52</v>
       </c>
-      <c r="AW6" t="inlineStr">
+      <c r="BA6" t="inlineStr">
         <is>
           <t>57.37</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="BB6" t="inlineStr">
         <is>
           <t>34.70</t>
         </is>
       </c>
-      <c r="AY6" t="n">
+      <c r="BC6" t="n">
         <v>-0.7</v>
       </c>
-      <c r="AZ6" t="n">
+      <c r="BD6" t="n">
         <v>-1.07</v>
       </c>
-      <c r="BA6" t="inlineStr">
+      <c r="BE6" t="inlineStr">
         <is>
           <t>7.3</t>
         </is>
       </c>
-      <c r="BB6" t="inlineStr">
+      <c r="BF6" t="inlineStr">
         <is>
           <t>-114.70</t>
         </is>
       </c>
-      <c r="BC6" t="inlineStr">
+      <c r="BG6" t="inlineStr">
         <is>
           <t>2025/11/26</t>
         </is>
       </c>
-      <c r="BD6" t="inlineStr">
+      <c r="BH6" t="inlineStr">
         <is>
           <t>88838.76825842698</t>
         </is>
       </c>
-      <c r="BE6" t="inlineStr">
+      <c r="BI6" t="inlineStr">
         <is>
           <t>3324.0</t>
         </is>
       </c>
-      <c r="BF6" t="n">
+      <c r="BJ6" t="n">
         <v>5108.2</v>
       </c>
-      <c r="BG6" t="inlineStr">
+      <c r="BK6" t="inlineStr">
         <is>
           <t>7304.7</t>
         </is>
       </c>
-      <c r="BH6" t="n">
+      <c r="BL6" t="n">
         <v>12325.42</v>
       </c>
-      <c r="BI6" t="inlineStr">
+      <c r="BM6" t="inlineStr">
         <is>
           <t>-2196</t>
         </is>
       </c>
-      <c r="BJ6" t="inlineStr">
+      <c r="BN6" t="inlineStr">
         <is>
           <t>-605.8996187432529</t>
         </is>
       </c>
-      <c r="BK6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>-852.5471439184039</t>
         </is>
       </c>
-      <c r="BL6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
         <is>
           <t>3324.0</t>
         </is>
       </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN6" t="inlineStr">
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
         <is>
           <t>55.5</t>
         </is>
       </c>
-      <c r="BO6" t="inlineStr">
+      <c r="BS6" t="inlineStr">
         <is>
           <t>2025/08/20</t>
         </is>
       </c>
-      <c r="BP6" t="inlineStr">
+      <c r="BT6" t="inlineStr">
         <is>
           <t>-4.14</t>
         </is>
       </c>
-      <c r="BQ6" t="inlineStr">
+      <c r="BU6" t="inlineStr">
         <is>
           <t>利機</t>
         </is>
       </c>
-      <c r="BR6" t="inlineStr">
+      <c r="BV6" t="inlineStr">
         <is>
           <t>利機</t>
         </is>
       </c>
-      <c r="BS6" t="inlineStr">
+      <c r="BW6" t="inlineStr">
         <is>
           <t>電子通路業</t>
         </is>
       </c>
-      <c r="BT6" t="inlineStr">
+      <c r="BX6" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU6" t="inlineStr">
+      <c r="BY6" t="inlineStr">
         <is>
           <t>1.09</t>
         </is>
       </c>
-      <c r="BV6" t="inlineStr">
+      <c r="BZ6" t="inlineStr">
         <is>
           <t>2.973959600876125</t>
         </is>
       </c>
-      <c r="BW6" t="inlineStr">
+      <c r="CA6" t="inlineStr">
         <is>
           <t>7.507647901781631</t>
         </is>
       </c>
-      <c r="BX6" t="inlineStr">
+      <c r="CB6" t="inlineStr">
         <is>
           <t>9.97333412563415</t>
         </is>
       </c>
-      <c r="BY6" t="inlineStr">
+      <c r="CC6" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ6" t="inlineStr">
+      <c r="CD6" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA6" t="inlineStr">
+      <c r="CE6" t="inlineStr">
         <is>
           <t>2.30</t>
         </is>
       </c>
-      <c r="CB6" t="inlineStr">
+      <c r="CF6" t="inlineStr">
         <is>
           <t>3.7</t>
         </is>
       </c>
-      <c r="CC6" t="inlineStr">
+      <c r="CG6" t="inlineStr">
         <is>
           <t>6.82</t>
         </is>
       </c>
-      <c r="CD6" t="inlineStr">
+      <c r="CH6" t="inlineStr">
         <is>
           <t>22.17</t>
         </is>
       </c>
-      <c r="CE6" t="inlineStr">
+      <c r="CI6" t="inlineStr">
         <is>
           <t>20.15%</t>
         </is>
       </c>
-      <c r="CF6" t="inlineStr">
+      <c r="CJ6" t="inlineStr">
         <is>
           <t>3.13%</t>
         </is>
       </c>
-      <c r="CG6" t="inlineStr">
+      <c r="CK6" t="inlineStr">
         <is>
           <t>32.43</t>
         </is>
       </c>
-      <c r="CH6" t="inlineStr">
+      <c r="CL6" t="inlineStr">
         <is>
           <t>2434</t>
         </is>
       </c>
-      <c r="CI6" t="inlineStr">
+      <c r="CM6" t="inlineStr">
         <is>
           <t>半導體產品60.53%、光電產品37.52%、其他產品1.95% (2024年)</t>
         </is>
       </c>
-      <c r="CJ6" t="inlineStr">
+      <c r="CN6" t="inlineStr">
         <is>
           <t>利機-電子通路業-上櫃</t>
         </is>
       </c>
-      <c r="CK6" t="inlineStr">
+      <c r="CO6" t="inlineStr">
         <is>
           <t>電子通路業右下上櫃</t>
         </is>
       </c>
-      <c r="CL6" t="inlineStr">
+      <c r="CP6" t="inlineStr">
         <is>
           <t>53.0</t>
         </is>
       </c>
-      <c r="CM6" t="inlineStr">
+      <c r="CQ6" t="inlineStr">
         <is>
           <t>53.3</t>
         </is>
       </c>
-      <c r="CN6" t="inlineStr">
+      <c r="CR6" t="inlineStr">
         <is>
           <t>52.4</t>
         </is>
       </c>
-      <c r="CO6" t="inlineStr">
+      <c r="CS6" t="inlineStr">
         <is>
           <t>53.2</t>
         </is>
       </c>
-      <c r="CP6" t="inlineStr">
+      <c r="CT6" t="inlineStr">
         <is>
           <t>23.11</t>
         </is>
       </c>
-      <c r="CQ6" t="inlineStr">
+      <c r="CU6" t="inlineStr">
         <is>
           <t>** 半導體 - 基板、導線架、IC封裝測試、IC模組、IC通路** 平面顯示器 - 驅動IC** 觸控面板 - 印刷材料** LED照明產業 - 封裝/模組</t>
         </is>
       </c>
-      <c r="CR6" t="inlineStr">
+      <c r="CV6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3358,325 +3478,345 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
           <t>2025/10/22</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>58.5</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>2025/06/11</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>55.7</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
       <c r="AG7" t="inlineStr">
         <is>
+          <t>2025/10/15</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>59.4</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>2025/09/11</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>61.3</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
           <t>2025-12-08</t>
         </is>
       </c>
-      <c r="AH7" t="inlineStr">
+      <c r="AL7" t="inlineStr">
         <is>
           <t>4.03</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
+      <c r="AM7" t="inlineStr">
         <is>
           <t>2.72</t>
         </is>
       </c>
-      <c r="AJ7" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="inlineStr">
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
+      <c r="AQ7" t="inlineStr">
         <is>
           <t>277</t>
         </is>
       </c>
-      <c r="AN7" t="inlineStr">
+      <c r="AR7" t="inlineStr">
         <is>
           <t>75.0</t>
         </is>
       </c>
-      <c r="AO7" t="inlineStr">
+      <c r="AS7" t="inlineStr">
         <is>
           <t>52.27</t>
         </is>
       </c>
-      <c r="AP7" t="n">
+      <c r="AT7" t="n">
         <v>0.84</v>
       </c>
-      <c r="AQ7" t="n">
+      <c r="AU7" t="n">
         <v>0.53</v>
       </c>
-      <c r="AR7" t="inlineStr">
+      <c r="AV7" t="inlineStr">
         <is>
           <t>-6.24</t>
         </is>
       </c>
-      <c r="AS7" t="inlineStr">
+      <c r="AW7" t="inlineStr">
         <is>
           <t>-2.97</t>
         </is>
       </c>
-      <c r="AT7" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>52.46</t>
         </is>
       </c>
-      <c r="AU7" t="n">
+      <c r="AY7" t="n">
         <v>52.18</v>
       </c>
-      <c r="AV7" t="n">
+      <c r="AZ7" t="n">
         <v>55.66</v>
       </c>
-      <c r="AW7" t="inlineStr">
+      <c r="BA7" t="inlineStr">
         <is>
           <t>57.36</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="BB7" t="inlineStr">
         <is>
           <t>29.22</t>
         </is>
       </c>
-      <c r="AY7" t="n">
+      <c r="BC7" t="n">
         <v>-0.83</v>
       </c>
-      <c r="AZ7" t="n">
+      <c r="BD7" t="n">
         <v>-1.17</v>
       </c>
-      <c r="BA7" t="inlineStr">
+      <c r="BE7" t="inlineStr">
         <is>
           <t>7.3</t>
         </is>
       </c>
-      <c r="BB7" t="inlineStr">
+      <c r="BF7" t="inlineStr">
         <is>
           <t>-115.98</t>
         </is>
       </c>
-      <c r="BC7" t="inlineStr">
+      <c r="BG7" t="inlineStr">
         <is>
           <t>2025/11/26</t>
         </is>
       </c>
-      <c r="BD7" t="inlineStr">
+      <c r="BH7" t="inlineStr">
         <is>
           <t>88838.76825842698</t>
         </is>
       </c>
-      <c r="BE7" t="inlineStr">
+      <c r="BI7" t="inlineStr">
         <is>
           <t>5833.0</t>
         </is>
       </c>
-      <c r="BF7" t="n">
+      <c r="BJ7" t="n">
         <v>5013.8</v>
       </c>
-      <c r="BG7" t="inlineStr">
+      <c r="BK7" t="inlineStr">
         <is>
           <t>8675.9</t>
         </is>
       </c>
-      <c r="BH7" t="n">
+      <c r="BL7" t="n">
         <v>12426.06</v>
       </c>
-      <c r="BI7" t="inlineStr">
+      <c r="BM7" t="inlineStr">
         <is>
           <t>-3662</t>
         </is>
       </c>
-      <c r="BJ7" t="inlineStr">
+      <c r="BN7" t="inlineStr">
         <is>
           <t>-561.0546141659527</t>
         </is>
       </c>
-      <c r="BK7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>-711.9510754432858</t>
         </is>
       </c>
-      <c r="BL7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>5833.0</t>
         </is>
       </c>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN7" t="inlineStr">
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
         <is>
           <t>55.5</t>
         </is>
       </c>
-      <c r="BO7" t="inlineStr">
+      <c r="BS7" t="inlineStr">
         <is>
           <t>2025/08/20</t>
         </is>
       </c>
-      <c r="BP7" t="inlineStr">
+      <c r="BT7" t="inlineStr">
         <is>
           <t>-4.68</t>
         </is>
       </c>
-      <c r="BQ7" t="inlineStr">
+      <c r="BU7" t="inlineStr">
         <is>
           <t>利機</t>
         </is>
       </c>
-      <c r="BR7" t="inlineStr">
+      <c r="BV7" t="inlineStr">
         <is>
           <t>利機</t>
         </is>
       </c>
-      <c r="BS7" t="inlineStr">
+      <c r="BW7" t="inlineStr">
         <is>
           <t>電子通路業</t>
         </is>
       </c>
-      <c r="BT7" t="inlineStr">
+      <c r="BX7" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU7" t="inlineStr">
+      <c r="BY7" t="inlineStr">
         <is>
           <t>1.09</t>
         </is>
       </c>
-      <c r="BV7" t="inlineStr">
+      <c r="BZ7" t="inlineStr">
         <is>
           <t>2.973959600876125</t>
         </is>
       </c>
-      <c r="BW7" t="inlineStr">
+      <c r="CA7" t="inlineStr">
         <is>
           <t>7.507647901781631</t>
         </is>
       </c>
-      <c r="BX7" t="inlineStr">
+      <c r="CB7" t="inlineStr">
         <is>
           <t>9.97333412563415</t>
         </is>
       </c>
-      <c r="BY7" t="inlineStr">
+      <c r="CC7" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ7" t="inlineStr">
+      <c r="CD7" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA7" t="inlineStr">
+      <c r="CE7" t="inlineStr">
         <is>
           <t>2.29</t>
         </is>
       </c>
-      <c r="CB7" t="inlineStr">
+      <c r="CF7" t="inlineStr">
         <is>
           <t>3.7</t>
         </is>
       </c>
-      <c r="CC7" t="inlineStr">
+      <c r="CG7" t="inlineStr">
         <is>
           <t>6.82</t>
         </is>
       </c>
-      <c r="CD7" t="inlineStr">
+      <c r="CH7" t="inlineStr">
         <is>
           <t>22.17</t>
         </is>
       </c>
-      <c r="CE7" t="inlineStr">
+      <c r="CI7" t="inlineStr">
         <is>
           <t>20.15%</t>
         </is>
       </c>
-      <c r="CF7" t="inlineStr">
+      <c r="CJ7" t="inlineStr">
         <is>
           <t>3.13%</t>
         </is>
       </c>
-      <c r="CG7" t="inlineStr">
+      <c r="CK7" t="inlineStr">
         <is>
           <t>32.43</t>
         </is>
       </c>
-      <c r="CH7" t="inlineStr">
+      <c r="CL7" t="inlineStr">
         <is>
           <t>2434</t>
         </is>
       </c>
-      <c r="CI7" t="inlineStr">
+      <c r="CM7" t="inlineStr">
         <is>
           <t>半導體產品60.53%、光電產品37.52%、其他產品1.95% (2024年)</t>
         </is>
       </c>
-      <c r="CJ7" t="inlineStr">
+      <c r="CN7" t="inlineStr">
         <is>
           <t>利機-電子通路業-上櫃</t>
         </is>
       </c>
-      <c r="CK7" t="inlineStr">
+      <c r="CO7" t="inlineStr">
         <is>
           <t>電子通路業右下上櫃</t>
         </is>
       </c>
-      <c r="CL7" t="inlineStr">
+      <c r="CP7" t="inlineStr">
         <is>
           <t>51.7</t>
         </is>
       </c>
-      <c r="CM7" t="inlineStr">
+      <c r="CQ7" t="inlineStr">
         <is>
           <t>52.9</t>
         </is>
       </c>
-      <c r="CN7" t="inlineStr">
+      <c r="CR7" t="inlineStr">
         <is>
           <t>51.5</t>
         </is>
       </c>
-      <c r="CO7" t="inlineStr">
+      <c r="CS7" t="inlineStr">
         <is>
           <t>52.9</t>
         </is>
       </c>
-      <c r="CP7" t="inlineStr">
+      <c r="CT7" t="inlineStr">
         <is>
           <t>23.11</t>
         </is>
       </c>
-      <c r="CQ7" t="inlineStr">
+      <c r="CU7" t="inlineStr">
         <is>
           <t>** 半導體 - 基板、導線架、IC封裝測試、IC模組、IC通路** 平面顯示器 - 驅動IC** 觸控面板 - 印刷材料** LED照明產業 - 封裝/模組</t>
         </is>
       </c>
-      <c r="CR7" t="inlineStr">
+      <c r="CV7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3820,325 +3960,345 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
           <t>2025/10/22</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>58.5</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>2025/06/11</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>55.7</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>-0.06</t>
-        </is>
-      </c>
       <c r="AG8" t="inlineStr">
         <is>
+          <t>2025/10/15</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>59.4</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>2025/09/11</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>61.3</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AH8" t="inlineStr">
+      <c r="AL8" t="inlineStr">
         <is>
           <t>3.31</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>-2.13</t>
         </is>
       </c>
-      <c r="AJ8" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="inlineStr">
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
+      <c r="AQ8" t="inlineStr">
         <is>
           <t>277</t>
         </is>
       </c>
-      <c r="AN8" t="inlineStr">
+      <c r="AR8" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO8" t="inlineStr">
+      <c r="AS8" t="inlineStr">
         <is>
           <t>56.74</t>
         </is>
       </c>
-      <c r="AP8" t="n">
+      <c r="AT8" t="n">
         <v>-1.11</v>
       </c>
-      <c r="AQ8" t="n">
+      <c r="AU8" t="n">
         <v>0.1</v>
       </c>
-      <c r="AR8" t="inlineStr">
+      <c r="AV8" t="inlineStr">
         <is>
           <t>-6.39</t>
         </is>
       </c>
-      <c r="AS8" t="inlineStr">
+      <c r="AW8" t="inlineStr">
         <is>
           <t>-2.71</t>
         </is>
       </c>
-      <c r="AT8" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>52.27999999999999</t>
         </is>
       </c>
-      <c r="AU8" t="n">
+      <c r="AY8" t="n">
         <v>52.23</v>
       </c>
-      <c r="AV8" t="n">
+      <c r="AZ8" t="n">
         <v>55.8</v>
       </c>
-      <c r="AW8" t="inlineStr">
+      <c r="BA8" t="inlineStr">
         <is>
           <t>57.35</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="BB8" t="inlineStr">
         <is>
           <t>24.71</t>
         </is>
       </c>
-      <c r="AY8" t="n">
+      <c r="BC8" t="n">
         <v>-0.9399999999999999</v>
       </c>
-      <c r="AZ8" t="n">
+      <c r="BD8" t="n">
         <v>-1.25</v>
       </c>
-      <c r="BA8" t="inlineStr">
+      <c r="BE8" t="inlineStr">
         <is>
           <t>7.3</t>
         </is>
       </c>
-      <c r="BB8" t="inlineStr">
+      <c r="BF8" t="inlineStr">
         <is>
           <t>-117.14</t>
         </is>
       </c>
-      <c r="BC8" t="inlineStr">
+      <c r="BG8" t="inlineStr">
         <is>
           <t>2025/11/26</t>
         </is>
       </c>
-      <c r="BD8" t="inlineStr">
+      <c r="BH8" t="inlineStr">
         <is>
           <t>88838.76825842698</t>
         </is>
       </c>
-      <c r="BE8" t="inlineStr">
+      <c r="BI8" t="inlineStr">
         <is>
           <t>4797.0</t>
         </is>
       </c>
-      <c r="BF8" t="n">
+      <c r="BJ8" t="n">
         <v>4673.8</v>
       </c>
-      <c r="BG8" t="inlineStr">
+      <c r="BK8" t="inlineStr">
         <is>
           <t>8324.9</t>
         </is>
       </c>
-      <c r="BH8" t="n">
+      <c r="BL8" t="n">
         <v>12556.78</v>
       </c>
-      <c r="BI8" t="inlineStr">
+      <c r="BM8" t="inlineStr">
         <is>
           <t>-3651</t>
         </is>
       </c>
-      <c r="BJ8" t="inlineStr">
+      <c r="BN8" t="inlineStr">
         <is>
           <t>-533.6188939337103</t>
         </is>
       </c>
-      <c r="BK8" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>-754.4941534987138</t>
         </is>
       </c>
-      <c r="BL8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
         <is>
           <t>4797.0</t>
         </is>
       </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN8" t="inlineStr">
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
         <is>
           <t>55.5</t>
         </is>
       </c>
-      <c r="BO8" t="inlineStr">
+      <c r="BS8" t="inlineStr">
         <is>
           <t>2025/08/20</t>
         </is>
       </c>
-      <c r="BP8" t="inlineStr">
+      <c r="BT8" t="inlineStr">
         <is>
           <t>-6.85</t>
         </is>
       </c>
-      <c r="BQ8" t="inlineStr">
+      <c r="BU8" t="inlineStr">
         <is>
           <t>利機</t>
         </is>
       </c>
-      <c r="BR8" t="inlineStr">
+      <c r="BV8" t="inlineStr">
         <is>
           <t>利機</t>
         </is>
       </c>
-      <c r="BS8" t="inlineStr">
+      <c r="BW8" t="inlineStr">
         <is>
           <t>電子通路業</t>
         </is>
       </c>
-      <c r="BT8" t="inlineStr">
+      <c r="BX8" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU8" t="inlineStr">
+      <c r="BY8" t="inlineStr">
         <is>
           <t>1.09</t>
         </is>
       </c>
-      <c r="BV8" t="inlineStr">
+      <c r="BZ8" t="inlineStr">
         <is>
           <t>2.973959600876125</t>
         </is>
       </c>
-      <c r="BW8" t="inlineStr">
+      <c r="CA8" t="inlineStr">
         <is>
           <t>7.507647901781631</t>
         </is>
       </c>
-      <c r="BX8" t="inlineStr">
+      <c r="CB8" t="inlineStr">
         <is>
           <t>9.97333412563415</t>
         </is>
       </c>
-      <c r="BY8" t="inlineStr">
+      <c r="CC8" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ8" t="inlineStr">
+      <c r="CD8" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA8" t="inlineStr">
+      <c r="CE8" t="inlineStr">
         <is>
           <t>2.24</t>
         </is>
       </c>
-      <c r="CB8" t="inlineStr">
+      <c r="CF8" t="inlineStr">
         <is>
           <t>3.7</t>
         </is>
       </c>
-      <c r="CC8" t="inlineStr">
+      <c r="CG8" t="inlineStr">
         <is>
           <t>6.82</t>
         </is>
       </c>
-      <c r="CD8" t="inlineStr">
+      <c r="CH8" t="inlineStr">
         <is>
           <t>22.17</t>
         </is>
       </c>
-      <c r="CE8" t="inlineStr">
+      <c r="CI8" t="inlineStr">
         <is>
           <t>20.15%</t>
         </is>
       </c>
-      <c r="CF8" t="inlineStr">
+      <c r="CJ8" t="inlineStr">
         <is>
           <t>3.13%</t>
         </is>
       </c>
-      <c r="CG8" t="inlineStr">
+      <c r="CK8" t="inlineStr">
         <is>
           <t>32.43</t>
         </is>
       </c>
-      <c r="CH8" t="inlineStr">
+      <c r="CL8" t="inlineStr">
         <is>
           <t>2434</t>
         </is>
       </c>
-      <c r="CI8" t="inlineStr">
+      <c r="CM8" t="inlineStr">
         <is>
           <t>半導體產品60.53%、光電產品37.52%、其他產品1.95% (2024年)</t>
         </is>
       </c>
-      <c r="CJ8" t="inlineStr">
+      <c r="CN8" t="inlineStr">
         <is>
           <t>利機-電子通路業-上櫃</t>
         </is>
       </c>
-      <c r="CK8" t="inlineStr">
+      <c r="CO8" t="inlineStr">
         <is>
           <t>電子通路業右下上櫃</t>
         </is>
       </c>
-      <c r="CL8" t="inlineStr">
+      <c r="CP8" t="inlineStr">
         <is>
           <t>52.5</t>
         </is>
       </c>
-      <c r="CM8" t="inlineStr">
+      <c r="CQ8" t="inlineStr">
         <is>
           <t>53.0</t>
         </is>
       </c>
-      <c r="CN8" t="inlineStr">
+      <c r="CR8" t="inlineStr">
         <is>
           <t>51.5</t>
         </is>
       </c>
-      <c r="CO8" t="inlineStr">
+      <c r="CS8" t="inlineStr">
         <is>
           <t>51.7</t>
         </is>
       </c>
-      <c r="CP8" t="inlineStr">
+      <c r="CT8" t="inlineStr">
         <is>
           <t>23.11</t>
         </is>
       </c>
-      <c r="CQ8" t="inlineStr">
+      <c r="CU8" t="inlineStr">
         <is>
           <t>** 半導體 - 基板、導線架、IC封裝測試、IC模組、IC通路** 平面顯示器 - 驅動IC** 觸控面板 - 印刷材料** LED照明產業 - 封裝/模組</t>
         </is>
       </c>
-      <c r="CR8" t="inlineStr">
+      <c r="CV8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4282,325 +4442,345 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
           <t>2025/10/22</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>58.5</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>2025/06/11</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
         <is>
           <t>55.7</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
       <c r="AG9" t="inlineStr">
         <is>
+          <t>2025/10/15</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>59.4</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>2025/09/11</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>61.3</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
           <t>2025-12-04</t>
         </is>
       </c>
-      <c r="AH9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>2.23</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>-1.71</t>
         </is>
       </c>
-      <c r="AJ9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr">
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
+      <c r="AQ9" t="inlineStr">
         <is>
           <t>277</t>
         </is>
       </c>
-      <c r="AN9" t="inlineStr">
+      <c r="AR9" t="inlineStr">
         <is>
           <t>81.82</t>
         </is>
       </c>
-      <c r="AO9" t="inlineStr">
+      <c r="AS9" t="inlineStr">
         <is>
           <t>78.48</t>
         </is>
       </c>
-      <c r="AP9" t="n">
+      <c r="AT9" t="n">
         <v>0.27</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AU9" t="n">
         <v>0.45</v>
       </c>
-      <c r="AR9" t="inlineStr">
+      <c r="AV9" t="inlineStr">
         <is>
           <t>-6.53</t>
         </is>
       </c>
-      <c r="AS9" t="inlineStr">
+      <c r="AW9" t="inlineStr">
         <is>
           <t>-2.38</t>
         </is>
       </c>
-      <c r="AT9" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>52.56</t>
         </is>
       </c>
-      <c r="AU9" t="n">
+      <c r="AY9" t="n">
         <v>52.32</v>
       </c>
-      <c r="AV9" t="n">
+      <c r="AZ9" t="n">
         <v>55.98</v>
       </c>
-      <c r="AW9" t="inlineStr">
+      <c r="BA9" t="inlineStr">
         <is>
           <t>57.34</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="BB9" t="inlineStr">
         <is>
           <t>28.11</t>
         </is>
       </c>
-      <c r="AY9" t="n">
+      <c r="BC9" t="n">
         <v>-0.96</v>
       </c>
-      <c r="AZ9" t="n">
+      <c r="BD9" t="n">
         <v>-1.33</v>
       </c>
-      <c r="BA9" t="inlineStr">
+      <c r="BE9" t="inlineStr">
         <is>
           <t>7.3</t>
         </is>
       </c>
-      <c r="BB9" t="inlineStr">
+      <c r="BF9" t="inlineStr">
         <is>
           <t>-118.20</t>
         </is>
       </c>
-      <c r="BC9" t="inlineStr">
+      <c r="BG9" t="inlineStr">
         <is>
           <t>2025/11/26</t>
         </is>
       </c>
-      <c r="BD9" t="inlineStr">
+      <c r="BH9" t="inlineStr">
         <is>
           <t>88838.76825842698</t>
         </is>
       </c>
-      <c r="BE9" t="inlineStr">
+      <c r="BI9" t="inlineStr">
         <is>
           <t>3296.0</t>
         </is>
       </c>
-      <c r="BF9" t="n">
+      <c r="BJ9" t="n">
         <v>5465.4</v>
       </c>
-      <c r="BG9" t="inlineStr">
+      <c r="BK9" t="inlineStr">
         <is>
           <t>8198.7</t>
         </is>
       </c>
-      <c r="BH9" t="n">
+      <c r="BL9" t="n">
         <v>12704.54</v>
       </c>
-      <c r="BI9" t="inlineStr">
+      <c r="BM9" t="inlineStr">
         <is>
           <t>-2733</t>
         </is>
       </c>
-      <c r="BJ9" t="inlineStr">
+      <c r="BN9" t="inlineStr">
         <is>
           <t>-493.4597558309824</t>
         </is>
       </c>
-      <c r="BK9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>-677.32375952437</t>
         </is>
       </c>
-      <c r="BL9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
         <is>
           <t>3296.0</t>
         </is>
       </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN9" t="inlineStr">
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
         <is>
           <t>55.5</t>
         </is>
       </c>
-      <c r="BO9" t="inlineStr">
+      <c r="BS9" t="inlineStr">
         <is>
           <t>2025/08/20</t>
         </is>
       </c>
-      <c r="BP9" t="inlineStr">
+      <c r="BT9" t="inlineStr">
         <is>
           <t>-5.05</t>
         </is>
       </c>
-      <c r="BQ9" t="inlineStr">
+      <c r="BU9" t="inlineStr">
         <is>
           <t>利機</t>
         </is>
       </c>
-      <c r="BR9" t="inlineStr">
+      <c r="BV9" t="inlineStr">
         <is>
           <t>利機</t>
         </is>
       </c>
-      <c r="BS9" t="inlineStr">
+      <c r="BW9" t="inlineStr">
         <is>
           <t>電子通路業</t>
         </is>
       </c>
-      <c r="BT9" t="inlineStr">
+      <c r="BX9" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU9" t="inlineStr">
+      <c r="BY9" t="inlineStr">
         <is>
           <t>1.09</t>
         </is>
       </c>
-      <c r="BV9" t="inlineStr">
+      <c r="BZ9" t="inlineStr">
         <is>
           <t>2.973959600876125</t>
         </is>
       </c>
-      <c r="BW9" t="inlineStr">
+      <c r="CA9" t="inlineStr">
         <is>
           <t>7.507647901781631</t>
         </is>
       </c>
-      <c r="BX9" t="inlineStr">
+      <c r="CB9" t="inlineStr">
         <is>
           <t>9.97333412563415</t>
         </is>
       </c>
-      <c r="BY9" t="inlineStr">
+      <c r="CC9" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ9" t="inlineStr">
+      <c r="CD9" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA9" t="inlineStr">
+      <c r="CE9" t="inlineStr">
         <is>
           <t>2.28</t>
         </is>
       </c>
-      <c r="CB9" t="inlineStr">
+      <c r="CF9" t="inlineStr">
         <is>
           <t>3.7</t>
         </is>
       </c>
-      <c r="CC9" t="inlineStr">
+      <c r="CG9" t="inlineStr">
         <is>
           <t>6.82</t>
         </is>
       </c>
-      <c r="CD9" t="inlineStr">
+      <c r="CH9" t="inlineStr">
         <is>
           <t>22.17</t>
         </is>
       </c>
-      <c r="CE9" t="inlineStr">
+      <c r="CI9" t="inlineStr">
         <is>
           <t>20.15%</t>
         </is>
       </c>
-      <c r="CF9" t="inlineStr">
+      <c r="CJ9" t="inlineStr">
         <is>
           <t>3.13%</t>
         </is>
       </c>
-      <c r="CG9" t="inlineStr">
+      <c r="CK9" t="inlineStr">
         <is>
           <t>32.43</t>
         </is>
       </c>
-      <c r="CH9" t="inlineStr">
+      <c r="CL9" t="inlineStr">
         <is>
           <t>2434</t>
         </is>
       </c>
-      <c r="CI9" t="inlineStr">
+      <c r="CM9" t="inlineStr">
         <is>
           <t>半導體產品60.53%、光電產品37.52%、其他產品1.95% (2024年)</t>
         </is>
       </c>
-      <c r="CJ9" t="inlineStr">
+      <c r="CN9" t="inlineStr">
         <is>
           <t>利機-電子通路業-上櫃</t>
         </is>
       </c>
-      <c r="CK9" t="inlineStr">
+      <c r="CO9" t="inlineStr">
         <is>
           <t>電子通路業右下上櫃</t>
         </is>
       </c>
-      <c r="CL9" t="inlineStr">
+      <c r="CP9" t="inlineStr">
         <is>
           <t>53.6</t>
         </is>
       </c>
-      <c r="CM9" t="inlineStr">
+      <c r="CQ9" t="inlineStr">
         <is>
           <t>53.7</t>
         </is>
       </c>
-      <c r="CN9" t="inlineStr">
+      <c r="CR9" t="inlineStr">
         <is>
           <t>52.6</t>
         </is>
       </c>
-      <c r="CO9" t="inlineStr">
+      <c r="CS9" t="inlineStr">
         <is>
           <t>52.7</t>
         </is>
       </c>
-      <c r="CP9" t="inlineStr">
+      <c r="CT9" t="inlineStr">
         <is>
           <t>23.11</t>
         </is>
       </c>
-      <c r="CQ9" t="inlineStr">
+      <c r="CU9" t="inlineStr">
         <is>
           <t>** 半導體 - 基板、導線架、IC封裝測試、IC模組、IC通路** 平面顯示器 - 驅動IC** 觸控面板 - 印刷材料** LED照明產業 - 封裝/模組</t>
         </is>
       </c>
-      <c r="CR9" t="inlineStr">
+      <c r="CV9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4744,325 +4924,345 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
           <t>2025/10/22</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>58.5</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>2025/06/11</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
         <is>
           <t>55.7</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
       <c r="AG10" t="inlineStr">
         <is>
+          <t>2025/10/15</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>59.4</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>2025/09/11</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>61.3</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
           <t>2025-12-03</t>
         </is>
       </c>
-      <c r="AH10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>5.62</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>-1.31</t>
         </is>
       </c>
-      <c r="AJ10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK10" t="inlineStr"/>
-      <c r="AL10" t="inlineStr">
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
+      <c r="AQ10" t="inlineStr">
         <is>
           <t>277</t>
         </is>
       </c>
-      <c r="AN10" t="inlineStr">
+      <c r="AR10" t="inlineStr">
         <is>
           <t>88.41</t>
         </is>
       </c>
-      <c r="AO10" t="inlineStr">
+      <c r="AS10" t="inlineStr">
         <is>
           <t>71.98</t>
         </is>
       </c>
-      <c r="AP10" t="n">
+      <c r="AT10" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AU10" t="n">
         <v>0.29</v>
       </c>
-      <c r="AR10" t="inlineStr">
+      <c r="AV10" t="inlineStr">
         <is>
           <t>-6.68</t>
         </is>
       </c>
-      <c r="AS10" t="inlineStr">
+      <c r="AW10" t="inlineStr">
         <is>
           <t>-2.07</t>
         </is>
       </c>
-      <c r="AT10" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>52.54</t>
         </is>
       </c>
-      <c r="AU10" t="n">
+      <c r="AY10" t="n">
         <v>52.39</v>
       </c>
-      <c r="AV10" t="n">
+      <c r="AZ10" t="n">
         <v>56.14</v>
       </c>
-      <c r="AW10" t="inlineStr">
+      <c r="BA10" t="inlineStr">
         <is>
           <t>57.32</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="BB10" t="inlineStr">
         <is>
           <t>25.48</t>
         </is>
       </c>
-      <c r="AY10" t="n">
+      <c r="BC10" t="n">
         <v>-1.06</v>
       </c>
-      <c r="AZ10" t="n">
+      <c r="BD10" t="n">
         <v>-1.42</v>
       </c>
-      <c r="BA10" t="inlineStr">
+      <c r="BE10" t="inlineStr">
         <is>
           <t>7.3</t>
         </is>
       </c>
-      <c r="BB10" t="inlineStr">
+      <c r="BF10" t="inlineStr">
         <is>
           <t>-119.48</t>
         </is>
       </c>
-      <c r="BC10" t="inlineStr">
+      <c r="BG10" t="inlineStr">
         <is>
           <t>2025/11/26</t>
         </is>
       </c>
-      <c r="BD10" t="inlineStr">
+      <c r="BH10" t="inlineStr">
         <is>
           <t>88838.76825842698</t>
         </is>
       </c>
-      <c r="BE10" t="inlineStr">
+      <c r="BI10" t="inlineStr">
         <is>
           <t>8291.0</t>
         </is>
       </c>
-      <c r="BF10" t="n">
+      <c r="BJ10" t="n">
         <v>7519</v>
       </c>
-      <c r="BG10" t="inlineStr">
+      <c r="BK10" t="inlineStr">
         <is>
           <t>8434.2</t>
         </is>
       </c>
-      <c r="BH10" t="n">
+      <c r="BL10" t="n">
         <v>12897.76</v>
       </c>
-      <c r="BI10" t="inlineStr">
+      <c r="BM10" t="inlineStr">
         <is>
           <t>-915</t>
         </is>
       </c>
-      <c r="BJ10" t="inlineStr">
+      <c r="BN10" t="inlineStr">
         <is>
           <t>-460.0299369776392</t>
         </is>
       </c>
-      <c r="BK10" t="inlineStr">
+      <c r="BO10" t="inlineStr">
         <is>
           <t>-382.0687767208665</t>
         </is>
       </c>
-      <c r="BL10" t="inlineStr">
+      <c r="BP10" t="inlineStr">
         <is>
           <t>8291.0</t>
         </is>
       </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN10" t="inlineStr">
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
         <is>
           <t>55.5</t>
         </is>
       </c>
-      <c r="BO10" t="inlineStr">
+      <c r="BS10" t="inlineStr">
         <is>
           <t>2025/08/20</t>
         </is>
       </c>
-      <c r="BP10" t="inlineStr">
+      <c r="BT10" t="inlineStr">
         <is>
           <t>-4.68</t>
         </is>
       </c>
-      <c r="BQ10" t="inlineStr">
+      <c r="BU10" t="inlineStr">
         <is>
           <t>利機</t>
         </is>
       </c>
-      <c r="BR10" t="inlineStr">
+      <c r="BV10" t="inlineStr">
         <is>
           <t>利機</t>
         </is>
       </c>
-      <c r="BS10" t="inlineStr">
+      <c r="BW10" t="inlineStr">
         <is>
           <t>電子通路業</t>
         </is>
       </c>
-      <c r="BT10" t="inlineStr">
+      <c r="BX10" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU10" t="inlineStr">
+      <c r="BY10" t="inlineStr">
         <is>
           <t>1.09</t>
         </is>
       </c>
-      <c r="BV10" t="inlineStr">
+      <c r="BZ10" t="inlineStr">
         <is>
           <t>2.973959600876125</t>
         </is>
       </c>
-      <c r="BW10" t="inlineStr">
+      <c r="CA10" t="inlineStr">
         <is>
           <t>7.507647901781631</t>
         </is>
       </c>
-      <c r="BX10" t="inlineStr">
+      <c r="CB10" t="inlineStr">
         <is>
           <t>9.97333412563415</t>
         </is>
       </c>
-      <c r="BY10" t="inlineStr">
+      <c r="CC10" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
-      <c r="BZ10" t="inlineStr">
+      <c r="CD10" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="CA10" t="inlineStr">
+      <c r="CE10" t="inlineStr">
         <is>
           <t>2.29</t>
         </is>
       </c>
-      <c r="CB10" t="inlineStr">
+      <c r="CF10" t="inlineStr">
         <is>
           <t>3.7</t>
         </is>
       </c>
-      <c r="CC10" t="inlineStr">
+      <c r="CG10" t="inlineStr">
         <is>
           <t>6.82</t>
         </is>
       </c>
-      <c r="CD10" t="inlineStr">
+      <c r="CH10" t="inlineStr">
         <is>
           <t>22.17</t>
         </is>
       </c>
-      <c r="CE10" t="inlineStr">
+      <c r="CI10" t="inlineStr">
         <is>
           <t>20.15%</t>
         </is>
       </c>
-      <c r="CF10" t="inlineStr">
+      <c r="CJ10" t="inlineStr">
         <is>
           <t>3.13%</t>
         </is>
       </c>
-      <c r="CG10" t="inlineStr">
+      <c r="CK10" t="inlineStr">
         <is>
           <t>32.43</t>
         </is>
       </c>
-      <c r="CH10" t="inlineStr">
+      <c r="CL10" t="inlineStr">
         <is>
           <t>2434</t>
         </is>
       </c>
-      <c r="CI10" t="inlineStr">
+      <c r="CM10" t="inlineStr">
         <is>
           <t>半導體產品60.53%、光電產品37.52%、其他產品1.95% (2024年)</t>
         </is>
       </c>
-      <c r="CJ10" t="inlineStr">
+      <c r="CN10" t="inlineStr">
         <is>
           <t>利機-電子通路業-上櫃</t>
         </is>
       </c>
-      <c r="CK10" t="inlineStr">
+      <c r="CO10" t="inlineStr">
         <is>
           <t>電子通路業右下上櫃</t>
         </is>
       </c>
-      <c r="CL10" t="inlineStr">
+      <c r="CP10" t="inlineStr">
         <is>
           <t>52.8</t>
         </is>
       </c>
-      <c r="CM10" t="inlineStr">
+      <c r="CQ10" t="inlineStr">
         <is>
           <t>54.3</t>
         </is>
       </c>
-      <c r="CN10" t="inlineStr">
+      <c r="CR10" t="inlineStr">
         <is>
           <t>52.2</t>
         </is>
       </c>
-      <c r="CO10" t="inlineStr">
+      <c r="CS10" t="inlineStr">
         <is>
           <t>52.9</t>
         </is>
       </c>
-      <c r="CP10" t="inlineStr">
+      <c r="CT10" t="inlineStr">
         <is>
           <t>23.11</t>
         </is>
       </c>
-      <c r="CQ10" t="inlineStr">
+      <c r="CU10" t="inlineStr">
         <is>
           <t>** 半導體 - 基板、導線架、IC封裝測試、IC模組、IC通路** 平面顯示器 - 驅動IC** 觸控面板 - 印刷材料** LED照明產業 - 封裝/模組</t>
         </is>
       </c>
-      <c r="CR10" t="inlineStr">
+      <c r="CV10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5206,325 +5406,345 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
+          <t>-0.0</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
           <t>2025/10/22</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AD11" t="inlineStr">
         <is>
           <t>58.5</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AE11" t="inlineStr">
         <is>
           <t>2025/06/11</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AF11" t="inlineStr">
         <is>
           <t>55.7</t>
         </is>
       </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
       <c r="AG11" t="inlineStr">
         <is>
+          <t>2025/10/15</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>59.4</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>2025/09/11</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>61.3</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
           <t>2025-12-02</t>
         </is>
       </c>
-      <c r="AH11" t="inlineStr">
+      <c r="AL11" t="inlineStr">
         <is>
           <t>1.95</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
+      <c r="AM11" t="inlineStr">
         <is>
           <t>-1.73</t>
         </is>
       </c>
-      <c r="AJ11" t="inlineStr">
+      <c r="AN11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="inlineStr">
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
+      <c r="AQ11" t="inlineStr">
         <is>
           <t>277</t>
         </is>
       </c>
-      <c r="AN11" t="inlineStr">
+      <c r="AR11" t="inlineStr">
         <is>
           <t>65.22</t>
         </is>
       </c>
-      <c r="AO11" t="inlineStr">
+      <c r="AS11" t="inlineStr">
         <is>
           <t>73.91</t>
         </is>
       </c>
-      <c r="AP11" t="n">
+      <c r="AT11" t="n">
         <v>-0.99</v>
       </c>
-      <c r="AQ11" t="n">
+      <c r="AU11" t="n">
         <v>0.35</v>
       </c>
-      <c r="AR11" t="inlineStr">
+      <c r="AV11" t="inlineStr">
         <is>
           <t>-6.88</t>
         </is>
       </c>
-      <c r="AS11" t="inlineStr">
+      <c r="AW11" t="inlineStr">
         <is>
           <t>-1.76</t>
         </is>
       </c>
-      <c r="AT11" t="inlineStr">
+      <c r="AX11" t="inlineStr">
         <is>
           <t>52.62</t>
         </is>
       </c>
-      <c r="AU11" t="n">
+      <c r="AY11" t="n">
         <v>52.44</v>
       </c>
-      <c r="AV11" t="n">
+      <c r="AZ11" t="n">
         <v>56.31</v>
       </c>
-      <c r="AW11" t="inlineStr">
+      <c r="BA11" t="inlineStr">
         <is>
           <t>57.32</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
+      <c r="BB11" t="inlineStr">
         <is>
           <t>20.79</t>
         </is>
       </c>
-      <c r="AY11" t="n">
+      <c r="BC11" t="n">
         <v>-1.2</v>
       </c>
-      <c r="AZ11" t="n">
+      <c r="BD11" t="n">
         <v>-1.51</v>
       </c>
-      <c r="BA11" t="inlineStr">
+      <c r="BE11" t="inlineStr">
         <is>
           <t>7.3</t>
         </is>
       </c>
-      <c r="BB11" t="inlineStr">
+      <c r="BF11" t="inlineStr">
         <is>
           <t>-120.72</t>
         </is>
       </c>
-      <c r="BC11" t="inlineStr">
+      <c r="BG11" t="inlineStr">
         <is>
           <t>2025/11/26</t>
         </is>
       </c>
-      <c r="BD11" t="inlineStr">
+      <c r="BH11" t="inlineStr">
         <is>
           <t>88838.76825842698</t>
         </is>
       </c>
-      <c r="BE11" t="inlineStr">
+      <c r="BI11" t="inlineStr">
         <is>
           <t>2852.0</t>
         </is>
       </c>
-      <c r="BF11" t="n">
+      <c r="BJ11" t="n">
         <v>9501.200000000001</v>
       </c>
-      <c r="BG11" t="inlineStr">
+      <c r="BK11" t="inlineStr">
         <is>
           <t>8244.2</t>
         </is>
       </c>
-      <c r="BH11" t="n">
+      <c r="BL11" t="n">
         <v>13064.54</v>
       </c>
-      <c r="BI11" t="inlineStr">
+      <c r="BM11" t="inlineStr">
         <is>
           <t>1257</t>
         </is>
       </c>
-      <c r="BJ11" t="inlineStr">
+      <c r="BN11" t="inlineStr">
         <is>
           <t>-474.2046933879615</t>
         </is>
       </c>
-      <c r="BK11" t="inlineStr">
+      <c r="BO11" t="inlineStr">
         <is>
           <t>-481.8092021186876</t>
         </is>
       </c>
-      <c r="BL11" t="inlineStr">
+      <c r="BP11" t="inlineStr">
         <is>
           <t>2852.0</t>
         </is>
       </c>
-      <c r="BM11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN11" t="inlineStr">
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
         <is>
           <t>55.5</t>
         </is>
       </c>
-      <c r="BO11" t="inlineStr">
+      <c r="BS11" t="inlineStr">
         <is>
           <t>2025/08/20</t>
         </is>
       </c>
-      <c r="BP11" t="inlineStr">
+      <c r="BT11" t="inlineStr">
         <is>
           <t>-6.13</t>
         </is>
       </c>
-      <c r="BQ11" t="inlineStr">
+      <c r="BU11" t="inlineStr">
         <is>
           <t>利機</t>
         </is>
       </c>
-      <c r="BR11" t="inlineStr">
+      <c r="BV11" t="inlineStr">
         <is>
           <t>利機</t>
         </is>
       </c>
-      <c r="BS11" t="inlineStr">
+      <c r="BW11" t="inlineStr">
         <is>
           <t>電子通路業</t>
         </is>
       </c>
-      <c r="BT11" t="inlineStr">
+      <c r="BX11" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU11" t="inlineStr">
+      <c r="BY11" t="inlineStr">
         <is>
           <t>1.09</t>
         </is>
       </c>
-      <c r="BV11" t="inlineStr">
+      <c r="BZ11" t="inlineStr">
         <is>
           <t>2.973959600876125</t>
         </is>
       </c>
-      <c r="BW11" t="inlineStr">
+      <c r="CA11" t="inlineStr">
         <is>
           <t>7.507647901781631</t>
         </is>
       </c>
-      <c r="BX11" t="inlineStr">
+      <c r="CB11" t="inlineStr">
         <is>
           <t>9.97333412563415</t>
         </is>
       </c>
-      <c r="BY11" t="inlineStr">
+      <c r="CC11" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ11" t="inlineStr">
+      <c r="CD11" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA11" t="inlineStr">
+      <c r="CE11" t="inlineStr">
         <is>
           <t>2.25</t>
         </is>
       </c>
-      <c r="CB11" t="inlineStr">
+      <c r="CF11" t="inlineStr">
         <is>
           <t>3.7</t>
         </is>
       </c>
-      <c r="CC11" t="inlineStr">
+      <c r="CG11" t="inlineStr">
         <is>
           <t>6.82</t>
         </is>
       </c>
-      <c r="CD11" t="inlineStr">
+      <c r="CH11" t="inlineStr">
         <is>
           <t>22.17</t>
         </is>
       </c>
-      <c r="CE11" t="inlineStr">
+      <c r="CI11" t="inlineStr">
         <is>
           <t>20.15%</t>
         </is>
       </c>
-      <c r="CF11" t="inlineStr">
+      <c r="CJ11" t="inlineStr">
         <is>
           <t>3.13%</t>
         </is>
       </c>
-      <c r="CG11" t="inlineStr">
+      <c r="CK11" t="inlineStr">
         <is>
           <t>32.43</t>
         </is>
       </c>
-      <c r="CH11" t="inlineStr">
+      <c r="CL11" t="inlineStr">
         <is>
           <t>2434</t>
         </is>
       </c>
-      <c r="CI11" t="inlineStr">
+      <c r="CM11" t="inlineStr">
         <is>
           <t>半導體產品60.53%、光電產品37.52%、其他產品1.95% (2024年)</t>
         </is>
       </c>
-      <c r="CJ11" t="inlineStr">
+      <c r="CN11" t="inlineStr">
         <is>
           <t>利機-電子通路業-上櫃</t>
         </is>
       </c>
-      <c r="CK11" t="inlineStr">
+      <c r="CO11" t="inlineStr">
         <is>
           <t>電子通路業右下上櫃</t>
         </is>
       </c>
-      <c r="CL11" t="inlineStr">
+      <c r="CP11" t="inlineStr">
         <is>
           <t>52.1</t>
         </is>
       </c>
-      <c r="CM11" t="inlineStr">
+      <c r="CQ11" t="inlineStr">
         <is>
           <t>53.0</t>
         </is>
       </c>
-      <c r="CN11" t="inlineStr">
+      <c r="CR11" t="inlineStr">
         <is>
           <t>52.1</t>
         </is>
       </c>
-      <c r="CO11" t="inlineStr">
+      <c r="CS11" t="inlineStr">
         <is>
           <t>52.1</t>
         </is>
       </c>
-      <c r="CP11" t="inlineStr">
+      <c r="CT11" t="inlineStr">
         <is>
           <t>23.11</t>
         </is>
       </c>
-      <c r="CQ11" t="inlineStr">
+      <c r="CU11" t="inlineStr">
         <is>
           <t>** 半導體 - 基板、導線架、IC封裝測試、IC模組、IC通路** 平面顯示器 - 驅動IC** 觸控面板 - 印刷材料** LED照明產業 - 封裝/模組</t>
         </is>
       </c>
-      <c r="CR11" t="inlineStr">
+      <c r="CV11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5668,325 +5888,345 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
           <t>2025/10/22</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AD12" t="inlineStr">
         <is>
           <t>58.5</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
+      <c r="AE12" t="inlineStr">
         <is>
           <t>2025/06/11</t>
         </is>
       </c>
-      <c r="AE12" t="inlineStr">
+      <c r="AF12" t="inlineStr">
         <is>
           <t>55.7</t>
         </is>
       </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
       <c r="AG12" t="inlineStr">
         <is>
+          <t>2025/10/15</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>59.4</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>2025/09/11</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>61.3</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
           <t>2025-12-01</t>
         </is>
       </c>
-      <c r="AH12" t="inlineStr">
+      <c r="AL12" t="inlineStr">
         <is>
           <t>2.85</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
+      <c r="AM12" t="inlineStr">
         <is>
           <t>-2.88</t>
         </is>
       </c>
-      <c r="AJ12" t="inlineStr">
+      <c r="AN12" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK12" t="inlineStr"/>
-      <c r="AL12" t="inlineStr">
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
+      <c r="AQ12" t="inlineStr">
         <is>
           <t>277</t>
         </is>
       </c>
-      <c r="AN12" t="inlineStr">
+      <c r="AR12" t="inlineStr">
         <is>
           <t>62.32</t>
         </is>
       </c>
-      <c r="AO12" t="inlineStr">
+      <c r="AS12" t="inlineStr">
         <is>
           <t>78.74</t>
         </is>
       </c>
-      <c r="AP12" t="n">
+      <c r="AT12" t="n">
         <v>-1.07</v>
       </c>
-      <c r="AQ12" t="n">
+      <c r="AU12" t="n">
         <v>0</v>
       </c>
-      <c r="AR12" t="inlineStr">
+      <c r="AV12" t="inlineStr">
         <is>
           <t>-6.98</t>
         </is>
       </c>
-      <c r="AS12" t="inlineStr">
+      <c r="AW12" t="inlineStr">
         <is>
           <t>-1.45</t>
         </is>
       </c>
-      <c r="AT12" t="inlineStr">
+      <c r="AX12" t="inlineStr">
         <is>
           <t>52.56</t>
         </is>
       </c>
-      <c r="AU12" t="n">
+      <c r="AY12" t="n">
         <v>52.56</v>
       </c>
-      <c r="AV12" t="n">
+      <c r="AZ12" t="n">
         <v>56.5</v>
       </c>
-      <c r="AW12" t="inlineStr">
+      <c r="BA12" t="inlineStr">
         <is>
           <t>57.33</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
+      <c r="BB12" t="inlineStr">
         <is>
           <t>19.82</t>
         </is>
       </c>
-      <c r="AY12" t="n">
+      <c r="BC12" t="n">
         <v>-1.28</v>
       </c>
-      <c r="AZ12" t="n">
+      <c r="BD12" t="n">
         <v>-1.59</v>
       </c>
-      <c r="BA12" t="inlineStr">
+      <c r="BE12" t="inlineStr">
         <is>
           <t>7.3</t>
         </is>
       </c>
-      <c r="BB12" t="inlineStr">
+      <c r="BF12" t="inlineStr">
         <is>
           <t>-121.80</t>
         </is>
       </c>
-      <c r="BC12" t="inlineStr">
+      <c r="BG12" t="inlineStr">
         <is>
           <t>2025/11/26</t>
         </is>
       </c>
-      <c r="BD12" t="inlineStr">
+      <c r="BH12" t="inlineStr">
         <is>
           <t>88838.76825842698</t>
         </is>
       </c>
-      <c r="BE12" t="inlineStr">
+      <c r="BI12" t="inlineStr">
         <is>
           <t>4133.0</t>
         </is>
       </c>
-      <c r="BF12" t="n">
+      <c r="BJ12" t="n">
         <v>12338</v>
       </c>
-      <c r="BG12" t="inlineStr">
+      <c r="BK12" t="inlineStr">
         <is>
           <t>8618.6</t>
         </is>
       </c>
-      <c r="BH12" t="n">
+      <c r="BL12" t="n">
         <v>13299.38</v>
       </c>
-      <c r="BI12" t="inlineStr">
+      <c r="BM12" t="inlineStr">
         <is>
           <t>3719</t>
         </is>
       </c>
-      <c r="BJ12" t="inlineStr">
+      <c r="BN12" t="inlineStr">
         <is>
           <t>-472.8220554369204</t>
         </is>
       </c>
-      <c r="BK12" t="inlineStr">
+      <c r="BO12" t="inlineStr">
         <is>
           <t>-24.33805261133421</t>
         </is>
       </c>
-      <c r="BL12" t="inlineStr">
+      <c r="BP12" t="inlineStr">
         <is>
           <t>4133.0</t>
         </is>
       </c>
-      <c r="BM12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN12" t="inlineStr">
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
         <is>
           <t>55.5</t>
         </is>
       </c>
-      <c r="BO12" t="inlineStr">
+      <c r="BS12" t="inlineStr">
         <is>
           <t>2025/08/20</t>
         </is>
       </c>
-      <c r="BP12" t="inlineStr">
+      <c r="BT12" t="inlineStr">
         <is>
           <t>-6.31</t>
         </is>
       </c>
-      <c r="BQ12" t="inlineStr">
+      <c r="BU12" t="inlineStr">
         <is>
           <t>利機</t>
         </is>
       </c>
-      <c r="BR12" t="inlineStr">
+      <c r="BV12" t="inlineStr">
         <is>
           <t>利機</t>
         </is>
       </c>
-      <c r="BS12" t="inlineStr">
+      <c r="BW12" t="inlineStr">
         <is>
           <t>電子通路業</t>
         </is>
       </c>
-      <c r="BT12" t="inlineStr">
+      <c r="BX12" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU12" t="inlineStr">
+      <c r="BY12" t="inlineStr">
         <is>
           <t>1.09</t>
         </is>
       </c>
-      <c r="BV12" t="inlineStr">
+      <c r="BZ12" t="inlineStr">
         <is>
           <t>2.973959600876125</t>
         </is>
       </c>
-      <c r="BW12" t="inlineStr">
+      <c r="CA12" t="inlineStr">
         <is>
           <t>7.507647901781631</t>
         </is>
       </c>
-      <c r="BX12" t="inlineStr">
+      <c r="CB12" t="inlineStr">
         <is>
           <t>9.97333412563415</t>
         </is>
       </c>
-      <c r="BY12" t="inlineStr">
+      <c r="CC12" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ12" t="inlineStr">
+      <c r="CD12" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA12" t="inlineStr">
+      <c r="CE12" t="inlineStr">
         <is>
           <t>2.25</t>
         </is>
       </c>
-      <c r="CB12" t="inlineStr">
+      <c r="CF12" t="inlineStr">
         <is>
           <t>3.7</t>
         </is>
       </c>
-      <c r="CC12" t="inlineStr">
+      <c r="CG12" t="inlineStr">
         <is>
           <t>6.82</t>
         </is>
       </c>
-      <c r="CD12" t="inlineStr">
+      <c r="CH12" t="inlineStr">
         <is>
           <t>22.17</t>
         </is>
       </c>
-      <c r="CE12" t="inlineStr">
+      <c r="CI12" t="inlineStr">
         <is>
           <t>20.15%</t>
         </is>
       </c>
-      <c r="CF12" t="inlineStr">
+      <c r="CJ12" t="inlineStr">
         <is>
           <t>3.13%</t>
         </is>
       </c>
-      <c r="CG12" t="inlineStr">
+      <c r="CK12" t="inlineStr">
         <is>
           <t>32.43</t>
         </is>
       </c>
-      <c r="CH12" t="inlineStr">
+      <c r="CL12" t="inlineStr">
         <is>
           <t>2434</t>
         </is>
       </c>
-      <c r="CI12" t="inlineStr">
+      <c r="CM12" t="inlineStr">
         <is>
           <t>半導體產品60.53%、光電產品37.52%、其他產品1.95% (2024年)</t>
         </is>
       </c>
-      <c r="CJ12" t="inlineStr">
+      <c r="CN12" t="inlineStr">
         <is>
           <t>利機-電子通路業-上櫃</t>
         </is>
       </c>
-      <c r="CK12" t="inlineStr">
+      <c r="CO12" t="inlineStr">
         <is>
           <t>電子通路業右下上櫃</t>
         </is>
       </c>
-      <c r="CL12" t="inlineStr">
+      <c r="CP12" t="inlineStr">
         <is>
           <t>53.5</t>
         </is>
       </c>
-      <c r="CM12" t="inlineStr">
+      <c r="CQ12" t="inlineStr">
         <is>
           <t>53.6</t>
         </is>
       </c>
-      <c r="CN12" t="inlineStr">
+      <c r="CR12" t="inlineStr">
         <is>
           <t>51.9</t>
         </is>
       </c>
-      <c r="CO12" t="inlineStr">
+      <c r="CS12" t="inlineStr">
         <is>
           <t>52.0</t>
         </is>
       </c>
-      <c r="CP12" t="inlineStr">
+      <c r="CT12" t="inlineStr">
         <is>
           <t>23.11</t>
         </is>
       </c>
-      <c r="CQ12" t="inlineStr">
+      <c r="CU12" t="inlineStr">
         <is>
           <t>** 半導體 - 基板、導線架、IC封裝測試、IC模組、IC通路** 平面顯示器 - 驅動IC** 觸控面板 - 印刷材料** LED照明產業 - 封裝/模組</t>
         </is>
       </c>
-      <c r="CR12" t="inlineStr">
+      <c r="CV12" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/印刷材料.xlsx
+++ b/Result/checksun_type/印刷材料.xlsx
@@ -943,12 +943,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>277.0</t>
+          <t>222.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>22.50</t>
+          <t>30.80</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1113,17 +1113,17 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>8.00</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1134,12 +1134,12 @@
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>222</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -1149,51 +1149,51 @@
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>62.22</t>
+          <t>82.22</t>
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>2.19</v>
+        <v>1.84</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>-5.52</t>
+          <t>-5.06</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>52.94000000000001</t>
+          <t>53.12</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>52.1</v>
+        <v>52.28</v>
       </c>
       <c r="AZ2" t="n">
-        <v>55.14</v>
+        <v>55.07</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>57.16</t>
+          <t>57.15</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>46.74</t>
+          <t>59.81</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-0.4</v>
+        <v>-0.26</v>
       </c>
       <c r="BD2" t="n">
-        <v>-0.75</v>
+        <v>-0.66</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>-110.33</t>
+          <t>-108.99</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
@@ -1212,43 +1212,43 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>88838.76825842698</t>
+          <t>88739.37727910238</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>14937.0</t>
+          <t>11982.0</t>
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>7924.6</v>
+        <v>9656.200000000001</v>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>6469.2</t>
+          <t>7382.2</t>
         </is>
       </c>
       <c r="BL2" t="n">
-        <v>12221.38</v>
+        <v>12339.64</v>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1455</t>
+          <t>2274</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-416.3587527715858</t>
+          <t>-269.1575538650869</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>281.0691610157046</t>
+          <t>540.4490401206567</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>14937.0</t>
+          <t>11982.0</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>32.43</t>
+          <t>32.04</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
@@ -1378,17 +1378,17 @@
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>54.3</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>55.2</t>
+          <t>54.7</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>277.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1450,17 +1450,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>13.27</t>
+          <t>22.50</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-11.78</t>
+          <t>-8.92</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1595,17 +1595,17 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1616,66 +1616,66 @@
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>222</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>46.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>51.11</t>
+          <t>62.22</t>
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>-0.57</v>
+        <v>2.19</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.41</v>
+        <v>1.62</v>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>-5.87</t>
+          <t>-5.52</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.94000000000001</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>51.97</v>
+        <v>52.1</v>
       </c>
       <c r="AZ3" t="n">
-        <v>55.21</v>
+        <v>55.14</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>57.22</t>
+          <t>57.16</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>32.10</t>
+          <t>46.74</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-0.57</v>
+        <v>-0.4</v>
       </c>
       <c r="BD3" t="n">
-        <v>-0.84</v>
+        <v>-0.75</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>-111.54</t>
+          <t>-110.33</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
@@ -1694,43 +1694,43 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>88838.76825842698</t>
+          <t>88739.37727910238</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>5171.0</t>
+          <t>14937.0</t>
         </is>
       </c>
       <c r="BJ3" t="n">
-        <v>6103.8</v>
+        <v>7924.6</v>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>5388.8</t>
+          <t>6469.2</t>
         </is>
       </c>
       <c r="BL3" t="n">
-        <v>12016.5</v>
+        <v>12221.38</v>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>1455</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-543.1638280056386</t>
+          <t>-416.3587527715858</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-416.1188505990758</t>
+          <t>281.0691610157046</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>5171.0</t>
+          <t>14937.0</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>-5.59</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1795,17 +1795,17 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>32.43</t>
+          <t>32.04</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
@@ -1860,22 +1860,22 @@
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>55.2</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1932,17 +1932,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>13.27</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-11.95</t>
+          <t>-11.78</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2077,17 +2077,17 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -2098,66 +2098,66 @@
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>222</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>46.67</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>68.89</t>
+          <t>51.11</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>-0.49</v>
+        <v>-0.57</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.13</v>
+        <v>1.41</v>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>-6.04</t>
+          <t>-5.87</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>52.56</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="AY4" t="n">
         <v>51.97</v>
       </c>
       <c r="AZ4" t="n">
-        <v>55.31</v>
+        <v>55.21</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.22</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>33.19</t>
+          <t>32.10</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-0.61</v>
+        <v>-0.57</v>
       </c>
       <c r="BD4" t="n">
-        <v>-0.91</v>
+        <v>-0.84</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>-112.47</t>
+          <t>-111.54</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
@@ -2176,43 +2176,43 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>88838.76825842698</t>
+          <t>88739.37727910238</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>8509.0</t>
+          <t>5171.0</t>
         </is>
       </c>
       <c r="BJ4" t="n">
-        <v>6029</v>
+        <v>6103.8</v>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>5747.2</t>
+          <t>5388.8</t>
         </is>
       </c>
       <c r="BL4" t="n">
-        <v>12110</v>
+        <v>12016.5</v>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>715</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-566.2629148068319</t>
+          <t>-543.1638280056386</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-350.8831939559377</t>
+          <t>-416.1188505990758</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>8509.0</t>
+          <t>5171.0</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>-5.77</t>
+          <t>-5.59</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>32.43</t>
+          <t>32.04</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
@@ -2342,22 +2342,22 @@
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>53.4</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2414,17 +2414,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-20.25</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-11.28</t>
+          <t>-11.95</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2559,17 +2559,17 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2580,66 +2580,66 @@
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>222</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>80.56</t>
+          <t>68.89</t>
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>0.11</v>
+        <v>-0.49</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>-6.01</t>
+          <t>-6.04</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>-3.40</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>52.64</t>
+          <t>52.56</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>52.08</v>
+        <v>51.97</v>
       </c>
       <c r="AZ5" t="n">
-        <v>55.41</v>
+        <v>55.31</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>57.36</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>35.57</t>
+          <t>33.19</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-0.63</v>
+        <v>-0.61</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.99</v>
+        <v>-0.91</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-113.50</t>
+          <t>-112.47</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -2658,43 +2658,43 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>88838.76825842698</t>
+          <t>88739.37727910238</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>7682.0</t>
+          <t>8509.0</t>
         </is>
       </c>
       <c r="BJ5" t="n">
-        <v>4986.4</v>
+        <v>6029</v>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>6252.7</t>
+          <t>5747.2</t>
         </is>
       </c>
       <c r="BL5" t="n">
-        <v>12234.7</v>
+        <v>12110</v>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>-1266</t>
+          <t>281</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-605.422864052449</t>
+          <t>-566.2629148068319</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-602.8007132530274</t>
+          <t>-350.8831939559377</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>7682.0</t>
+          <t>8509.0</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>-5.05</t>
+          <t>-5.77</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>32.43</t>
+          <t>32.04</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
@@ -2824,22 +2824,22 @@
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>54.8</t>
+          <t>53.4</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
@@ -2871,12 +2871,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2896,17 +2896,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-30.07</t>
+          <t>-20.25</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-10.44</t>
+          <t>-11.28</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -3062,66 +3062,66 @@
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>222</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>58.33</t>
+          <t>80.56</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>0.99</v>
+        <v>0.11</v>
       </c>
       <c r="AU6" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>-6.06</t>
+          <t>-6.01</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-3.40</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>52.67999999999999</t>
+          <t>52.64</t>
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>52.16</v>
+        <v>52.08</v>
       </c>
       <c r="AZ6" t="n">
-        <v>55.52</v>
+        <v>55.41</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>57.37</t>
+          <t>57.36</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>34.70</t>
+          <t>35.57</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-0.7</v>
+        <v>-0.63</v>
       </c>
       <c r="BD6" t="n">
-        <v>-1.07</v>
+        <v>-0.99</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>-114.70</t>
+          <t>-113.50</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -3140,43 +3140,43 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>88838.76825842698</t>
+          <t>88739.37727910238</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>3324.0</t>
+          <t>7682.0</t>
         </is>
       </c>
       <c r="BJ6" t="n">
-        <v>5108.2</v>
+        <v>4986.4</v>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>7304.7</t>
+          <t>6252.7</t>
         </is>
       </c>
       <c r="BL6" t="n">
-        <v>12325.42</v>
+        <v>12234.7</v>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>-2196</t>
+          <t>-1266</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-605.8996187432529</t>
+          <t>-605.422864052449</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-852.5471439184039</t>
+          <t>-602.8007132530274</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>3324.0</t>
+          <t>7682.0</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-5.05</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>32.43</t>
+          <t>32.04</t>
         </is>
       </c>
       <c r="CL6" t="inlineStr">
@@ -3306,22 +3306,22 @@
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>54.8</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3378,17 +3378,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-42.21</t>
+          <t>-30.07</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-10.94</t>
+          <t>-10.44</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3544,66 +3544,66 @@
       <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>222</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>52.27</t>
+          <t>58.33</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>0.84</v>
+        <v>0.99</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.53</v>
+        <v>1</v>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>-6.24</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>52.46</t>
+          <t>52.67999999999999</t>
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>52.18</v>
+        <v>52.16</v>
       </c>
       <c r="AZ7" t="n">
-        <v>55.66</v>
+        <v>55.52</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>57.36</t>
+          <t>57.37</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>29.22</t>
+          <t>34.70</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-0.83</v>
+        <v>-0.7</v>
       </c>
       <c r="BD7" t="n">
-        <v>-1.17</v>
+        <v>-1.07</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>-115.98</t>
+          <t>-114.70</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -3622,43 +3622,43 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>88838.76825842698</t>
+          <t>88739.37727910238</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>5833.0</t>
+          <t>3324.0</t>
         </is>
       </c>
       <c r="BJ7" t="n">
-        <v>5013.8</v>
+        <v>5108.2</v>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>8675.9</t>
+          <t>7304.7</t>
         </is>
       </c>
       <c r="BL7" t="n">
-        <v>12426.06</v>
+        <v>12325.42</v>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>-3662</t>
+          <t>-2196</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-561.0546141659527</t>
+          <t>-605.8996187432529</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-711.9510754432858</t>
+          <t>-852.5471439184039</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>5833.0</t>
+          <t>3324.0</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
@@ -3733,7 +3733,7 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>32.43</t>
+          <t>32.04</t>
         </is>
       </c>
       <c r="CL7" t="inlineStr">
@@ -3788,22 +3788,22 @@
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3860,17 +3860,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-43.86</t>
+          <t>-42.21</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-12.96</t>
+          <t>-10.94</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -4026,66 +4026,66 @@
       <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>222</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>56.74</t>
+          <t>52.27</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>-1.11</v>
+        <v>0.84</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.1</v>
+        <v>0.53</v>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>-6.39</t>
+          <t>-6.24</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-2.71</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>52.27999999999999</t>
+          <t>52.46</t>
         </is>
       </c>
       <c r="AY8" t="n">
-        <v>52.23</v>
+        <v>52.18</v>
       </c>
       <c r="AZ8" t="n">
-        <v>55.8</v>
+        <v>55.66</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>57.35</t>
+          <t>57.36</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>29.22</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.83</v>
       </c>
       <c r="BD8" t="n">
-        <v>-1.25</v>
+        <v>-1.17</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>-117.14</t>
+          <t>-115.98</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
@@ -4104,43 +4104,43 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>88838.76825842698</t>
+          <t>88739.37727910238</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>4797.0</t>
+          <t>5833.0</t>
         </is>
       </c>
       <c r="BJ8" t="n">
-        <v>4673.8</v>
+        <v>5013.8</v>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>8324.9</t>
+          <t>8675.9</t>
         </is>
       </c>
       <c r="BL8" t="n">
-        <v>12556.78</v>
+        <v>12426.06</v>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>-3651</t>
+          <t>-3662</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-533.6188939337103</t>
+          <t>-561.0546141659527</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-754.4941534987138</t>
+          <t>-711.9510754432858</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>4797.0</t>
+          <t>5833.0</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>-6.85</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -4205,7 +4205,7 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>32.43</t>
+          <t>32.04</t>
         </is>
       </c>
       <c r="CL8" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
@@ -4285,7 +4285,7 @@
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4342,17 +4342,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-33.34</t>
+          <t>-43.86</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-11.28</t>
+          <t>-12.96</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4487,17 +4487,17 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -4508,66 +4508,66 @@
       <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>222</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>81.82</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>78.48</t>
+          <t>56.74</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>0.27</v>
+        <v>-1.11</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.45</v>
+        <v>0.1</v>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>-6.53</t>
+          <t>-6.39</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-2.71</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>52.56</t>
+          <t>52.27999999999999</t>
         </is>
       </c>
       <c r="AY9" t="n">
-        <v>52.32</v>
+        <v>52.23</v>
       </c>
       <c r="AZ9" t="n">
-        <v>55.98</v>
+        <v>55.8</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>57.34</t>
+          <t>57.35</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>28.11</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-0.96</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="BD9" t="n">
-        <v>-1.33</v>
+        <v>-1.25</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>-118.20</t>
+          <t>-117.14</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -4586,43 +4586,43 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>88838.76825842698</t>
+          <t>88739.37727910238</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>3296.0</t>
+          <t>4797.0</t>
         </is>
       </c>
       <c r="BJ9" t="n">
-        <v>5465.4</v>
+        <v>4673.8</v>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>8198.7</t>
+          <t>8324.9</t>
         </is>
       </c>
       <c r="BL9" t="n">
-        <v>12704.54</v>
+        <v>12556.78</v>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>-2733</t>
+          <t>-3651</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-493.4597558309824</t>
+          <t>-533.6188939337103</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-677.32375952437</t>
+          <t>-754.4941534987138</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>3296.0</t>
+          <t>4797.0</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>-5.05</t>
+          <t>-6.85</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
@@ -4727,7 +4727,7 @@
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>32.43</t>
+          <t>32.04</t>
         </is>
       </c>
       <c r="CL9" t="inlineStr">
@@ -4752,22 +4752,22 @@
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>156.0</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4824,17 +4824,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-10.85</t>
+          <t>-33.34</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-10.94</t>
+          <t>-11.28</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -4969,17 +4969,17 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -4990,66 +4990,66 @@
       <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>222</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>88.41</t>
+          <t>81.82</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>71.98</t>
+          <t>78.48</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.27</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.29</v>
+        <v>0.45</v>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>-6.68</t>
+          <t>-6.53</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>52.54</t>
+          <t>52.56</t>
         </is>
       </c>
       <c r="AY10" t="n">
-        <v>52.39</v>
+        <v>52.32</v>
       </c>
       <c r="AZ10" t="n">
-        <v>56.14</v>
+        <v>55.98</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>57.32</t>
+          <t>57.34</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>25.48</t>
+          <t>28.11</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-1.06</v>
+        <v>-0.96</v>
       </c>
       <c r="BD10" t="n">
-        <v>-1.42</v>
+        <v>-1.33</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>-119.48</t>
+          <t>-118.20</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
@@ -5068,43 +5068,43 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>88838.76825842698</t>
+          <t>88739.37727910238</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>8291.0</t>
+          <t>3296.0</t>
         </is>
       </c>
       <c r="BJ10" t="n">
-        <v>7519</v>
+        <v>5465.4</v>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>8434.2</t>
+          <t>8198.7</t>
         </is>
       </c>
       <c r="BL10" t="n">
-        <v>12897.76</v>
+        <v>12704.54</v>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>-915</t>
+          <t>-2733</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-460.0299369776392</t>
+          <t>-493.4597558309824</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-382.0687767208665</t>
+          <t>-677.32375952437</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>8291.0</t>
+          <t>3296.0</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-5.05</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
@@ -5179,7 +5179,7 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>32.43</t>
+          <t>32.04</t>
         </is>
       </c>
       <c r="CL10" t="inlineStr">
@@ -5234,22 +5234,22 @@
       </c>
       <c r="CP10" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>54.3</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>156.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5306,17 +5306,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>15.25</t>
+          <t>-10.85</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-12.29</t>
+          <t>-10.94</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5451,17 +5451,17 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -5472,50 +5472,50 @@
       <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>222</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>65.22</t>
+          <t>88.41</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>73.91</t>
+          <t>71.98</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>-0.99</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.35</v>
+        <v>0.29</v>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>-6.88</t>
+          <t>-6.68</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>52.62</t>
+          <t>52.54</t>
         </is>
       </c>
       <c r="AY11" t="n">
-        <v>52.44</v>
+        <v>52.39</v>
       </c>
       <c r="AZ11" t="n">
-        <v>56.31</v>
+        <v>56.14</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5524,14 +5524,14 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>20.79</t>
+          <t>25.48</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-1.2</v>
+        <v>-1.06</v>
       </c>
       <c r="BD11" t="n">
-        <v>-1.51</v>
+        <v>-1.42</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>-120.72</t>
+          <t>-119.48</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
@@ -5550,43 +5550,43 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>88838.76825842698</t>
+          <t>88739.37727910238</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>2852.0</t>
+          <t>8291.0</t>
         </is>
       </c>
       <c r="BJ11" t="n">
-        <v>9501.200000000001</v>
+        <v>7519</v>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>8244.2</t>
+          <t>8434.2</t>
         </is>
       </c>
       <c r="BL11" t="n">
-        <v>13064.54</v>
+        <v>12897.76</v>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1257</t>
+          <t>-915</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-474.2046933879615</t>
+          <t>-460.0299369776392</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-481.8092021186876</t>
+          <t>-382.0687767208665</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>2852.0</t>
+          <t>8291.0</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>-6.13</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
@@ -5691,7 +5691,7 @@
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>32.43</t>
+          <t>32.04</t>
         </is>
       </c>
       <c r="CL11" t="inlineStr">
@@ -5716,22 +5716,22 @@
       </c>
       <c r="CP11" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>54.3</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
@@ -5763,12 +5763,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5788,17 +5788,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>43.16</t>
+          <t>15.25</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-12.46</t>
+          <t>-12.29</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5933,17 +5933,17 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -5954,66 +5954,66 @@
       <c r="AO12" t="inlineStr"/>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>222</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>62.32</t>
+          <t>65.22</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>78.74</t>
+          <t>73.91</t>
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>-1.07</v>
+        <v>-0.99</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>-6.98</t>
+          <t>-6.88</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>52.56</t>
+          <t>52.62</t>
         </is>
       </c>
       <c r="AY12" t="n">
-        <v>52.56</v>
+        <v>52.44</v>
       </c>
       <c r="AZ12" t="n">
-        <v>56.5</v>
+        <v>56.31</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>57.33</t>
+          <t>57.32</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>19.82</t>
+          <t>20.79</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-1.28</v>
+        <v>-1.2</v>
       </c>
       <c r="BD12" t="n">
-        <v>-1.59</v>
+        <v>-1.51</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>-121.80</t>
+          <t>-120.72</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
@@ -6032,43 +6032,43 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>88838.76825842698</t>
+          <t>88739.37727910238</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>4133.0</t>
+          <t>2852.0</t>
         </is>
       </c>
       <c r="BJ12" t="n">
-        <v>12338</v>
+        <v>9501.200000000001</v>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>8618.6</t>
+          <t>8244.2</t>
         </is>
       </c>
       <c r="BL12" t="n">
-        <v>13299.38</v>
+        <v>13064.54</v>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>3719</t>
+          <t>1257</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-472.8220554369204</t>
+          <t>-474.2046933879615</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-24.33805261133421</t>
+          <t>-481.8092021186876</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>4133.0</t>
+          <t>2852.0</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>-6.31</t>
+          <t>-6.13</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="CK12" t="inlineStr">
         <is>
-          <t>32.43</t>
+          <t>32.04</t>
         </is>
       </c>
       <c r="CL12" t="inlineStr">
@@ -6198,22 +6198,22 @@
       </c>
       <c r="CP12" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">

--- a/Result/checksun_type/印刷材料.xlsx
+++ b/Result/checksun_type/印刷材料.xlsx
@@ -933,7 +933,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>價_量;【d1】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -943,42 +943,42 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>2.73</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>915.0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>55.6</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>222.0</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>54.1</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>30.80</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-8.92</t>
+          <t>-6.40</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1113,17 +1113,17 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>8.00</t>
+          <t>32.96</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1134,12 +1134,12 @@
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>915</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -1149,51 +1149,51 @@
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>82.22</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>1.84</v>
+        <v>3.54</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.6</v>
+        <v>2.24</v>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>-5.06</t>
+          <t>-4.55</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>53.12</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>52.28</v>
+        <v>52.52</v>
       </c>
       <c r="AZ2" t="n">
-        <v>55.07</v>
+        <v>55.02</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>57.15</t>
+          <t>57.11</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>59.81</t>
+          <t>93.81</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-0.26</v>
+        <v>-0.03</v>
       </c>
       <c r="BD2" t="n">
-        <v>-0.66</v>
+        <v>-0.53</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>-108.99</t>
+          <t>-107.28</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
@@ -1212,43 +1212,43 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>88739.37727910238</t>
+          <t>88721.8193277311</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>11982.0</t>
+          <t>50802.0</t>
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>9656.200000000001</v>
+        <v>18280.2</v>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>7382.2</t>
+          <t>11633.3</t>
         </is>
       </c>
       <c r="BL2" t="n">
-        <v>12339.64</v>
+        <v>13182.46</v>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>2274</t>
+          <t>6646</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-269.1575538650869</t>
+          <t>329.1749512666356</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>540.4490401206567</t>
+          <t>3620.003729491109</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>11982.0</t>
+          <t>50802.0</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1313,22 +1313,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>22.17</t>
+          <t>22.79</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>32.04</t>
+          <t>32.22</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>2434</t>
+          <t>2502</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
@@ -1378,22 +1378,22 @@
       </c>
       <c r="CP2" t="inlineStr">
         <is>
+          <t>54.9</t>
+        </is>
+      </c>
+      <c r="CQ2" t="inlineStr">
+        <is>
+          <t>56.9</t>
+        </is>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
           <t>54.3</t>
         </is>
       </c>
-      <c r="CQ2" t="inlineStr">
-        <is>
-          <t>54.7</t>
-        </is>
-      </c>
-      <c r="CR2" t="inlineStr">
-        <is>
-          <t>53.3</t>
-        </is>
-      </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="CV2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1425,12 +1425,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>277.0</t>
+          <t>222.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,17 +1450,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>22.50</t>
+          <t>30.80</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1595,17 +1595,17 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>8.00</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1616,12 +1616,12 @@
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>915</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -1631,51 +1631,51 @@
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>62.22</t>
+          <t>82.22</t>
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>2.19</v>
+        <v>1.84</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>-5.52</t>
+          <t>-5.06</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>52.94000000000001</t>
+          <t>53.12</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>52.1</v>
+        <v>52.28</v>
       </c>
       <c r="AZ3" t="n">
-        <v>55.14</v>
+        <v>55.07</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>57.16</t>
+          <t>57.15</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>46.74</t>
+          <t>59.81</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-0.4</v>
+        <v>-0.26</v>
       </c>
       <c r="BD3" t="n">
-        <v>-0.75</v>
+        <v>-0.66</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>-110.33</t>
+          <t>-108.99</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
@@ -1694,43 +1694,43 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>88739.37727910238</t>
+          <t>88721.8193277311</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>14937.0</t>
+          <t>11982.0</t>
         </is>
       </c>
       <c r="BJ3" t="n">
-        <v>7924.6</v>
+        <v>9656.200000000001</v>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>6469.2</t>
+          <t>7382.2</t>
         </is>
       </c>
       <c r="BL3" t="n">
-        <v>12221.38</v>
+        <v>12339.64</v>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1455</t>
+          <t>2274</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-416.3587527715858</t>
+          <t>-269.1575538650869</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>281.0691610157046</t>
+          <t>540.4490401206567</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>14937.0</t>
+          <t>11982.0</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>22.17</t>
+          <t>22.79</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>32.04</t>
+          <t>32.22</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>2434</t>
+          <t>2502</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
@@ -1860,17 +1860,17 @@
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>54.3</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>55.2</t>
+          <t>54.7</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="CV3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>277.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1932,17 +1932,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>13.27</t>
+          <t>22.50</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-11.78</t>
+          <t>-8.92</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2077,17 +2077,17 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -2098,66 +2098,66 @@
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>915</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>46.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>51.11</t>
+          <t>62.22</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>-0.57</v>
+        <v>2.19</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.41</v>
+        <v>1.62</v>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>-5.87</t>
+          <t>-5.52</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.94000000000001</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>51.97</v>
+        <v>52.1</v>
       </c>
       <c r="AZ4" t="n">
-        <v>55.21</v>
+        <v>55.14</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>57.22</t>
+          <t>57.16</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>32.10</t>
+          <t>46.74</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-0.57</v>
+        <v>-0.4</v>
       </c>
       <c r="BD4" t="n">
-        <v>-0.84</v>
+        <v>-0.75</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>-111.54</t>
+          <t>-110.33</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
@@ -2176,43 +2176,43 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>88739.37727910238</t>
+          <t>88721.8193277311</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>5171.0</t>
+          <t>14937.0</t>
         </is>
       </c>
       <c r="BJ4" t="n">
-        <v>6103.8</v>
+        <v>7924.6</v>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>5388.8</t>
+          <t>6469.2</t>
         </is>
       </c>
       <c r="BL4" t="n">
-        <v>12016.5</v>
+        <v>12221.38</v>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>1455</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-543.1638280056386</t>
+          <t>-416.3587527715858</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-416.1188505990758</t>
+          <t>281.0691610157046</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>5171.0</t>
+          <t>14937.0</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>-5.59</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2277,22 +2277,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>22.17</t>
+          <t>22.79</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
@@ -2317,12 +2317,12 @@
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>32.04</t>
+          <t>32.22</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>2434</t>
+          <t>2502</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
@@ -2342,22 +2342,22 @@
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>55.2</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>52